--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARISAFARI\Works\Project Applications\tool-fcost\example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARISAFARI\Works\Project Applications\ExcelAutoTool\masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4045" uniqueCount="2126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="2179">
   <si>
     <t>DSGY-F704JBKZ</t>
   </si>
@@ -6096,7 +6096,451 @@
     <t>*</t>
   </si>
   <si>
-    <t>garis / line</t>
+    <t>BLANK</t>
+  </si>
+  <si>
+    <t>X ADA GAMBAR</t>
+  </si>
+  <si>
+    <t>MATI</t>
+  </si>
+  <si>
+    <t>HANYA SUARA SAJA</t>
+  </si>
+  <si>
+    <t>TIDAK BISA HIDUP</t>
+  </si>
+  <si>
+    <t>TIDAK BS HIDUP</t>
+  </si>
+  <si>
+    <t>LOGO</t>
+  </si>
+  <si>
+    <t>HDMI</t>
+  </si>
+  <si>
+    <t>SIARAN</t>
+  </si>
+  <si>
+    <t>CHANNEL</t>
+  </si>
+  <si>
+    <t>Diff Month</t>
+  </si>
+  <si>
+    <t>0-12</t>
+  </si>
+  <si>
+    <t>&lt; 1 Year</t>
+  </si>
+  <si>
+    <t>13-24</t>
+  </si>
+  <si>
+    <t>1 - 2 Years</t>
+  </si>
+  <si>
+    <t>25-36</t>
+  </si>
+  <si>
+    <t>2 - 3 Years</t>
+  </si>
+  <si>
+    <t>=&gt;37</t>
+  </si>
+  <si>
+    <t>&gt; 3 Years</t>
+  </si>
+  <si>
+    <t>Panel Usage</t>
+  </si>
+  <si>
+    <t>init</t>
+  </si>
+  <si>
+    <t>branch</t>
+  </si>
+  <si>
+    <t>CIDENG</t>
+  </si>
+  <si>
+    <t>JAKARTA</t>
+  </si>
+  <si>
+    <t>PULOGADUNG</t>
+  </si>
+  <si>
+    <t>JAKARTA SELATAN</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>replace_power_unit</t>
+  </si>
+  <si>
+    <t>replace_panel</t>
+  </si>
+  <si>
+    <t>replace_main_unit</t>
+  </si>
+  <si>
+    <t>Remote Control</t>
+  </si>
+  <si>
+    <t>replace_remote_control</t>
+  </si>
+  <si>
+    <t>repair_comment</t>
+  </si>
+  <si>
+    <t>*bawa</t>
+  </si>
+  <si>
+    <t>ZY</t>
+  </si>
+  <si>
+    <t>*ext</t>
+  </si>
+  <si>
+    <t>external</t>
+  </si>
+  <si>
+    <t>UPGRADE</t>
+  </si>
+  <si>
+    <t>upgrade</t>
+  </si>
+  <si>
+    <t>*factor</t>
+  </si>
+  <si>
+    <t>factory_reset</t>
+  </si>
+  <si>
+    <t>JELAS</t>
+  </si>
+  <si>
+    <t>explanation</t>
+  </si>
+  <si>
+    <t>BATAL</t>
+  </si>
+  <si>
+    <t>cancel</t>
+  </si>
+  <si>
+    <t>Repair Action</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Defect</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Repair LVDS</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Reinsert Speaker</t>
+  </si>
+  <si>
+    <t>Subtitusi</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Replace Panel - Before Change</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>Non Defect</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Explanation</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Replace Panel</t>
+  </si>
+  <si>
+    <t>Panel</t>
+  </si>
+  <si>
+    <t>Repair Panel</t>
+  </si>
+  <si>
+    <t>Replace Main Unit</t>
+  </si>
+  <si>
+    <t>Main Unit</t>
+  </si>
+  <si>
+    <t>Repair Main Unit</t>
+  </si>
+  <si>
+    <t>Replace Power Unit</t>
+  </si>
+  <si>
+    <t>Power Unit</t>
+  </si>
+  <si>
+    <t>Replace TCON</t>
+  </si>
+  <si>
+    <t>Repair Power Unit</t>
+  </si>
+  <si>
+    <t>Factory Reset</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Upgrade</t>
+  </si>
+  <si>
+    <t>Reinsert LVDS</t>
+  </si>
+  <si>
+    <t>Repair IR Unit</t>
+  </si>
+  <si>
+    <t>Repair LED BAR</t>
+  </si>
+  <si>
+    <t>Repair Speaker</t>
+  </si>
+  <si>
+    <t>Replace Speaker</t>
+  </si>
+  <si>
+    <t>Replace Led Bar</t>
+  </si>
+  <si>
+    <t>Replace LVDS</t>
+  </si>
+  <si>
+    <t>Replace IR Unit</t>
+  </si>
+  <si>
+    <t>Replace Wifi Unit</t>
+  </si>
+  <si>
+    <t>Repair TCON</t>
+  </si>
+  <si>
+    <t>Repair Wifi Unit</t>
+  </si>
+  <si>
+    <t>Reinsert Wifi Unit</t>
+  </si>
+  <si>
+    <t>Reinsert Cabinet</t>
+  </si>
+  <si>
+    <t>Reinsert Socket</t>
+  </si>
+  <si>
+    <t>Replace Remote</t>
+  </si>
+  <si>
+    <t>Repair Remote</t>
+  </si>
+  <si>
+    <t>Replace Tape</t>
+  </si>
+  <si>
+    <t>Verified OK</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>External</t>
+  </si>
+  <si>
+    <t>Before Improve - Remote</t>
+  </si>
+  <si>
+    <t>Before Improve</t>
+  </si>
+  <si>
+    <t>TOTAL_OFF</t>
+  </si>
+  <si>
+    <t>LINE</t>
+  </si>
+  <si>
+    <t>STANDBY</t>
+  </si>
+  <si>
+    <t>LOGO_FREEZE</t>
+  </si>
+  <si>
+    <t>HDMI_NG</t>
+  </si>
+  <si>
+    <t>NO_CHANNEL</t>
+  </si>
+  <si>
+    <t>*garis*</t>
+  </si>
+  <si>
+    <t>*line*</t>
+  </si>
+  <si>
+    <t>*GOYANG*</t>
+  </si>
+  <si>
+    <t>DISPLAY NG</t>
+  </si>
+  <si>
+    <t>*BAYANG*</t>
+  </si>
+  <si>
+    <t>BLUR</t>
+  </si>
+  <si>
+    <t>DOT</t>
+  </si>
+  <si>
+    <t>*DOT*</t>
+  </si>
+  <si>
+    <t>*BERGERAK*</t>
+  </si>
+  <si>
+    <t>*SETENGAH*</t>
+  </si>
+  <si>
+    <t>HALF</t>
+  </si>
+  <si>
+    <t>*RUSAK PANEL*</t>
+  </si>
+  <si>
+    <t>BROKEN</t>
+  </si>
+  <si>
+    <t>*BURAM*</t>
+  </si>
+  <si>
+    <t>MURA</t>
+  </si>
+  <si>
+    <t>*PIXEL*</t>
+  </si>
+  <si>
+    <t>*GAMBAR TDK KELUAR*</t>
+  </si>
+  <si>
+    <t>*BLANK*</t>
+  </si>
+  <si>
+    <t>NO_PICTURE</t>
+  </si>
+  <si>
+    <t>TDK ADA GAMABAR</t>
+  </si>
+  <si>
+    <t>TIDAK AD AGAMBAR</t>
+  </si>
+  <si>
+    <t>TIDAK AD GAMBAR</t>
+  </si>
+  <si>
+    <t>*TIDAK BISA HIDUP*</t>
+  </si>
+  <si>
+    <t>*STANDBY*</t>
+  </si>
+  <si>
+    <t>*STAND BY*</t>
+  </si>
+  <si>
+    <t>*STANBY*</t>
+  </si>
+  <si>
+    <t>*MATOT*</t>
+  </si>
+  <si>
+    <t>*MATOL*</t>
+  </si>
+  <si>
+    <t>LAYAR BLANK</t>
+  </si>
+  <si>
+    <t>*TDK ADA GAMBAR*</t>
+  </si>
+  <si>
+    <t>*TIDAK ADA GAMBAR*</t>
+  </si>
+  <si>
+    <t>ERROR</t>
+  </si>
+  <si>
+    <t>*NETFLIX*</t>
+  </si>
+  <si>
+    <t>*MATI*</t>
+  </si>
+  <si>
+    <t>SIGNAL</t>
+  </si>
+  <si>
+    <t>SINYAL</t>
+  </si>
+  <si>
+    <t>INDIKATOR</t>
+  </si>
+  <si>
+    <t>PROTECT</t>
+  </si>
+  <si>
+    <t>REMOT</t>
+  </si>
+  <si>
+    <t>SENSOR_NG</t>
+  </si>
+  <si>
+    <t>REMOTE</t>
+  </si>
+  <si>
+    <t>SENSOR</t>
+  </si>
+  <si>
+    <t>TIDAK ADA SUARA</t>
+  </si>
+  <si>
+    <t>CHANEL</t>
+  </si>
+  <si>
+    <t>SOUND_NG</t>
+  </si>
+  <si>
+    <t>TOMBOL</t>
+  </si>
+  <si>
+    <t>BUTTON_NG</t>
+  </si>
+  <si>
+    <t>EROR</t>
   </si>
   <si>
     <t>TIDAK ADA GAMBAR</t>
@@ -6105,313 +6549,28 @@
     <t>TDK ADA GAMBAR</t>
   </si>
   <si>
-    <t>BLANK</t>
-  </si>
-  <si>
-    <t>X ADA GAMBAR</t>
-  </si>
-  <si>
-    <t>MATI</t>
-  </si>
-  <si>
-    <t>HANYA SUARA SAJA</t>
-  </si>
-  <si>
-    <t>TIDAK BISA HIDUP</t>
-  </si>
-  <si>
-    <t>TIDAK BS HIDUP</t>
-  </si>
-  <si>
-    <t>STANDBY / STAND BY</t>
-  </si>
-  <si>
-    <t>LOGO</t>
-  </si>
-  <si>
-    <t>HDMI</t>
-  </si>
-  <si>
-    <t>SIARAN</t>
-  </si>
-  <si>
-    <t>SIGNAL / SINYAL</t>
-  </si>
-  <si>
-    <t>CHANNEL</t>
-  </si>
-  <si>
-    <t>Diff Month</t>
-  </si>
-  <si>
-    <t>0-12</t>
-  </si>
-  <si>
-    <t>&lt; 1 Year</t>
-  </si>
-  <si>
-    <t>13-24</t>
-  </si>
-  <si>
-    <t>1 - 2 Years</t>
-  </si>
-  <si>
-    <t>25-36</t>
-  </si>
-  <si>
-    <t>2 - 3 Years</t>
-  </si>
-  <si>
-    <t>=&gt;37</t>
-  </si>
-  <si>
-    <t>&gt; 3 Years</t>
-  </si>
-  <si>
-    <t>Panel Usage</t>
-  </si>
-  <si>
-    <t>init</t>
-  </si>
-  <si>
-    <t>branch</t>
-  </si>
-  <si>
-    <t>CIDENG</t>
-  </si>
-  <si>
-    <t>JAKARTA</t>
-  </si>
-  <si>
-    <t>PULOGADUNG</t>
-  </si>
-  <si>
-    <t>JAKARTA SELATAN</t>
-  </si>
-  <si>
-    <t>action</t>
-  </si>
-  <si>
-    <t>replace_power_unit</t>
-  </si>
-  <si>
-    <t>replace_panel</t>
-  </si>
-  <si>
-    <t>replace_main_unit</t>
-  </si>
-  <si>
-    <t>Remote Control</t>
-  </si>
-  <si>
-    <t>replace_remote_control</t>
-  </si>
-  <si>
-    <t>repair_comment</t>
-  </si>
-  <si>
-    <t>*bawa</t>
-  </si>
-  <si>
-    <t>ZY</t>
-  </si>
-  <si>
-    <t>*ext</t>
-  </si>
-  <si>
-    <t>external</t>
-  </si>
-  <si>
-    <t>UPGRADE</t>
-  </si>
-  <si>
-    <t>upgrade</t>
-  </si>
-  <si>
-    <t>*factor</t>
-  </si>
-  <si>
-    <t>factory_reset</t>
-  </si>
-  <si>
-    <t>JELAS</t>
-  </si>
-  <si>
-    <t>explanation</t>
-  </si>
-  <si>
-    <t>BATAL</t>
-  </si>
-  <si>
-    <t>cancel</t>
-  </si>
-  <si>
-    <t>Repair Action</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Defect</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Repair LVDS</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Reinsert Speaker</t>
-  </si>
-  <si>
-    <t>Subtitusi</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Replace Panel - Before Change</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>Non Defect</t>
-  </si>
-  <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>Explanation</t>
-  </si>
-  <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Replace Panel</t>
-  </si>
-  <si>
-    <t>Panel</t>
-  </si>
-  <si>
-    <t>Repair Panel</t>
-  </si>
-  <si>
-    <t>Replace Main Unit</t>
-  </si>
-  <si>
-    <t>Main Unit</t>
-  </si>
-  <si>
-    <t>Repair Main Unit</t>
-  </si>
-  <si>
-    <t>Replace Power Unit</t>
-  </si>
-  <si>
-    <t>Power Unit</t>
-  </si>
-  <si>
-    <t>Replace TCON</t>
-  </si>
-  <si>
-    <t>Repair Power Unit</t>
-  </si>
-  <si>
-    <t>Factory Reset</t>
-  </si>
-  <si>
-    <t>Software</t>
-  </si>
-  <si>
-    <t>Upgrade</t>
-  </si>
-  <si>
-    <t>Reinsert LVDS</t>
-  </si>
-  <si>
-    <t>Repair IR Unit</t>
-  </si>
-  <si>
-    <t>Repair LED BAR</t>
-  </si>
-  <si>
-    <t>Repair Speaker</t>
-  </si>
-  <si>
-    <t>Replace Speaker</t>
-  </si>
-  <si>
-    <t>Replace Led Bar</t>
-  </si>
-  <si>
-    <t>Replace LVDS</t>
-  </si>
-  <si>
-    <t>Replace IR Unit</t>
-  </si>
-  <si>
-    <t>Replace Wifi Unit</t>
-  </si>
-  <si>
-    <t>Repair TCON</t>
-  </si>
-  <si>
-    <t>Repair Wifi Unit</t>
-  </si>
-  <si>
-    <t>Reinsert Wifi Unit</t>
-  </si>
-  <si>
-    <t>Reinsert Cabinet</t>
-  </si>
-  <si>
-    <t>Reinsert Socket</t>
-  </si>
-  <si>
-    <t>Replace Remote</t>
-  </si>
-  <si>
-    <t>Repair Remote</t>
-  </si>
-  <si>
-    <t>Replace Tape</t>
-  </si>
-  <si>
-    <t>Verified OK</t>
-  </si>
-  <si>
-    <t>Cancel</t>
-  </si>
-  <si>
-    <t>External</t>
-  </si>
-  <si>
-    <t>Before Improve - Remote</t>
-  </si>
-  <si>
-    <t>Before Improve</t>
-  </si>
-  <si>
-    <t>TOTAL_OFF</t>
-  </si>
-  <si>
-    <t>LINE</t>
-  </si>
-  <si>
-    <t>STANDBY</t>
-  </si>
-  <si>
-    <t>LOGO_FREEZE</t>
-  </si>
-  <si>
-    <t>HDMI_NG</t>
-  </si>
-  <si>
-    <t>NO_CHANNEL</t>
+    <t>TIDAK ADA SIARAN</t>
+  </si>
+  <si>
+    <t>DOMINAN</t>
+  </si>
+  <si>
+    <t>MERAH</t>
+  </si>
+  <si>
+    <t>PUTIH</t>
+  </si>
+  <si>
+    <t>SEBELAH</t>
+  </si>
+  <si>
+    <t>NO DISPLAY</t>
+  </si>
+  <si>
+    <t>PECAH</t>
+  </si>
+  <si>
+    <t>RC_NG</t>
   </si>
 </sst>
 </file>
@@ -6421,7 +6580,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6520,6 +6679,10 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -6609,7 +6772,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6706,6 +6869,8 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -29923,12 +30088,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="49.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="45.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -29950,7 +30116,7 @@
         <v>2019</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>2120</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -29958,10 +30124,10 @@
         <v>1853</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>2020</v>
+        <v>2121</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>2121</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -29969,10 +30135,10 @@
         <v>1853</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>2021</v>
+        <v>2122</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>2023</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -29980,21 +30146,21 @@
         <v>1853</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>2022</v>
+        <v>2140</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="23" t="s">
         <v>1853</v>
       </c>
-      <c r="B6" s="23" t="s">
-        <v>2023</v>
+      <c r="B6" t="s">
+        <v>2170</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -30002,10 +30168,10 @@
         <v>1853</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>2024</v>
+        <v>2141</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -30013,10 +30179,10 @@
         <v>1853</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>2025</v>
+        <v>2142</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -30024,113 +30190,598 @@
         <v>1853</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>2026</v>
+        <v>2169</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>2029</v>
+        <v>2171</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>2122</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>2120</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>2027</v>
+        <v>2021</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>2120</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>2028</v>
+        <v>2176</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>2120</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>2030</v>
+        <v>2022</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>2123</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>2031</v>
+        <v>2023</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>2124</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>2032</v>
+        <v>2123</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>2033</v>
+        <v>2172</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>2034</v>
+        <v>2173</v>
       </c>
       <c r="C18" s="23" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>2174</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B20" s="23" t="s">
         <v>2125</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>2175</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B42" s="23" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B45" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C48" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C49" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C50" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C51" s="42" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C52" s="42" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C53" s="42" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>2157</v>
+      </c>
+      <c r="C54" s="42" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>2159</v>
+      </c>
+      <c r="C55" s="42" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C56" s="42" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C57" s="42" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C58" s="42" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C59" s="42" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="43" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C60" s="42" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="43" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C61" s="42" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="23" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>2169</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>2139</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -30144,42 +30795,42 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="25" t="s">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>2044</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="26" t="s">
-        <v>2036</v>
+        <v>2031</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>2037</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="26" t="s">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>2039</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="26" t="s">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="27" t="s">
-        <v>2042</v>
+        <v>2037</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>2043</v>
+        <v>2038</v>
       </c>
     </row>
   </sheetData>
@@ -30198,34 +30849,34 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="25" t="s">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>2046</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="26" t="s">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="26" t="s">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="26" t="s">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
     </row>
   </sheetData>
@@ -30249,28 +30900,28 @@
         <v>1841</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>2057</v>
+        <v>2052</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>2051</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="31" customFormat="1">
       <c r="A2" s="36"/>
       <c r="B2" s="29" t="s">
-        <v>2060</v>
+        <v>2055</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="31" customFormat="1">
       <c r="A3" s="36"/>
       <c r="B3" s="32" t="s">
-        <v>2068</v>
+        <v>2063</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>2069</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -30281,7 +30932,7 @@
         <v>2019</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>2052</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -30292,7 +30943,7 @@
         <v>2019</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>2053</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -30303,63 +30954,63 @@
         <v>2019</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>2054</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="32" t="s">
-        <v>2055</v>
+        <v>2050</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>2019</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>2056</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="32"/>
       <c r="B8" s="32" t="s">
-        <v>2058</v>
+        <v>2053</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>2059</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="32"/>
       <c r="B9" s="32" t="s">
-        <v>2059</v>
+        <v>2054</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>2059</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="32"/>
       <c r="B10" s="32" t="s">
-        <v>2062</v>
+        <v>2057</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>2063</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="32"/>
       <c r="B11" s="32" t="s">
-        <v>2064</v>
+        <v>2059</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>2065</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="32"/>
       <c r="B12" s="32" t="s">
-        <v>2066</v>
+        <v>2061</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>2067</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -30388,27 +31039,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="37" t="s">
-        <v>2070</v>
+        <v>2065</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>2071</v>
+        <v>2066</v>
       </c>
       <c r="C1" s="37" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>2073</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="39" t="s">
-        <v>2074</v>
+        <v>2069</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D2" s="40">
         <v>0</v>
@@ -30416,13 +31067,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="39" t="s">
-        <v>2076</v>
+        <v>2071</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D3" s="40">
         <v>0</v>
@@ -30430,13 +31081,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="41" t="s">
-        <v>2077</v>
+        <v>2072</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="D4" s="40">
         <v>0</v>
@@ -30444,13 +31095,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="41" t="s">
-        <v>2079</v>
+        <v>2074</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="D5" s="40">
         <v>0</v>
@@ -30458,13 +31109,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="39" t="s">
-        <v>2059</v>
+        <v>2054</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="D6" s="40">
         <v>0</v>
@@ -30472,13 +31123,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="41" t="s">
-        <v>2079</v>
+        <v>2074</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="D7" s="40">
         <v>0</v>
@@ -30486,13 +31137,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="39" t="s">
-        <v>2059</v>
+        <v>2054</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="D8" s="40">
         <v>0</v>
@@ -30500,13 +31151,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="40" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>2081</v>
+        <v>2076</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="D9" s="40">
         <v>11</v>
@@ -30514,13 +31165,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="40" t="s">
-        <v>2082</v>
+        <v>2077</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>2081</v>
+        <v>2076</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>2082</v>
+        <v>2077</v>
       </c>
       <c r="D10" s="40">
         <v>12</v>
@@ -30528,13 +31179,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="40" t="s">
-        <v>2083</v>
+        <v>2078</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>2081</v>
+        <v>2076</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>2083</v>
+        <v>2078</v>
       </c>
       <c r="D11" s="40">
         <v>13</v>
@@ -30542,13 +31193,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="40" t="s">
-        <v>2084</v>
+        <v>2079</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>2081</v>
+        <v>2076</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>2084</v>
+        <v>2079</v>
       </c>
       <c r="D12" s="40">
         <v>14</v>
@@ -30556,13 +31207,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="39" t="s">
-        <v>2085</v>
+        <v>2080</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>2086</v>
+        <v>2081</v>
       </c>
       <c r="D13" s="40">
         <v>20</v>
@@ -30570,13 +31221,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="39" t="s">
-        <v>2087</v>
+        <v>2082</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>2086</v>
+        <v>2081</v>
       </c>
       <c r="D14" s="40">
         <v>21</v>
@@ -30584,13 +31235,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="39" t="s">
-        <v>2088</v>
+        <v>2083</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>2089</v>
+        <v>2084</v>
       </c>
       <c r="D15" s="40">
         <v>30</v>
@@ -30598,13 +31249,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="39" t="s">
-        <v>2090</v>
+        <v>2085</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>2089</v>
+        <v>2084</v>
       </c>
       <c r="D16" s="40">
         <v>31</v>
@@ -30612,13 +31263,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="41" t="s">
-        <v>2091</v>
+        <v>2086</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>2092</v>
+        <v>2087</v>
       </c>
       <c r="D17" s="40">
         <v>40</v>
@@ -30626,13 +31277,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="40" t="s">
-        <v>2093</v>
+        <v>2088</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D18" s="40">
         <v>42</v>
@@ -30640,13 +31291,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="41" t="s">
-        <v>2094</v>
+        <v>2089</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>2092</v>
+        <v>2087</v>
       </c>
       <c r="D19" s="40">
         <v>41</v>
@@ -30654,13 +31305,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="39" t="s">
-        <v>2095</v>
+        <v>2090</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>2096</v>
+        <v>2091</v>
       </c>
       <c r="D20" s="40">
         <v>50</v>
@@ -30668,13 +31319,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="39" t="s">
-        <v>2097</v>
+        <v>2092</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>2096</v>
+        <v>2091</v>
       </c>
       <c r="D21" s="40">
         <v>51</v>
@@ -30682,13 +31333,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="41" t="s">
-        <v>2098</v>
+        <v>2093</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D22" s="40">
         <v>60</v>
@@ -30696,13 +31347,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="40" t="s">
-        <v>2099</v>
+        <v>2094</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D23" s="40">
         <v>61</v>
@@ -30710,13 +31361,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="39" t="s">
-        <v>2100</v>
+        <v>2095</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D24" s="40">
         <v>62</v>
@@ -30724,13 +31375,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="41" t="s">
-        <v>2101</v>
+        <v>2096</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D25" s="40">
         <v>63</v>
@@ -30738,13 +31389,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="40" t="s">
-        <v>2102</v>
+        <v>2097</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D26" s="40">
         <v>66</v>
@@ -30752,13 +31403,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="40" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D27" s="40">
         <v>67</v>
@@ -30766,13 +31417,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="39" t="s">
-        <v>2104</v>
+        <v>2099</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D28" s="40">
         <v>68</v>
@@ -30780,13 +31431,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="39" t="s">
-        <v>2105</v>
+        <v>2100</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D29" s="40">
         <v>69</v>
@@ -30794,13 +31445,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="40" t="s">
-        <v>2106</v>
+        <v>2101</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D30" s="40">
         <v>70</v>
@@ -30808,13 +31459,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="40" t="s">
-        <v>2107</v>
+        <v>2102</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D31" s="40">
         <v>71</v>
@@ -30822,13 +31473,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="40" t="s">
-        <v>2108</v>
+        <v>2103</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D32" s="40">
         <v>72</v>
@@ -30836,13 +31487,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="40" t="s">
-        <v>2109</v>
+        <v>2104</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D33" s="40">
         <v>73</v>
@@ -30850,13 +31501,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="39" t="s">
-        <v>2110</v>
+        <v>2105</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D34" s="40">
         <v>74</v>
@@ -30864,13 +31515,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="39" t="s">
-        <v>2111</v>
+        <v>2106</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D35" s="40">
         <v>76</v>
@@ -30878,13 +31529,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="39" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D36" s="40">
         <v>75</v>
@@ -30892,13 +31543,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="39" t="s">
-        <v>2113</v>
+        <v>2108</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D37" s="40">
         <v>77</v>
@@ -30906,13 +31557,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="39" t="s">
-        <v>2114</v>
+        <v>2109</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="D38" s="40">
         <v>78</v>
@@ -30920,72 +31571,72 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="39" t="s">
-        <v>2115</v>
+        <v>2110</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="D39" s="40" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="39" t="s">
-        <v>2116</v>
+        <v>2111</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="39" t="s">
-        <v>2117</v>
+        <v>2112</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="40" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="C42" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="40" t="s">
-        <v>2119</v>
+        <v>2114</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="C43" s="40" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
     </row>
   </sheetData>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="4800" windowHeight="10590" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="4800" windowHeight="10590" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="2179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4476" uniqueCount="2243">
   <si>
     <t>DSGY-F704JBKZ</t>
   </si>
@@ -5784,9 +5784,6 @@
     <t>STAND_POST</t>
   </si>
   <si>
-    <t>IC_</t>
-  </si>
-  <si>
     <t>JOG_KEY_UNIT</t>
   </si>
   <si>
@@ -6105,9 +6102,6 @@
     <t>MATI</t>
   </si>
   <si>
-    <t>HANYA SUARA SAJA</t>
-  </si>
-  <si>
     <t>TIDAK BISA HIDUP</t>
   </si>
   <si>
@@ -6177,60 +6171,27 @@
     <t>action</t>
   </si>
   <si>
-    <t>replace_power_unit</t>
-  </si>
-  <si>
-    <t>replace_panel</t>
-  </si>
-  <si>
-    <t>replace_main_unit</t>
-  </si>
-  <si>
-    <t>Remote Control</t>
-  </si>
-  <si>
-    <t>replace_remote_control</t>
-  </si>
-  <si>
     <t>repair_comment</t>
   </si>
   <si>
-    <t>*bawa</t>
-  </si>
-  <si>
     <t>ZY</t>
   </si>
   <si>
     <t>*ext</t>
   </si>
   <si>
-    <t>external</t>
-  </si>
-  <si>
     <t>UPGRADE</t>
   </si>
   <si>
-    <t>upgrade</t>
-  </si>
-  <si>
     <t>*factor</t>
   </si>
   <si>
-    <t>factory_reset</t>
-  </si>
-  <si>
     <t>JELAS</t>
   </si>
   <si>
-    <t>explanation</t>
-  </si>
-  <si>
     <t>BATAL</t>
   </si>
   <si>
-    <t>cancel</t>
-  </si>
-  <si>
     <t>Repair Action</t>
   </si>
   <si>
@@ -6246,9 +6207,6 @@
     <t>Repair LVDS</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
     <t>Reinsert Speaker</t>
   </si>
   <si>
@@ -6264,9 +6222,6 @@
     <t>User</t>
   </si>
   <si>
-    <t>Non Defect</t>
-  </si>
-  <si>
     <t>Setting</t>
   </si>
   <si>
@@ -6279,27 +6234,18 @@
     <t>Replace Panel</t>
   </si>
   <si>
-    <t>Panel</t>
-  </si>
-  <si>
     <t>Repair Panel</t>
   </si>
   <si>
     <t>Replace Main Unit</t>
   </si>
   <si>
-    <t>Main Unit</t>
-  </si>
-  <si>
     <t>Repair Main Unit</t>
   </si>
   <si>
     <t>Replace Power Unit</t>
   </si>
   <si>
-    <t>Power Unit</t>
-  </si>
-  <si>
     <t>Replace TCON</t>
   </si>
   <si>
@@ -6309,9 +6255,6 @@
     <t>Factory Reset</t>
   </si>
   <si>
-    <t>Software</t>
-  </si>
-  <si>
     <t>Upgrade</t>
   </si>
   <si>
@@ -6333,9 +6276,6 @@
     <t>Replace Led Bar</t>
   </si>
   <si>
-    <t>Replace LVDS</t>
-  </si>
-  <si>
     <t>Replace IR Unit</t>
   </si>
   <si>
@@ -6408,9 +6348,6 @@
     <t>*GOYANG*</t>
   </si>
   <si>
-    <t>DISPLAY NG</t>
-  </si>
-  <si>
     <t>*BAYANG*</t>
   </si>
   <si>
@@ -6571,6 +6508,261 @@
   </si>
   <si>
     <t>RC_NG</t>
+  </si>
+  <si>
+    <t>DISPLAY_NG</t>
+  </si>
+  <si>
+    <t>GELAP</t>
+  </si>
+  <si>
+    <t>HANYA SUARA</t>
+  </si>
+  <si>
+    <t>SUARA SAJA</t>
+  </si>
+  <si>
+    <t>LAYAR BERMASALAH</t>
+  </si>
+  <si>
+    <t>LAYAR BLUE SCREEN</t>
+  </si>
+  <si>
+    <t>LAYAR REDUP DAN WARNA UNGU</t>
+  </si>
+  <si>
+    <t>ANTENE</t>
+  </si>
+  <si>
+    <t>LAYAR MERAH</t>
+  </si>
+  <si>
+    <t>PICTURE_NG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIDAK NYALA </t>
+  </si>
+  <si>
+    <t>TIDAK BISA NYALA</t>
+  </si>
+  <si>
+    <t>KLISE</t>
+  </si>
+  <si>
+    <t>EXTERNAL</t>
+  </si>
+  <si>
+    <t>CANCEL</t>
+  </si>
+  <si>
+    <t>REPLACE_POWER_UNIT</t>
+  </si>
+  <si>
+    <t>REPLACE_PANEL</t>
+  </si>
+  <si>
+    <t>REPLACE_MAIN_UNIT</t>
+  </si>
+  <si>
+    <t>REPLACE_REMOTE_CONTROL</t>
+  </si>
+  <si>
+    <t>FACTORY_RESET</t>
+  </si>
+  <si>
+    <t>EXPLANATION</t>
+  </si>
+  <si>
+    <t>REPAIR_POWER_UNIT</t>
+  </si>
+  <si>
+    <t>REPLACE_LED_BAR</t>
+  </si>
+  <si>
+    <t>REPLACE_LVDS_WIRE</t>
+  </si>
+  <si>
+    <t>REPLACE_AC_CORD</t>
+  </si>
+  <si>
+    <t>REPLACE_FFC_WIRE</t>
+  </si>
+  <si>
+    <t>CARRY</t>
+  </si>
+  <si>
+    <t>RESOLDERING PSU</t>
+  </si>
+  <si>
+    <t>UNIT CEK OK</t>
+  </si>
+  <si>
+    <t>USER</t>
+  </si>
+  <si>
+    <t>PERBAIKI MAIN UNIT</t>
+  </si>
+  <si>
+    <t>REPAIR_MAIN_UNIT</t>
+  </si>
+  <si>
+    <t>RESET PROGRAM</t>
+  </si>
+  <si>
+    <t>SETTING</t>
+  </si>
+  <si>
+    <t>bawa</t>
+  </si>
+  <si>
+    <t>UPDATE</t>
+  </si>
+  <si>
+    <t>NORMAL</t>
+  </si>
+  <si>
+    <t>ACC BIAYA</t>
+  </si>
+  <si>
+    <t>REPAIR MAIN</t>
+  </si>
+  <si>
+    <t>REPAIR POWER</t>
+  </si>
+  <si>
+    <t>RESOLDERING MAIN</t>
+  </si>
+  <si>
+    <t>RESOLDERING MB</t>
+  </si>
+  <si>
+    <t>SET UP DATA</t>
+  </si>
+  <si>
+    <t>RESOLDERING IC7801</t>
+  </si>
+  <si>
+    <t>CEK FUNGSI OK</t>
+  </si>
+  <si>
+    <t>RISET PROGRAM</t>
+  </si>
+  <si>
+    <t>RESET-ULANG</t>
+  </si>
+  <si>
+    <t>PERBAIKAN POWER</t>
+  </si>
+  <si>
+    <t>PERBAIKAN MODUL POWER</t>
+  </si>
+  <si>
+    <t>EXS</t>
+  </si>
+  <si>
+    <t>RESOLDER PCB MAIN</t>
+  </si>
+  <si>
+    <t>RESOLDRING D7801</t>
+  </si>
+  <si>
+    <t>SERVICE MODE</t>
+  </si>
+  <si>
+    <t>CEK OK</t>
+  </si>
+  <si>
+    <t>TO WS</t>
+  </si>
+  <si>
+    <t>PERBAIKI POWER</t>
+  </si>
+  <si>
+    <t>PERBAIKAN MAIN</t>
+  </si>
+  <si>
+    <t>BERSIHKAN</t>
+  </si>
+  <si>
+    <t>KOTOR</t>
+  </si>
+  <si>
+    <t>RESET PABRIK</t>
+  </si>
+  <si>
+    <t>SOLDERING MAIN</t>
+  </si>
+  <si>
+    <t>DEFECT</t>
+  </si>
+  <si>
+    <t>NON DEFECT</t>
+  </si>
+  <si>
+    <t>MAIN UNIT</t>
+  </si>
+  <si>
+    <t>POWER UNIT</t>
+  </si>
+  <si>
+    <t>SOFTWARE</t>
+  </si>
+  <si>
+    <t>STEL ULANG PROGRAM</t>
+  </si>
+  <si>
+    <t>TEST FUNGSI</t>
+  </si>
+  <si>
+    <t>SOLDER MAIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESOLDERING MODUL </t>
+  </si>
+  <si>
+    <t>REPAIR PWB MAIN</t>
+  </si>
+  <si>
+    <t>REPAIR REGULATOR</t>
+  </si>
+  <si>
+    <t>REPAIR REMOTE</t>
+  </si>
+  <si>
+    <t>REPAIR_REMOTE</t>
+  </si>
+  <si>
+    <t>RESTAR PROGRAM</t>
+  </si>
+  <si>
+    <t>TDK ACC</t>
+  </si>
+  <si>
+    <t>RESET UNIT</t>
+  </si>
+  <si>
+    <t>RESET ULANG</t>
+  </si>
+  <si>
+    <t>REPLACE_TCON_UNIT</t>
+  </si>
+  <si>
+    <t>REPLACE_TAPE</t>
+  </si>
+  <si>
+    <t>REPLACE_SWITCH</t>
+  </si>
+  <si>
+    <t>REPLACE_IR_UNIT</t>
+  </si>
+  <si>
+    <t>REPLACE_LED_IR_UNIT</t>
+  </si>
+  <si>
+    <t>REPLACE_SPEAKER</t>
+  </si>
+  <si>
+    <t>REPLACE_IC</t>
   </si>
 </sst>
 </file>
@@ -6772,7 +6964,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6871,6 +7063,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7338,7 +7535,7 @@
         <v>956</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7354,7 +7551,7 @@
         <v>954</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7362,7 +7559,7 @@
         <v>1626</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7370,7 +7567,7 @@
         <v>1320</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7378,7 +7575,7 @@
         <v>953</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7386,7 +7583,7 @@
         <v>1774</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7394,7 +7591,7 @@
         <v>1025</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7458,7 +7655,7 @@
         <v>949</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7466,7 +7663,7 @@
         <v>948</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7850,7 +8047,7 @@
         <v>900</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1916</v>
+        <v>907</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7858,7 +8055,7 @@
         <v>901</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1916</v>
+        <v>907</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7866,7 +8063,7 @@
         <v>905</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1916</v>
+        <v>907</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7874,7 +8071,7 @@
         <v>902</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1916</v>
+        <v>907</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7882,7 +8079,7 @@
         <v>903</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1916</v>
+        <v>907</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -7890,7 +8087,7 @@
         <v>897</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -7898,7 +8095,7 @@
         <v>898</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -7906,7 +8103,7 @@
         <v>899</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -8298,7 +8495,7 @@
         <v>868</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -8306,7 +8503,7 @@
         <v>869</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -8314,7 +8511,7 @@
         <v>1398</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -8450,7 +8647,7 @@
         <v>1779</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -9266,7 +9463,7 @@
         <v>814</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -9490,7 +9687,7 @@
         <v>1147</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -9498,7 +9695,7 @@
         <v>1355</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -9506,7 +9703,7 @@
         <v>1356</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -10402,7 +10599,7 @@
         <v>1039</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -14258,7 +14455,7 @@
         <v>1394</v>
       </c>
       <c r="B884" s="3" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="885" spans="1:2">
@@ -14266,7 +14463,7 @@
         <v>1464</v>
       </c>
       <c r="B885" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="886" spans="1:2">
@@ -14274,7 +14471,7 @@
         <v>1471</v>
       </c>
       <c r="B886" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="887" spans="1:2">
@@ -14282,7 +14479,7 @@
         <v>1467</v>
       </c>
       <c r="B887" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="888" spans="1:2">
@@ -14290,7 +14487,7 @@
         <v>1472</v>
       </c>
       <c r="B888" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="889" spans="1:2">
@@ -14298,7 +14495,7 @@
         <v>1469</v>
       </c>
       <c r="B889" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="890" spans="1:2">
@@ -14306,7 +14503,7 @@
         <v>1473</v>
       </c>
       <c r="B890" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="891" spans="1:2">
@@ -14314,7 +14511,7 @@
         <v>1476</v>
       </c>
       <c r="B891" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="892" spans="1:2">
@@ -14322,7 +14519,7 @@
         <v>1482</v>
       </c>
       <c r="B892" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="893" spans="1:2">
@@ -14330,7 +14527,7 @@
         <v>1478</v>
       </c>
       <c r="B893" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="894" spans="1:2">
@@ -14338,7 +14535,7 @@
         <v>1483</v>
       </c>
       <c r="B894" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="895" spans="1:2">
@@ -14346,7 +14543,7 @@
         <v>1480</v>
       </c>
       <c r="B895" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="896" spans="1:2">
@@ -14354,7 +14551,7 @@
         <v>1484</v>
       </c>
       <c r="B896" s="3" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="897" spans="1:2">
@@ -14362,7 +14559,7 @@
         <v>1400</v>
       </c>
       <c r="B897" s="3" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="898" spans="1:2">
@@ -17975,7 +18172,7 @@
         <v>271</v>
       </c>
       <c r="B1347" s="3" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="1348" spans="1:2">
@@ -17999,7 +18196,7 @@
         <v>268</v>
       </c>
       <c r="B1350" s="3" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1351" spans="1:2">
@@ -18007,7 +18204,7 @@
         <v>1319</v>
       </c>
       <c r="B1351" s="3" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1352" spans="1:2">
@@ -18015,7 +18212,7 @@
         <v>1331</v>
       </c>
       <c r="B1352" s="3" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1353" spans="1:2">
@@ -19783,7 +19980,7 @@
         <v>1188</v>
       </c>
       <c r="B1573" s="3" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1574" spans="1:2">
@@ -19791,7 +19988,7 @@
         <v>1422</v>
       </c>
       <c r="B1574" s="3" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1575" spans="1:2">
@@ -19799,7 +19996,7 @@
         <v>1421</v>
       </c>
       <c r="B1575" s="3" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1576" spans="1:2">
@@ -20927,7 +21124,7 @@
         <v>39</v>
       </c>
       <c r="B1716" s="3" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1717" spans="1:2">
@@ -21519,7 +21716,7 @@
         <v>19</v>
       </c>
       <c r="B1790" s="3" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="1791" spans="1:2">
@@ -21527,7 +21724,7 @@
         <v>1216</v>
       </c>
       <c r="B1791" s="3" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="1792" spans="1:2">
@@ -21543,7 +21740,7 @@
         <v>17</v>
       </c>
       <c r="B1793" s="3" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1794" spans="1:2">
@@ -21575,7 +21772,7 @@
         <v>1625</v>
       </c>
       <c r="B1797" s="3" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="1798" spans="1:2">
@@ -21591,7 +21788,7 @@
         <v>14</v>
       </c>
       <c r="B1799" s="3" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="1800" spans="1:2">
@@ -21599,7 +21796,7 @@
         <v>13</v>
       </c>
       <c r="B1800" s="3" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="1801" spans="1:2">
@@ -21743,7 +21940,7 @@
         <v>3</v>
       </c>
       <c r="B1818" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1819" spans="1:2">
@@ -21751,7 +21948,7 @@
         <v>4</v>
       </c>
       <c r="B1819" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1820" spans="1:2">
@@ -21759,7 +21956,7 @@
         <v>1341</v>
       </c>
       <c r="B1820" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1821" spans="1:2">
@@ -21767,7 +21964,7 @@
         <v>1340</v>
       </c>
       <c r="B1821" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1822" spans="1:2">
@@ -21775,7 +21972,7 @@
         <v>1184</v>
       </c>
       <c r="B1822" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1823" spans="1:2">
@@ -21783,7 +21980,7 @@
         <v>1090</v>
       </c>
       <c r="B1823" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1824" spans="1:2">
@@ -21791,7 +21988,7 @@
         <v>1714</v>
       </c>
       <c r="B1824" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1825" spans="1:2">
@@ -21799,7 +21996,7 @@
         <v>1321</v>
       </c>
       <c r="B1825" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1826" spans="1:2">
@@ -21807,7 +22004,7 @@
         <v>1769</v>
       </c>
       <c r="B1826" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1827" spans="1:2">
@@ -21815,7 +22012,7 @@
         <v>1602</v>
       </c>
       <c r="B1827" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1828" spans="1:2">
@@ -21839,7 +22036,7 @@
         <v>1</v>
       </c>
       <c r="B1830" s="3" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1831" spans="1:2">
@@ -21891,10 +22088,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1">
       <c r="A1" s="20" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
@@ -21904,74 +22101,74 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="8" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="8" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="8" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="8" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="8" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="8" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="8" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="8" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -21979,15 +22176,15 @@
         <v>187</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="8" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -21995,119 +22192,119 @@
         <v>1027</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="8" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="8" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="8" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="8" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="8" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="8" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="8" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="8" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="8" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="8" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="8" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="8" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="8" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -22115,71 +22312,71 @@
         <v>263</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="8" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="8" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="8" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="8" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="8" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="8" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="8" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="8" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -22187,207 +22384,207 @@
         <v>1020</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="8" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="9" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="8" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="8" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="8" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="8" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="8" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="8" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="8" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="8" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="8" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="8" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="8" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="8" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="8" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="8" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="10" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="10" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="10" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="10" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="10" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="10" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="10" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="11" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -22395,55 +22592,55 @@
         <v>66</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="8" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="8" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="8" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="8" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="11" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="8" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -22451,15 +22648,15 @@
         <v>43</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="8" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>2012</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>2013</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -30088,7 +30285,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -30102,10 +30299,10 @@
         <v>1841</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -30113,10 +30310,10 @@
         <v>1882</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>2115</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -30124,10 +30321,10 @@
         <v>1853</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>2121</v>
+        <v>2101</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>2116</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -30135,10 +30332,10 @@
         <v>1853</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>2122</v>
+        <v>2102</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>2116</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -30146,10 +30343,10 @@
         <v>1853</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>2140</v>
+        <v>2119</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -30157,10 +30354,10 @@
         <v>1853</v>
       </c>
       <c r="B6" t="s">
-        <v>2170</v>
+        <v>2149</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -30168,10 +30365,10 @@
         <v>1853</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>2141</v>
+        <v>2120</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -30179,10 +30376,10 @@
         <v>1853</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>2142</v>
+        <v>2121</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -30190,10 +30387,10 @@
         <v>1853</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>2169</v>
+        <v>2148</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -30201,10 +30398,10 @@
         <v>1853</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>2171</v>
+        <v>2150</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -30212,10 +30409,10 @@
         <v>1853</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -30223,10 +30420,10 @@
         <v>1853</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -30234,10 +30431,10 @@
         <v>1853</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>2176</v>
+        <v>2155</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -30245,10 +30442,10 @@
         <v>1853</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -30256,10 +30453,10 @@
         <v>1853</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>2023</v>
+        <v>2160</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -30267,10 +30464,10 @@
         <v>1853</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>2123</v>
+        <v>2161</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>2124</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -30278,10 +30475,10 @@
         <v>1853</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>2172</v>
+        <v>2159</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>2124</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -30289,10 +30486,10 @@
         <v>1853</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>2173</v>
+        <v>2103</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>2124</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -30300,10 +30497,10 @@
         <v>1853</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>2174</v>
+        <v>2151</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>2124</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -30311,21 +30508,21 @@
         <v>1853</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>2125</v>
+        <v>2152</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>2126</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="23" t="s">
         <v>1853</v>
       </c>
-      <c r="B21" t="s">
-        <v>2126</v>
+      <c r="B21" s="23" t="s">
+        <v>2153</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>2126</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -30333,10 +30530,10 @@
         <v>1853</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>2128</v>
+        <v>2162</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>2127</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -30344,10 +30541,10 @@
         <v>1853</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>2136</v>
+        <v>2163</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>2127</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -30355,10 +30552,10 @@
         <v>1853</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>2143</v>
+        <v>2164</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>2115</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -30366,21 +30563,21 @@
         <v>1853</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>2129</v>
+        <v>2104</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>2124</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="23" t="s">
         <v>1853</v>
       </c>
-      <c r="B26" s="23" t="s">
-        <v>2130</v>
+      <c r="B26" t="s">
+        <v>2105</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>2131</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -30388,10 +30585,10 @@
         <v>1853</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>2175</v>
+        <v>2107</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>2131</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -30399,10 +30596,10 @@
         <v>1853</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>2132</v>
+        <v>2115</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>2133</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -30410,10 +30607,10 @@
         <v>1853</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>2177</v>
+        <v>2122</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>2133</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -30421,10 +30618,10 @@
         <v>1853</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>2134</v>
+        <v>2108</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>2135</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -30432,76 +30629,76 @@
         <v>1853</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>2137</v>
+        <v>2109</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>2020</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>2144</v>
+        <v>2154</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>2117</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>2146</v>
+        <v>2111</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>2117</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>2145</v>
+        <v>2156</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>2117</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>2154</v>
+        <v>2113</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="23" t="s">
-        <v>1871</v>
+        <v>1853</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>2147</v>
+        <v>2116</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>2115</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="23" t="s">
-        <v>1871</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>2148</v>
+        <v>1853</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2097</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>2115</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -30509,10 +30706,10 @@
         <v>1871</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>2149</v>
+        <v>2123</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>2115</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -30520,10 +30717,10 @@
         <v>1871</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>2024</v>
+        <v>2125</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>2115</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -30531,10 +30728,10 @@
         <v>1871</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>2025</v>
+        <v>2124</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>2115</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -30542,10 +30739,10 @@
         <v>1871</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>2026</v>
+        <v>2133</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>2118</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -30553,10 +30750,10 @@
         <v>1871</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>2027</v>
+        <v>2126</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>2119</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -30564,10 +30761,10 @@
         <v>1871</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>2028</v>
+        <v>2127</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>2120</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -30575,21 +30772,21 @@
         <v>1871</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>2156</v>
+        <v>2128</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>2120</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="23" t="s">
         <v>1871</v>
       </c>
-      <c r="B45" t="s">
-        <v>2155</v>
+      <c r="B45" s="23" t="s">
+        <v>2022</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>2120</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -30597,21 +30794,21 @@
         <v>1871</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>2029</v>
+        <v>2023</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>2120</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="23" t="s">
         <v>1871</v>
       </c>
-      <c r="B47" t="s">
-        <v>2164</v>
+      <c r="B47" s="23" t="s">
+        <v>2169</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>2120</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -30619,10 +30816,10 @@
         <v>1871</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>2150</v>
-      </c>
-      <c r="C48" s="42" t="s">
-        <v>2139</v>
+        <v>2168</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>2095</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -30630,10 +30827,10 @@
         <v>1871</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>2151</v>
-      </c>
-      <c r="C49" s="42" t="s">
-        <v>2139</v>
+        <v>2024</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>2098</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -30641,10 +30838,10 @@
         <v>1871</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>2138</v>
-      </c>
-      <c r="C50" s="42" t="s">
-        <v>2139</v>
+        <v>2025</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>2099</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -30652,10 +30849,10 @@
         <v>1871</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>2153</v>
-      </c>
-      <c r="C51" s="42" t="s">
-        <v>2152</v>
+        <v>2026</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>2100</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -30663,21 +30860,21 @@
         <v>1871</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>2168</v>
-      </c>
-      <c r="C52" s="42" t="s">
-        <v>2152</v>
+        <v>2135</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>2100</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="23" t="s">
         <v>1871</v>
       </c>
-      <c r="B53" s="23" t="s">
-        <v>2152</v>
-      </c>
-      <c r="C53" s="42" t="s">
-        <v>2152</v>
+      <c r="B53" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>2100</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -30685,21 +30882,21 @@
         <v>1871</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>2157</v>
-      </c>
-      <c r="C54" s="42" t="s">
-        <v>2158</v>
+        <v>2027</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>2100</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="23" t="s">
         <v>1871</v>
       </c>
-      <c r="B55" s="23" t="s">
-        <v>2159</v>
-      </c>
-      <c r="C55" s="42" t="s">
-        <v>2160</v>
+      <c r="B55" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C55" s="23" t="s">
+        <v>2100</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -30707,10 +30904,10 @@
         <v>1871</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>2161</v>
+        <v>2129</v>
       </c>
       <c r="C56" s="42" t="s">
-        <v>2160</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -30718,10 +30915,10 @@
         <v>1871</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>2162</v>
+        <v>2130</v>
       </c>
       <c r="C57" s="42" t="s">
-        <v>2160</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -30729,10 +30926,10 @@
         <v>1871</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>2163</v>
+        <v>2117</v>
       </c>
       <c r="C58" s="42" t="s">
-        <v>2165</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -30740,43 +30937,843 @@
         <v>1871</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>2166</v>
+        <v>2132</v>
       </c>
       <c r="C59" s="42" t="s">
-        <v>2167</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="43" t="s">
-        <v>1870</v>
+      <c r="A60" s="23" t="s">
+        <v>1871</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>2162</v>
+        <v>2147</v>
       </c>
       <c r="C60" s="42" t="s">
-        <v>2178</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="43" t="s">
-        <v>1870</v>
+      <c r="A61" s="23" t="s">
+        <v>1871</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>2161</v>
+        <v>2131</v>
       </c>
       <c r="C61" s="42" t="s">
-        <v>2178</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C62" s="42" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C63" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C64" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C65" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C66" s="42" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C67" s="42" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B68" s="23" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C68" s="42" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C69" s="42" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B70" s="23" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C70" s="42" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="23" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B71" s="23" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C71" s="42" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="43" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B72" s="23" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C72" s="42" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="43" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B73" s="23" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C73" s="42" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="43" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B74" s="23" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C74" s="42" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="23" t="s">
         <v>1878</v>
       </c>
-      <c r="B62" s="23" t="s">
+      <c r="B75" s="23" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C75" s="23" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="23"/>
+      <c r="B76" s="23" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="23"/>
+      <c r="B77" s="23" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C77" s="23" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="23"/>
+      <c r="B78" s="23" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C78" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="23"/>
+      <c r="B79" s="23" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C79" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="23"/>
+      <c r="B80" s="23" t="s">
+        <v>2120</v>
+      </c>
+      <c r="C80" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="23"/>
+      <c r="B81" s="23" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C81" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="23"/>
+      <c r="B82" s="23" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C82" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="23"/>
+      <c r="B83" s="23" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C83" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="23"/>
+      <c r="B84" s="23" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C84" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="23"/>
+      <c r="B85" s="23" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C85" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="23"/>
+      <c r="B86" s="23" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C86" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="23"/>
+      <c r="B87" s="23" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C87" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="23"/>
+      <c r="B88" s="23" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C88" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="23"/>
+      <c r="B89" s="23" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C89" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="23"/>
+      <c r="B90" s="23" t="s">
+        <v>2159</v>
+      </c>
+      <c r="C90" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="23"/>
+      <c r="B91" s="23" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C91" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="23"/>
+      <c r="B92" s="23" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C92" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="23"/>
+      <c r="B93" s="23" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C93" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="23"/>
+      <c r="B94" s="23" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C94" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="23"/>
+      <c r="B95" s="23" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C95" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="23"/>
+      <c r="B96" s="23" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C96" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="23"/>
+      <c r="B97" s="23" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C97" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="23"/>
+      <c r="B98" s="23" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C98" s="23" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="23"/>
+      <c r="B99" s="23" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C99" s="23" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="23"/>
+      <c r="B100" s="23" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C100" s="23" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="23"/>
+      <c r="B101" s="23" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C101" s="23" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="23"/>
+      <c r="B102" s="23" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C102" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="23"/>
+      <c r="B103" s="23" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C103" s="23" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="23"/>
+      <c r="B104" s="23" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C104" s="23" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="23"/>
+      <c r="B105" s="23" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C105" s="23" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="23"/>
+      <c r="B106" s="23" t="s">
+        <v>2111</v>
+      </c>
+      <c r="C106" s="23" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="23"/>
+      <c r="B107" s="23" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C107" s="23" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="23"/>
+      <c r="B108" s="23" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C108" s="23" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="23"/>
+      <c r="B109" s="23" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C109" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="23"/>
+      <c r="B110" s="23" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C110" s="23" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="23"/>
+      <c r="B111" s="23" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C111" s="23" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="23"/>
+      <c r="B112" s="23" t="s">
+        <v>2125</v>
+      </c>
+      <c r="C112" s="23" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="23"/>
+      <c r="B113" s="23" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C113" s="23" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="23"/>
+      <c r="B114" s="23" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C114" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="23"/>
+      <c r="B115" s="23" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C115" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="23"/>
+      <c r="B116" s="23" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C116" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="23"/>
+      <c r="B117" s="23" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C117" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="23"/>
+      <c r="B118" s="23" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C118" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="23"/>
+      <c r="B119" s="23" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C119" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="23"/>
+      <c r="B120" s="23" t="s">
         <v>2169</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C120" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="23"/>
+      <c r="B121" s="23" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C121" s="23" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="23"/>
+      <c r="B122" s="23" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C122" s="23" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="23"/>
+      <c r="B123" s="23" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C123" s="23" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="23"/>
+      <c r="B124" s="23" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C124" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="23"/>
+      <c r="B125" s="23" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C125" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="23"/>
+      <c r="B126" s="23" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C126" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="23"/>
+      <c r="B127" s="23" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C127" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="23"/>
+      <c r="B128" s="23" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C128" s="23" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="23"/>
+      <c r="B129" s="23" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C129" s="42" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="23"/>
+      <c r="B130" s="23" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C130" s="42" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="23"/>
+      <c r="B131" s="23" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C131" s="42" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="23"/>
+      <c r="B132" s="23" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C132" s="42" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="23"/>
+      <c r="B133" s="23" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C133" s="42" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="23"/>
+      <c r="B134" s="23" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C134" s="42" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="23"/>
+      <c r="B135" s="23" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C135" s="42" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="23"/>
+      <c r="B136" s="23" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C136" s="42" t="s">
         <v>2139</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="23"/>
+      <c r="B137" s="23" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C137" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="23"/>
+      <c r="B138" s="23" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C138" s="42" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="23"/>
+      <c r="B139" s="23" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C139" s="42" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" s="23"/>
+      <c r="B140" s="23" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C140" s="42" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" s="23"/>
+      <c r="B141" s="23" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C141" s="42" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" s="23"/>
+      <c r="B142" s="23" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C142" s="42" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" s="23"/>
+      <c r="B143" s="23" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C143" s="42" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" s="23"/>
+      <c r="B144" s="23" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C144" s="42" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="23"/>
+      <c r="B145" s="23" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C145" s="42" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="23"/>
+      <c r="B146" s="23" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C146" s="42" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" s="23"/>
+      <c r="B147" s="23" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C147" s="42" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" s="23"/>
+      <c r="B148" s="23" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C148" s="23" t="s">
+        <v>2118</v>
       </c>
     </row>
   </sheetData>
@@ -30795,42 +31792,42 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="25" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="26" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="26" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="26" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="27" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
     </row>
   </sheetData>
@@ -30849,34 +31846,34 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="25" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="26" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="26" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="26" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
     </row>
   </sheetData>
@@ -30886,142 +31883,651 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" style="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" style="30" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:6">
       <c r="A1" s="34" t="s">
         <v>1841</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>2052</v>
+        <v>2045</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>2046</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="31" customFormat="1">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="31" customFormat="1">
       <c r="A2" s="36"/>
       <c r="B2" s="29" t="s">
-        <v>2055</v>
+        <v>2047</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="31" customFormat="1">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="31" customFormat="1">
       <c r="A3" s="36"/>
       <c r="B3" s="32" t="s">
-        <v>2063</v>
+        <v>2051</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="32" t="s">
         <v>1882</v>
       </c>
-      <c r="B4" s="32" t="s">
-        <v>2019</v>
-      </c>
+      <c r="B4" s="32"/>
       <c r="C4" s="32" t="s">
-        <v>2047</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>2173</v>
+      </c>
+      <c r="F4" s="31"/>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="32" t="s">
         <v>1853</v>
       </c>
-      <c r="B5" s="32" t="s">
-        <v>2019</v>
-      </c>
+      <c r="B5" s="32"/>
       <c r="C5" s="32" t="s">
+        <v>2174</v>
+      </c>
+      <c r="F5" s="31"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="32" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32" t="s">
+        <v>2175</v>
+      </c>
+      <c r="F6" s="31"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="32" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32" t="s">
+        <v>2176</v>
+      </c>
+      <c r="F7" s="31"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="32" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B8" s="32"/>
+      <c r="C8" s="44" t="s">
+        <v>2179</v>
+      </c>
+      <c r="F8" s="31"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="44" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B9" s="32"/>
+      <c r="C9" s="44" t="s">
+        <v>2180</v>
+      </c>
+      <c r="F9" s="31"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="44" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="44" t="s">
+        <v>2181</v>
+      </c>
+      <c r="F10" s="31"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="44" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B11" s="32"/>
+      <c r="C11" s="44" t="s">
+        <v>2182</v>
+      </c>
+      <c r="F11" s="31"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="44" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B12" s="32"/>
+      <c r="C12" s="44" t="s">
+        <v>2183</v>
+      </c>
+      <c r="F12" s="31"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="44" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="44" t="s">
+        <v>2236</v>
+      </c>
+      <c r="F13" s="31"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="44" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B14" s="32"/>
+      <c r="C14" s="44" t="s">
+        <v>2237</v>
+      </c>
+      <c r="F14" s="31"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="32"/>
+      <c r="C15" s="44" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F15" s="31"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="44" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B16" s="32"/>
+      <c r="C16" s="44" t="s">
+        <v>2239</v>
+      </c>
+      <c r="F16" s="31"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="44" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B17" s="32"/>
+      <c r="C17" s="44" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F17" s="31"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="44" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B18" s="32"/>
+      <c r="C18" s="44" t="s">
+        <v>2241</v>
+      </c>
+      <c r="F18" s="31"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="44" t="s">
+        <v>907</v>
+      </c>
+      <c r="B19" s="32"/>
+      <c r="C19" s="44" t="s">
+        <v>2242</v>
+      </c>
+      <c r="F19" s="31"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="44"/>
+      <c r="B20" s="32" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C20" s="44" t="s">
+        <v>2191</v>
+      </c>
+      <c r="F20" s="31"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="32"/>
+      <c r="B21" s="44" t="s">
+        <v>2192</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>2046</v>
+      </c>
+      <c r="F21" s="31"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="32"/>
+      <c r="B22" s="32" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>2046</v>
+      </c>
+      <c r="F22" s="31"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="32"/>
+      <c r="B23" s="32" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>2046</v>
+      </c>
+      <c r="F23" s="31"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="32"/>
+      <c r="B24" s="32" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C24" s="44" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="32"/>
+      <c r="B25" s="32" t="s">
         <v>2048</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="32" t="s">
-        <v>1871</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C6" s="32" t="s">
+      <c r="C25" s="32" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F25" s="31"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="32"/>
+      <c r="B26" s="44" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F26" s="31"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="32"/>
+      <c r="B27" s="32" t="s">
         <v>2049</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="32" t="s">
+      <c r="C27" s="32" t="s">
+        <v>2177</v>
+      </c>
+      <c r="F27" s="31"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="32"/>
+      <c r="B28" s="32" t="s">
         <v>2050</v>
       </c>
-      <c r="B7" s="32" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32" t="s">
-        <v>2053</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>2054</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32" t="s">
-        <v>2054</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>2054</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32" t="s">
-        <v>2057</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>2058</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="32"/>
-      <c r="B11" s="32" t="s">
-        <v>2059</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32" t="s">
-        <v>2061</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>2062</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="32"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
+      <c r="C28" s="32" t="s">
+        <v>2178</v>
+      </c>
+      <c r="F28" s="31"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="32"/>
+      <c r="B29" s="32" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="32"/>
+      <c r="B30" s="32" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="32"/>
+      <c r="B31" s="32" t="s">
+        <v>2188</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="32"/>
+      <c r="B32" s="32" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="32"/>
+      <c r="B33" s="32" t="s">
+        <v>2194</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="32"/>
+      <c r="B34" s="32" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="32"/>
+      <c r="B35" s="32" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="32"/>
+      <c r="B36" s="32" t="s">
+        <v>2196</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="32"/>
+      <c r="B37" s="32" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C37" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="32"/>
+      <c r="B38" s="32" t="s">
+        <v>2198</v>
+      </c>
+      <c r="C38" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="32"/>
+      <c r="B39" s="32" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C39" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="32"/>
+      <c r="B40" s="32" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C40" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="32"/>
+      <c r="B41" s="32" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C41" s="44" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="32"/>
+      <c r="B42" s="32" t="s">
+        <v>2201</v>
+      </c>
+      <c r="C42" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="B43" s="30" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C43" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="32"/>
+      <c r="B44" s="32" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C44" s="44" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="32"/>
+      <c r="B45" s="32" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C45" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="32"/>
+      <c r="B46" s="32" t="s">
+        <v>2204</v>
+      </c>
+      <c r="C46" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="32"/>
+      <c r="B47" s="32" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C47" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="32"/>
+      <c r="B48" s="32" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C48" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="32"/>
+      <c r="B49" s="32" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C49" s="44" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="32"/>
+      <c r="B50" s="32" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C50" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="32"/>
+      <c r="B51" s="32" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C51" s="44" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="32"/>
+      <c r="B52" s="32" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C52" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="32"/>
+      <c r="B53" s="32" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C53" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="32"/>
+      <c r="B54" s="32" t="s">
+        <v>2215</v>
+      </c>
+      <c r="C54" s="44" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="32"/>
+      <c r="B55" s="44" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C55" s="44" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="32"/>
+      <c r="B56" s="32" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C56" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="32"/>
+      <c r="B57" s="32" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C57" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="32"/>
+      <c r="B58" s="44" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C58" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="32"/>
+      <c r="B59" s="32" t="s">
+        <v>2224</v>
+      </c>
+      <c r="C59" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="32"/>
+      <c r="B60" s="32" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C60" s="44" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="32"/>
+      <c r="B61" s="32" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C61" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="32"/>
+      <c r="B62" s="43" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C62" s="44" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="32"/>
+      <c r="B63" s="43" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C63" s="44" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="32"/>
+      <c r="B64" s="43" t="s">
+        <v>2230</v>
+      </c>
+      <c r="C64" s="44" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="32"/>
+      <c r="B65" s="32" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C65" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="32"/>
+      <c r="B66" s="32" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C66" s="44" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="32"/>
+      <c r="B67" s="32" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C67" s="44" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="32"/>
+      <c r="B68" s="32" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C68" s="44" t="s">
+        <v>2191</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -31030,7 +32536,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="24" style="38" bestFit="1" customWidth="1"/>
@@ -31039,607 +32545,632 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="37" t="s">
-        <v>2065</v>
+        <v>2052</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>2066</v>
+        <v>2053</v>
       </c>
       <c r="C1" s="37" t="s">
-        <v>2067</v>
+        <v>2054</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>2068</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="39" t="s">
-        <v>2069</v>
+        <v>2056</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D2" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D2" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="39" t="s">
-        <v>2071</v>
+        <v>2057</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D3" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D3" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="41" t="s">
-        <v>2072</v>
+        <v>2058</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>2073</v>
-      </c>
-      <c r="D4" s="40">
+        <v>2059</v>
+      </c>
+      <c r="D4" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="41" t="s">
-        <v>2074</v>
+        <v>2060</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>2073</v>
-      </c>
-      <c r="D5" s="40">
+        <v>2059</v>
+      </c>
+      <c r="D5" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="39" t="s">
-        <v>2054</v>
+        <v>2046</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>2073</v>
-      </c>
-      <c r="D6" s="40">
+        <v>2059</v>
+      </c>
+      <c r="D6" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="41" t="s">
-        <v>2074</v>
+        <v>2060</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>2073</v>
-      </c>
-      <c r="D7" s="40">
+        <v>2059</v>
+      </c>
+      <c r="D7" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="39" t="s">
-        <v>2054</v>
+        <v>2046</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>2073</v>
-      </c>
-      <c r="D8" s="40">
+        <v>2059</v>
+      </c>
+      <c r="D8" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="40" t="s">
-        <v>2075</v>
+        <v>2061</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>2076</v>
+        <v>2220</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D9" s="40">
+        <v>2187</v>
+      </c>
+      <c r="D9" s="45">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="40" t="s">
-        <v>2077</v>
+        <v>2062</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>2076</v>
+        <v>2220</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>2077</v>
-      </c>
-      <c r="D10" s="40">
+        <v>2191</v>
+      </c>
+      <c r="D10" s="45">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="40" t="s">
-        <v>2078</v>
+        <v>2063</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>2076</v>
+        <v>2220</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>2078</v>
-      </c>
-      <c r="D11" s="40">
+        <v>2178</v>
+      </c>
+      <c r="D11" s="45">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="40" t="s">
-        <v>2079</v>
+        <v>2064</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>2076</v>
+        <v>2220</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>2079</v>
-      </c>
-      <c r="D12" s="40">
+        <v>2134</v>
+      </c>
+      <c r="D12" s="45">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="39" t="s">
-        <v>2080</v>
+        <v>2065</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>2081</v>
-      </c>
-      <c r="D13" s="40">
+        <v>1853</v>
+      </c>
+      <c r="D13" s="45">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="39" t="s">
-        <v>2082</v>
+        <v>2066</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>2081</v>
-      </c>
-      <c r="D14" s="40">
+        <v>1853</v>
+      </c>
+      <c r="D14" s="45">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="39" t="s">
-        <v>2083</v>
+        <v>2067</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>2084</v>
-      </c>
-      <c r="D15" s="40">
+        <v>2221</v>
+      </c>
+      <c r="D15" s="45">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="39" t="s">
-        <v>2085</v>
+        <v>2068</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>2084</v>
-      </c>
-      <c r="D16" s="40">
+        <v>2221</v>
+      </c>
+      <c r="D16" s="45">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="41" t="s">
-        <v>2086</v>
+        <v>2069</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>2087</v>
-      </c>
-      <c r="D17" s="40">
+        <v>2222</v>
+      </c>
+      <c r="D17" s="45">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="40" t="s">
-        <v>2088</v>
+        <v>2070</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D18" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D18" s="45">
         <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="41" t="s">
-        <v>2089</v>
+        <v>2071</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>2087</v>
-      </c>
-      <c r="D19" s="40">
+        <v>2222</v>
+      </c>
+      <c r="D19" s="45">
         <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="39" t="s">
-        <v>2090</v>
+        <v>2072</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>2091</v>
-      </c>
-      <c r="D20" s="40">
+        <v>2223</v>
+      </c>
+      <c r="D20" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="39" t="s">
-        <v>2092</v>
+        <v>2073</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>2091</v>
-      </c>
-      <c r="D21" s="40">
+        <v>2223</v>
+      </c>
+      <c r="D21" s="45">
         <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="41" t="s">
-        <v>2093</v>
+        <v>2074</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D22" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D22" s="45">
         <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="40" t="s">
-        <v>2094</v>
+        <v>2075</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D23" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D23" s="45">
         <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="39" t="s">
-        <v>2095</v>
+        <v>2076</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D24" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D24" s="45">
         <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="41" t="s">
-        <v>2096</v>
+        <v>2077</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D25" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D25" s="45">
         <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="40" t="s">
-        <v>2097</v>
+        <v>2078</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D26" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D26" s="45">
         <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="40" t="s">
-        <v>2098</v>
+        <v>2079</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D27" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D27" s="45">
         <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="39" t="s">
-        <v>2099</v>
+      <c r="A28" s="38" t="s">
+        <v>2181</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D28" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D28" s="45">
         <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="39" t="s">
-        <v>2100</v>
+        <v>2080</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D29" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D29" s="45">
         <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="40" t="s">
-        <v>2101</v>
+        <v>2081</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D30" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D30" s="45">
         <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="40" t="s">
-        <v>2102</v>
+        <v>2082</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D31" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D31" s="45">
         <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="40" t="s">
-        <v>2103</v>
+        <v>2083</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D32" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D32" s="45">
         <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="40" t="s">
-        <v>2104</v>
+        <v>2084</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D33" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D33" s="45">
         <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="39" t="s">
-        <v>2105</v>
+        <v>2085</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D34" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D34" s="45">
         <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="39" t="s">
-        <v>2106</v>
+        <v>2086</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D35" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D35" s="45">
         <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="39" t="s">
-        <v>2107</v>
+        <v>2087</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D36" s="40">
+        <v>1870</v>
+      </c>
+      <c r="D36" s="45">
         <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="39" t="s">
-        <v>2108</v>
+        <v>2088</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D37" s="40">
+        <v>1870</v>
+      </c>
+      <c r="D37" s="45">
         <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="39" t="s">
-        <v>2109</v>
+        <v>2089</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>2067</v>
+        <v>2219</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D38" s="40">
+        <v>1855</v>
+      </c>
+      <c r="D38" s="45">
         <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="39" t="s">
-        <v>2110</v>
+        <v>2090</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="D39" s="40" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="39" t="s">
-        <v>2111</v>
+        <v>2091</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="39" t="s">
-        <v>2112</v>
+        <v>2092</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="40" t="s">
-        <v>2113</v>
+        <v>2093</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="C42" s="39" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="40" t="s">
-        <v>2114</v>
+        <v>2094</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="C43" s="40" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>2073</v>
-      </c>
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="40" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B44" s="40" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C44" s="40" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D44" s="40"/>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="46" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B45" s="40" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C45" s="40" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D45" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARISAFARI\Works\Project Applications\ExcelAuto\ExcelAutoTool_1.1\masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARISAFARI\Works\Project Applications\tool-fcost\masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4407" uniqueCount="2276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4412" uniqueCount="2262">
   <si>
     <t>part_used</t>
   </si>
@@ -6753,109 +6753,67 @@
     <t>DEFECT</t>
   </si>
   <si>
-    <t>REINSERT SPEAKER</t>
-  </si>
-  <si>
     <t>SUBTITUSI</t>
   </si>
   <si>
-    <t>REPLACE PANEL - BEFORE CHANGE</t>
-  </si>
-  <si>
-    <t>NON DEFECT</t>
-  </si>
-  <si>
     <t>SIGNAL</t>
   </si>
   <si>
-    <t>REPLACE PANEL</t>
-  </si>
-  <si>
-    <t>REPAIR PANEL</t>
-  </si>
-  <si>
-    <t>REPLACE MAIN UNIT</t>
-  </si>
-  <si>
-    <t>MAIN UNIT</t>
-  </si>
-  <si>
-    <t>REPAIR MAIN UNIT</t>
-  </si>
-  <si>
-    <t>REPLACE POWER UNIT</t>
-  </si>
-  <si>
-    <t>POWER UNIT</t>
-  </si>
-  <si>
-    <t>REPLACE TCON</t>
-  </si>
-  <si>
-    <t>REPAIR POWER UNIT</t>
-  </si>
-  <si>
-    <t>FACTORY RESET</t>
-  </si>
-  <si>
-    <t>REINSERT LVDS</t>
-  </si>
-  <si>
-    <t>REPAIR IR UNIT</t>
-  </si>
-  <si>
-    <t>REPAIR LED BAR</t>
-  </si>
-  <si>
-    <t>REPAIR SPEAKER</t>
-  </si>
-  <si>
-    <t>REPLACE SPEAKER</t>
-  </si>
-  <si>
-    <t>REPLACE LED BAR</t>
-  </si>
-  <si>
-    <t>REPLACE LVDS</t>
-  </si>
-  <si>
-    <t>REPLACE IR UNIT</t>
-  </si>
-  <si>
-    <t>REPLACE WIFI UNIT</t>
-  </si>
-  <si>
-    <t>REPAIR TCON</t>
-  </si>
-  <si>
-    <t>REPAIR WIFI UNIT</t>
-  </si>
-  <si>
-    <t>REINSERT WIFI UNIT</t>
-  </si>
-  <si>
-    <t>REINSERT CABINET</t>
-  </si>
-  <si>
-    <t>REINSERT SOCKET</t>
-  </si>
-  <si>
-    <t>REPLACE REMOTE</t>
-  </si>
-  <si>
-    <t>REPLACE TAPE</t>
-  </si>
-  <si>
-    <t>VERIFIED OK</t>
-  </si>
-  <si>
-    <t>BEFORE IMPROVE - REMOTE</t>
-  </si>
-  <si>
-    <t>BEFORE IMPROVE</t>
-  </si>
-  <si>
     <t>SOFWARE</t>
+  </si>
+  <si>
+    <t>BEFORE_IMPROVE</t>
+  </si>
+  <si>
+    <t>NON_DEFECT</t>
+  </si>
+  <si>
+    <t>REINSERT_SOCKET</t>
+  </si>
+  <si>
+    <t>REINSERT_SPEAKER</t>
+  </si>
+  <si>
+    <t>REINSERT_WIFI_UNIT</t>
+  </si>
+  <si>
+    <t>REPAIR_IR_UNIT</t>
+  </si>
+  <si>
+    <t>REPAIR_LED_BAR</t>
+  </si>
+  <si>
+    <t>REPAIR_LVDS</t>
+  </si>
+  <si>
+    <t>REPAIR_PANEL</t>
+  </si>
+  <si>
+    <t>REPAIR_SPEAKER</t>
+  </si>
+  <si>
+    <t>REPAIR_TCON</t>
+  </si>
+  <si>
+    <t>REPAIR_WIFI_UNIT</t>
+  </si>
+  <si>
+    <t>REPLACE_TAPE</t>
+  </si>
+  <si>
+    <t>REPLACE_WIFI_UNIT</t>
+  </si>
+  <si>
+    <t>VERIFIED_OK</t>
+  </si>
+  <si>
+    <t>BEFORE_IMPROVE_REMOTE</t>
+  </si>
+  <si>
+    <t>REPLACE_PANEL_BEFORE_CHANGE</t>
+  </si>
+  <si>
+    <t>CEK NORMAL</t>
   </si>
 </sst>
 </file>
@@ -31459,7 +31417,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" style="27" bestFit="1" customWidth="1"/>
@@ -31499,62 +31457,62 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="26" t="s">
-        <v>1428</v>
-      </c>
+      <c r="A4" s="31"/>
       <c r="B4" s="26" t="s">
-        <v>2110</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>2149</v>
+        <v>2261</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>2169</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="26" t="s">
-        <v>989</v>
+        <v>1428</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>2110</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="26" t="s">
-        <v>459</v>
+        <v>989</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>2110</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="26" t="s">
-        <v>1659</v>
+        <v>459</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>2110</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="26" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="26" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C8" s="38" t="s">
         <v>2165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26" t="s">
-        <v>2152</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>2111</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="26"/>
       <c r="B9" s="26" t="s">
-        <v>2111</v>
+        <v>2152</v>
       </c>
       <c r="C9" s="26" t="s">
         <v>2111</v>
@@ -31563,166 +31521,166 @@
     <row r="10" spans="1:3">
       <c r="A10" s="26"/>
       <c r="B10" s="26" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="26"/>
       <c r="B11" s="26" t="s">
-        <v>2153</v>
+        <v>2112</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>2154</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="26"/>
       <c r="B12" s="26" t="s">
-        <v>2113</v>
+        <v>2153</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="26"/>
       <c r="B13" s="26" t="s">
-        <v>2156</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>2157</v>
+        <v>2113</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>2155</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="26"/>
       <c r="B14" s="26" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="26"/>
+      <c r="B15" s="26" t="s">
         <v>2158</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C15" s="38" t="s">
         <v>2147</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="26" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="26" t="s">
         <v>1397</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>2110</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>2159</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="39" t="s">
-        <v>214</v>
       </c>
       <c r="B16" s="38" t="s">
         <v>2110</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="39" t="s">
-        <v>109</v>
+        <v>214</v>
       </c>
       <c r="B17" s="38" t="s">
         <v>2110</v>
       </c>
       <c r="C17" s="38" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C18" s="38" t="s">
         <v>2161</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="26" t="s">
-        <v>2162</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>2112</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="26"/>
       <c r="B19" s="26" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>2164</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="26"/>
       <c r="B20" s="26" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>2159</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="26"/>
       <c r="B21" s="26" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>2111</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="26"/>
       <c r="B22" s="26" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>2169</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="26"/>
       <c r="B23" s="26" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>2147</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="26"/>
       <c r="B24" s="26" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>2161</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="26"/>
-      <c r="B25" s="40" t="s">
-        <v>2157</v>
+      <c r="B25" s="26" t="s">
+        <v>2171</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>2157</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="26"/>
-      <c r="B26" s="41" t="s">
-        <v>2172</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>2111</v>
+      <c r="B26" s="40" t="s">
+        <v>2157</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>2157</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="26"/>
-      <c r="B27" s="40" t="s">
-        <v>2111</v>
+      <c r="B27" s="41" t="s">
+        <v>2172</v>
       </c>
       <c r="C27" s="26" t="s">
         <v>2111</v>
@@ -31731,7 +31689,7 @@
     <row r="28" spans="1:3">
       <c r="A28" s="26"/>
       <c r="B28" s="40" t="s">
-        <v>2173</v>
+        <v>2111</v>
       </c>
       <c r="C28" s="26" t="s">
         <v>2111</v>
@@ -31740,25 +31698,25 @@
     <row r="29" spans="1:3">
       <c r="A29" s="26"/>
       <c r="B29" s="40" t="s">
-        <v>2174</v>
-      </c>
-      <c r="C29" s="38" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C29" s="26" t="s">
         <v>2111</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="26"/>
       <c r="B30" s="40" t="s">
-        <v>2112</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>2112</v>
+        <v>2174</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>2111</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="26"/>
-      <c r="B31" s="41" t="s">
-        <v>2162</v>
+      <c r="B31" s="40" t="s">
+        <v>2112</v>
       </c>
       <c r="C31" s="26" t="s">
         <v>2112</v>
@@ -31766,71 +31724,71 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="26"/>
-      <c r="B32" s="40" t="s">
-        <v>2175</v>
+      <c r="B32" s="41" t="s">
+        <v>2162</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>2154</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="26"/>
       <c r="B33" s="40" t="s">
-        <v>2113</v>
+        <v>2175</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="26"/>
       <c r="B34" s="40" t="s">
-        <v>2166</v>
-      </c>
-      <c r="C34" s="38" t="s">
-        <v>2159</v>
+        <v>2113</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>2155</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="26"/>
       <c r="B35" s="40" t="s">
-        <v>2176</v>
+        <v>2166</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>2169</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="26"/>
       <c r="B36" s="40" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>2161</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="26"/>
       <c r="B37" s="40" t="s">
-        <v>2156</v>
+        <v>2177</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>2157</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="26"/>
       <c r="B38" s="40" t="s">
-        <v>2178</v>
+        <v>2156</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>2169</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="26"/>
       <c r="B39" s="40" t="s">
-        <v>2168</v>
+        <v>2178</v>
       </c>
       <c r="C39" s="38" t="s">
         <v>2169</v>
@@ -31839,43 +31797,43 @@
     <row r="40" spans="1:3">
       <c r="A40" s="26"/>
       <c r="B40" s="40" t="s">
-        <v>2179</v>
+        <v>2168</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>2148</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="26"/>
       <c r="B41" s="40" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>2161</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="26"/>
       <c r="B42" s="40" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="26"/>
       <c r="B43" s="40" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="26"/>
       <c r="B44" s="40" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="C44" s="38" t="s">
         <v>2161</v>
@@ -31884,34 +31842,34 @@
     <row r="45" spans="1:3">
       <c r="A45" s="26"/>
       <c r="B45" s="40" t="s">
-        <v>2166</v>
+        <v>2183</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="26"/>
       <c r="B46" s="40" t="s">
-        <v>2184</v>
+        <v>2166</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>2169</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="26"/>
       <c r="B47" s="40" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>2161</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="26"/>
-      <c r="B48" s="27" t="s">
-        <v>2186</v>
+      <c r="B48" s="40" t="s">
+        <v>2185</v>
       </c>
       <c r="C48" s="38" t="s">
         <v>2161</v>
@@ -31919,26 +31877,26 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="26"/>
-      <c r="B49" s="40" t="s">
-        <v>2187</v>
+      <c r="B49" s="27" t="s">
+        <v>2186</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>2169</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="26"/>
       <c r="B50" s="40" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>2157</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="26"/>
       <c r="B51" s="40" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="C51" s="38" t="s">
         <v>2157</v>
@@ -31947,16 +31905,16 @@
     <row r="52" spans="1:3">
       <c r="A52" s="26"/>
       <c r="B52" s="40" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="26"/>
       <c r="B53" s="40" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="C53" s="38" t="s">
         <v>2159</v>
@@ -31965,61 +31923,61 @@
     <row r="54" spans="1:3">
       <c r="A54" s="26"/>
       <c r="B54" s="40" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>2147</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="26"/>
       <c r="B55" s="40" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>2161</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="26"/>
       <c r="B56" s="40" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>2154</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="26"/>
       <c r="B57" s="40" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="26"/>
       <c r="B58" s="40" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="26"/>
       <c r="B59" s="40" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>2147</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="26"/>
-      <c r="B60" s="41" t="s">
-        <v>2170</v>
+      <c r="B60" s="40" t="s">
+        <v>2197</v>
       </c>
       <c r="C60" s="38" t="s">
         <v>2147</v>
@@ -32027,62 +31985,62 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="26"/>
-      <c r="B61" s="40" t="s">
-        <v>2198</v>
+      <c r="B61" s="41" t="s">
+        <v>2170</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>2157</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="26"/>
       <c r="B62" s="40" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="C62" s="38" t="s">
-        <v>2161</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="26"/>
-      <c r="B63" s="41" t="s">
-        <v>2200</v>
+      <c r="B63" s="40" t="s">
+        <v>2199</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="26"/>
-      <c r="B64" s="40" t="s">
-        <v>2201</v>
+      <c r="B64" s="41" t="s">
+        <v>2200</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="26"/>
       <c r="B65" s="40" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>2169</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="26"/>
       <c r="B66" s="40" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>2161</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="26"/>
-      <c r="B67" s="42" t="s">
-        <v>2204</v>
+      <c r="B67" s="40" t="s">
+        <v>2203</v>
       </c>
       <c r="C67" s="38" t="s">
         <v>2161</v>
@@ -32091,252 +32049,252 @@
     <row r="68" spans="1:3">
       <c r="A68" s="26"/>
       <c r="B68" s="42" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="26"/>
       <c r="B69" s="42" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>2164</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="26"/>
-      <c r="B70" s="40" t="s">
-        <v>2207</v>
+      <c r="B70" s="42" t="s">
+        <v>2206</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>2157</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="26"/>
       <c r="B71" s="40" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>2148</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="26"/>
       <c r="B72" s="40" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="C72" s="38" t="s">
-        <v>2157</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="26"/>
       <c r="B73" s="40" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="C73" s="38" t="s">
         <v>2157</v>
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="39" t="s">
+      <c r="A74" s="26"/>
+      <c r="B74" s="40" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C74" s="38" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="39" t="s">
         <v>345</v>
       </c>
-      <c r="B74" s="38" t="s">
+      <c r="B75" s="38" t="s">
         <v>2110</v>
       </c>
-      <c r="C74" s="38" t="s">
+      <c r="C75" s="38" t="s">
         <v>2211</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" s="26"/>
-      <c r="C75" s="38" t="s">
-        <v>2212</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="38" t="s">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="B76" s="26"/>
       <c r="C76" s="38" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="38" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="B77" s="26"/>
       <c r="C77" s="38" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="38" t="s">
-        <v>1731</v>
+        <v>128</v>
       </c>
       <c r="B78" s="26"/>
       <c r="C78" s="38" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="38" t="s">
-        <v>1825</v>
+        <v>1731</v>
       </c>
       <c r="B79" s="26"/>
       <c r="C79" s="38" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="38" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B80" s="26"/>
+      <c r="C80" s="38" t="s">
         <v>2216</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="26"/>
-      <c r="B80" s="26" t="s">
-        <v>2217</v>
-      </c>
-      <c r="C80" s="38" t="s">
-        <v>2150</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="26"/>
       <c r="B81" s="26" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>2169</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="26"/>
       <c r="B82" s="26" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>2161</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="26"/>
       <c r="B83" s="26" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>2221</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="26"/>
       <c r="B84" s="26" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>2150</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="26"/>
       <c r="B85" s="26" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>2224</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="26"/>
       <c r="B86" s="26" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>2148</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="26"/>
       <c r="B87" s="26" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="26"/>
       <c r="B88" s="26" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>2159</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="26"/>
       <c r="B89" s="26" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>2112</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="26"/>
       <c r="B90" s="26" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>2147</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="26"/>
       <c r="B91" s="26" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>2169</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="26"/>
       <c r="B92" s="26" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="C92" s="38" t="s">
-        <v>2147</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="26"/>
       <c r="B93" s="26" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="C93" s="38" t="s">
-        <v>2224</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="26"/>
       <c r="B94" s="26" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>2148</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="26"/>
       <c r="B95" s="26" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="C95" s="38" t="s">
         <v>2148</v>
@@ -32345,63 +32303,72 @@
     <row r="96" spans="1:3">
       <c r="A96" s="26"/>
       <c r="B96" s="26" t="s">
-        <v>1888</v>
+        <v>2234</v>
       </c>
       <c r="C96" s="38" t="s">
-        <v>2161</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="26"/>
       <c r="B97" s="26" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C97" s="38" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="26"/>
+      <c r="B98" s="26" t="s">
         <v>2235</v>
       </c>
-      <c r="C97" s="38" t="s">
+      <c r="C98" s="38" t="s">
         <v>2111</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="39"/>
-      <c r="B98" s="26" t="s">
+    <row r="99" spans="1:3">
+      <c r="A99" s="39"/>
+      <c r="B99" s="26" t="s">
         <v>2236</v>
       </c>
-      <c r="C98" s="38" t="s">
+      <c r="C99" s="38" t="s">
         <v>2148</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="26"/>
-      <c r="B99" s="26" t="s">
-        <v>2237</v>
-      </c>
-      <c r="C99" s="38" t="s">
-        <v>2111</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="26"/>
       <c r="B100" s="26" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>2159</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="26"/>
-      <c r="B101" s="38" t="s">
-        <v>2275</v>
+      <c r="B101" s="26" t="s">
+        <v>2238</v>
       </c>
       <c r="C101" s="38" t="s">
-        <v>2112</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="26"/>
-      <c r="B102" s="26" t="s">
+      <c r="B102" s="38" t="s">
+        <v>2243</v>
+      </c>
+      <c r="C102" s="38" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="26"/>
+      <c r="B103" s="26" t="s">
         <v>2239</v>
       </c>
-      <c r="C102" s="38" t="s">
+      <c r="C103" s="38" t="s">
         <v>2112</v>
       </c>
     </row>
@@ -32412,7 +32379,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="33.85546875" style="33" customWidth="1"/>
@@ -32438,7 +32405,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="35" t="s">
-        <v>2274</v>
+        <v>2244</v>
       </c>
       <c r="B2" s="34" t="s">
         <v>2118</v>
@@ -32452,7 +32419,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="35" t="s">
-        <v>2273</v>
+        <v>2259</v>
       </c>
       <c r="B3" s="34" t="s">
         <v>2118</v>
@@ -32483,7 +32450,7 @@
         <v>2155</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>2155</v>
@@ -32508,7 +32475,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="34" t="s">
-        <v>2255</v>
+        <v>2154</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>2240</v>
@@ -32522,7 +32489,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="34" t="s">
-        <v>2268</v>
+        <v>2221</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>2240</v>
@@ -32536,7 +32503,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="36" t="s">
-        <v>2256</v>
+        <v>2224</v>
       </c>
       <c r="B9" s="34" t="s">
         <v>2240</v>
@@ -32550,7 +32517,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="34" t="s">
-        <v>2269</v>
+        <v>2246</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>2240</v>
@@ -32564,7 +32531,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="34" t="s">
-        <v>2241</v>
+        <v>2247</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>2240</v>
@@ -32578,7 +32545,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="35" t="s">
-        <v>2267</v>
+        <v>2248</v>
       </c>
       <c r="B12" s="34" t="s">
         <v>2240</v>
@@ -32592,7 +32559,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="35" t="s">
-        <v>2257</v>
+        <v>2249</v>
       </c>
       <c r="B13" s="35" t="s">
         <v>2240</v>
@@ -32606,7 +32573,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="34" t="s">
-        <v>2258</v>
+        <v>2250</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>2240</v>
@@ -32620,7 +32587,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="34" t="s">
-        <v>2232</v>
+        <v>2251</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>2240</v>
@@ -32634,13 +32601,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="34" t="s">
-        <v>2250</v>
+        <v>2161</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>2240</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>2249</v>
+        <v>459</v>
       </c>
       <c r="D16" s="43">
         <v>31</v>
@@ -32648,7 +32615,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="34" t="s">
-        <v>2247</v>
+        <v>2252</v>
       </c>
       <c r="B17" s="34" t="s">
         <v>2240</v>
@@ -32662,13 +32629,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="36" t="s">
-        <v>2254</v>
+        <v>2159</v>
       </c>
       <c r="B18" s="34" t="s">
         <v>2240</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>2252</v>
+        <v>1428</v>
       </c>
       <c r="D18" s="43">
         <v>41</v>
@@ -32676,7 +32643,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="34" t="s">
-        <v>2206</v>
+        <v>2164</v>
       </c>
       <c r="B19" s="34" t="s">
         <v>2240</v>
@@ -32690,7 +32657,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="36" t="s">
-        <v>2259</v>
+        <v>2253</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>2240</v>
@@ -32704,7 +32671,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="35" t="s">
-        <v>2265</v>
+        <v>2254</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>2240</v>
@@ -32718,7 +32685,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="35" t="s">
-        <v>2266</v>
+        <v>2255</v>
       </c>
       <c r="B22" s="34" t="s">
         <v>2240</v>
@@ -32732,7 +32699,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="34" t="s">
-        <v>2263</v>
+        <v>2214</v>
       </c>
       <c r="B23" s="34" t="s">
         <v>2240</v>
@@ -32746,7 +32713,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="35" t="s">
-        <v>2261</v>
+        <v>2160</v>
       </c>
       <c r="B24" s="35" t="s">
         <v>2240</v>
@@ -32760,7 +32727,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="34" t="s">
-        <v>2262</v>
+        <v>2211</v>
       </c>
       <c r="B25" s="34" t="s">
         <v>2240</v>
@@ -32774,13 +32741,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="34" t="s">
-        <v>2248</v>
+        <v>2151</v>
       </c>
       <c r="B26" s="34" t="s">
         <v>2240</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>2249</v>
+        <v>459</v>
       </c>
       <c r="D26" s="43">
         <v>30</v>
@@ -32788,7 +32755,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="34" t="s">
-        <v>2246</v>
+        <v>2150</v>
       </c>
       <c r="B27" s="34" t="s">
         <v>2240</v>
@@ -32802,7 +32769,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="36" t="s">
-        <v>2243</v>
+        <v>2260</v>
       </c>
       <c r="B28" s="34" t="s">
         <v>2118</v>
@@ -32816,13 +32783,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="36" t="s">
-        <v>2251</v>
+        <v>2149</v>
       </c>
       <c r="B29" s="35" t="s">
         <v>2240</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>2252</v>
+        <v>1428</v>
       </c>
       <c r="D29" s="43">
         <v>40</v>
@@ -32830,7 +32797,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="34" t="s">
-        <v>2270</v>
+        <v>2165</v>
       </c>
       <c r="B30" s="34" t="s">
         <v>2240</v>
@@ -32844,7 +32811,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="35" t="s">
-        <v>2260</v>
+        <v>2215</v>
       </c>
       <c r="B31" s="35" t="s">
         <v>2240</v>
@@ -32858,7 +32825,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="34" t="s">
-        <v>2271</v>
+        <v>2256</v>
       </c>
       <c r="B32" s="34" t="s">
         <v>2240</v>
@@ -32872,7 +32839,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="35" t="s">
-        <v>2253</v>
+        <v>2216</v>
       </c>
       <c r="B33" s="35" t="s">
         <v>2240</v>
@@ -32886,7 +32853,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="35" t="s">
-        <v>2264</v>
+        <v>2257</v>
       </c>
       <c r="B34" s="34" t="s">
         <v>2240</v>
@@ -32903,7 +32870,7 @@
         <v>2157</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="C35" s="35" t="s">
         <v>2157</v>
@@ -32914,13 +32881,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="35" t="s">
+        <v>2242</v>
+      </c>
+      <c r="B36" s="34" t="s">
         <v>2245</v>
       </c>
-      <c r="B36" s="34" t="s">
-        <v>2244</v>
-      </c>
       <c r="C36" s="35" t="s">
-        <v>2245</v>
+        <v>2242</v>
       </c>
       <c r="D36" s="43">
         <v>14</v>
@@ -32928,7 +32895,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="36" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="B37" s="35" t="s">
         <v>2118</v>
@@ -32959,7 +32926,7 @@
         <v>2169</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="C39" s="35" t="s">
         <v>2169</v>
@@ -32970,7 +32937,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="34" t="s">
-        <v>2272</v>
+        <v>2258</v>
       </c>
       <c r="B40" s="34" t="s">
         <v>2118</v>
@@ -32997,18 +32964,28 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="34" t="s">
-        <v>2111</v>
-      </c>
-      <c r="B42" s="34" t="s">
-        <v>2118</v>
+      <c r="A42" s="35" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B42" s="35" t="s">
+        <v>2240</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>2118</v>
-      </c>
-      <c r="D42" s="43">
-        <v>0</v>
-      </c>
+        <v>964</v>
+      </c>
+      <c r="D42" s="35"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="35" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B43" s="35" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C43" s="35" t="s">
+        <v>964</v>
+      </c>
+      <c r="D43" s="35"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1">

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Koding\tool-fcost\masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1080E9AE-6924-48C5-A751-85A6F1C3D94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB07C0C-E8EC-40D7-9A64-8B46618CB569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4639" uniqueCount="2376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4651" uniqueCount="2384">
   <si>
     <t>part_used</t>
   </si>
@@ -6507,9 +6507,6 @@
     <t>REPLACE_TCON_UNIT</t>
   </si>
   <si>
-    <t>(?i).*(BAWA|ZY|DITARIK|KIRIM|WS|bawa|CARRY|TO\ WS.).*</t>
-  </si>
-  <si>
     <t>ZY</t>
   </si>
   <si>
@@ -6573,15 +6570,6 @@
     <t>(?i).*RESOLDERING\ MB.*</t>
   </si>
   <si>
-    <t>(?i).*RESOLDERING\ IC7801.*</t>
-  </si>
-  <si>
-    <t>(?i).*RESOLDRING\ D7801.*</t>
-  </si>
-  <si>
-    <t>(?i).*SOLDERING\ MAIN.*</t>
-  </si>
-  <si>
     <t>(?i).*PERBAIKAN\ MAIN.*</t>
   </si>
   <si>
@@ -6624,9 +6612,6 @@
     <t>(?i).*RESOLDERING.*</t>
   </si>
   <si>
-    <t>(?i).*repair\ modul.*|GANTI DIODA</t>
-  </si>
-  <si>
     <t>(?i).*PERBAIKI\ POWER.*</t>
   </si>
   <si>
@@ -6636,9 +6621,6 @@
     <t>(?i).*BERSIHKAN.*</t>
   </si>
   <si>
-    <t>(?i).*PERBAIKI\ REMOTE.*</t>
-  </si>
-  <si>
     <t>REPAIR_REMOTE</t>
   </si>
   <si>
@@ -6648,9 +6630,6 @@
     <t>(?i).*(SUDAH\ OKE|TES\ OK|CEK\-UNIT\-OKE).*</t>
   </si>
   <si>
-    <t>(?i).*DITUKAR.*</t>
-  </si>
-  <si>
     <t>(?i).*ACC\ BIAYA.*</t>
   </si>
   <si>
@@ -6669,18 +6648,12 @@
     <t>(?i).*TEST\ FUNGSI.*</t>
   </si>
   <si>
-    <t>(?i).*CEK\ UNIT.*|REPOSISI ANTENA</t>
-  </si>
-  <si>
     <t>(?i).*SET\ UP\ DATA.*</t>
   </si>
   <si>
     <t>(?i).*CEK\ FUNGSI\ OK.*</t>
   </si>
   <si>
-    <t>(?i).*SETTING.*</t>
-  </si>
-  <si>
     <t>(?i).*RESET\ PABRIK.*</t>
   </si>
   <si>
@@ -6834,9 +6807,6 @@
     <t>EXS|EXTRNAL|EXTERNAL</t>
   </si>
   <si>
-    <t>RESOLDERING|RESOLDRING|RESOLDER</t>
-  </si>
-  <si>
     <t>RESOLDER</t>
   </si>
   <si>
@@ -6852,9 +6822,6 @@
     <t>UNIT</t>
   </si>
   <si>
-    <t>EPAIR</t>
-  </si>
-  <si>
     <t>REPAIR</t>
   </si>
   <si>
@@ -6963,9 +6930,6 @@
     <t>KENCANGKAN</t>
   </si>
   <si>
-    <t>TUNNER</t>
-  </si>
-  <si>
     <t>JLSKAN</t>
   </si>
   <si>
@@ -7089,9 +7053,6 @@
     <t>UPGARDE|UPGRDE</t>
   </si>
   <si>
-    <t>SOFWARE|SOFTWERE|SOFT WERE</t>
-  </si>
-  <si>
     <t>UNIL|UNTIT</t>
   </si>
   <si>
@@ -7159,6 +7120,69 @@
   </si>
   <si>
     <t>SINYAL</t>
+  </si>
+  <si>
+    <t>(?i).*GANTI.*</t>
+  </si>
+  <si>
+    <t>REPLACE SWITCH</t>
+  </si>
+  <si>
+    <t>SOFWARE|SOFTWERE|SOFT WERE|SOFEWERE</t>
+  </si>
+  <si>
+    <t>IC780I</t>
+  </si>
+  <si>
+    <t>IC7801</t>
+  </si>
+  <si>
+    <t>(?i).*(SETTING|DATA ERROR-RESET).*</t>
+  </si>
+  <si>
+    <t>EPAIR|REPAIRE</t>
+  </si>
+  <si>
+    <t>P.W.B</t>
+  </si>
+  <si>
+    <t>(?i).*(CEK\ UNIT|REPOSISI ANTENA|ANTENA).*</t>
+  </si>
+  <si>
+    <t>TUNNER|TONER</t>
+  </si>
+  <si>
+    <t>(?i).*(RESOLDER D7801).*</t>
+  </si>
+  <si>
+    <t>(?i).*(RESOLDER POWER|RESOLDER BLOK POWER|RESOLDER MODUL POWER).*</t>
+  </si>
+  <si>
+    <t>(?i).*(BAWA|ZY|Z1|DITARIK|KIRIM|WS|bawa|CARRY|TO\ WS.|DIANTAR).*</t>
+  </si>
+  <si>
+    <t>ANTHENA</t>
+  </si>
+  <si>
+    <t>ANTENA</t>
+  </si>
+  <si>
+    <t>RESOLDERING|RESOLDRING|RESOLDER|SOLDER|SOLDERING</t>
+  </si>
+  <si>
+    <t>(?i).*(RESOLDER BLOK MAIN|RESOLDER PWB|RESOLDER MAIN).*</t>
+  </si>
+  <si>
+    <t>(?i).*(RESOLDER IC7801|RESOLDER IC MEMORY).*</t>
+  </si>
+  <si>
+    <t>(?i).*(DITUKAR|SUBSTITUSI|PENGECEKAN).*</t>
+  </si>
+  <si>
+    <t>(?i).*(PERBAIKAN REMOTE|RESOLDER ULANG SENSOR).*</t>
+  </si>
+  <si>
+    <t>(?i).*(repair\ modul|GANTI D1012|GANTI DIODA).*|</t>
   </si>
 </sst>
 </file>
@@ -7360,7 +7384,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -7432,6 +7456,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -31700,7 +31725,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" style="25" bestFit="1" customWidth="1"/>
@@ -31743,7 +31768,7 @@
       <c r="D2" t="s">
         <v>2137</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" t="s">
         <v>2138</v>
       </c>
       <c r="F2" t="s">
@@ -32071,14 +32096,15 @@
       <c r="B19">
         <v>1</v>
       </c>
-      <c r="D19" t="s">
-        <v>2137</v>
-      </c>
+      <c r="C19" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D19"/>
       <c r="E19" t="s">
-        <v>2158</v>
+        <v>2363</v>
       </c>
       <c r="F19" t="s">
-        <v>2159</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -32088,14 +32114,15 @@
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="D20" t="s">
-        <v>2137</v>
-      </c>
+      <c r="C20" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="D20"/>
       <c r="E20" t="s">
-        <v>2160</v>
+        <v>2363</v>
       </c>
       <c r="F20" t="s">
-        <v>2161</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -32108,11 +32135,11 @@
       <c r="D21" t="s">
         <v>2137</v>
       </c>
-      <c r="E21" t="s">
-        <v>2162</v>
+      <c r="E21" s="32" t="s">
+        <v>2375</v>
       </c>
       <c r="F21" t="s">
-        <v>2163</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -32126,10 +32153,10 @@
         <v>2137</v>
       </c>
       <c r="E22" t="s">
-        <v>2164</v>
+        <v>2159</v>
       </c>
       <c r="F22" t="s">
-        <v>2165</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -32143,10 +32170,10 @@
         <v>2137</v>
       </c>
       <c r="E23" t="s">
-        <v>2166</v>
+        <v>2161</v>
       </c>
       <c r="F23" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -32160,10 +32187,10 @@
         <v>2137</v>
       </c>
       <c r="E24" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
       <c r="F24" t="s">
-        <v>2139</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -32174,13 +32201,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>2036</v>
+        <v>2137</v>
       </c>
       <c r="E25" t="s">
-        <v>2169</v>
+        <v>2165</v>
       </c>
       <c r="F25" t="s">
-        <v>2149</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -32191,13 +32218,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>2170</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>2171</v>
+        <v>2137</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2167</v>
       </c>
       <c r="F26" t="s">
-        <v>2149</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -32207,11 +32234,14 @@
       <c r="B27">
         <v>1</v>
       </c>
-      <c r="E27" s="25" t="s">
-        <v>2172</v>
+      <c r="D27" t="s">
+        <v>2036</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2168</v>
       </c>
       <c r="F27" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -32222,13 +32252,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>2029</v>
+        <v>2169</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="F28" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -32239,7 +32269,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>2174</v>
+        <v>2171</v>
       </c>
       <c r="F29" t="s">
         <v>2151</v>
@@ -32253,10 +32283,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>2137</v>
-      </c>
-      <c r="E30" t="s">
-        <v>2175</v>
+        <v>2029</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>2172</v>
       </c>
       <c r="F30" t="s">
         <v>2151</v>
@@ -32269,11 +32299,8 @@
       <c r="B31">
         <v>1</v>
       </c>
-      <c r="D31" t="s">
-        <v>2137</v>
-      </c>
-      <c r="E31" t="s">
-        <v>2176</v>
+      <c r="E31" s="25" t="s">
+        <v>2173</v>
       </c>
       <c r="F31" t="s">
         <v>2151</v>
@@ -32290,7 +32317,7 @@
         <v>2137</v>
       </c>
       <c r="E32" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
       <c r="F32" t="s">
         <v>2151</v>
@@ -32307,7 +32334,7 @@
         <v>2137</v>
       </c>
       <c r="E33" t="s">
-        <v>2178</v>
+        <v>2175</v>
       </c>
       <c r="F33" t="s">
         <v>2151</v>
@@ -32324,7 +32351,7 @@
         <v>2137</v>
       </c>
       <c r="E34" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
       <c r="F34" t="s">
         <v>2151</v>
@@ -32341,7 +32368,7 @@
         <v>2137</v>
       </c>
       <c r="E35" t="s">
-        <v>2180</v>
+        <v>2177</v>
       </c>
       <c r="F35" t="s">
         <v>2151</v>
@@ -32358,7 +32385,7 @@
         <v>2137</v>
       </c>
       <c r="E36" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
       <c r="F36" t="s">
         <v>2151</v>
@@ -32374,8 +32401,8 @@
       <c r="D37" t="s">
         <v>2137</v>
       </c>
-      <c r="E37" t="s">
-        <v>2182</v>
+      <c r="E37" s="33" t="s">
+        <v>2380</v>
       </c>
       <c r="F37" t="s">
         <v>2151</v>
@@ -32391,8 +32418,8 @@
       <c r="D38" t="s">
         <v>2137</v>
       </c>
-      <c r="E38" t="s">
-        <v>2183</v>
+      <c r="E38" s="33" t="s">
+        <v>2373</v>
       </c>
       <c r="F38" t="s">
         <v>2151</v>
@@ -32408,8 +32435,8 @@
       <c r="D39" t="s">
         <v>2137</v>
       </c>
-      <c r="E39" t="s">
-        <v>2184</v>
+      <c r="E39" s="33" t="s">
+        <v>2379</v>
       </c>
       <c r="F39" t="s">
         <v>2151</v>
@@ -32426,7 +32453,7 @@
         <v>2137</v>
       </c>
       <c r="E40" t="s">
-        <v>2185</v>
+        <v>2179</v>
       </c>
       <c r="F40" t="s">
         <v>2151</v>
@@ -32443,7 +32470,7 @@
         <v>2137</v>
       </c>
       <c r="E41" t="s">
-        <v>2186</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="s">
         <v>2151</v>
@@ -32460,7 +32487,7 @@
         <v>2137</v>
       </c>
       <c r="E42" t="s">
-        <v>2187</v>
+        <v>2181</v>
       </c>
       <c r="F42" t="s">
         <v>2151</v>
@@ -32477,7 +32504,7 @@
         <v>2137</v>
       </c>
       <c r="E43" t="s">
-        <v>2188</v>
+        <v>2182</v>
       </c>
       <c r="F43" t="s">
         <v>2151</v>
@@ -32494,10 +32521,10 @@
         <v>2137</v>
       </c>
       <c r="E44" t="s">
-        <v>2189</v>
+        <v>2183</v>
       </c>
       <c r="F44" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -32511,10 +32538,10 @@
         <v>2137</v>
       </c>
       <c r="E45" t="s">
-        <v>2190</v>
+        <v>2184</v>
       </c>
       <c r="F45" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -32528,10 +32555,10 @@
         <v>2137</v>
       </c>
       <c r="E46" t="s">
-        <v>2191</v>
+        <v>2185</v>
       </c>
       <c r="F46" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -32544,8 +32571,8 @@
       <c r="D47" t="s">
         <v>2137</v>
       </c>
-      <c r="E47" t="s">
-        <v>2192</v>
+      <c r="E47" s="33" t="s">
+        <v>2374</v>
       </c>
       <c r="F47" t="s">
         <v>2149</v>
@@ -32562,7 +32589,7 @@
         <v>2137</v>
       </c>
       <c r="E48" t="s">
-        <v>2193</v>
+        <v>2187</v>
       </c>
       <c r="F48" t="s">
         <v>2149</v>
@@ -32579,7 +32606,7 @@
         <v>2137</v>
       </c>
       <c r="E49" t="s">
-        <v>2194</v>
+        <v>2188</v>
       </c>
       <c r="F49" t="s">
         <v>2149</v>
@@ -32596,7 +32623,7 @@
         <v>2137</v>
       </c>
       <c r="E50" t="s">
-        <v>2195</v>
+        <v>2189</v>
       </c>
       <c r="F50" t="s">
         <v>2149</v>
@@ -32613,7 +32640,7 @@
         <v>2137</v>
       </c>
       <c r="E51" t="s">
-        <v>2196</v>
+        <v>2190</v>
       </c>
       <c r="F51" t="s">
         <v>2149</v>
@@ -32630,7 +32657,7 @@
         <v>2137</v>
       </c>
       <c r="E52" t="s">
-        <v>2197</v>
+        <v>2191</v>
       </c>
       <c r="F52" t="s">
         <v>2149</v>
@@ -32647,7 +32674,7 @@
         <v>2137</v>
       </c>
       <c r="E53" t="s">
-        <v>2198</v>
+        <v>2192</v>
       </c>
       <c r="F53" t="s">
         <v>2149</v>
@@ -32663,8 +32690,8 @@
       <c r="D54" t="s">
         <v>2137</v>
       </c>
-      <c r="E54" t="s">
-        <v>2190</v>
+      <c r="E54" s="32" t="s">
+        <v>2383</v>
       </c>
       <c r="F54" t="s">
         <v>2149</v>
@@ -32681,10 +32708,10 @@
         <v>2137</v>
       </c>
       <c r="E55" t="s">
-        <v>2199</v>
+        <v>2193</v>
       </c>
       <c r="F55" t="s">
-        <v>2139</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -32698,10 +32725,10 @@
         <v>2137</v>
       </c>
       <c r="E56" t="s">
-        <v>2200</v>
+        <v>2186</v>
       </c>
       <c r="F56" t="s">
-        <v>2139</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -32715,7 +32742,7 @@
         <v>2137</v>
       </c>
       <c r="E57" t="s">
-        <v>2199</v>
+        <v>2194</v>
       </c>
       <c r="F57" t="s">
         <v>2139</v>
@@ -32732,10 +32759,10 @@
         <v>2137</v>
       </c>
       <c r="E58" t="s">
-        <v>2201</v>
+        <v>2195</v>
       </c>
       <c r="F58" t="s">
-        <v>2202</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -32749,10 +32776,10 @@
         <v>2137</v>
       </c>
       <c r="E59" t="s">
-        <v>2203</v>
+        <v>2194</v>
       </c>
       <c r="F59" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -32766,10 +32793,10 @@
         <v>2137</v>
       </c>
       <c r="E60" t="s">
-        <v>2204</v>
+        <v>2382</v>
       </c>
       <c r="F60" t="s">
-        <v>2142</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -32783,7 +32810,7 @@
         <v>2137</v>
       </c>
       <c r="E61" t="s">
-        <v>2205</v>
+        <v>2197</v>
       </c>
       <c r="F61" t="s">
         <v>2142</v>
@@ -32800,7 +32827,7 @@
         <v>2137</v>
       </c>
       <c r="E62" t="s">
-        <v>2206</v>
+        <v>2198</v>
       </c>
       <c r="F62" t="s">
         <v>2142</v>
@@ -32816,11 +32843,11 @@
       <c r="D63" t="s">
         <v>2137</v>
       </c>
-      <c r="E63" t="s">
-        <v>2207</v>
+      <c r="E63" s="33" t="s">
+        <v>2381</v>
       </c>
       <c r="F63" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -32834,10 +32861,10 @@
         <v>2137</v>
       </c>
       <c r="E64" t="s">
-        <v>2208</v>
+        <v>2199</v>
       </c>
       <c r="F64" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -32851,7 +32878,7 @@
         <v>2137</v>
       </c>
       <c r="E65" t="s">
-        <v>2209</v>
+        <v>2200</v>
       </c>
       <c r="F65" t="s">
         <v>2144</v>
@@ -32868,7 +32895,7 @@
         <v>2137</v>
       </c>
       <c r="E66" t="s">
-        <v>2210</v>
+        <v>2201</v>
       </c>
       <c r="F66" t="s">
         <v>2144</v>
@@ -32885,7 +32912,7 @@
         <v>2137</v>
       </c>
       <c r="E67" t="s">
-        <v>2211</v>
+        <v>2202</v>
       </c>
       <c r="F67" t="s">
         <v>2144</v>
@@ -32902,7 +32929,7 @@
         <v>2137</v>
       </c>
       <c r="E68" t="s">
-        <v>2143</v>
+        <v>2203</v>
       </c>
       <c r="F68" t="s">
         <v>2144</v>
@@ -32919,7 +32946,7 @@
         <v>2137</v>
       </c>
       <c r="E69" t="s">
-        <v>2212</v>
+        <v>2204</v>
       </c>
       <c r="F69" t="s">
         <v>2144</v>
@@ -32936,7 +32963,7 @@
         <v>2137</v>
       </c>
       <c r="E70" t="s">
-        <v>2213</v>
+        <v>2143</v>
       </c>
       <c r="F70" t="s">
         <v>2144</v>
@@ -32952,8 +32979,8 @@
       <c r="D71" t="s">
         <v>2137</v>
       </c>
-      <c r="E71" t="s">
-        <v>2214</v>
+      <c r="E71" s="32" t="s">
+        <v>2371</v>
       </c>
       <c r="F71" t="s">
         <v>2144</v>
@@ -32970,10 +32997,10 @@
         <v>2137</v>
       </c>
       <c r="E72" t="s">
-        <v>2215</v>
+        <v>2205</v>
       </c>
       <c r="F72" t="s">
-        <v>2167</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -32987,10 +33014,10 @@
         <v>2137</v>
       </c>
       <c r="E73" t="s">
-        <v>2166</v>
+        <v>2206</v>
       </c>
       <c r="F73" t="s">
-        <v>2167</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -33004,10 +33031,10 @@
         <v>2137</v>
       </c>
       <c r="E74" t="s">
-        <v>2216</v>
+        <v>2368</v>
       </c>
       <c r="F74" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -33021,10 +33048,10 @@
         <v>2137</v>
       </c>
       <c r="E75" t="s">
-        <v>2217</v>
+        <v>2165</v>
       </c>
       <c r="F75" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -33038,10 +33065,10 @@
         <v>2137</v>
       </c>
       <c r="E76" t="s">
-        <v>2218</v>
+        <v>2207</v>
       </c>
       <c r="F76" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -33055,10 +33082,10 @@
         <v>2137</v>
       </c>
       <c r="E77" t="s">
-        <v>2219</v>
+        <v>2208</v>
       </c>
       <c r="F77" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -33072,10 +33099,10 @@
         <v>2137</v>
       </c>
       <c r="E78" t="s">
-        <v>2220</v>
+        <v>2209</v>
       </c>
       <c r="F78" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -33089,10 +33116,10 @@
         <v>2137</v>
       </c>
       <c r="E79" t="s">
-        <v>2221</v>
+        <v>2210</v>
       </c>
       <c r="F79" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -33106,10 +33133,10 @@
         <v>2137</v>
       </c>
       <c r="E80" t="s">
-        <v>2222</v>
+        <v>2211</v>
       </c>
       <c r="F80" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -33123,10 +33150,10 @@
         <v>2137</v>
       </c>
       <c r="E81" t="s">
-        <v>2160</v>
+        <v>2212</v>
       </c>
       <c r="F81" t="s">
-        <v>2161</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -33140,10 +33167,10 @@
         <v>2137</v>
       </c>
       <c r="E82" t="s">
-        <v>2223</v>
+        <v>2213</v>
       </c>
       <c r="F82" t="s">
-        <v>2161</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -33157,10 +33184,10 @@
         <v>2137</v>
       </c>
       <c r="E83" t="s">
-        <v>2224</v>
+        <v>2159</v>
       </c>
       <c r="F83" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -33174,10 +33201,10 @@
         <v>2137</v>
       </c>
       <c r="E84" t="s">
-        <v>2225</v>
+        <v>2214</v>
       </c>
       <c r="F84" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -33191,10 +33218,10 @@
         <v>2137</v>
       </c>
       <c r="E85" t="s">
-        <v>2223</v>
+        <v>2215</v>
       </c>
       <c r="F85" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -33208,10 +33235,10 @@
         <v>2137</v>
       </c>
       <c r="E86" t="s">
-        <v>2164</v>
+        <v>2216</v>
       </c>
       <c r="F86" t="s">
-        <v>2165</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -33225,10 +33252,10 @@
         <v>2137</v>
       </c>
       <c r="E87" t="s">
-        <v>2226</v>
+        <v>2214</v>
       </c>
       <c r="F87" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -33242,10 +33269,10 @@
         <v>2137</v>
       </c>
       <c r="E88" t="s">
-        <v>2227</v>
+        <v>2163</v>
       </c>
       <c r="F88" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -33259,10 +33286,10 @@
         <v>2137</v>
       </c>
       <c r="E89" t="s">
-        <v>2228</v>
+        <v>2217</v>
       </c>
       <c r="F89" t="s">
-        <v>2202</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -33276,10 +33303,10 @@
         <v>2137</v>
       </c>
       <c r="E90" t="s">
-        <v>2229</v>
+        <v>2218</v>
       </c>
       <c r="F90" t="s">
-        <v>2146</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -33293,10 +33320,10 @@
         <v>2137</v>
       </c>
       <c r="E91" t="s">
-        <v>2230</v>
+        <v>2219</v>
       </c>
       <c r="F91" t="s">
-        <v>2146</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -33310,10 +33337,10 @@
         <v>2137</v>
       </c>
       <c r="E92" t="s">
-        <v>2231</v>
+        <v>2220</v>
       </c>
       <c r="F92" t="s">
-        <v>2232</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -33327,10 +33354,10 @@
         <v>2137</v>
       </c>
       <c r="E93" t="s">
-        <v>2233</v>
+        <v>2221</v>
       </c>
       <c r="F93" t="s">
-        <v>2234</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -33344,10 +33371,44 @@
         <v>2137</v>
       </c>
       <c r="E94" t="s">
-        <v>2235</v>
+        <v>2222</v>
       </c>
       <c r="F94" t="s">
-        <v>2234</v>
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="D95" t="s">
+        <v>2137</v>
+      </c>
+      <c r="E95" t="s">
+        <v>2224</v>
+      </c>
+      <c r="F95" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="D96" t="s">
+        <v>2137</v>
+      </c>
+      <c r="E96" t="s">
+        <v>2226</v>
+      </c>
+      <c r="F96" t="s">
+        <v>2225</v>
       </c>
     </row>
   </sheetData>
@@ -33370,44 +33431,44 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="26" t="s">
-        <v>2236</v>
+        <v>2227</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>2237</v>
+        <v>2228</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>2238</v>
+        <v>2229</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>2239</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="29" t="s">
-        <v>2240</v>
+        <v>2231</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="29" t="s">
-        <v>2242</v>
+        <v>2233</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -33415,24 +33476,24 @@
         <v>2142</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="29" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>2243</v>
+        <v>2234</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="D5" s="29">
         <v>13</v>
@@ -33443,24 +33504,24 @@
         <v>2139</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="28" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>2245</v>
+        <v>2236</v>
       </c>
       <c r="D7" s="29">
         <v>50</v>
@@ -33468,10 +33529,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="28" t="s">
-        <v>2232</v>
+        <v>2223</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>964</v>
@@ -33482,10 +33543,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="30" t="s">
-        <v>2234</v>
+        <v>2225</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>964</v>
@@ -33496,10 +33557,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="28" t="s">
-        <v>2246</v>
+        <v>2237</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>964</v>
@@ -33510,10 +33571,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="28" t="s">
-        <v>2247</v>
+        <v>2238</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C11" s="29" t="s">
         <v>964</v>
@@ -33524,10 +33585,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="29" t="s">
-        <v>2248</v>
+        <v>2239</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C12" s="29" t="s">
         <v>964</v>
@@ -33538,10 +33599,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="29" t="s">
-        <v>2249</v>
+        <v>2240</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C13" s="29" t="s">
         <v>964</v>
@@ -33552,10 +33613,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="28" t="s">
-        <v>2250</v>
+        <v>2241</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C14" s="29" t="s">
         <v>964</v>
@@ -33566,10 +33627,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="28" t="s">
-        <v>2251</v>
+        <v>2242</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C15" s="29" t="s">
         <v>964</v>
@@ -33583,7 +33644,7 @@
         <v>2151</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C16" s="29" t="s">
         <v>459</v>
@@ -33594,10 +33655,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="28" t="s">
-        <v>2252</v>
+        <v>2243</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C17" s="29" t="s">
         <v>989</v>
@@ -33611,7 +33672,7 @@
         <v>2149</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C18" s="29" t="s">
         <v>1428</v>
@@ -33622,10 +33683,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="28" t="s">
-        <v>2202</v>
+        <v>2196</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C19" s="28" t="s">
         <v>964</v>
@@ -33636,10 +33697,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="30" t="s">
-        <v>2253</v>
+        <v>2244</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C20" s="29" t="s">
         <v>964</v>
@@ -33650,10 +33711,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="29" t="s">
-        <v>2254</v>
+        <v>2245</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C21" s="29" t="s">
         <v>964</v>
@@ -33664,10 +33725,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="29" t="s">
-        <v>2255</v>
+        <v>2246</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C22" s="29" t="s">
         <v>964</v>
@@ -33681,7 +33742,7 @@
         <v>2155</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C23" s="29" t="s">
         <v>964</v>
@@ -33695,7 +33756,7 @@
         <v>2150</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C24" s="29" t="s">
         <v>964</v>
@@ -33709,7 +33770,7 @@
         <v>2152</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C25" s="29" t="s">
         <v>964</v>
@@ -33723,7 +33784,7 @@
         <v>2147</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C26" s="29" t="s">
         <v>459</v>
@@ -33737,7 +33798,7 @@
         <v>2146</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C27" s="29" t="s">
         <v>989</v>
@@ -33748,13 +33809,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="30" t="s">
-        <v>2256</v>
+        <v>2247</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="D28" s="29">
         <v>0</v>
@@ -33765,7 +33826,7 @@
         <v>2145</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C29" s="29" t="s">
         <v>1428</v>
@@ -33779,7 +33840,7 @@
         <v>2148</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C30" s="28" t="s">
         <v>964</v>
@@ -33793,7 +33854,7 @@
         <v>2156</v>
       </c>
       <c r="B31" s="29" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C31" s="29" t="s">
         <v>964</v>
@@ -33804,10 +33865,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="28" t="s">
-        <v>2257</v>
+        <v>2248</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C32" s="28" t="s">
         <v>964</v>
@@ -33821,7 +33882,7 @@
         <v>2157</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>964</v>
@@ -33832,10 +33893,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="29" t="s">
-        <v>2258</v>
+        <v>2249</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C34" s="29" t="s">
         <v>964</v>
@@ -33846,13 +33907,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="29" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>2243</v>
+        <v>2234</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="D35" s="29">
         <v>12</v>
@@ -33860,13 +33921,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="29" t="s">
-        <v>2259</v>
+        <v>2250</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>2243</v>
+        <v>2234</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>2259</v>
+        <v>2250</v>
       </c>
       <c r="D36" s="29">
         <v>14</v>
@@ -33874,13 +33935,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="30" t="s">
-        <v>2260</v>
+        <v>2251</v>
       </c>
       <c r="B37" s="29" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="D37" s="29">
         <v>0</v>
@@ -33888,13 +33949,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="28" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>2245</v>
+        <v>2236</v>
       </c>
       <c r="D38" s="29">
         <v>51</v>
@@ -33905,7 +33966,7 @@
         <v>2144</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>2243</v>
+        <v>2234</v>
       </c>
       <c r="C39" s="29" t="s">
         <v>2144</v>
@@ -33916,27 +33977,27 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="28" t="s">
-        <v>2261</v>
+        <v>2252</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="28" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="D41" s="29">
         <v>0</v>
@@ -33947,7 +34008,7 @@
         <v>2153</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C42" s="29" t="s">
         <v>964</v>
@@ -33959,7 +34020,7 @@
         <v>2154</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="C43" s="29" t="s">
         <v>964</v>
@@ -33978,164 +34039,164 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="89.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="104.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>2262</v>
+        <v>2253</v>
       </c>
       <c r="B1" t="s">
-        <v>2263</v>
+        <v>2254</v>
       </c>
       <c r="C1" t="s">
-        <v>2264</v>
+        <v>2255</v>
       </c>
       <c r="D1" t="s">
-        <v>2265</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2271</v>
+        <v>2261</v>
       </c>
       <c r="B2" t="s">
         <v>2067</v>
       </c>
       <c r="C2" t="s">
-        <v>2267</v>
+        <v>2378</v>
       </c>
       <c r="D2" t="s">
-        <v>2268</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2349</v>
+        <v>2337</v>
       </c>
       <c r="B3" t="s">
-        <v>2270</v>
+        <v>2260</v>
       </c>
       <c r="C3" t="s">
-        <v>2336</v>
+        <v>2324</v>
       </c>
       <c r="D3" t="s">
-        <v>2269</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2372</v>
+        <v>2359</v>
       </c>
       <c r="B4" t="s">
-        <v>2342</v>
+        <v>2330</v>
       </c>
       <c r="C4" t="s">
-        <v>2349</v>
+        <v>2337</v>
       </c>
       <c r="D4" t="s">
-        <v>2270</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2280</v>
+        <v>2269</v>
       </c>
       <c r="B5" t="s">
         <v>2028</v>
       </c>
       <c r="C5" t="s">
-        <v>2266</v>
+        <v>2257</v>
       </c>
       <c r="D5" t="s">
-        <v>2374</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2281</v>
+        <v>2270</v>
       </c>
       <c r="B6" t="s">
-        <v>2282</v>
+        <v>2271</v>
       </c>
       <c r="C6" t="s">
-        <v>2353</v>
+        <v>2340</v>
       </c>
       <c r="D6" t="s">
-        <v>2272</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2287</v>
+        <v>2276</v>
       </c>
       <c r="B7" t="s">
-        <v>2288</v>
+        <v>2277</v>
       </c>
       <c r="C7" t="s">
-        <v>2273</v>
+        <v>2369</v>
       </c>
       <c r="D7" t="s">
-        <v>2274</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2354</v>
+        <v>2341</v>
       </c>
       <c r="B8" t="s">
-        <v>2355</v>
+        <v>2342</v>
       </c>
       <c r="C8" t="s">
-        <v>2275</v>
+        <v>2264</v>
       </c>
       <c r="D8" t="s">
-        <v>2276</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2356</v>
+        <v>2343</v>
       </c>
       <c r="B9" t="s">
-        <v>2288</v>
+        <v>2277</v>
       </c>
       <c r="C9" t="s">
-        <v>2277</v>
+        <v>2266</v>
       </c>
       <c r="D9" t="s">
-        <v>2284</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2281</v>
+        <v>2270</v>
       </c>
       <c r="B10" t="s">
-        <v>2282</v>
+        <v>2271</v>
       </c>
       <c r="C10" t="s">
-        <v>2319</v>
+        <v>2307</v>
       </c>
       <c r="D10" t="s">
-        <v>2278</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2348</v>
+        <v>2336</v>
       </c>
       <c r="B11" t="s">
-        <v>2347</v>
+        <v>2335</v>
       </c>
       <c r="C11" t="s">
-        <v>2279</v>
+        <v>2268</v>
       </c>
       <c r="D11" t="s">
         <v>2028</v>
@@ -34143,41 +34204,41 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2357</v>
+        <v>2344</v>
       </c>
       <c r="B12" t="s">
-        <v>2358</v>
+        <v>2345</v>
       </c>
       <c r="C12" t="s">
-        <v>2281</v>
+        <v>2270</v>
       </c>
       <c r="D12" t="s">
-        <v>2282</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="31" t="s">
-        <v>2359</v>
+        <v>2346</v>
       </c>
       <c r="B13" t="s">
         <v>2089</v>
       </c>
       <c r="C13" t="s">
-        <v>2352</v>
+        <v>2365</v>
       </c>
       <c r="D13" t="s">
-        <v>2245</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2360</v>
+        <v>2347</v>
       </c>
       <c r="B14" t="s">
-        <v>2361</v>
+        <v>2348</v>
       </c>
       <c r="C14" t="s">
-        <v>2283</v>
+        <v>2272</v>
       </c>
       <c r="D14" t="s">
         <v>989</v>
@@ -34185,171 +34246,171 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2362</v>
+        <v>2349</v>
       </c>
       <c r="B15" t="s">
-        <v>2363</v>
+        <v>2350</v>
       </c>
       <c r="C15" t="s">
-        <v>2285</v>
+        <v>2274</v>
       </c>
       <c r="D15" t="s">
-        <v>2274</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="31" t="s">
-        <v>2364</v>
+        <v>2351</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>2365</v>
+        <v>2352</v>
       </c>
       <c r="C16" t="s">
-        <v>2286</v>
+        <v>2275</v>
       </c>
       <c r="D16" t="s">
-        <v>2272</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2366</v>
+        <v>2353</v>
       </c>
       <c r="B17" t="s">
-        <v>2367</v>
+        <v>2354</v>
       </c>
       <c r="C17" t="s">
-        <v>2287</v>
+        <v>2276</v>
       </c>
       <c r="D17" t="s">
-        <v>2288</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2368</v>
+        <v>2355</v>
       </c>
       <c r="B18" t="s">
-        <v>2369</v>
+        <v>2356</v>
       </c>
       <c r="C18" t="s">
-        <v>2289</v>
+        <v>2278</v>
       </c>
       <c r="D18" t="s">
-        <v>2290</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2371</v>
+        <v>2358</v>
       </c>
       <c r="B19" t="s">
-        <v>2370</v>
+        <v>2357</v>
       </c>
       <c r="C19" t="s">
-        <v>2291</v>
+        <v>2280</v>
       </c>
       <c r="D19" t="s">
-        <v>2292</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2259</v>
+        <v>2250</v>
       </c>
       <c r="B20" t="s">
-        <v>2375</v>
+        <v>2362</v>
       </c>
       <c r="C20" t="s">
-        <v>2293</v>
+        <v>2282</v>
       </c>
       <c r="D20" t="s">
-        <v>2294</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="C21" t="s">
-        <v>2295</v>
+        <v>2284</v>
       </c>
       <c r="D21" t="s">
-        <v>2294</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="C22" t="s">
-        <v>2296</v>
+        <v>2285</v>
       </c>
       <c r="D22" t="s">
-        <v>2297</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="C23" t="s">
-        <v>2298</v>
+        <v>2287</v>
       </c>
       <c r="D23" t="s">
-        <v>2294</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="C24" t="s">
-        <v>2318</v>
+        <v>2306</v>
       </c>
       <c r="D24" t="s">
-        <v>2299</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="C25" t="s">
-        <v>2300</v>
+        <v>2289</v>
       </c>
       <c r="D25" t="s">
-        <v>2301</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="C26" t="s">
-        <v>2302</v>
+        <v>2291</v>
       </c>
       <c r="D26" t="s">
-        <v>2274</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="C27" t="s">
-        <v>2303</v>
+        <v>2292</v>
       </c>
       <c r="D27" t="s">
-        <v>2304</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="C28" t="s">
-        <v>2305</v>
+        <v>2294</v>
       </c>
       <c r="D28" t="s">
-        <v>2306</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="C29" t="s">
-        <v>2307</v>
+        <v>2296</v>
       </c>
       <c r="D29" t="s">
-        <v>2294</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="C30" t="s">
-        <v>2308</v>
+        <v>2297</v>
       </c>
       <c r="D30" t="s">
-        <v>2309</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="C31" t="s">
-        <v>2310</v>
+        <v>2372</v>
       </c>
       <c r="D31" t="s">
         <v>1888</v>
@@ -34357,119 +34418,119 @@
     </row>
     <row r="32" spans="1:4">
       <c r="C32" t="s">
-        <v>2311</v>
+        <v>2299</v>
       </c>
       <c r="D32" t="s">
-        <v>2312</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="33" spans="3:4">
       <c r="C33" t="s">
-        <v>2317</v>
+        <v>2305</v>
       </c>
       <c r="D33" t="s">
-        <v>2313</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="34" spans="3:4">
       <c r="C34" t="s">
-        <v>2314</v>
+        <v>2302</v>
       </c>
       <c r="D34" t="s">
-        <v>2297</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="35" spans="3:4">
       <c r="C35" t="s">
-        <v>2315</v>
+        <v>2303</v>
       </c>
       <c r="D35" t="s">
-        <v>2316</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="36" spans="3:4">
       <c r="C36" t="s">
-        <v>2321</v>
+        <v>2309</v>
       </c>
       <c r="D36" t="s">
-        <v>2320</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="37" spans="3:4">
       <c r="C37" t="s">
-        <v>2350</v>
+        <v>2338</v>
       </c>
       <c r="D37" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="38" spans="3:4">
       <c r="C38" t="s">
-        <v>2322</v>
+        <v>2310</v>
       </c>
       <c r="D38" t="s">
-        <v>2323</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="39" spans="3:4">
       <c r="C39" t="s">
-        <v>2324</v>
+        <v>2312</v>
       </c>
       <c r="D39" t="s">
-        <v>2325</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="40" spans="3:4">
       <c r="C40" t="s">
-        <v>2326</v>
+        <v>2314</v>
       </c>
       <c r="D40" t="s">
-        <v>2327</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="41" spans="3:4">
       <c r="C41" t="s">
-        <v>2328</v>
+        <v>2316</v>
       </c>
       <c r="D41" t="s">
-        <v>2329</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="42" spans="3:4">
       <c r="C42" t="s">
-        <v>2373</v>
+        <v>2360</v>
       </c>
       <c r="D42" t="s">
-        <v>2330</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="43" spans="3:4">
       <c r="C43" t="s">
-        <v>2331</v>
+        <v>2319</v>
       </c>
       <c r="D43" t="s">
-        <v>2332</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="44" spans="3:4">
       <c r="C44" t="s">
-        <v>2333</v>
+        <v>2321</v>
       </c>
       <c r="D44" t="s">
-        <v>2334</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="45" spans="3:4">
       <c r="C45" t="s">
-        <v>2344</v>
+        <v>2332</v>
       </c>
       <c r="D45" t="s">
-        <v>2335</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="46" spans="3:4">
       <c r="C46" t="s">
-        <v>2337</v>
+        <v>2325</v>
       </c>
       <c r="D46" t="s">
         <v>2029</v>
@@ -34477,15 +34538,15 @@
     </row>
     <row r="47" spans="3:4">
       <c r="C47" t="s">
-        <v>2338</v>
+        <v>2326</v>
       </c>
       <c r="D47" t="s">
-        <v>2339</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="48" spans="3:4">
       <c r="C48" t="s">
-        <v>2340</v>
+        <v>2328</v>
       </c>
       <c r="D48" t="s">
         <v>2067</v>
@@ -34493,42 +34554,66 @@
     </row>
     <row r="49" spans="3:4">
       <c r="C49" t="s">
-        <v>2341</v>
+        <v>2329</v>
       </c>
       <c r="D49" t="s">
-        <v>2342</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="50" spans="3:4">
       <c r="C50" t="s">
-        <v>2343</v>
+        <v>2331</v>
       </c>
       <c r="D50" t="s">
-        <v>2294</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="51" spans="3:4">
       <c r="C51" t="s">
-        <v>2345</v>
+        <v>2333</v>
       </c>
       <c r="D51" t="s">
-        <v>2346</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="52" spans="3:4">
       <c r="C52" t="s">
-        <v>2348</v>
+        <v>2336</v>
       </c>
       <c r="D52" t="s">
-        <v>2347</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="53" spans="3:4">
       <c r="C53" t="s">
-        <v>2351</v>
+        <v>2339</v>
       </c>
       <c r="D53" t="s">
-        <v>2161</v>
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4">
+      <c r="C54" t="s">
+        <v>2366</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4">
+      <c r="C55" t="s">
+        <v>2370</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4">
+      <c r="C56" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2377</v>
       </c>
     </row>
   </sheetData>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Koding\tool-fcost\masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB07C0C-E8EC-40D7-9A64-8B46618CB569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD67A39-8DAE-4496-B444-D5DAA856388E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4651" uniqueCount="2384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4653" uniqueCount="2385">
   <si>
     <t>part_used</t>
   </si>
@@ -7183,6 +7183,9 @@
   </si>
   <si>
     <t>(?i).*(repair\ modul|GANTI D1012|GANTI DIODA).*|</t>
+  </si>
+  <si>
+    <t>9TAHN7000CE002</t>
   </si>
 </sst>
 </file>
@@ -7758,7 +7761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T1833"/>
+  <dimension ref="A1:T1834"/>
   <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="21.7109375" style="4" customWidth="1"/>
@@ -16300,8 +16303,8 @@
       </c>
     </row>
     <row r="1066" spans="1:2">
-      <c r="A1066" s="7" t="s">
-        <v>1131</v>
+      <c r="A1066" s="4" t="s">
+        <v>2384</v>
       </c>
       <c r="B1066" s="3" t="s">
         <v>989</v>
@@ -16309,7 +16312,7 @@
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" s="7" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1067" s="3" t="s">
         <v>989</v>
@@ -16317,7 +16320,7 @@
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" s="7" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1068" s="3" t="s">
         <v>989</v>
@@ -16325,7 +16328,7 @@
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" s="7" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1069" s="3" t="s">
         <v>989</v>
@@ -16333,7 +16336,7 @@
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" s="7" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1070" s="3" t="s">
         <v>989</v>
@@ -16341,7 +16344,7 @@
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" s="7" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1071" s="3" t="s">
         <v>989</v>
@@ -16349,7 +16352,7 @@
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" s="7" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B1072" s="3" t="s">
         <v>989</v>
@@ -16357,7 +16360,7 @@
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" s="7" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B1073" s="3" t="s">
         <v>989</v>
@@ -16365,39 +16368,39 @@
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B1074" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:2">
+      <c r="A1075" s="7" t="s">
         <v>1139</v>
       </c>
-      <c r="B1074" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1075" spans="1:2">
-      <c r="A1075" s="10" t="s">
+      <c r="B1075" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:2">
+      <c r="A1076" s="10" t="s">
         <v>1140</v>
       </c>
-      <c r="B1075" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1076" spans="1:2">
-      <c r="A1076" s="7" t="s">
+      <c r="B1076" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:2">
+      <c r="A1077" s="7" t="s">
         <v>1141</v>
       </c>
-      <c r="B1076" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1077" spans="1:2">
-      <c r="A1077" s="10" t="s">
+      <c r="B1077" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:2">
+      <c r="A1078" s="10" t="s">
         <v>1142</v>
-      </c>
-      <c r="B1077" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1078" spans="1:2">
-      <c r="A1078" s="7" t="s">
-        <v>1143</v>
       </c>
       <c r="B1078" s="3" t="s">
         <v>989</v>
@@ -16405,7 +16408,7 @@
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" s="7" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B1079" s="3" t="s">
         <v>989</v>
@@ -16413,7 +16416,7 @@
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" s="7" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B1080" s="3" t="s">
         <v>989</v>
@@ -16421,7 +16424,7 @@
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" s="7" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B1081" s="3" t="s">
         <v>989</v>
@@ -16429,7 +16432,7 @@
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" s="7" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B1082" s="3" t="s">
         <v>989</v>
@@ -16437,23 +16440,23 @@
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" s="7" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B1083" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:2">
+      <c r="A1084" s="7" t="s">
         <v>1148</v>
       </c>
-      <c r="B1083" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1084" spans="1:2">
-      <c r="A1084" s="10" t="s">
+      <c r="B1084" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:2">
+      <c r="A1085" s="10" t="s">
         <v>1149</v>
-      </c>
-      <c r="B1084" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1085" spans="1:2">
-      <c r="A1085" s="7" t="s">
-        <v>1150</v>
       </c>
       <c r="B1085" s="3" t="s">
         <v>989</v>
@@ -16461,7 +16464,7 @@
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" s="7" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B1086" s="3" t="s">
         <v>989</v>
@@ -16469,7 +16472,7 @@
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B1087" s="3" t="s">
         <v>989</v>
@@ -16477,7 +16480,7 @@
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" s="7" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B1088" s="3" t="s">
         <v>989</v>
@@ -16485,7 +16488,7 @@
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" s="7" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B1089" s="3" t="s">
         <v>989</v>
@@ -16493,23 +16496,23 @@
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B1090" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:2">
+      <c r="A1091" s="7" t="s">
         <v>1155</v>
       </c>
-      <c r="B1090" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1091" spans="1:2">
-      <c r="A1091" s="13" t="s">
+      <c r="B1091" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:2">
+      <c r="A1092" s="13" t="s">
         <v>1156</v>
-      </c>
-      <c r="B1091" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1092" spans="1:2">
-      <c r="A1092" s="7" t="s">
-        <v>1157</v>
       </c>
       <c r="B1092" s="3" t="s">
         <v>989</v>
@@ -16517,7 +16520,7 @@
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" s="7" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B1093" s="3" t="s">
         <v>989</v>
@@ -16525,7 +16528,7 @@
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B1094" s="3" t="s">
         <v>989</v>
@@ -16533,7 +16536,7 @@
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" s="7" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B1095" s="3" t="s">
         <v>989</v>
@@ -16541,7 +16544,7 @@
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" s="7" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B1096" s="3" t="s">
         <v>989</v>
@@ -16549,7 +16552,7 @@
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" s="7" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B1097" s="3" t="s">
         <v>989</v>
@@ -16557,7 +16560,7 @@
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" s="7" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B1098" s="3" t="s">
         <v>989</v>
@@ -16565,7 +16568,7 @@
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" s="7" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B1099" s="3" t="s">
         <v>989</v>
@@ -16573,7 +16576,7 @@
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" s="7" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B1100" s="3" t="s">
         <v>989</v>
@@ -16581,7 +16584,7 @@
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" s="7" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B1101" s="3" t="s">
         <v>989</v>
@@ -16589,7 +16592,7 @@
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" s="7" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B1102" s="3" t="s">
         <v>989</v>
@@ -16597,7 +16600,7 @@
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" s="7" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B1103" s="3" t="s">
         <v>989</v>
@@ -16605,7 +16608,7 @@
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" s="7" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B1104" s="3" t="s">
         <v>989</v>
@@ -16613,7 +16616,7 @@
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" s="7" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B1105" s="3" t="s">
         <v>989</v>
@@ -16621,7 +16624,7 @@
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" s="7" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B1106" s="3" t="s">
         <v>989</v>
@@ -16629,7 +16632,7 @@
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" s="7" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B1107" s="3" t="s">
         <v>989</v>
@@ -16637,7 +16640,7 @@
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" s="7" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B1108" s="3" t="s">
         <v>989</v>
@@ -16645,15 +16648,15 @@
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B1109" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:2">
+      <c r="A1110" s="7" t="s">
         <v>1174</v>
-      </c>
-      <c r="B1109" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1110" spans="1:2">
-      <c r="A1110" s="10" t="s">
-        <v>1175</v>
       </c>
       <c r="B1110" s="3" t="s">
         <v>989</v>
@@ -16661,15 +16664,15 @@
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" s="10" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B1111" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:2">
+      <c r="A1112" s="10" t="s">
         <v>1176</v>
-      </c>
-      <c r="B1111" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1112" spans="1:2">
-      <c r="A1112" s="7" t="s">
-        <v>1177</v>
       </c>
       <c r="B1112" s="3" t="s">
         <v>989</v>
@@ -16677,7 +16680,7 @@
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" s="7" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1113" s="3" t="s">
         <v>989</v>
@@ -16685,7 +16688,7 @@
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" s="7" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B1114" s="3" t="s">
         <v>989</v>
@@ -16693,7 +16696,7 @@
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" s="7" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B1115" s="3" t="s">
         <v>989</v>
@@ -16701,23 +16704,23 @@
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" s="7" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B1116" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:2">
+      <c r="A1117" s="7" t="s">
         <v>1181</v>
       </c>
-      <c r="B1116" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1117" spans="1:2">
-      <c r="A1117" s="10" t="s">
+      <c r="B1117" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:2">
+      <c r="A1118" s="10" t="s">
         <v>1182</v>
-      </c>
-      <c r="B1117" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1118" spans="1:2">
-      <c r="A1118" s="7" t="s">
-        <v>1183</v>
       </c>
       <c r="B1118" s="3" t="s">
         <v>989</v>
@@ -16725,7 +16728,7 @@
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" s="7" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B1119" s="3" t="s">
         <v>989</v>
@@ -16733,7 +16736,7 @@
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" s="7" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B1120" s="3" t="s">
         <v>989</v>
@@ -16741,23 +16744,23 @@
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B1121" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:2">
+      <c r="A1122" s="7" t="s">
         <v>1186</v>
       </c>
-      <c r="B1121" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1122" spans="1:2">
-      <c r="A1122" s="10" t="s">
+      <c r="B1122" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:2">
+      <c r="A1123" s="10" t="s">
         <v>1187</v>
-      </c>
-      <c r="B1122" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1123" spans="1:2">
-      <c r="A1123" s="7" t="s">
-        <v>1188</v>
       </c>
       <c r="B1123" s="3" t="s">
         <v>989</v>
@@ -16765,23 +16768,23 @@
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" s="7" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B1124" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:2">
+      <c r="A1125" s="7" t="s">
         <v>1189</v>
       </c>
-      <c r="B1124" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1125" spans="1:2">
-      <c r="A1125" s="10" t="s">
+      <c r="B1125" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:2">
+      <c r="A1126" s="10" t="s">
         <v>1190</v>
-      </c>
-      <c r="B1125" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1126" spans="1:2">
-      <c r="A1126" s="7" t="s">
-        <v>1191</v>
       </c>
       <c r="B1126" s="3" t="s">
         <v>989</v>
@@ -16789,7 +16792,7 @@
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" s="7" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B1127" s="3" t="s">
         <v>989</v>
@@ -16797,7 +16800,7 @@
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" s="7" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B1128" s="3" t="s">
         <v>989</v>
@@ -16805,7 +16808,7 @@
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" s="7" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B1129" s="3" t="s">
         <v>989</v>
@@ -16813,7 +16816,7 @@
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" s="7" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B1130" s="3" t="s">
         <v>989</v>
@@ -16821,7 +16824,7 @@
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" s="7" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B1131" s="3" t="s">
         <v>989</v>
@@ -16829,23 +16832,23 @@
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" s="7" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B1132" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:2">
+      <c r="A1133" s="7" t="s">
         <v>1197</v>
       </c>
-      <c r="B1132" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1133" spans="1:2">
-      <c r="A1133" s="9" t="s">
+      <c r="B1133" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:2">
+      <c r="A1134" s="9" t="s">
         <v>1198</v>
-      </c>
-      <c r="B1133" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1134" spans="1:2">
-      <c r="A1134" s="7" t="s">
-        <v>1199</v>
       </c>
       <c r="B1134" s="3" t="s">
         <v>989</v>
@@ -16853,7 +16856,7 @@
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" s="7" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B1135" s="3" t="s">
         <v>989</v>
@@ -16861,7 +16864,7 @@
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" s="7" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B1136" s="3" t="s">
         <v>989</v>
@@ -16869,7 +16872,7 @@
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" s="7" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B1137" s="3" t="s">
         <v>989</v>
@@ -16877,7 +16880,7 @@
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" s="7" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B1138" s="3" t="s">
         <v>989</v>
@@ -16885,7 +16888,7 @@
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" s="7" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B1139" s="3" t="s">
         <v>989</v>
@@ -16893,7 +16896,7 @@
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" s="7" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B1140" s="3" t="s">
         <v>989</v>
@@ -16901,7 +16904,7 @@
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" s="7" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B1141" s="3" t="s">
         <v>989</v>
@@ -16909,7 +16912,7 @@
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" s="7" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B1142" s="3" t="s">
         <v>989</v>
@@ -16917,7 +16920,7 @@
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" s="7" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B1143" s="3" t="s">
         <v>989</v>
@@ -16925,7 +16928,7 @@
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" s="7" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B1144" s="3" t="s">
         <v>989</v>
@@ -16933,7 +16936,7 @@
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" s="7" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B1145" s="3" t="s">
         <v>989</v>
@@ -16941,7 +16944,7 @@
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" s="7" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B1146" s="3" t="s">
         <v>989</v>
@@ -16949,7 +16952,7 @@
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" s="7" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B1147" s="3" t="s">
         <v>989</v>
@@ -16957,7 +16960,7 @@
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" s="7" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B1148" s="3" t="s">
         <v>989</v>
@@ -16965,7 +16968,7 @@
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" s="7" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B1149" s="3" t="s">
         <v>989</v>
@@ -16973,7 +16976,7 @@
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" s="7" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B1150" s="3" t="s">
         <v>989</v>
@@ -16981,7 +16984,7 @@
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" s="7" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B1151" s="3" t="s">
         <v>989</v>
@@ -16989,7 +16992,7 @@
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" s="7" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B1152" s="3" t="s">
         <v>989</v>
@@ -16997,7 +17000,7 @@
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" s="7" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B1153" s="3" t="s">
         <v>989</v>
@@ -17005,7 +17008,7 @@
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" s="7" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B1154" s="3" t="s">
         <v>989</v>
@@ -17013,7 +17016,7 @@
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" s="7" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B1155" s="3" t="s">
         <v>989</v>
@@ -17021,7 +17024,7 @@
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" s="7" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="B1156" s="3" t="s">
         <v>989</v>
@@ -17029,7 +17032,7 @@
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" s="7" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B1157" s="3" t="s">
         <v>989</v>
@@ -17037,7 +17040,7 @@
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" s="7" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="B1158" s="3" t="s">
         <v>989</v>
@@ -17045,7 +17048,7 @@
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" s="7" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B1159" s="3" t="s">
         <v>989</v>
@@ -17053,7 +17056,7 @@
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" s="7" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B1160" s="3" t="s">
         <v>989</v>
@@ -17061,7 +17064,7 @@
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B1161" s="3" t="s">
         <v>989</v>
@@ -17069,7 +17072,7 @@
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" s="7" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="B1162" s="3" t="s">
         <v>989</v>
@@ -17077,7 +17080,7 @@
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="B1163" s="3" t="s">
         <v>989</v>
@@ -17085,7 +17088,7 @@
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" s="7" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B1164" s="3" t="s">
         <v>989</v>
@@ -17093,15 +17096,15 @@
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" s="7" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B1165" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:2">
+      <c r="A1166" s="7" t="s">
         <v>1230</v>
-      </c>
-      <c r="B1165" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1166" spans="1:2">
-      <c r="A1166" s="10" t="s">
-        <v>1231</v>
       </c>
       <c r="B1166" s="3" t="s">
         <v>989</v>
@@ -17109,15 +17112,15 @@
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" s="10" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B1167" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:2">
+      <c r="A1168" s="10" t="s">
         <v>1232</v>
-      </c>
-      <c r="B1167" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1168" spans="1:2">
-      <c r="A1168" s="7" t="s">
-        <v>1233</v>
       </c>
       <c r="B1168" s="3" t="s">
         <v>989</v>
@@ -17125,7 +17128,7 @@
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" s="7" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B1169" s="3" t="s">
         <v>989</v>
@@ -17133,7 +17136,7 @@
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" s="7" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B1170" s="3" t="s">
         <v>989</v>
@@ -17141,7 +17144,7 @@
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" s="7" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B1171" s="3" t="s">
         <v>989</v>
@@ -17149,39 +17152,39 @@
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" s="7" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B1172" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:2">
+      <c r="A1173" s="7" t="s">
         <v>1237</v>
       </c>
-      <c r="B1172" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1173" spans="1:2">
-      <c r="A1173" s="9" t="s">
+      <c r="B1173" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:2">
+      <c r="A1174" s="9" t="s">
         <v>1238</v>
       </c>
-      <c r="B1173" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1174" spans="1:2">
-      <c r="A1174" s="7" t="s">
+      <c r="B1174" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:2">
+      <c r="A1175" s="7" t="s">
         <v>1239</v>
       </c>
-      <c r="B1174" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1175" spans="1:2">
-      <c r="A1175" s="9" t="s">
+      <c r="B1175" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:2">
+      <c r="A1176" s="9" t="s">
         <v>1240</v>
-      </c>
-      <c r="B1175" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1176" spans="1:2">
-      <c r="A1176" s="7" t="s">
-        <v>1241</v>
       </c>
       <c r="B1176" s="3" t="s">
         <v>989</v>
@@ -17189,7 +17192,7 @@
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" s="7" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B1177" s="3" t="s">
         <v>989</v>
@@ -17197,7 +17200,7 @@
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" s="7" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B1178" s="3" t="s">
         <v>989</v>
@@ -17205,23 +17208,23 @@
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" s="7" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B1179" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:2">
+      <c r="A1180" s="7" t="s">
         <v>1244</v>
       </c>
-      <c r="B1179" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1180" spans="1:2">
-      <c r="A1180" s="9" t="s">
+      <c r="B1180" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:2">
+      <c r="A1181" s="9" t="s">
         <v>1245</v>
-      </c>
-      <c r="B1180" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1181" spans="1:2">
-      <c r="A1181" s="7" t="s">
-        <v>1246</v>
       </c>
       <c r="B1181" s="3" t="s">
         <v>989</v>
@@ -17229,7 +17232,7 @@
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" s="7" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B1182" s="3" t="s">
         <v>989</v>
@@ -17237,7 +17240,7 @@
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" s="7" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B1183" s="3" t="s">
         <v>989</v>
@@ -17245,7 +17248,7 @@
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" s="7" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B1184" s="3" t="s">
         <v>989</v>
@@ -17253,32 +17256,32 @@
     </row>
     <row r="1185" spans="1:4">
       <c r="A1185" s="7" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B1185" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:4">
+      <c r="A1186" s="7" t="s">
         <v>1250</v>
       </c>
-      <c r="B1185" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1186" spans="1:4" s="2" customFormat="1">
-      <c r="A1186" s="7" t="s">
+      <c r="B1186" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:4" s="2" customFormat="1">
+      <c r="A1187" s="7" t="s">
         <v>1251</v>
       </c>
-      <c r="B1186" s="3" t="s">
-        <v>989</v>
-      </c>
-      <c r="D1186" s="4"/>
-    </row>
-    <row r="1187" spans="1:4">
-      <c r="A1187" s="7" t="s">
-        <v>1252</v>
-      </c>
       <c r="B1187" s="3" t="s">
         <v>989</v>
       </c>
+      <c r="D1187" s="4"/>
     </row>
     <row r="1188" spans="1:4">
       <c r="A1188" s="7" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B1188" s="3" t="s">
         <v>989</v>
@@ -17286,7 +17289,7 @@
     </row>
     <row r="1189" spans="1:4">
       <c r="A1189" s="7" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B1189" s="3" t="s">
         <v>989</v>
@@ -17294,7 +17297,7 @@
     </row>
     <row r="1190" spans="1:4">
       <c r="A1190" s="7" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B1190" s="3" t="s">
         <v>989</v>
@@ -17302,7 +17305,7 @@
     </row>
     <row r="1191" spans="1:4">
       <c r="A1191" s="7" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B1191" s="3" t="s">
         <v>989</v>
@@ -17310,7 +17313,7 @@
     </row>
     <row r="1192" spans="1:4">
       <c r="A1192" s="7" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B1192" s="3" t="s">
         <v>989</v>
@@ -17318,7 +17321,7 @@
     </row>
     <row r="1193" spans="1:4">
       <c r="A1193" s="7" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B1193" s="3" t="s">
         <v>989</v>
@@ -17326,7 +17329,7 @@
     </row>
     <row r="1194" spans="1:4">
       <c r="A1194" s="7" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B1194" s="3" t="s">
         <v>989</v>
@@ -17334,7 +17337,7 @@
     </row>
     <row r="1195" spans="1:4">
       <c r="A1195" s="7" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B1195" s="3" t="s">
         <v>989</v>
@@ -17342,7 +17345,7 @@
     </row>
     <row r="1196" spans="1:4">
       <c r="A1196" s="7" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B1196" s="3" t="s">
         <v>989</v>
@@ -17350,7 +17353,7 @@
     </row>
     <row r="1197" spans="1:4">
       <c r="A1197" s="7" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B1197" s="3" t="s">
         <v>989</v>
@@ -17358,7 +17361,7 @@
     </row>
     <row r="1198" spans="1:4">
       <c r="A1198" s="7" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="B1198" s="3" t="s">
         <v>989</v>
@@ -17366,7 +17369,7 @@
     </row>
     <row r="1199" spans="1:4">
       <c r="A1199" s="7" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B1199" s="3" t="s">
         <v>989</v>
@@ -17374,7 +17377,7 @@
     </row>
     <row r="1200" spans="1:4">
       <c r="A1200" s="7" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="B1200" s="3" t="s">
         <v>989</v>
@@ -17382,7 +17385,7 @@
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" s="7" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B1201" s="3" t="s">
         <v>989</v>
@@ -17390,7 +17393,7 @@
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" s="7" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B1202" s="3" t="s">
         <v>989</v>
@@ -17398,7 +17401,7 @@
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" s="7" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B1203" s="3" t="s">
         <v>989</v>
@@ -17406,7 +17409,7 @@
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B1204" s="3" t="s">
         <v>989</v>
@@ -17414,7 +17417,7 @@
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" s="7" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B1205" s="3" t="s">
         <v>989</v>
@@ -17422,7 +17425,7 @@
     </row>
     <row r="1206" spans="1:2">
       <c r="A1206" s="7" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B1206" s="3" t="s">
         <v>989</v>
@@ -17430,7 +17433,7 @@
     </row>
     <row r="1207" spans="1:2">
       <c r="A1207" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B1207" s="3" t="s">
         <v>989</v>
@@ -17438,7 +17441,7 @@
     </row>
     <row r="1208" spans="1:2">
       <c r="A1208" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B1208" s="3" t="s">
         <v>989</v>
@@ -17446,7 +17449,7 @@
     </row>
     <row r="1209" spans="1:2">
       <c r="A1209" s="7" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B1209" s="3" t="s">
         <v>989</v>
@@ -17454,7 +17457,7 @@
     </row>
     <row r="1210" spans="1:2">
       <c r="A1210" s="7" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B1210" s="3" t="s">
         <v>989</v>
@@ -17462,7 +17465,7 @@
     </row>
     <row r="1211" spans="1:2">
       <c r="A1211" s="7" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B1211" s="3" t="s">
         <v>989</v>
@@ -17470,7 +17473,7 @@
     </row>
     <row r="1212" spans="1:2">
       <c r="A1212" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B1212" s="3" t="s">
         <v>989</v>
@@ -17478,7 +17481,7 @@
     </row>
     <row r="1213" spans="1:2">
       <c r="A1213" s="7" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B1213" s="3" t="s">
         <v>989</v>
@@ -17486,7 +17489,7 @@
     </row>
     <row r="1214" spans="1:2">
       <c r="A1214" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B1214" s="3" t="s">
         <v>989</v>
@@ -17494,7 +17497,7 @@
     </row>
     <row r="1215" spans="1:2">
       <c r="A1215" s="7" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B1215" s="3" t="s">
         <v>989</v>
@@ -17502,7 +17505,7 @@
     </row>
     <row r="1216" spans="1:2">
       <c r="A1216" s="7" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B1216" s="3" t="s">
         <v>989</v>
@@ -17510,7 +17513,7 @@
     </row>
     <row r="1217" spans="1:2">
       <c r="A1217" s="7" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B1217" s="3" t="s">
         <v>989</v>
@@ -17518,7 +17521,7 @@
     </row>
     <row r="1218" spans="1:2">
       <c r="A1218" s="7" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B1218" s="3" t="s">
         <v>989</v>
@@ -17526,7 +17529,7 @@
     </row>
     <row r="1219" spans="1:2">
       <c r="A1219" s="7" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B1219" s="3" t="s">
         <v>989</v>
@@ -17534,7 +17537,7 @@
     </row>
     <row r="1220" spans="1:2">
       <c r="A1220" s="7" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B1220" s="3" t="s">
         <v>989</v>
@@ -17542,7 +17545,7 @@
     </row>
     <row r="1221" spans="1:2">
       <c r="A1221" s="7" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B1221" s="3" t="s">
         <v>989</v>
@@ -17550,7 +17553,7 @@
     </row>
     <row r="1222" spans="1:2">
       <c r="A1222" s="7" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B1222" s="3" t="s">
         <v>989</v>
@@ -17558,7 +17561,7 @@
     </row>
     <row r="1223" spans="1:2">
       <c r="A1223" s="7" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B1223" s="3" t="s">
         <v>989</v>
@@ -17566,7 +17569,7 @@
     </row>
     <row r="1224" spans="1:2">
       <c r="A1224" s="7" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B1224" s="3" t="s">
         <v>989</v>
@@ -17574,7 +17577,7 @@
     </row>
     <row r="1225" spans="1:2">
       <c r="A1225" s="7" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B1225" s="3" t="s">
         <v>989</v>
@@ -17582,7 +17585,7 @@
     </row>
     <row r="1226" spans="1:2">
       <c r="A1226" s="7" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B1226" s="3" t="s">
         <v>989</v>
@@ -17590,7 +17593,7 @@
     </row>
     <row r="1227" spans="1:2">
       <c r="A1227" s="7" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B1227" s="3" t="s">
         <v>989</v>
@@ -17598,7 +17601,7 @@
     </row>
     <row r="1228" spans="1:2">
       <c r="A1228" s="7" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B1228" s="3" t="s">
         <v>989</v>
@@ -17606,7 +17609,7 @@
     </row>
     <row r="1229" spans="1:2">
       <c r="A1229" s="7" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B1229" s="3" t="s">
         <v>989</v>
@@ -17614,7 +17617,7 @@
     </row>
     <row r="1230" spans="1:2">
       <c r="A1230" s="7" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B1230" s="3" t="s">
         <v>989</v>
@@ -17622,7 +17625,7 @@
     </row>
     <row r="1231" spans="1:2">
       <c r="A1231" s="7" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B1231" s="3" t="s">
         <v>989</v>
@@ -17630,7 +17633,7 @@
     </row>
     <row r="1232" spans="1:2">
       <c r="A1232" s="7" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B1232" s="3" t="s">
         <v>989</v>
@@ -17638,7 +17641,7 @@
     </row>
     <row r="1233" spans="1:2">
       <c r="A1233" s="7" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B1233" s="3" t="s">
         <v>989</v>
@@ -17646,7 +17649,7 @@
     </row>
     <row r="1234" spans="1:2">
       <c r="A1234" s="7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B1234" s="3" t="s">
         <v>989</v>
@@ -17654,7 +17657,7 @@
     </row>
     <row r="1235" spans="1:2">
       <c r="A1235" s="7" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B1235" s="3" t="s">
         <v>989</v>
@@ -17662,7 +17665,7 @@
     </row>
     <row r="1236" spans="1:2">
       <c r="A1236" s="7" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B1236" s="3" t="s">
         <v>989</v>
@@ -17670,7 +17673,7 @@
     </row>
     <row r="1237" spans="1:2">
       <c r="A1237" s="7" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B1237" s="3" t="s">
         <v>989</v>
@@ -17678,7 +17681,7 @@
     </row>
     <row r="1238" spans="1:2">
       <c r="A1238" s="7" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B1238" s="3" t="s">
         <v>989</v>
@@ -17686,23 +17689,23 @@
     </row>
     <row r="1239" spans="1:2">
       <c r="A1239" s="7" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B1239" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:2">
+      <c r="A1240" s="7" t="s">
         <v>1304</v>
       </c>
-      <c r="B1239" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1240" spans="1:2">
-      <c r="A1240" s="4" t="s">
+      <c r="B1240" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:2">
+      <c r="A1241" s="4" t="s">
         <v>1305</v>
-      </c>
-      <c r="B1240" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1241" spans="1:2">
-      <c r="A1241" s="7" t="s">
-        <v>1306</v>
       </c>
       <c r="B1241" s="3" t="s">
         <v>989</v>
@@ -17710,7 +17713,7 @@
     </row>
     <row r="1242" spans="1:2">
       <c r="A1242" s="7" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B1242" s="3" t="s">
         <v>989</v>
@@ -17718,7 +17721,7 @@
     </row>
     <row r="1243" spans="1:2">
       <c r="A1243" s="7" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B1243" s="3" t="s">
         <v>989</v>
@@ -17726,7 +17729,7 @@
     </row>
     <row r="1244" spans="1:2">
       <c r="A1244" s="7" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B1244" s="3" t="s">
         <v>989</v>
@@ -17734,7 +17737,7 @@
     </row>
     <row r="1245" spans="1:2">
       <c r="A1245" s="7" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="B1245" s="3" t="s">
         <v>989</v>
@@ -17742,7 +17745,7 @@
     </row>
     <row r="1246" spans="1:2">
       <c r="A1246" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B1246" s="3" t="s">
         <v>989</v>
@@ -17750,7 +17753,7 @@
     </row>
     <row r="1247" spans="1:2">
       <c r="A1247" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="B1247" s="3" t="s">
         <v>989</v>
@@ -17758,7 +17761,7 @@
     </row>
     <row r="1248" spans="1:2">
       <c r="A1248" s="7" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B1248" s="3" t="s">
         <v>989</v>
@@ -17766,7 +17769,7 @@
     </row>
     <row r="1249" spans="1:2">
       <c r="A1249" s="7" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B1249" s="3" t="s">
         <v>989</v>
@@ -17774,7 +17777,7 @@
     </row>
     <row r="1250" spans="1:2">
       <c r="A1250" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B1250" s="3" t="s">
         <v>989</v>
@@ -17782,7 +17785,7 @@
     </row>
     <row r="1251" spans="1:2">
       <c r="A1251" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B1251" s="3" t="s">
         <v>989</v>
@@ -17790,7 +17793,7 @@
     </row>
     <row r="1252" spans="1:2">
       <c r="A1252" s="7" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B1252" s="3" t="s">
         <v>989</v>
@@ -17798,7 +17801,7 @@
     </row>
     <row r="1253" spans="1:2">
       <c r="A1253" s="7" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B1253" s="3" t="s">
         <v>989</v>
@@ -17806,7 +17809,7 @@
     </row>
     <row r="1254" spans="1:2">
       <c r="A1254" s="7" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B1254" s="3" t="s">
         <v>989</v>
@@ -17814,7 +17817,7 @@
     </row>
     <row r="1255" spans="1:2">
       <c r="A1255" s="7" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="B1255" s="3" t="s">
         <v>989</v>
@@ -17822,23 +17825,23 @@
     </row>
     <row r="1256" spans="1:2">
       <c r="A1256" s="7" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B1256" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:2">
+      <c r="A1257" s="7" t="s">
         <v>1321</v>
       </c>
-      <c r="B1256" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1257" spans="1:2">
-      <c r="A1257" s="13" t="s">
+      <c r="B1257" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:2">
+      <c r="A1258" s="13" t="s">
         <v>1322</v>
-      </c>
-      <c r="B1257" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1258" spans="1:2">
-      <c r="A1258" s="7" t="s">
-        <v>1323</v>
       </c>
       <c r="B1258" s="3" t="s">
         <v>989</v>
@@ -17846,7 +17849,7 @@
     </row>
     <row r="1259" spans="1:2">
       <c r="A1259" s="7" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B1259" s="3" t="s">
         <v>989</v>
@@ -17854,7 +17857,7 @@
     </row>
     <row r="1260" spans="1:2">
       <c r="A1260" s="7" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B1260" s="3" t="s">
         <v>989</v>
@@ -17862,7 +17865,7 @@
     </row>
     <row r="1261" spans="1:2">
       <c r="A1261" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="B1261" s="3" t="s">
         <v>989</v>
@@ -17870,7 +17873,7 @@
     </row>
     <row r="1262" spans="1:2">
       <c r="A1262" s="7" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B1262" s="3" t="s">
         <v>989</v>
@@ -17878,7 +17881,7 @@
     </row>
     <row r="1263" spans="1:2">
       <c r="A1263" s="7" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B1263" s="3" t="s">
         <v>989</v>
@@ -17886,7 +17889,7 @@
     </row>
     <row r="1264" spans="1:2">
       <c r="A1264" s="7" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B1264" s="3" t="s">
         <v>989</v>
@@ -17894,7 +17897,7 @@
     </row>
     <row r="1265" spans="1:2">
       <c r="A1265" s="7" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="B1265" s="3" t="s">
         <v>989</v>
@@ -17902,7 +17905,7 @@
     </row>
     <row r="1266" spans="1:2">
       <c r="A1266" s="7" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="B1266" s="3" t="s">
         <v>989</v>
@@ -17910,7 +17913,7 @@
     </row>
     <row r="1267" spans="1:2">
       <c r="A1267" s="7" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B1267" s="3" t="s">
         <v>989</v>
@@ -17918,7 +17921,7 @@
     </row>
     <row r="1268" spans="1:2">
       <c r="A1268" s="7" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B1268" s="3" t="s">
         <v>989</v>
@@ -17926,7 +17929,7 @@
     </row>
     <row r="1269" spans="1:2">
       <c r="A1269" s="7" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B1269" s="3" t="s">
         <v>989</v>
@@ -17934,7 +17937,7 @@
     </row>
     <row r="1270" spans="1:2">
       <c r="A1270" s="7" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="B1270" s="3" t="s">
         <v>989</v>
@@ -17942,7 +17945,7 @@
     </row>
     <row r="1271" spans="1:2">
       <c r="A1271" s="7" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="B1271" s="3" t="s">
         <v>989</v>
@@ -17950,7 +17953,7 @@
     </row>
     <row r="1272" spans="1:2">
       <c r="A1272" s="7" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B1272" s="3" t="s">
         <v>989</v>
@@ -17958,7 +17961,7 @@
     </row>
     <row r="1273" spans="1:2">
       <c r="A1273" s="7" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="B1273" s="3" t="s">
         <v>989</v>
@@ -17966,7 +17969,7 @@
     </row>
     <row r="1274" spans="1:2">
       <c r="A1274" s="7" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B1274" s="3" t="s">
         <v>989</v>
@@ -17974,7 +17977,7 @@
     </row>
     <row r="1275" spans="1:2">
       <c r="A1275" s="7" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="B1275" s="3" t="s">
         <v>989</v>
@@ -17982,7 +17985,7 @@
     </row>
     <row r="1276" spans="1:2">
       <c r="A1276" s="7" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B1276" s="3" t="s">
         <v>989</v>
@@ -17990,7 +17993,7 @@
     </row>
     <row r="1277" spans="1:2">
       <c r="A1277" s="7" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B1277" s="3" t="s">
         <v>989</v>
@@ -17998,7 +18001,7 @@
     </row>
     <row r="1278" spans="1:2">
       <c r="A1278" s="7" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B1278" s="3" t="s">
         <v>989</v>
@@ -18006,7 +18009,7 @@
     </row>
     <row r="1279" spans="1:2">
       <c r="A1279" s="7" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="B1279" s="3" t="s">
         <v>989</v>
@@ -18014,7 +18017,7 @@
     </row>
     <row r="1280" spans="1:2">
       <c r="A1280" s="7" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="B1280" s="3" t="s">
         <v>989</v>
@@ -18022,7 +18025,7 @@
     </row>
     <row r="1281" spans="1:5">
       <c r="A1281" s="7" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="B1281" s="3" t="s">
         <v>989</v>
@@ -18030,7 +18033,7 @@
     </row>
     <row r="1282" spans="1:5">
       <c r="A1282" s="7" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B1282" s="3" t="s">
         <v>989</v>
@@ -18038,23 +18041,23 @@
     </row>
     <row r="1283" spans="1:5">
       <c r="A1283" s="7" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B1283" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:5">
+      <c r="A1284" s="7" t="s">
         <v>1348</v>
       </c>
-      <c r="B1283" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1284" spans="1:5">
-      <c r="A1284" s="4" t="s">
+      <c r="B1284" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:5">
+      <c r="A1285" s="4" t="s">
         <v>1349</v>
-      </c>
-      <c r="B1284" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1285" spans="1:5">
-      <c r="A1285" s="7" t="s">
-        <v>1350</v>
       </c>
       <c r="B1285" s="3" t="s">
         <v>989</v>
@@ -18062,7 +18065,7 @@
     </row>
     <row r="1286" spans="1:5">
       <c r="A1286" s="7" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B1286" s="3" t="s">
         <v>989</v>
@@ -18070,7 +18073,7 @@
     </row>
     <row r="1287" spans="1:5">
       <c r="A1287" s="7" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="B1287" s="3" t="s">
         <v>989</v>
@@ -18078,7 +18081,7 @@
     </row>
     <row r="1288" spans="1:5">
       <c r="A1288" s="7" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B1288" s="3" t="s">
         <v>989</v>
@@ -18086,7 +18089,7 @@
     </row>
     <row r="1289" spans="1:5">
       <c r="A1289" s="7" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="B1289" s="3" t="s">
         <v>989</v>
@@ -18094,7 +18097,7 @@
     </row>
     <row r="1290" spans="1:5">
       <c r="A1290" s="7" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B1290" s="3" t="s">
         <v>989</v>
@@ -18102,7 +18105,7 @@
     </row>
     <row r="1291" spans="1:5">
       <c r="A1291" s="7" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B1291" s="3" t="s">
         <v>989</v>
@@ -18110,48 +18113,48 @@
     </row>
     <row r="1292" spans="1:5">
       <c r="A1292" s="7" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="B1292" s="3" t="s">
         <v>989</v>
-      </c>
-      <c r="E1292" s="4">
-        <v>97</v>
       </c>
     </row>
     <row r="1293" spans="1:5">
       <c r="A1293" s="7" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="B1293" s="3" t="s">
         <v>989</v>
       </c>
       <c r="E1293" s="4">
-        <v>72</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1294" spans="1:5">
       <c r="A1294" s="7" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="B1294" s="3" t="s">
         <v>989</v>
       </c>
       <c r="E1294" s="4">
-        <v>100</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1295" spans="1:5">
       <c r="A1295" s="7" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="B1295" s="3" t="s">
         <v>989</v>
+      </c>
+      <c r="E1295" s="4">
+        <v>100</v>
       </c>
     </row>
     <row r="1296" spans="1:5">
       <c r="A1296" s="7" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B1296" s="3" t="s">
         <v>989</v>
@@ -18159,23 +18162,23 @@
     </row>
     <row r="1297" spans="1:2">
       <c r="A1297" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B1297" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:2">
+      <c r="A1298" s="7" t="s">
         <v>1362</v>
       </c>
-      <c r="B1297" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1298" spans="1:2">
-      <c r="A1298" s="10" t="s">
+      <c r="B1298" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:2">
+      <c r="A1299" s="10" t="s">
         <v>1363</v>
-      </c>
-      <c r="B1298" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1299" spans="1:2">
-      <c r="A1299" s="7" t="s">
-        <v>1364</v>
       </c>
       <c r="B1299" s="3" t="s">
         <v>989</v>
@@ -18183,23 +18186,23 @@
     </row>
     <row r="1300" spans="1:2">
       <c r="A1300" s="7" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B1300" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:2">
+      <c r="A1301" s="7" t="s">
         <v>1365</v>
       </c>
-      <c r="B1300" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1301" spans="1:2">
-      <c r="A1301" s="14" t="s">
+      <c r="B1301" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:2">
+      <c r="A1302" s="14" t="s">
         <v>1366</v>
-      </c>
-      <c r="B1301" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1302" spans="1:2">
-      <c r="A1302" s="7" t="s">
-        <v>1367</v>
       </c>
       <c r="B1302" s="3" t="s">
         <v>989</v>
@@ -18207,7 +18210,7 @@
     </row>
     <row r="1303" spans="1:2">
       <c r="A1303" s="7" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="B1303" s="3" t="s">
         <v>989</v>
@@ -18215,7 +18218,7 @@
     </row>
     <row r="1304" spans="1:2">
       <c r="A1304" s="7" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="B1304" s="3" t="s">
         <v>989</v>
@@ -18223,7 +18226,7 @@
     </row>
     <row r="1305" spans="1:2">
       <c r="A1305" s="7" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="B1305" s="3" t="s">
         <v>989</v>
@@ -18231,23 +18234,23 @@
     </row>
     <row r="1306" spans="1:2">
       <c r="A1306" s="7" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B1306" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:2">
+      <c r="A1307" s="7" t="s">
         <v>1371</v>
       </c>
-      <c r="B1306" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1307" spans="1:2">
-      <c r="A1307" s="9" t="s">
+      <c r="B1307" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:2">
+      <c r="A1308" s="9" t="s">
         <v>1372</v>
-      </c>
-      <c r="B1307" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1308" spans="1:2">
-      <c r="A1308" s="7" t="s">
-        <v>1373</v>
       </c>
       <c r="B1308" s="3" t="s">
         <v>989</v>
@@ -18255,7 +18258,7 @@
     </row>
     <row r="1309" spans="1:2">
       <c r="A1309" s="7" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="B1309" s="3" t="s">
         <v>989</v>
@@ -18263,7 +18266,7 @@
     </row>
     <row r="1310" spans="1:2">
       <c r="A1310" s="7" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="B1310" s="3" t="s">
         <v>989</v>
@@ -18271,7 +18274,7 @@
     </row>
     <row r="1311" spans="1:2">
       <c r="A1311" s="7" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="B1311" s="3" t="s">
         <v>989</v>
@@ -18279,7 +18282,7 @@
     </row>
     <row r="1312" spans="1:2">
       <c r="A1312" s="7" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="B1312" s="3" t="s">
         <v>989</v>
@@ -18287,7 +18290,7 @@
     </row>
     <row r="1313" spans="1:2">
       <c r="A1313" s="7" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="B1313" s="3" t="s">
         <v>989</v>
@@ -18295,7 +18298,7 @@
     </row>
     <row r="1314" spans="1:2">
       <c r="A1314" s="7" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="B1314" s="3" t="s">
         <v>989</v>
@@ -18303,23 +18306,23 @@
     </row>
     <row r="1315" spans="1:2">
       <c r="A1315" s="7" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B1315" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:2">
+      <c r="A1316" s="7" t="s">
         <v>1380</v>
       </c>
-      <c r="B1315" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1316" spans="1:2">
-      <c r="A1316" s="6" t="s">
+      <c r="B1316" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:2">
+      <c r="A1317" s="6" t="s">
         <v>1381</v>
-      </c>
-      <c r="B1316" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1317" spans="1:2">
-      <c r="A1317" s="7" t="s">
-        <v>1382</v>
       </c>
       <c r="B1317" s="3" t="s">
         <v>989</v>
@@ -18327,39 +18330,39 @@
     </row>
     <row r="1318" spans="1:2">
       <c r="A1318" s="7" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B1318" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:2">
+      <c r="A1319" s="7" t="s">
         <v>1383</v>
       </c>
-      <c r="B1318" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1319" spans="1:2">
-      <c r="A1319" s="6" t="s">
+      <c r="B1319" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:2">
+      <c r="A1320" s="6" t="s">
         <v>1384</v>
       </c>
-      <c r="B1319" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1320" spans="1:2">
-      <c r="A1320" s="7" t="s">
+      <c r="B1320" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:2">
+      <c r="A1321" s="7" t="s">
         <v>1385</v>
       </c>
-      <c r="B1320" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1321" spans="1:2">
-      <c r="A1321" s="10" t="s">
+      <c r="B1321" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:2">
+      <c r="A1322" s="10" t="s">
         <v>1386</v>
-      </c>
-      <c r="B1321" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1322" spans="1:2">
-      <c r="A1322" s="7" t="s">
-        <v>1387</v>
       </c>
       <c r="B1322" s="3" t="s">
         <v>989</v>
@@ -18367,7 +18370,7 @@
     </row>
     <row r="1323" spans="1:2">
       <c r="A1323" s="7" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B1323" s="3" t="s">
         <v>989</v>
@@ -18375,23 +18378,23 @@
     </row>
     <row r="1324" spans="1:2">
       <c r="A1324" s="7" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B1324" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:2">
+      <c r="A1325" s="7" t="s">
         <v>1389</v>
       </c>
-      <c r="B1324" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1325" spans="1:2">
-      <c r="A1325" s="10" t="s">
+      <c r="B1325" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:2">
+      <c r="A1326" s="10" t="s">
         <v>1390</v>
-      </c>
-      <c r="B1325" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="1326" spans="1:2">
-      <c r="A1326" s="7" t="s">
-        <v>1391</v>
       </c>
       <c r="B1326" s="3" t="s">
         <v>989</v>
@@ -18399,7 +18402,7 @@
     </row>
     <row r="1327" spans="1:2">
       <c r="A1327" s="7" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B1327" s="3" t="s">
         <v>989</v>
@@ -18407,7 +18410,7 @@
     </row>
     <row r="1328" spans="1:2">
       <c r="A1328" s="7" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B1328" s="3" t="s">
         <v>989</v>
@@ -18415,7 +18418,7 @@
     </row>
     <row r="1329" spans="1:2">
       <c r="A1329" s="7" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B1329" s="3" t="s">
         <v>989</v>
@@ -18423,7 +18426,7 @@
     </row>
     <row r="1330" spans="1:2">
       <c r="A1330" s="7" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B1330" s="3" t="s">
         <v>989</v>
@@ -18431,15 +18434,15 @@
     </row>
     <row r="1331" spans="1:2">
       <c r="A1331" s="7" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B1331" s="3" t="s">
-        <v>1397</v>
+        <v>989</v>
       </c>
     </row>
     <row r="1332" spans="1:2">
       <c r="A1332" s="7" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B1332" s="3" t="s">
         <v>1397</v>
@@ -18447,7 +18450,7 @@
     </row>
     <row r="1333" spans="1:2">
       <c r="A1333" s="7" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="B1333" s="3" t="s">
         <v>1397</v>
@@ -18455,23 +18458,23 @@
     </row>
     <row r="1334" spans="1:2">
       <c r="A1334" s="7" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B1334" s="3" t="s">
         <v>1397</v>
       </c>
     </row>
     <row r="1335" spans="1:2">
-      <c r="A1335" s="15" t="s">
-        <v>1401</v>
+      <c r="A1335" s="7" t="s">
+        <v>1400</v>
       </c>
       <c r="B1335" s="3" t="s">
         <v>1397</v>
       </c>
     </row>
     <row r="1336" spans="1:2">
-      <c r="A1336" s="7" t="s">
-        <v>1402</v>
+      <c r="A1336" s="15" t="s">
+        <v>1401</v>
       </c>
       <c r="B1336" s="3" t="s">
         <v>1397</v>
@@ -18479,7 +18482,7 @@
     </row>
     <row r="1337" spans="1:2">
       <c r="A1337" s="7" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="B1337" s="3" t="s">
         <v>1397</v>
@@ -18487,7 +18490,7 @@
     </row>
     <row r="1338" spans="1:2">
       <c r="A1338" s="7" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="B1338" s="3" t="s">
         <v>1397</v>
@@ -18495,7 +18498,7 @@
     </row>
     <row r="1339" spans="1:2">
       <c r="A1339" s="7" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="B1339" s="3" t="s">
         <v>1397</v>
@@ -18503,7 +18506,7 @@
     </row>
     <row r="1340" spans="1:2">
       <c r="A1340" s="7" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="B1340" s="3" t="s">
         <v>1397</v>
@@ -18511,7 +18514,7 @@
     </row>
     <row r="1341" spans="1:2">
       <c r="A1341" s="7" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B1341" s="3" t="s">
         <v>1397</v>
@@ -18519,7 +18522,7 @@
     </row>
     <row r="1342" spans="1:2">
       <c r="A1342" s="7" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="B1342" s="3" t="s">
         <v>1397</v>
@@ -18527,7 +18530,7 @@
     </row>
     <row r="1343" spans="1:2">
       <c r="A1343" s="7" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B1343" s="3" t="s">
         <v>1397</v>
@@ -18535,7 +18538,7 @@
     </row>
     <row r="1344" spans="1:2">
       <c r="A1344" s="7" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="B1344" s="3" t="s">
         <v>1397</v>
@@ -18543,7 +18546,7 @@
     </row>
     <row r="1345" spans="1:2">
       <c r="A1345" s="7" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="B1345" s="3" t="s">
         <v>1397</v>
@@ -18551,7 +18554,7 @@
     </row>
     <row r="1346" spans="1:2">
       <c r="A1346" s="7" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B1346" s="3" t="s">
         <v>1397</v>
@@ -18559,79 +18562,79 @@
     </row>
     <row r="1347" spans="1:2">
       <c r="A1347" s="7" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B1347" s="3" t="s">
-        <v>1414</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="1348" spans="1:2">
       <c r="A1348" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="B1348" s="3" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="1349" spans="1:2">
       <c r="A1349" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B1349" s="3" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="1350" spans="1:2">
       <c r="A1350" s="7" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="B1350" s="3" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="1351" spans="1:2">
       <c r="A1351" s="7" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B1351" s="3" t="s">
         <v>1420</v>
       </c>
     </row>
     <row r="1352" spans="1:2">
-      <c r="A1352" s="9" t="s">
-        <v>1422</v>
+      <c r="A1352" s="7" t="s">
+        <v>1421</v>
       </c>
       <c r="B1352" s="3" t="s">
         <v>1420</v>
       </c>
     </row>
     <row r="1353" spans="1:2">
-      <c r="A1353" s="7" t="s">
-        <v>1423</v>
+      <c r="A1353" s="9" t="s">
+        <v>1422</v>
       </c>
       <c r="B1353" s="3" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="1354" spans="1:2">
       <c r="A1354" s="7" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="B1354" s="3" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="1355" spans="1:2">
       <c r="A1355" s="7" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B1355" s="3" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="1356" spans="1:2">
       <c r="A1356" s="7" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="B1356" s="3" t="s">
         <v>1428</v>
@@ -18639,7 +18642,7 @@
     </row>
     <row r="1357" spans="1:2">
       <c r="A1357" s="7" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B1357" s="3" t="s">
         <v>1428</v>
@@ -18647,7 +18650,7 @@
     </row>
     <row r="1358" spans="1:2">
       <c r="A1358" s="7" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B1358" s="3" t="s">
         <v>1428</v>
@@ -18655,7 +18658,7 @@
     </row>
     <row r="1359" spans="1:2">
       <c r="A1359" s="7" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B1359" s="3" t="s">
         <v>1428</v>
@@ -18663,7 +18666,7 @@
     </row>
     <row r="1360" spans="1:2">
       <c r="A1360" s="7" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B1360" s="3" t="s">
         <v>1428</v>
@@ -18671,7 +18674,7 @@
     </row>
     <row r="1361" spans="1:2">
       <c r="A1361" s="7" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B1361" s="3" t="s">
         <v>1428</v>
@@ -18679,7 +18682,7 @@
     </row>
     <row r="1362" spans="1:2">
       <c r="A1362" s="7" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B1362" s="3" t="s">
         <v>1428</v>
@@ -18687,7 +18690,7 @@
     </row>
     <row r="1363" spans="1:2">
       <c r="A1363" s="7" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B1363" s="3" t="s">
         <v>1428</v>
@@ -18695,7 +18698,7 @@
     </row>
     <row r="1364" spans="1:2">
       <c r="A1364" s="7" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B1364" s="3" t="s">
         <v>1428</v>
@@ -18703,7 +18706,7 @@
     </row>
     <row r="1365" spans="1:2">
       <c r="A1365" s="7" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B1365" s="3" t="s">
         <v>1428</v>
@@ -18711,7 +18714,7 @@
     </row>
     <row r="1366" spans="1:2">
       <c r="A1366" s="7" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B1366" s="3" t="s">
         <v>1428</v>
@@ -18719,7 +18722,7 @@
     </row>
     <row r="1367" spans="1:2">
       <c r="A1367" s="7" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B1367" s="3" t="s">
         <v>1428</v>
@@ -18727,7 +18730,7 @@
     </row>
     <row r="1368" spans="1:2">
       <c r="A1368" s="7" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B1368" s="3" t="s">
         <v>1428</v>
@@ -18735,7 +18738,7 @@
     </row>
     <row r="1369" spans="1:2">
       <c r="A1369" s="7" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B1369" s="3" t="s">
         <v>1428</v>
@@ -18743,7 +18746,7 @@
     </row>
     <row r="1370" spans="1:2">
       <c r="A1370" s="7" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B1370" s="3" t="s">
         <v>1428</v>
@@ -18751,7 +18754,7 @@
     </row>
     <row r="1371" spans="1:2">
       <c r="A1371" s="7" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B1371" s="3" t="s">
         <v>1428</v>
@@ -18759,7 +18762,7 @@
     </row>
     <row r="1372" spans="1:2">
       <c r="A1372" s="7" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B1372" s="3" t="s">
         <v>1428</v>
@@ -18767,7 +18770,7 @@
     </row>
     <row r="1373" spans="1:2">
       <c r="A1373" s="7" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B1373" s="3" t="s">
         <v>1428</v>
@@ -18775,7 +18778,7 @@
     </row>
     <row r="1374" spans="1:2">
       <c r="A1374" s="7" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B1374" s="3" t="s">
         <v>1428</v>
@@ -18783,7 +18786,7 @@
     </row>
     <row r="1375" spans="1:2">
       <c r="A1375" s="7" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B1375" s="3" t="s">
         <v>1428</v>
@@ -18791,23 +18794,23 @@
     </row>
     <row r="1376" spans="1:2">
       <c r="A1376" s="7" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B1376" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1377" spans="1:2">
-      <c r="A1377" s="13" t="s">
-        <v>1450</v>
+      <c r="A1377" s="7" t="s">
+        <v>1449</v>
       </c>
       <c r="B1377" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1378" spans="1:2">
-      <c r="A1378" s="7" t="s">
-        <v>1451</v>
+      <c r="A1378" s="13" t="s">
+        <v>1450</v>
       </c>
       <c r="B1378" s="3" t="s">
         <v>1428</v>
@@ -18815,7 +18818,7 @@
     </row>
     <row r="1379" spans="1:2">
       <c r="A1379" s="7" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B1379" s="3" t="s">
         <v>1428</v>
@@ -18823,7 +18826,7 @@
     </row>
     <row r="1380" spans="1:2">
       <c r="A1380" s="7" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B1380" s="3" t="s">
         <v>1428</v>
@@ -18831,7 +18834,7 @@
     </row>
     <row r="1381" spans="1:2">
       <c r="A1381" s="7" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B1381" s="3" t="s">
         <v>1428</v>
@@ -18839,7 +18842,7 @@
     </row>
     <row r="1382" spans="1:2">
       <c r="A1382" s="7" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B1382" s="3" t="s">
         <v>1428</v>
@@ -18847,7 +18850,7 @@
     </row>
     <row r="1383" spans="1:2">
       <c r="A1383" s="7" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B1383" s="3" t="s">
         <v>1428</v>
@@ -18855,7 +18858,7 @@
     </row>
     <row r="1384" spans="1:2">
       <c r="A1384" s="7" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B1384" s="3" t="s">
         <v>1428</v>
@@ -18863,7 +18866,7 @@
     </row>
     <row r="1385" spans="1:2">
       <c r="A1385" s="7" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B1385" s="3" t="s">
         <v>1428</v>
@@ -18871,7 +18874,7 @@
     </row>
     <row r="1386" spans="1:2">
       <c r="A1386" s="7" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B1386" s="3" t="s">
         <v>1428</v>
@@ -18879,7 +18882,7 @@
     </row>
     <row r="1387" spans="1:2">
       <c r="A1387" s="7" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B1387" s="3" t="s">
         <v>1428</v>
@@ -18887,7 +18890,7 @@
     </row>
     <row r="1388" spans="1:2">
       <c r="A1388" s="7" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B1388" s="3" t="s">
         <v>1428</v>
@@ -18895,7 +18898,7 @@
     </row>
     <row r="1389" spans="1:2">
       <c r="A1389" s="7" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B1389" s="3" t="s">
         <v>1428</v>
@@ -18903,7 +18906,7 @@
     </row>
     <row r="1390" spans="1:2">
       <c r="A1390" s="7" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B1390" s="3" t="s">
         <v>1428</v>
@@ -18911,7 +18914,7 @@
     </row>
     <row r="1391" spans="1:2">
       <c r="A1391" s="7" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B1391" s="3" t="s">
         <v>1428</v>
@@ -18919,7 +18922,7 @@
     </row>
     <row r="1392" spans="1:2">
       <c r="A1392" s="7" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="B1392" s="3" t="s">
         <v>1428</v>
@@ -18927,23 +18930,23 @@
     </row>
     <row r="1393" spans="1:2">
       <c r="A1393" s="7" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B1393" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1394" spans="1:2">
-      <c r="A1394" s="18" t="s">
-        <v>1467</v>
+      <c r="A1394" s="7" t="s">
+        <v>1466</v>
       </c>
       <c r="B1394" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1395" spans="1:2">
-      <c r="A1395" s="7" t="s">
-        <v>1468</v>
+      <c r="A1395" s="18" t="s">
+        <v>1467</v>
       </c>
       <c r="B1395" s="3" t="s">
         <v>1428</v>
@@ -18951,7 +18954,7 @@
     </row>
     <row r="1396" spans="1:2">
       <c r="A1396" s="7" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B1396" s="3" t="s">
         <v>1428</v>
@@ -18959,7 +18962,7 @@
     </row>
     <row r="1397" spans="1:2">
       <c r="A1397" s="7" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B1397" s="3" t="s">
         <v>1428</v>
@@ -18967,7 +18970,7 @@
     </row>
     <row r="1398" spans="1:2">
       <c r="A1398" s="7" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B1398" s="3" t="s">
         <v>1428</v>
@@ -18975,7 +18978,7 @@
     </row>
     <row r="1399" spans="1:2">
       <c r="A1399" s="7" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B1399" s="3" t="s">
         <v>1428</v>
@@ -18983,7 +18986,7 @@
     </row>
     <row r="1400" spans="1:2">
       <c r="A1400" s="7" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B1400" s="3" t="s">
         <v>1428</v>
@@ -18991,7 +18994,7 @@
     </row>
     <row r="1401" spans="1:2">
       <c r="A1401" s="7" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B1401" s="3" t="s">
         <v>1428</v>
@@ -18999,7 +19002,7 @@
     </row>
     <row r="1402" spans="1:2">
       <c r="A1402" s="7" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B1402" s="3" t="s">
         <v>1428</v>
@@ -19007,7 +19010,7 @@
     </row>
     <row r="1403" spans="1:2">
       <c r="A1403" s="7" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B1403" s="3" t="s">
         <v>1428</v>
@@ -19015,7 +19018,7 @@
     </row>
     <row r="1404" spans="1:2">
       <c r="A1404" s="7" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="B1404" s="3" t="s">
         <v>1428</v>
@@ -19023,7 +19026,7 @@
     </row>
     <row r="1405" spans="1:2">
       <c r="A1405" s="7" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B1405" s="3" t="s">
         <v>1428</v>
@@ -19031,7 +19034,7 @@
     </row>
     <row r="1406" spans="1:2">
       <c r="A1406" s="7" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B1406" s="3" t="s">
         <v>1428</v>
@@ -19039,7 +19042,7 @@
     </row>
     <row r="1407" spans="1:2">
       <c r="A1407" s="7" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B1407" s="3" t="s">
         <v>1428</v>
@@ -19047,7 +19050,7 @@
     </row>
     <row r="1408" spans="1:2">
       <c r="A1408" s="7" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="B1408" s="3" t="s">
         <v>1428</v>
@@ -19055,7 +19058,7 @@
     </row>
     <row r="1409" spans="1:2">
       <c r="A1409" s="7" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B1409" s="3" t="s">
         <v>1428</v>
@@ -19063,7 +19066,7 @@
     </row>
     <row r="1410" spans="1:2">
       <c r="A1410" s="7" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B1410" s="3" t="s">
         <v>1428</v>
@@ -19071,7 +19074,7 @@
     </row>
     <row r="1411" spans="1:2">
       <c r="A1411" s="7" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B1411" s="3" t="s">
         <v>1428</v>
@@ -19079,7 +19082,7 @@
     </row>
     <row r="1412" spans="1:2">
       <c r="A1412" s="7" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B1412" s="3" t="s">
         <v>1428</v>
@@ -19087,7 +19090,7 @@
     </row>
     <row r="1413" spans="1:2">
       <c r="A1413" s="7" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B1413" s="3" t="s">
         <v>1428</v>
@@ -19095,7 +19098,7 @@
     </row>
     <row r="1414" spans="1:2">
       <c r="A1414" s="7" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B1414" s="3" t="s">
         <v>1428</v>
@@ -19103,7 +19106,7 @@
     </row>
     <row r="1415" spans="1:2">
       <c r="A1415" s="7" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="B1415" s="3" t="s">
         <v>1428</v>
@@ -19111,7 +19114,7 @@
     </row>
     <row r="1416" spans="1:2">
       <c r="A1416" s="7" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="B1416" s="3" t="s">
         <v>1428</v>
@@ -19119,7 +19122,7 @@
     </row>
     <row r="1417" spans="1:2">
       <c r="A1417" s="7" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B1417" s="3" t="s">
         <v>1428</v>
@@ -19127,7 +19130,7 @@
     </row>
     <row r="1418" spans="1:2">
       <c r="A1418" s="7" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="B1418" s="3" t="s">
         <v>1428</v>
@@ -19135,7 +19138,7 @@
     </row>
     <row r="1419" spans="1:2">
       <c r="A1419" s="7" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="B1419" s="3" t="s">
         <v>1428</v>
@@ -19143,7 +19146,7 @@
     </row>
     <row r="1420" spans="1:2">
       <c r="A1420" s="7" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="B1420" s="3" t="s">
         <v>1428</v>
@@ -19151,7 +19154,7 @@
     </row>
     <row r="1421" spans="1:2">
       <c r="A1421" s="7" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="B1421" s="3" t="s">
         <v>1428</v>
@@ -19159,7 +19162,7 @@
     </row>
     <row r="1422" spans="1:2">
       <c r="A1422" s="7" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="B1422" s="3" t="s">
         <v>1428</v>
@@ -19167,7 +19170,7 @@
     </row>
     <row r="1423" spans="1:2">
       <c r="A1423" s="7" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="B1423" s="3" t="s">
         <v>1428</v>
@@ -19175,7 +19178,7 @@
     </row>
     <row r="1424" spans="1:2">
       <c r="A1424" s="7" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="B1424" s="3" t="s">
         <v>1428</v>
@@ -19183,7 +19186,7 @@
     </row>
     <row r="1425" spans="1:2">
       <c r="A1425" s="7" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="B1425" s="3" t="s">
         <v>1428</v>
@@ -19191,7 +19194,7 @@
     </row>
     <row r="1426" spans="1:2">
       <c r="A1426" s="7" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B1426" s="3" t="s">
         <v>1428</v>
@@ -19199,7 +19202,7 @@
     </row>
     <row r="1427" spans="1:2">
       <c r="A1427" s="7" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="B1427" s="3" t="s">
         <v>1428</v>
@@ -19207,7 +19210,7 @@
     </row>
     <row r="1428" spans="1:2">
       <c r="A1428" s="7" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="B1428" s="3" t="s">
         <v>1428</v>
@@ -19215,7 +19218,7 @@
     </row>
     <row r="1429" spans="1:2">
       <c r="A1429" s="7" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B1429" s="3" t="s">
         <v>1428</v>
@@ -19223,7 +19226,7 @@
     </row>
     <row r="1430" spans="1:2">
       <c r="A1430" s="7" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B1430" s="3" t="s">
         <v>1428</v>
@@ -19231,7 +19234,7 @@
     </row>
     <row r="1431" spans="1:2">
       <c r="A1431" s="7" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B1431" s="3" t="s">
         <v>1428</v>
@@ -19239,7 +19242,7 @@
     </row>
     <row r="1432" spans="1:2">
       <c r="A1432" s="7" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="B1432" s="3" t="s">
         <v>1428</v>
@@ -19247,23 +19250,23 @@
     </row>
     <row r="1433" spans="1:2">
       <c r="A1433" s="7" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B1433" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1434" spans="1:2">
-      <c r="A1434" s="10" t="s">
-        <v>1507</v>
+      <c r="A1434" s="7" t="s">
+        <v>1506</v>
       </c>
       <c r="B1434" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1435" spans="1:2">
-      <c r="A1435" s="7" t="s">
-        <v>1508</v>
+      <c r="A1435" s="10" t="s">
+        <v>1507</v>
       </c>
       <c r="B1435" s="3" t="s">
         <v>1428</v>
@@ -19271,7 +19274,7 @@
     </row>
     <row r="1436" spans="1:2">
       <c r="A1436" s="7" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B1436" s="3" t="s">
         <v>1428</v>
@@ -19279,7 +19282,7 @@
     </row>
     <row r="1437" spans="1:2">
       <c r="A1437" s="7" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B1437" s="3" t="s">
         <v>1428</v>
@@ -19287,7 +19290,7 @@
     </row>
     <row r="1438" spans="1:2">
       <c r="A1438" s="7" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B1438" s="3" t="s">
         <v>1428</v>
@@ -19295,23 +19298,23 @@
     </row>
     <row r="1439" spans="1:2">
       <c r="A1439" s="7" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B1439" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1440" spans="1:2">
-      <c r="A1440" s="9" t="s">
-        <v>1513</v>
+      <c r="A1440" s="7" t="s">
+        <v>1512</v>
       </c>
       <c r="B1440" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1441" spans="1:2">
-      <c r="A1441" s="7" t="s">
-        <v>1514</v>
+      <c r="A1441" s="9" t="s">
+        <v>1513</v>
       </c>
       <c r="B1441" s="3" t="s">
         <v>1428</v>
@@ -19319,7 +19322,7 @@
     </row>
     <row r="1442" spans="1:2">
       <c r="A1442" s="7" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="B1442" s="3" t="s">
         <v>1428</v>
@@ -19327,23 +19330,23 @@
     </row>
     <row r="1443" spans="1:2">
       <c r="A1443" s="7" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="B1443" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1444" spans="1:2">
-      <c r="A1444" s="10" t="s">
-        <v>1517</v>
+      <c r="A1444" s="7" t="s">
+        <v>1516</v>
       </c>
       <c r="B1444" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1445" spans="1:2">
-      <c r="A1445" s="7" t="s">
-        <v>1518</v>
+      <c r="A1445" s="10" t="s">
+        <v>1517</v>
       </c>
       <c r="B1445" s="3" t="s">
         <v>1428</v>
@@ -19351,7 +19354,7 @@
     </row>
     <row r="1446" spans="1:2">
       <c r="A1446" s="7" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B1446" s="3" t="s">
         <v>1428</v>
@@ -19359,7 +19362,7 @@
     </row>
     <row r="1447" spans="1:2">
       <c r="A1447" s="7" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="B1447" s="3" t="s">
         <v>1428</v>
@@ -19367,7 +19370,7 @@
     </row>
     <row r="1448" spans="1:2">
       <c r="A1448" s="7" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B1448" s="3" t="s">
         <v>1428</v>
@@ -19375,7 +19378,7 @@
     </row>
     <row r="1449" spans="1:2">
       <c r="A1449" s="7" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B1449" s="3" t="s">
         <v>1428</v>
@@ -19383,7 +19386,7 @@
     </row>
     <row r="1450" spans="1:2">
       <c r="A1450" s="7" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="B1450" s="3" t="s">
         <v>1428</v>
@@ -19391,7 +19394,7 @@
     </row>
     <row r="1451" spans="1:2">
       <c r="A1451" s="7" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="B1451" s="3" t="s">
         <v>1428</v>
@@ -19399,7 +19402,7 @@
     </row>
     <row r="1452" spans="1:2">
       <c r="A1452" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="B1452" s="3" t="s">
         <v>1428</v>
@@ -19407,7 +19410,7 @@
     </row>
     <row r="1453" spans="1:2">
       <c r="A1453" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B1453" s="3" t="s">
         <v>1428</v>
@@ -19415,7 +19418,7 @@
     </row>
     <row r="1454" spans="1:2">
       <c r="A1454" s="7" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B1454" s="3" t="s">
         <v>1428</v>
@@ -19423,7 +19426,7 @@
     </row>
     <row r="1455" spans="1:2">
       <c r="A1455" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B1455" s="3" t="s">
         <v>1428</v>
@@ -19431,7 +19434,7 @@
     </row>
     <row r="1456" spans="1:2">
       <c r="A1456" s="7" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B1456" s="3" t="s">
         <v>1428</v>
@@ -19439,7 +19442,7 @@
     </row>
     <row r="1457" spans="1:2">
       <c r="A1457" s="7" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B1457" s="3" t="s">
         <v>1428</v>
@@ -19447,7 +19450,7 @@
     </row>
     <row r="1458" spans="1:2">
       <c r="A1458" s="7" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B1458" s="3" t="s">
         <v>1428</v>
@@ -19455,7 +19458,7 @@
     </row>
     <row r="1459" spans="1:2">
       <c r="A1459" s="7" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B1459" s="3" t="s">
         <v>1428</v>
@@ -19463,23 +19466,23 @@
     </row>
     <row r="1460" spans="1:2">
       <c r="A1460" s="7" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B1460" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1461" spans="1:2">
-      <c r="A1461" s="10" t="s">
-        <v>1534</v>
+      <c r="A1461" s="7" t="s">
+        <v>1533</v>
       </c>
       <c r="B1461" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1462" spans="1:2">
-      <c r="A1462" s="7" t="s">
-        <v>1535</v>
+      <c r="A1462" s="10" t="s">
+        <v>1534</v>
       </c>
       <c r="B1462" s="3" t="s">
         <v>1428</v>
@@ -19487,7 +19490,7 @@
     </row>
     <row r="1463" spans="1:2">
       <c r="A1463" s="7" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B1463" s="3" t="s">
         <v>1428</v>
@@ -19495,7 +19498,7 @@
     </row>
     <row r="1464" spans="1:2">
       <c r="A1464" s="7" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B1464" s="3" t="s">
         <v>1428</v>
@@ -19503,7 +19506,7 @@
     </row>
     <row r="1465" spans="1:2">
       <c r="A1465" s="7" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B1465" s="3" t="s">
         <v>1428</v>
@@ -19511,7 +19514,7 @@
     </row>
     <row r="1466" spans="1:2">
       <c r="A1466" s="7" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="B1466" s="3" t="s">
         <v>1428</v>
@@ -19519,7 +19522,7 @@
     </row>
     <row r="1467" spans="1:2">
       <c r="A1467" s="7" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="B1467" s="3" t="s">
         <v>1428</v>
@@ -19527,7 +19530,7 @@
     </row>
     <row r="1468" spans="1:2">
       <c r="A1468" s="7" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B1468" s="3" t="s">
         <v>1428</v>
@@ -19535,7 +19538,7 @@
     </row>
     <row r="1469" spans="1:2">
       <c r="A1469" s="7" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B1469" s="3" t="s">
         <v>1428</v>
@@ -19543,7 +19546,7 @@
     </row>
     <row r="1470" spans="1:2">
       <c r="A1470" s="7" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="B1470" s="3" t="s">
         <v>1428</v>
@@ -19551,7 +19554,7 @@
     </row>
     <row r="1471" spans="1:2">
       <c r="A1471" s="7" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="B1471" s="3" t="s">
         <v>1428</v>
@@ -19559,7 +19562,7 @@
     </row>
     <row r="1472" spans="1:2">
       <c r="A1472" s="7" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="B1472" s="3" t="s">
         <v>1428</v>
@@ -19567,7 +19570,7 @@
     </row>
     <row r="1473" spans="1:2">
       <c r="A1473" s="7" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="B1473" s="3" t="s">
         <v>1428</v>
@@ -19575,7 +19578,7 @@
     </row>
     <row r="1474" spans="1:2">
       <c r="A1474" s="7" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B1474" s="3" t="s">
         <v>1428</v>
@@ -19583,7 +19586,7 @@
     </row>
     <row r="1475" spans="1:2">
       <c r="A1475" s="7" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="B1475" s="3" t="s">
         <v>1428</v>
@@ -19591,7 +19594,7 @@
     </row>
     <row r="1476" spans="1:2">
       <c r="A1476" s="7" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B1476" s="3" t="s">
         <v>1428</v>
@@ -19599,7 +19602,7 @@
     </row>
     <row r="1477" spans="1:2">
       <c r="A1477" s="7" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="B1477" s="3" t="s">
         <v>1428</v>
@@ -19607,7 +19610,7 @@
     </row>
     <row r="1478" spans="1:2">
       <c r="A1478" s="7" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="B1478" s="3" t="s">
         <v>1428</v>
@@ -19615,7 +19618,7 @@
     </row>
     <row r="1479" spans="1:2">
       <c r="A1479" s="7" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="B1479" s="3" t="s">
         <v>1428</v>
@@ -19623,7 +19626,7 @@
     </row>
     <row r="1480" spans="1:2">
       <c r="A1480" s="7" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B1480" s="3" t="s">
         <v>1428</v>
@@ -19631,7 +19634,7 @@
     </row>
     <row r="1481" spans="1:2">
       <c r="A1481" s="7" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B1481" s="3" t="s">
         <v>1428</v>
@@ -19639,7 +19642,7 @@
     </row>
     <row r="1482" spans="1:2">
       <c r="A1482" s="7" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="B1482" s="3" t="s">
         <v>1428</v>
@@ -19647,7 +19650,7 @@
     </row>
     <row r="1483" spans="1:2">
       <c r="A1483" s="7" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B1483" s="3" t="s">
         <v>1428</v>
@@ -19655,7 +19658,7 @@
     </row>
     <row r="1484" spans="1:2">
       <c r="A1484" s="7" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="B1484" s="3" t="s">
         <v>1428</v>
@@ -19663,7 +19666,7 @@
     </row>
     <row r="1485" spans="1:2">
       <c r="A1485" s="7" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B1485" s="3" t="s">
         <v>1428</v>
@@ -19671,7 +19674,7 @@
     </row>
     <row r="1486" spans="1:2">
       <c r="A1486" s="7" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="B1486" s="3" t="s">
         <v>1428</v>
@@ -19679,7 +19682,7 @@
     </row>
     <row r="1487" spans="1:2">
       <c r="A1487" s="7" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="B1487" s="3" t="s">
         <v>1428</v>
@@ -19687,7 +19690,7 @@
     </row>
     <row r="1488" spans="1:2">
       <c r="A1488" s="7" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B1488" s="3" t="s">
         <v>1428</v>
@@ -19695,7 +19698,7 @@
     </row>
     <row r="1489" spans="1:2">
       <c r="A1489" s="7" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="B1489" s="3" t="s">
         <v>1428</v>
@@ -19703,7 +19706,7 @@
     </row>
     <row r="1490" spans="1:2">
       <c r="A1490" s="7" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B1490" s="3" t="s">
         <v>1428</v>
@@ -19711,7 +19714,7 @@
     </row>
     <row r="1491" spans="1:2">
       <c r="A1491" s="7" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="B1491" s="3" t="s">
         <v>1428</v>
@@ -19719,7 +19722,7 @@
     </row>
     <row r="1492" spans="1:2">
       <c r="A1492" s="7" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B1492" s="3" t="s">
         <v>1428</v>
@@ -19727,7 +19730,7 @@
     </row>
     <row r="1493" spans="1:2">
       <c r="A1493" s="7" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B1493" s="3" t="s">
         <v>1428</v>
@@ -19735,7 +19738,7 @@
     </row>
     <row r="1494" spans="1:2">
       <c r="A1494" s="7" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="B1494" s="3" t="s">
         <v>1428</v>
@@ -19743,7 +19746,7 @@
     </row>
     <row r="1495" spans="1:2">
       <c r="A1495" s="7" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="B1495" s="3" t="s">
         <v>1428</v>
@@ -19751,7 +19754,7 @@
     </row>
     <row r="1496" spans="1:2">
       <c r="A1496" s="7" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B1496" s="3" t="s">
         <v>1428</v>
@@ -19759,7 +19762,7 @@
     </row>
     <row r="1497" spans="1:2">
       <c r="A1497" s="7" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="B1497" s="3" t="s">
         <v>1428</v>
@@ -19767,7 +19770,7 @@
     </row>
     <row r="1498" spans="1:2">
       <c r="A1498" s="7" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B1498" s="3" t="s">
         <v>1428</v>
@@ -19775,7 +19778,7 @@
     </row>
     <row r="1499" spans="1:2">
       <c r="A1499" s="7" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="B1499" s="3" t="s">
         <v>1428</v>
@@ -19783,7 +19786,7 @@
     </row>
     <row r="1500" spans="1:2">
       <c r="A1500" s="7" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="B1500" s="3" t="s">
         <v>1428</v>
@@ -19791,23 +19794,23 @@
     </row>
     <row r="1501" spans="1:2">
       <c r="A1501" s="7" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="B1501" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1502" spans="1:2">
-      <c r="A1502" s="14" t="s">
-        <v>1575</v>
+      <c r="A1502" s="7" t="s">
+        <v>1574</v>
       </c>
       <c r="B1502" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1503" spans="1:2">
-      <c r="A1503" s="7" t="s">
-        <v>1576</v>
+      <c r="A1503" s="14" t="s">
+        <v>1575</v>
       </c>
       <c r="B1503" s="3" t="s">
         <v>1428</v>
@@ -19815,7 +19818,7 @@
     </row>
     <row r="1504" spans="1:2">
       <c r="A1504" s="7" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="B1504" s="3" t="s">
         <v>1428</v>
@@ -19823,7 +19826,7 @@
     </row>
     <row r="1505" spans="1:2">
       <c r="A1505" s="7" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="B1505" s="3" t="s">
         <v>1428</v>
@@ -19831,31 +19834,31 @@
     </row>
     <row r="1506" spans="1:2">
       <c r="A1506" s="7" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="B1506" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1507" spans="1:2">
-      <c r="A1507" s="10" t="s">
-        <v>1580</v>
+      <c r="A1507" s="7" t="s">
+        <v>1579</v>
       </c>
       <c r="B1507" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1508" spans="1:2">
-      <c r="A1508" s="7" t="s">
-        <v>1581</v>
+      <c r="A1508" s="10" t="s">
+        <v>1580</v>
       </c>
       <c r="B1508" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1509" spans="1:2">
-      <c r="A1509" s="10" t="s">
-        <v>1582</v>
+      <c r="A1509" s="7" t="s">
+        <v>1581</v>
       </c>
       <c r="B1509" s="3" t="s">
         <v>1428</v>
@@ -19863,15 +19866,15 @@
     </row>
     <row r="1510" spans="1:2">
       <c r="A1510" s="10" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B1510" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1511" spans="1:2">
-      <c r="A1511" s="7" t="s">
-        <v>1584</v>
+      <c r="A1511" s="10" t="s">
+        <v>1583</v>
       </c>
       <c r="B1511" s="3" t="s">
         <v>1428</v>
@@ -19879,7 +19882,7 @@
     </row>
     <row r="1512" spans="1:2">
       <c r="A1512" s="7" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="B1512" s="3" t="s">
         <v>1428</v>
@@ -19887,7 +19890,7 @@
     </row>
     <row r="1513" spans="1:2">
       <c r="A1513" s="7" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="B1513" s="3" t="s">
         <v>1428</v>
@@ -19895,7 +19898,7 @@
     </row>
     <row r="1514" spans="1:2">
       <c r="A1514" s="7" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="B1514" s="3" t="s">
         <v>1428</v>
@@ -19903,7 +19906,7 @@
     </row>
     <row r="1515" spans="1:2">
       <c r="A1515" s="7" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B1515" s="3" t="s">
         <v>1428</v>
@@ -19911,7 +19914,7 @@
     </row>
     <row r="1516" spans="1:2">
       <c r="A1516" s="7" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B1516" s="3" t="s">
         <v>1428</v>
@@ -19919,7 +19922,7 @@
     </row>
     <row r="1517" spans="1:2">
       <c r="A1517" s="7" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="B1517" s="3" t="s">
         <v>1428</v>
@@ -19927,7 +19930,7 @@
     </row>
     <row r="1518" spans="1:2">
       <c r="A1518" s="7" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B1518" s="3" t="s">
         <v>1428</v>
@@ -19935,7 +19938,7 @@
     </row>
     <row r="1519" spans="1:2">
       <c r="A1519" s="7" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="B1519" s="3" t="s">
         <v>1428</v>
@@ -19943,7 +19946,7 @@
     </row>
     <row r="1520" spans="1:2">
       <c r="A1520" s="7" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B1520" s="3" t="s">
         <v>1428</v>
@@ -19951,7 +19954,7 @@
     </row>
     <row r="1521" spans="1:2">
       <c r="A1521" s="7" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="B1521" s="3" t="s">
         <v>1428</v>
@@ -19959,7 +19962,7 @@
     </row>
     <row r="1522" spans="1:2">
       <c r="A1522" s="7" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="B1522" s="3" t="s">
         <v>1428</v>
@@ -19967,7 +19970,7 @@
     </row>
     <row r="1523" spans="1:2">
       <c r="A1523" s="7" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="B1523" s="3" t="s">
         <v>1428</v>
@@ -19975,7 +19978,7 @@
     </row>
     <row r="1524" spans="1:2">
       <c r="A1524" s="7" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="B1524" s="3" t="s">
         <v>1428</v>
@@ -19983,7 +19986,7 @@
     </row>
     <row r="1525" spans="1:2">
       <c r="A1525" s="7" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="B1525" s="3" t="s">
         <v>1428</v>
@@ -19991,23 +19994,23 @@
     </row>
     <row r="1526" spans="1:2">
       <c r="A1526" s="7" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="B1526" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1527" spans="1:2">
-      <c r="A1527" s="13" t="s">
-        <v>1600</v>
+      <c r="A1527" s="7" t="s">
+        <v>1599</v>
       </c>
       <c r="B1527" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1528" spans="1:2">
-      <c r="A1528" s="7" t="s">
-        <v>1601</v>
+      <c r="A1528" s="13" t="s">
+        <v>1600</v>
       </c>
       <c r="B1528" s="3" t="s">
         <v>1428</v>
@@ -20015,7 +20018,7 @@
     </row>
     <row r="1529" spans="1:2">
       <c r="A1529" s="7" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B1529" s="3" t="s">
         <v>1428</v>
@@ -20023,7 +20026,7 @@
     </row>
     <row r="1530" spans="1:2">
       <c r="A1530" s="7" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="B1530" s="3" t="s">
         <v>1428</v>
@@ -20031,7 +20034,7 @@
     </row>
     <row r="1531" spans="1:2">
       <c r="A1531" s="7" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="B1531" s="3" t="s">
         <v>1428</v>
@@ -20039,7 +20042,7 @@
     </row>
     <row r="1532" spans="1:2">
       <c r="A1532" s="7" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="B1532" s="3" t="s">
         <v>1428</v>
@@ -20047,7 +20050,7 @@
     </row>
     <row r="1533" spans="1:2">
       <c r="A1533" s="7" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B1533" s="3" t="s">
         <v>1428</v>
@@ -20055,7 +20058,7 @@
     </row>
     <row r="1534" spans="1:2">
       <c r="A1534" s="7" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="B1534" s="3" t="s">
         <v>1428</v>
@@ -20063,7 +20066,7 @@
     </row>
     <row r="1535" spans="1:2">
       <c r="A1535" s="7" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="B1535" s="3" t="s">
         <v>1428</v>
@@ -20071,7 +20074,7 @@
     </row>
     <row r="1536" spans="1:2">
       <c r="A1536" s="7" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="B1536" s="3" t="s">
         <v>1428</v>
@@ -20079,7 +20082,7 @@
     </row>
     <row r="1537" spans="1:2">
       <c r="A1537" s="7" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="B1537" s="3" t="s">
         <v>1428</v>
@@ -20087,7 +20090,7 @@
     </row>
     <row r="1538" spans="1:2">
       <c r="A1538" s="7" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="B1538" s="3" t="s">
         <v>1428</v>
@@ -20095,7 +20098,7 @@
     </row>
     <row r="1539" spans="1:2">
       <c r="A1539" s="7" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="B1539" s="3" t="s">
         <v>1428</v>
@@ -20103,7 +20106,7 @@
     </row>
     <row r="1540" spans="1:2">
       <c r="A1540" s="7" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="B1540" s="3" t="s">
         <v>1428</v>
@@ -20111,7 +20114,7 @@
     </row>
     <row r="1541" spans="1:2">
       <c r="A1541" s="7" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="B1541" s="3" t="s">
         <v>1428</v>
@@ -20119,23 +20122,23 @@
     </row>
     <row r="1542" spans="1:2">
       <c r="A1542" s="7" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="B1542" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1543" spans="1:2">
-      <c r="A1543" s="13" t="s">
-        <v>1616</v>
+      <c r="A1543" s="7" t="s">
+        <v>1615</v>
       </c>
       <c r="B1543" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1544" spans="1:2">
-      <c r="A1544" s="7" t="s">
-        <v>1617</v>
+      <c r="A1544" s="13" t="s">
+        <v>1616</v>
       </c>
       <c r="B1544" s="3" t="s">
         <v>1428</v>
@@ -20143,7 +20146,7 @@
     </row>
     <row r="1545" spans="1:2">
       <c r="A1545" s="7" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="B1545" s="3" t="s">
         <v>1428</v>
@@ -20151,7 +20154,7 @@
     </row>
     <row r="1546" spans="1:2">
       <c r="A1546" s="7" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="B1546" s="3" t="s">
         <v>1428</v>
@@ -20159,7 +20162,7 @@
     </row>
     <row r="1547" spans="1:2">
       <c r="A1547" s="7" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B1547" s="3" t="s">
         <v>1428</v>
@@ -20167,7 +20170,7 @@
     </row>
     <row r="1548" spans="1:2">
       <c r="A1548" s="7" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="B1548" s="3" t="s">
         <v>1428</v>
@@ -20175,31 +20178,31 @@
     </row>
     <row r="1549" spans="1:2">
       <c r="A1549" s="7" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="B1549" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1550" spans="1:2">
-      <c r="A1550" s="13" t="s">
-        <v>1623</v>
+      <c r="A1550" s="7" t="s">
+        <v>1622</v>
       </c>
       <c r="B1550" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1551" spans="1:2">
-      <c r="A1551" s="10" t="s">
-        <v>1624</v>
+      <c r="A1551" s="13" t="s">
+        <v>1623</v>
       </c>
       <c r="B1551" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1552" spans="1:2">
-      <c r="A1552" s="7" t="s">
-        <v>1625</v>
+      <c r="A1552" s="10" t="s">
+        <v>1624</v>
       </c>
       <c r="B1552" s="3" t="s">
         <v>1428</v>
@@ -20207,7 +20210,7 @@
     </row>
     <row r="1553" spans="1:2">
       <c r="A1553" s="7" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="B1553" s="3" t="s">
         <v>1428</v>
@@ -20215,7 +20218,7 @@
     </row>
     <row r="1554" spans="1:2">
       <c r="A1554" s="7" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="B1554" s="3" t="s">
         <v>1428</v>
@@ -20223,7 +20226,7 @@
     </row>
     <row r="1555" spans="1:2">
       <c r="A1555" s="7" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B1555" s="3" t="s">
         <v>1428</v>
@@ -20231,7 +20234,7 @@
     </row>
     <row r="1556" spans="1:2">
       <c r="A1556" s="7" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="B1556" s="3" t="s">
         <v>1428</v>
@@ -20239,7 +20242,7 @@
     </row>
     <row r="1557" spans="1:2">
       <c r="A1557" s="7" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="B1557" s="3" t="s">
         <v>1428</v>
@@ -20247,15 +20250,15 @@
     </row>
     <row r="1558" spans="1:2">
       <c r="A1558" s="7" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="B1558" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1559" spans="1:2">
-      <c r="A1559" s="10" t="s">
-        <v>1632</v>
+      <c r="A1559" s="7" t="s">
+        <v>1631</v>
       </c>
       <c r="B1559" s="3" t="s">
         <v>1428</v>
@@ -20263,7 +20266,7 @@
     </row>
     <row r="1560" spans="1:2">
       <c r="A1560" s="10" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B1560" s="3" t="s">
         <v>1428</v>
@@ -20271,15 +20274,15 @@
     </row>
     <row r="1561" spans="1:2">
       <c r="A1561" s="10" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B1561" s="3" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="1562" spans="1:2">
-      <c r="A1562" s="7" t="s">
-        <v>1635</v>
+      <c r="A1562" s="10" t="s">
+        <v>1634</v>
       </c>
       <c r="B1562" s="3" t="s">
         <v>1428</v>
@@ -20287,7 +20290,7 @@
     </row>
     <row r="1563" spans="1:2">
       <c r="A1563" s="7" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="B1563" s="3" t="s">
         <v>1428</v>
@@ -20295,7 +20298,7 @@
     </row>
     <row r="1564" spans="1:2">
       <c r="A1564" s="7" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="B1564" s="3" t="s">
         <v>1428</v>
@@ -20303,7 +20306,7 @@
     </row>
     <row r="1565" spans="1:2">
       <c r="A1565" s="7" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="B1565" s="3" t="s">
         <v>1428</v>
@@ -20311,7 +20314,7 @@
     </row>
     <row r="1566" spans="1:2">
       <c r="A1566" s="7" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="B1566" s="3" t="s">
         <v>1428</v>
@@ -20319,7 +20322,7 @@
     </row>
     <row r="1567" spans="1:2">
       <c r="A1567" s="7" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="B1567" s="3" t="s">
         <v>1428</v>
@@ -20327,7 +20330,7 @@
     </row>
     <row r="1568" spans="1:2">
       <c r="A1568" s="7" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="B1568" s="3" t="s">
         <v>1428</v>
@@ -20335,7 +20338,7 @@
     </row>
     <row r="1569" spans="1:2">
       <c r="A1569" s="7" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="B1569" s="3" t="s">
         <v>1428</v>
@@ -20343,7 +20346,7 @@
     </row>
     <row r="1570" spans="1:2">
       <c r="A1570" s="7" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="B1570" s="3" t="s">
         <v>1428</v>
@@ -20351,7 +20354,7 @@
     </row>
     <row r="1571" spans="1:2">
       <c r="A1571" s="7" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="B1571" s="3" t="s">
         <v>1428</v>
@@ -20359,7 +20362,7 @@
     </row>
     <row r="1572" spans="1:2">
       <c r="A1572" s="7" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="B1572" s="3" t="s">
         <v>1428</v>
@@ -20367,15 +20370,15 @@
     </row>
     <row r="1573" spans="1:2">
       <c r="A1573" s="7" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="B1573" s="3" t="s">
-        <v>1647</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1574" spans="1:2">
       <c r="A1574" s="7" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="B1574" s="3" t="s">
         <v>1647</v>
@@ -20383,7 +20386,7 @@
     </row>
     <row r="1575" spans="1:2">
       <c r="A1575" s="7" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="B1575" s="3" t="s">
         <v>1647</v>
@@ -20391,15 +20394,15 @@
     </row>
     <row r="1576" spans="1:2">
       <c r="A1576" s="7" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="B1576" s="3" t="s">
-        <v>1651</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="1577" spans="1:2">
       <c r="A1577" s="7" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="B1577" s="3" t="s">
         <v>1651</v>
@@ -20407,15 +20410,15 @@
     </row>
     <row r="1578" spans="1:2">
       <c r="A1578" s="7" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="B1578" s="3" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="1579" spans="1:2">
       <c r="A1579" s="7" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="B1579" s="3" t="s">
         <v>1654</v>
@@ -20423,7 +20426,7 @@
     </row>
     <row r="1580" spans="1:2">
       <c r="A1580" s="7" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="B1580" s="3" t="s">
         <v>1654</v>
@@ -20431,7 +20434,7 @@
     </row>
     <row r="1581" spans="1:2">
       <c r="A1581" s="7" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="B1581" s="3" t="s">
         <v>1654</v>
@@ -20439,15 +20442,15 @@
     </row>
     <row r="1582" spans="1:2">
       <c r="A1582" s="7" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="B1582" s="3" t="s">
-        <v>1659</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="1583" spans="1:2">
       <c r="A1583" s="7" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="B1583" s="3" t="s">
         <v>1659</v>
@@ -20455,7 +20458,7 @@
     </row>
     <row r="1584" spans="1:2">
       <c r="A1584" s="7" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="B1584" s="3" t="s">
         <v>1659</v>
@@ -20463,7 +20466,7 @@
     </row>
     <row r="1585" spans="1:2">
       <c r="A1585" s="7" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="B1585" s="3" t="s">
         <v>1659</v>
@@ -20471,7 +20474,7 @@
     </row>
     <row r="1586" spans="1:2">
       <c r="A1586" s="7" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="B1586" s="3" t="s">
         <v>1659</v>
@@ -20479,7 +20482,7 @@
     </row>
     <row r="1587" spans="1:2">
       <c r="A1587" s="7" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="B1587" s="3" t="s">
         <v>1659</v>
@@ -20487,7 +20490,7 @@
     </row>
     <row r="1588" spans="1:2">
       <c r="A1588" s="7" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="B1588" s="3" t="s">
         <v>1659</v>
@@ -20495,7 +20498,7 @@
     </row>
     <row r="1589" spans="1:2">
       <c r="A1589" s="7" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="B1589" s="3" t="s">
         <v>1659</v>
@@ -20503,7 +20506,7 @@
     </row>
     <row r="1590" spans="1:2">
       <c r="A1590" s="7" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="B1590" s="3" t="s">
         <v>1659</v>
@@ -20511,7 +20514,7 @@
     </row>
     <row r="1591" spans="1:2">
       <c r="A1591" s="7" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="B1591" s="3" t="s">
         <v>1659</v>
@@ -20519,7 +20522,7 @@
     </row>
     <row r="1592" spans="1:2">
       <c r="A1592" s="7" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="B1592" s="3" t="s">
         <v>1659</v>
@@ -20527,7 +20530,7 @@
     </row>
     <row r="1593" spans="1:2">
       <c r="A1593" s="7" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="B1593" s="3" t="s">
         <v>1659</v>
@@ -20535,7 +20538,7 @@
     </row>
     <row r="1594" spans="1:2">
       <c r="A1594" s="7" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="B1594" s="3" t="s">
         <v>1659</v>
@@ -20543,7 +20546,7 @@
     </row>
     <row r="1595" spans="1:2">
       <c r="A1595" s="7" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="B1595" s="3" t="s">
         <v>1659</v>
@@ -20551,7 +20554,7 @@
     </row>
     <row r="1596" spans="1:2">
       <c r="A1596" s="7" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="B1596" s="3" t="s">
         <v>1659</v>
@@ -20559,7 +20562,7 @@
     </row>
     <row r="1597" spans="1:2">
       <c r="A1597" s="7" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="B1597" s="3" t="s">
         <v>1659</v>
@@ -20567,7 +20570,7 @@
     </row>
     <row r="1598" spans="1:2">
       <c r="A1598" s="7" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="B1598" s="3" t="s">
         <v>1659</v>
@@ -20575,23 +20578,23 @@
     </row>
     <row r="1599" spans="1:2">
       <c r="A1599" s="7" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="B1599" s="3" t="s">
         <v>1659</v>
       </c>
     </row>
     <row r="1600" spans="1:2">
-      <c r="A1600" s="14" t="s">
-        <v>1677</v>
+      <c r="A1600" s="7" t="s">
+        <v>1676</v>
       </c>
       <c r="B1600" s="3" t="s">
         <v>1659</v>
       </c>
     </row>
     <row r="1601" spans="1:2">
-      <c r="A1601" s="7" t="s">
-        <v>1678</v>
+      <c r="A1601" s="14" t="s">
+        <v>1677</v>
       </c>
       <c r="B1601" s="3" t="s">
         <v>1659</v>
@@ -20599,7 +20602,7 @@
     </row>
     <row r="1602" spans="1:2">
       <c r="A1602" s="7" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="B1602" s="3" t="s">
         <v>1659</v>
@@ -20607,7 +20610,7 @@
     </row>
     <row r="1603" spans="1:2">
       <c r="A1603" s="7" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="B1603" s="3" t="s">
         <v>1659</v>
@@ -20615,7 +20618,7 @@
     </row>
     <row r="1604" spans="1:2">
       <c r="A1604" s="7" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="B1604" s="3" t="s">
         <v>1659</v>
@@ -20623,7 +20626,7 @@
     </row>
     <row r="1605" spans="1:2">
       <c r="A1605" s="7" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="B1605" s="3" t="s">
         <v>1659</v>
@@ -20631,7 +20634,7 @@
     </row>
     <row r="1606" spans="1:2">
       <c r="A1606" s="7" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="B1606" s="3" t="s">
         <v>1659</v>
@@ -20639,7 +20642,7 @@
     </row>
     <row r="1607" spans="1:2">
       <c r="A1607" s="7" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="B1607" s="3" t="s">
         <v>1659</v>
@@ -20647,7 +20650,7 @@
     </row>
     <row r="1608" spans="1:2">
       <c r="A1608" s="7" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B1608" s="3" t="s">
         <v>1659</v>
@@ -20655,7 +20658,7 @@
     </row>
     <row r="1609" spans="1:2">
       <c r="A1609" s="7" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="B1609" s="3" t="s">
         <v>1659</v>
@@ -20663,7 +20666,7 @@
     </row>
     <row r="1610" spans="1:2">
       <c r="A1610" s="7" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="B1610" s="3" t="s">
         <v>1659</v>
@@ -20671,23 +20674,23 @@
     </row>
     <row r="1611" spans="1:2">
       <c r="A1611" s="7" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="B1611" s="3" t="s">
         <v>1659</v>
       </c>
     </row>
     <row r="1612" spans="1:2">
-      <c r="A1612" s="13" t="s">
-        <v>1689</v>
+      <c r="A1612" s="7" t="s">
+        <v>1688</v>
       </c>
       <c r="B1612" s="3" t="s">
         <v>1659</v>
       </c>
     </row>
     <row r="1613" spans="1:2">
-      <c r="A1613" s="7" t="s">
-        <v>1690</v>
+      <c r="A1613" s="13" t="s">
+        <v>1689</v>
       </c>
       <c r="B1613" s="3" t="s">
         <v>1659</v>
@@ -20695,7 +20698,7 @@
     </row>
     <row r="1614" spans="1:2">
       <c r="A1614" s="7" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="B1614" s="3" t="s">
         <v>1659</v>
@@ -20703,7 +20706,7 @@
     </row>
     <row r="1615" spans="1:2">
       <c r="A1615" s="7" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="B1615" s="3" t="s">
         <v>1659</v>
@@ -20711,7 +20714,7 @@
     </row>
     <row r="1616" spans="1:2">
       <c r="A1616" s="7" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="B1616" s="3" t="s">
         <v>1659</v>
@@ -20719,7 +20722,7 @@
     </row>
     <row r="1617" spans="1:2">
       <c r="A1617" s="7" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B1617" s="3" t="s">
         <v>1659</v>
@@ -20727,7 +20730,7 @@
     </row>
     <row r="1618" spans="1:2">
       <c r="A1618" s="7" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="B1618" s="3" t="s">
         <v>1659</v>
@@ -20735,7 +20738,7 @@
     </row>
     <row r="1619" spans="1:2">
       <c r="A1619" s="7" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="B1619" s="3" t="s">
         <v>1659</v>
@@ -20743,7 +20746,7 @@
     </row>
     <row r="1620" spans="1:2">
       <c r="A1620" s="7" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="B1620" s="3" t="s">
         <v>1659</v>
@@ -20751,7 +20754,7 @@
     </row>
     <row r="1621" spans="1:2">
       <c r="A1621" s="7" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="B1621" s="3" t="s">
         <v>1659</v>
@@ -20759,15 +20762,15 @@
     </row>
     <row r="1622" spans="1:2">
       <c r="A1622" s="7" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="B1622" s="3" t="s">
         <v>1659</v>
       </c>
     </row>
     <row r="1623" spans="1:2">
-      <c r="A1623" s="9" t="s">
-        <v>1700</v>
+      <c r="A1623" s="7" t="s">
+        <v>1699</v>
       </c>
       <c r="B1623" s="3" t="s">
         <v>1659</v>
@@ -20775,15 +20778,15 @@
     </row>
     <row r="1624" spans="1:2">
       <c r="A1624" s="9" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="B1624" s="3" t="s">
         <v>1659</v>
       </c>
     </row>
     <row r="1625" spans="1:2">
-      <c r="A1625" s="7" t="s">
-        <v>1702</v>
+      <c r="A1625" s="9" t="s">
+        <v>1701</v>
       </c>
       <c r="B1625" s="3" t="s">
         <v>1659</v>
@@ -20791,7 +20794,7 @@
     </row>
     <row r="1626" spans="1:2">
       <c r="A1626" s="7" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="B1626" s="3" t="s">
         <v>1659</v>
@@ -20799,7 +20802,7 @@
     </row>
     <row r="1627" spans="1:2">
       <c r="A1627" s="7" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="B1627" s="3" t="s">
         <v>1659</v>
@@ -20807,7 +20810,7 @@
     </row>
     <row r="1628" spans="1:2">
       <c r="A1628" s="7" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="B1628" s="3" t="s">
         <v>1659</v>
@@ -20815,7 +20818,7 @@
     </row>
     <row r="1629" spans="1:2">
       <c r="A1629" s="7" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="B1629" s="3" t="s">
         <v>1659</v>
@@ -20823,7 +20826,7 @@
     </row>
     <row r="1630" spans="1:2">
       <c r="A1630" s="7" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="B1630" s="3" t="s">
         <v>1659</v>
@@ -20831,7 +20834,7 @@
     </row>
     <row r="1631" spans="1:2">
       <c r="A1631" s="7" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="B1631" s="3" t="s">
         <v>1659</v>
@@ -20839,7 +20842,7 @@
     </row>
     <row r="1632" spans="1:2">
       <c r="A1632" s="7" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="B1632" s="3" t="s">
         <v>1659</v>
@@ -20847,7 +20850,7 @@
     </row>
     <row r="1633" spans="1:2">
       <c r="A1633" s="7" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="B1633" s="3" t="s">
         <v>1659</v>
@@ -20855,7 +20858,7 @@
     </row>
     <row r="1634" spans="1:2">
       <c r="A1634" s="7" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="B1634" s="3" t="s">
         <v>1659</v>
@@ -20863,7 +20866,7 @@
     </row>
     <row r="1635" spans="1:2">
       <c r="A1635" s="7" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="B1635" s="3" t="s">
         <v>1659</v>
@@ -20871,7 +20874,7 @@
     </row>
     <row r="1636" spans="1:2">
       <c r="A1636" s="7" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="B1636" s="3" t="s">
         <v>1659</v>
@@ -20879,7 +20882,7 @@
     </row>
     <row r="1637" spans="1:2">
       <c r="A1637" s="7" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="B1637" s="3" t="s">
         <v>1659</v>
@@ -20887,7 +20890,7 @@
     </row>
     <row r="1638" spans="1:2">
       <c r="A1638" s="7" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="B1638" s="3" t="s">
         <v>1659</v>
@@ -20895,7 +20898,7 @@
     </row>
     <row r="1639" spans="1:2">
       <c r="A1639" s="7" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="B1639" s="3" t="s">
         <v>1659</v>
@@ -20903,23 +20906,23 @@
     </row>
     <row r="1640" spans="1:2">
       <c r="A1640" s="7" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="B1640" s="3" t="s">
         <v>1659</v>
       </c>
     </row>
     <row r="1641" spans="1:2">
-      <c r="A1641" s="14" t="s">
+      <c r="A1641" s="7" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B1641" s="3" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:2">
+      <c r="A1642" s="14" t="s">
         <v>1718</v>
-      </c>
-      <c r="B1641" s="3" t="s">
-        <v>1719</v>
-      </c>
-    </row>
-    <row r="1642" spans="1:2">
-      <c r="A1642" s="10" t="s">
-        <v>1720</v>
       </c>
       <c r="B1642" s="3" t="s">
         <v>1719</v>
@@ -20927,23 +20930,23 @@
     </row>
     <row r="1643" spans="1:2">
       <c r="A1643" s="10" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="B1643" s="3" t="s">
         <v>1719</v>
       </c>
     </row>
     <row r="1644" spans="1:2">
-      <c r="A1644" s="13" t="s">
-        <v>1722</v>
+      <c r="A1644" s="10" t="s">
+        <v>1721</v>
       </c>
       <c r="B1644" s="3" t="s">
         <v>1719</v>
       </c>
     </row>
     <row r="1645" spans="1:2">
-      <c r="A1645" s="7" t="s">
-        <v>1723</v>
+      <c r="A1645" s="13" t="s">
+        <v>1722</v>
       </c>
       <c r="B1645" s="3" t="s">
         <v>1719</v>
@@ -20951,7 +20954,7 @@
     </row>
     <row r="1646" spans="1:2">
       <c r="A1646" s="7" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="B1646" s="3" t="s">
         <v>1719</v>
@@ -20959,7 +20962,7 @@
     </row>
     <row r="1647" spans="1:2">
       <c r="A1647" s="7" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="B1647" s="3" t="s">
         <v>1719</v>
@@ -20967,7 +20970,7 @@
     </row>
     <row r="1648" spans="1:2">
       <c r="A1648" s="7" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="B1648" s="3" t="s">
         <v>1719</v>
@@ -20975,31 +20978,31 @@
     </row>
     <row r="1649" spans="1:2">
       <c r="A1649" s="7" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="B1649" s="3" t="s">
-        <v>1728</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1650" spans="1:2">
       <c r="A1650" s="7" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="B1650" s="3" t="s">
         <v>1728</v>
       </c>
     </row>
     <row r="1651" spans="1:2">
-      <c r="A1651" s="9" t="s">
+      <c r="A1651" s="7" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B1651" s="3" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:2">
+      <c r="A1652" s="9" t="s">
         <v>1730</v>
-      </c>
-      <c r="B1651" s="3" t="s">
-        <v>1731</v>
-      </c>
-    </row>
-    <row r="1652" spans="1:2">
-      <c r="A1652" s="7" t="s">
-        <v>1732</v>
       </c>
       <c r="B1652" s="3" t="s">
         <v>1731</v>
@@ -21007,7 +21010,7 @@
     </row>
     <row r="1653" spans="1:2">
       <c r="A1653" s="7" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="B1653" s="3" t="s">
         <v>1731</v>
@@ -21015,7 +21018,7 @@
     </row>
     <row r="1654" spans="1:2">
       <c r="A1654" s="7" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="B1654" s="3" t="s">
         <v>1731</v>
@@ -21023,7 +21026,7 @@
     </row>
     <row r="1655" spans="1:2">
       <c r="A1655" s="7" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="B1655" s="3" t="s">
         <v>1731</v>
@@ -21031,39 +21034,39 @@
     </row>
     <row r="1656" spans="1:2">
       <c r="A1656" s="7" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="B1656" s="3" t="s">
         <v>1731</v>
       </c>
     </row>
     <row r="1657" spans="1:2">
-      <c r="A1657" s="13" t="s">
-        <v>1737</v>
+      <c r="A1657" s="7" t="s">
+        <v>1736</v>
       </c>
       <c r="B1657" s="3" t="s">
         <v>1731</v>
       </c>
     </row>
     <row r="1658" spans="1:2">
-      <c r="A1658" s="7" t="s">
-        <v>1738</v>
+      <c r="A1658" s="13" t="s">
+        <v>1737</v>
       </c>
       <c r="B1658" s="3" t="s">
         <v>1731</v>
       </c>
     </row>
     <row r="1659" spans="1:2">
-      <c r="A1659" s="10" t="s">
-        <v>1739</v>
+      <c r="A1659" s="7" t="s">
+        <v>1738</v>
       </c>
       <c r="B1659" s="3" t="s">
         <v>1731</v>
       </c>
     </row>
     <row r="1660" spans="1:2">
-      <c r="A1660" s="7" t="s">
-        <v>1740</v>
+      <c r="A1660" s="10" t="s">
+        <v>1739</v>
       </c>
       <c r="B1660" s="3" t="s">
         <v>1731</v>
@@ -21071,7 +21074,7 @@
     </row>
     <row r="1661" spans="1:2">
       <c r="A1661" s="7" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="B1661" s="3" t="s">
         <v>1731</v>
@@ -21079,7 +21082,7 @@
     </row>
     <row r="1662" spans="1:2">
       <c r="A1662" s="7" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="B1662" s="3" t="s">
         <v>1731</v>
@@ -21087,7 +21090,7 @@
     </row>
     <row r="1663" spans="1:2">
       <c r="A1663" s="7" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B1663" s="3" t="s">
         <v>1731</v>
@@ -21095,7 +21098,7 @@
     </row>
     <row r="1664" spans="1:2">
       <c r="A1664" s="7" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="B1664" s="3" t="s">
         <v>1731</v>
@@ -21103,7 +21106,7 @@
     </row>
     <row r="1665" spans="1:2">
       <c r="A1665" s="7" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="B1665" s="3" t="s">
         <v>1731</v>
@@ -21111,7 +21114,7 @@
     </row>
     <row r="1666" spans="1:2">
       <c r="A1666" s="7" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="B1666" s="3" t="s">
         <v>1731</v>
@@ -21119,7 +21122,7 @@
     </row>
     <row r="1667" spans="1:2">
       <c r="A1667" s="7" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="B1667" s="3" t="s">
         <v>1731</v>
@@ -21127,7 +21130,7 @@
     </row>
     <row r="1668" spans="1:2">
       <c r="A1668" s="7" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B1668" s="3" t="s">
         <v>1731</v>
@@ -21135,7 +21138,7 @@
     </row>
     <row r="1669" spans="1:2">
       <c r="A1669" s="7" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="B1669" s="3" t="s">
         <v>1731</v>
@@ -21143,7 +21146,7 @@
     </row>
     <row r="1670" spans="1:2">
       <c r="A1670" s="7" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="B1670" s="3" t="s">
         <v>1731</v>
@@ -21151,7 +21154,7 @@
     </row>
     <row r="1671" spans="1:2">
       <c r="A1671" s="7" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="B1671" s="3" t="s">
         <v>1731</v>
@@ -21159,7 +21162,7 @@
     </row>
     <row r="1672" spans="1:2">
       <c r="A1672" s="7" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="B1672" s="3" t="s">
         <v>1731</v>
@@ -21167,7 +21170,7 @@
     </row>
     <row r="1673" spans="1:2">
       <c r="A1673" s="7" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="B1673" s="3" t="s">
         <v>1731</v>
@@ -21175,7 +21178,7 @@
     </row>
     <row r="1674" spans="1:2">
       <c r="A1674" s="7" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="B1674" s="3" t="s">
         <v>1731</v>
@@ -21183,7 +21186,7 @@
     </row>
     <row r="1675" spans="1:2">
       <c r="A1675" s="7" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="B1675" s="3" t="s">
         <v>1731</v>
@@ -21191,7 +21194,7 @@
     </row>
     <row r="1676" spans="1:2">
       <c r="A1676" s="7" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="B1676" s="3" t="s">
         <v>1731</v>
@@ -21199,7 +21202,7 @@
     </row>
     <row r="1677" spans="1:2">
       <c r="A1677" s="7" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="B1677" s="3" t="s">
         <v>1731</v>
@@ -21207,7 +21210,7 @@
     </row>
     <row r="1678" spans="1:2">
       <c r="A1678" s="7" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="B1678" s="3" t="s">
         <v>1731</v>
@@ -21215,7 +21218,7 @@
     </row>
     <row r="1679" spans="1:2">
       <c r="A1679" s="7" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="B1679" s="3" t="s">
         <v>1731</v>
@@ -21223,7 +21226,7 @@
     </row>
     <row r="1680" spans="1:2">
       <c r="A1680" s="7" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="B1680" s="3" t="s">
         <v>1731</v>
@@ -21231,39 +21234,39 @@
     </row>
     <row r="1681" spans="1:2">
       <c r="A1681" s="7" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="B1681" s="3" t="s">
         <v>1731</v>
       </c>
     </row>
     <row r="1682" spans="1:2">
-      <c r="A1682" s="10" t="s">
-        <v>1762</v>
+      <c r="A1682" s="7" t="s">
+        <v>1761</v>
       </c>
       <c r="B1682" s="3" t="s">
         <v>1731</v>
       </c>
     </row>
     <row r="1683" spans="1:2">
-      <c r="A1683" s="7" t="s">
-        <v>1763</v>
+      <c r="A1683" s="10" t="s">
+        <v>1762</v>
       </c>
       <c r="B1683" s="3" t="s">
         <v>1731</v>
       </c>
     </row>
     <row r="1684" spans="1:2">
-      <c r="A1684" s="10" t="s">
-        <v>1764</v>
+      <c r="A1684" s="7" t="s">
+        <v>1763</v>
       </c>
       <c r="B1684" s="3" t="s">
         <v>1731</v>
       </c>
     </row>
     <row r="1685" spans="1:2">
-      <c r="A1685" s="7" t="s">
-        <v>1765</v>
+      <c r="A1685" s="10" t="s">
+        <v>1764</v>
       </c>
       <c r="B1685" s="3" t="s">
         <v>1731</v>
@@ -21271,7 +21274,7 @@
     </row>
     <row r="1686" spans="1:2">
       <c r="A1686" s="7" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B1686" s="3" t="s">
         <v>1731</v>
@@ -21279,7 +21282,7 @@
     </row>
     <row r="1687" spans="1:2">
       <c r="A1687" s="7" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B1687" s="3" t="s">
         <v>1731</v>
@@ -21287,7 +21290,7 @@
     </row>
     <row r="1688" spans="1:2">
       <c r="A1688" s="7" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="B1688" s="3" t="s">
         <v>1731</v>
@@ -21295,7 +21298,7 @@
     </row>
     <row r="1689" spans="1:2">
       <c r="A1689" s="7" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="B1689" s="3" t="s">
         <v>1731</v>
@@ -21303,7 +21306,7 @@
     </row>
     <row r="1690" spans="1:2">
       <c r="A1690" s="7" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="B1690" s="3" t="s">
         <v>1731</v>
@@ -21311,23 +21314,23 @@
     </row>
     <row r="1691" spans="1:2">
       <c r="A1691" s="7" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="B1691" s="3" t="s">
         <v>1731</v>
       </c>
     </row>
     <row r="1692" spans="1:2">
-      <c r="A1692" s="10" t="s">
-        <v>1772</v>
+      <c r="A1692" s="7" t="s">
+        <v>1771</v>
       </c>
       <c r="B1692" s="3" t="s">
         <v>1731</v>
       </c>
     </row>
     <row r="1693" spans="1:2">
-      <c r="A1693" s="7" t="s">
-        <v>1773</v>
+      <c r="A1693" s="10" t="s">
+        <v>1772</v>
       </c>
       <c r="B1693" s="3" t="s">
         <v>1731</v>
@@ -21335,7 +21338,7 @@
     </row>
     <row r="1694" spans="1:2">
       <c r="A1694" s="7" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="B1694" s="3" t="s">
         <v>1731</v>
@@ -21343,7 +21346,7 @@
     </row>
     <row r="1695" spans="1:2">
       <c r="A1695" s="7" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B1695" s="3" t="s">
         <v>1731</v>
@@ -21351,7 +21354,7 @@
     </row>
     <row r="1696" spans="1:2">
       <c r="A1696" s="7" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="B1696" s="3" t="s">
         <v>1731</v>
@@ -21359,7 +21362,7 @@
     </row>
     <row r="1697" spans="1:2">
       <c r="A1697" s="7" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="B1697" s="3" t="s">
         <v>1731</v>
@@ -21367,7 +21370,7 @@
     </row>
     <row r="1698" spans="1:2">
       <c r="A1698" s="7" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="B1698" s="3" t="s">
         <v>1731</v>
@@ -21375,7 +21378,7 @@
     </row>
     <row r="1699" spans="1:2">
       <c r="A1699" s="7" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="B1699" s="3" t="s">
         <v>1731</v>
@@ -21383,7 +21386,7 @@
     </row>
     <row r="1700" spans="1:2">
       <c r="A1700" s="7" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="B1700" s="3" t="s">
         <v>1731</v>
@@ -21391,7 +21394,7 @@
     </row>
     <row r="1701" spans="1:2">
       <c r="A1701" s="7" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="B1701" s="3" t="s">
         <v>1731</v>
@@ -21399,7 +21402,7 @@
     </row>
     <row r="1702" spans="1:2">
       <c r="A1702" s="7" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="B1702" s="3" t="s">
         <v>1731</v>
@@ -21407,7 +21410,7 @@
     </row>
     <row r="1703" spans="1:2">
       <c r="A1703" s="7" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="B1703" s="3" t="s">
         <v>1731</v>
@@ -21415,7 +21418,7 @@
     </row>
     <row r="1704" spans="1:2">
       <c r="A1704" s="7" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="B1704" s="3" t="s">
         <v>1731</v>
@@ -21423,7 +21426,7 @@
     </row>
     <row r="1705" spans="1:2">
       <c r="A1705" s="7" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="B1705" s="3" t="s">
         <v>1731</v>
@@ -21431,7 +21434,7 @@
     </row>
     <row r="1706" spans="1:2">
       <c r="A1706" s="7" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="B1706" s="3" t="s">
         <v>1731</v>
@@ -21439,7 +21442,7 @@
     </row>
     <row r="1707" spans="1:2">
       <c r="A1707" s="7" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="B1707" s="3" t="s">
         <v>1731</v>
@@ -21447,7 +21450,7 @@
     </row>
     <row r="1708" spans="1:2">
       <c r="A1708" s="7" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B1708" s="3" t="s">
         <v>1731</v>
@@ -21455,7 +21458,7 @@
     </row>
     <row r="1709" spans="1:2">
       <c r="A1709" s="7" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B1709" s="3" t="s">
         <v>1731</v>
@@ -21463,7 +21466,7 @@
     </row>
     <row r="1710" spans="1:2">
       <c r="A1710" s="7" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="B1710" s="3" t="s">
         <v>1731</v>
@@ -21471,7 +21474,7 @@
     </row>
     <row r="1711" spans="1:2">
       <c r="A1711" s="7" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="B1711" s="3" t="s">
         <v>1731</v>
@@ -21479,7 +21482,7 @@
     </row>
     <row r="1712" spans="1:2">
       <c r="A1712" s="7" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="B1712" s="3" t="s">
         <v>1731</v>
@@ -21487,15 +21490,15 @@
     </row>
     <row r="1713" spans="1:2">
       <c r="A1713" s="7" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="B1713" s="3" t="s">
-        <v>1794</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1714" spans="1:2">
       <c r="A1714" s="7" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="B1714" s="3" t="s">
         <v>1794</v>
@@ -21503,31 +21506,31 @@
     </row>
     <row r="1715" spans="1:2">
       <c r="A1715" s="7" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="B1715" s="3" t="s">
-        <v>1797</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1716" spans="1:2">
       <c r="A1716" s="7" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="B1716" s="3" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1717" spans="1:2">
       <c r="A1717" s="7" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="B1717" s="3" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1718" spans="1:2">
       <c r="A1718" s="7" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="B1718" s="3" t="s">
         <v>1801</v>
@@ -21535,23 +21538,23 @@
     </row>
     <row r="1719" spans="1:2">
       <c r="A1719" s="7" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="B1719" s="3" t="s">
         <v>1801</v>
       </c>
     </row>
     <row r="1720" spans="1:2">
-      <c r="A1720" s="10" t="s">
-        <v>1804</v>
+      <c r="A1720" s="7" t="s">
+        <v>1803</v>
       </c>
       <c r="B1720" s="3" t="s">
         <v>1801</v>
       </c>
     </row>
     <row r="1721" spans="1:2">
-      <c r="A1721" s="7" t="s">
-        <v>1805</v>
+      <c r="A1721" s="10" t="s">
+        <v>1804</v>
       </c>
       <c r="B1721" s="3" t="s">
         <v>1801</v>
@@ -21559,7 +21562,7 @@
     </row>
     <row r="1722" spans="1:2">
       <c r="A1722" s="7" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="B1722" s="3" t="s">
         <v>1801</v>
@@ -21567,7 +21570,7 @@
     </row>
     <row r="1723" spans="1:2">
       <c r="A1723" s="7" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B1723" s="3" t="s">
         <v>1801</v>
@@ -21575,7 +21578,7 @@
     </row>
     <row r="1724" spans="1:2">
       <c r="A1724" s="7" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="B1724" s="3" t="s">
         <v>1801</v>
@@ -21583,31 +21586,31 @@
     </row>
     <row r="1725" spans="1:2">
       <c r="A1725" s="7" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="B1725" s="3" t="s">
-        <v>1810</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1726" spans="1:2">
       <c r="A1726" s="7" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="B1726" s="3" t="s">
         <v>1810</v>
       </c>
     </row>
     <row r="1727" spans="1:2">
-      <c r="A1727" s="4" t="s">
-        <v>1812</v>
+      <c r="A1727" s="7" t="s">
+        <v>1811</v>
       </c>
       <c r="B1727" s="3" t="s">
         <v>1810</v>
       </c>
     </row>
     <row r="1728" spans="1:2">
-      <c r="A1728" s="7" t="s">
-        <v>1813</v>
+      <c r="A1728" s="4" t="s">
+        <v>1812</v>
       </c>
       <c r="B1728" s="3" t="s">
         <v>1810</v>
@@ -21615,15 +21618,15 @@
     </row>
     <row r="1729" spans="1:2">
       <c r="A1729" s="7" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="B1729" s="3" t="s">
-        <v>1815</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1730" spans="1:2">
       <c r="A1730" s="7" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="B1730" s="3" t="s">
         <v>1815</v>
@@ -21631,7 +21634,7 @@
     </row>
     <row r="1731" spans="1:2">
       <c r="A1731" s="7" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B1731" s="3" t="s">
         <v>1815</v>
@@ -21639,7 +21642,7 @@
     </row>
     <row r="1732" spans="1:2">
       <c r="A1732" s="7" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="B1732" s="3" t="s">
         <v>1815</v>
@@ -21647,7 +21650,7 @@
     </row>
     <row r="1733" spans="1:2">
       <c r="A1733" s="7" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="B1733" s="3" t="s">
         <v>1815</v>
@@ -21655,7 +21658,7 @@
     </row>
     <row r="1734" spans="1:2">
       <c r="A1734" s="7" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="B1734" s="3" t="s">
         <v>1815</v>
@@ -21663,7 +21666,7 @@
     </row>
     <row r="1735" spans="1:2">
       <c r="A1735" s="7" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="B1735" s="3" t="s">
         <v>1815</v>
@@ -21671,7 +21674,7 @@
     </row>
     <row r="1736" spans="1:2">
       <c r="A1736" s="7" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="B1736" s="3" t="s">
         <v>1815</v>
@@ -21679,7 +21682,7 @@
     </row>
     <row r="1737" spans="1:2">
       <c r="A1737" s="7" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="B1737" s="3" t="s">
         <v>1815</v>
@@ -21687,15 +21690,15 @@
     </row>
     <row r="1738" spans="1:2">
       <c r="A1738" s="7" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="B1738" s="3" t="s">
-        <v>1825</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1739" spans="1:2">
       <c r="A1739" s="7" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="B1739" s="3" t="s">
         <v>1825</v>
@@ -21703,7 +21706,7 @@
     </row>
     <row r="1740" spans="1:2">
       <c r="A1740" s="7" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="B1740" s="3" t="s">
         <v>1825</v>
@@ -21711,7 +21714,7 @@
     </row>
     <row r="1741" spans="1:2">
       <c r="A1741" s="7" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="B1741" s="3" t="s">
         <v>1825</v>
@@ -21719,7 +21722,7 @@
     </row>
     <row r="1742" spans="1:2">
       <c r="A1742" s="7" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="B1742" s="3" t="s">
         <v>1825</v>
@@ -21727,7 +21730,7 @@
     </row>
     <row r="1743" spans="1:2">
       <c r="A1743" s="7" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="B1743" s="3" t="s">
         <v>1825</v>
@@ -21735,7 +21738,7 @@
     </row>
     <row r="1744" spans="1:2">
       <c r="A1744" s="7" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="B1744" s="3" t="s">
         <v>1825</v>
@@ -21743,7 +21746,7 @@
     </row>
     <row r="1745" spans="1:2">
       <c r="A1745" s="7" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="B1745" s="3" t="s">
         <v>1825</v>
@@ -21751,7 +21754,7 @@
     </row>
     <row r="1746" spans="1:2">
       <c r="A1746" s="7" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="B1746" s="3" t="s">
         <v>1825</v>
@@ -21759,7 +21762,7 @@
     </row>
     <row r="1747" spans="1:2">
       <c r="A1747" s="7" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="B1747" s="3" t="s">
         <v>1825</v>
@@ -21767,7 +21770,7 @@
     </row>
     <row r="1748" spans="1:2">
       <c r="A1748" s="7" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="B1748" s="3" t="s">
         <v>1825</v>
@@ -21775,7 +21778,7 @@
     </row>
     <row r="1749" spans="1:2">
       <c r="A1749" s="7" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="B1749" s="3" t="s">
         <v>1825</v>
@@ -21783,7 +21786,7 @@
     </row>
     <row r="1750" spans="1:2">
       <c r="A1750" s="7" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="B1750" s="3" t="s">
         <v>1825</v>
@@ -21791,7 +21794,7 @@
     </row>
     <row r="1751" spans="1:2">
       <c r="A1751" s="7" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="B1751" s="3" t="s">
         <v>1825</v>
@@ -21799,7 +21802,7 @@
     </row>
     <row r="1752" spans="1:2">
       <c r="A1752" s="7" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="B1752" s="3" t="s">
         <v>1825</v>
@@ -21807,7 +21810,7 @@
     </row>
     <row r="1753" spans="1:2">
       <c r="A1753" s="7" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="B1753" s="3" t="s">
         <v>1825</v>
@@ -21815,7 +21818,7 @@
     </row>
     <row r="1754" spans="1:2">
       <c r="A1754" s="7" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="B1754" s="3" t="s">
         <v>1825</v>
@@ -21823,7 +21826,7 @@
     </row>
     <row r="1755" spans="1:2">
       <c r="A1755" s="7" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="B1755" s="3" t="s">
         <v>1825</v>
@@ -21831,7 +21834,7 @@
     </row>
     <row r="1756" spans="1:2">
       <c r="A1756" s="7" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B1756" s="3" t="s">
         <v>1825</v>
@@ -21839,7 +21842,7 @@
     </row>
     <row r="1757" spans="1:2">
       <c r="A1757" s="7" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="B1757" s="3" t="s">
         <v>1825</v>
@@ -21847,15 +21850,15 @@
     </row>
     <row r="1758" spans="1:2">
       <c r="A1758" s="7" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="B1758" s="3" t="s">
         <v>1825</v>
       </c>
     </row>
     <row r="1759" spans="1:2">
-      <c r="A1759" s="13" t="s">
-        <v>1846</v>
+      <c r="A1759" s="7" t="s">
+        <v>1845</v>
       </c>
       <c r="B1759" s="3" t="s">
         <v>1825</v>
@@ -21863,15 +21866,15 @@
     </row>
     <row r="1760" spans="1:2">
       <c r="A1760" s="13" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="B1760" s="3" t="s">
         <v>1825</v>
       </c>
     </row>
     <row r="1761" spans="1:2">
-      <c r="A1761" s="7" t="s">
-        <v>1848</v>
+      <c r="A1761" s="13" t="s">
+        <v>1847</v>
       </c>
       <c r="B1761" s="3" t="s">
         <v>1825</v>
@@ -21879,7 +21882,7 @@
     </row>
     <row r="1762" spans="1:2">
       <c r="A1762" s="7" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="B1762" s="3" t="s">
         <v>1825</v>
@@ -21887,7 +21890,7 @@
     </row>
     <row r="1763" spans="1:2">
       <c r="A1763" s="7" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="B1763" s="3" t="s">
         <v>1825</v>
@@ -21895,7 +21898,7 @@
     </row>
     <row r="1764" spans="1:2">
       <c r="A1764" s="7" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="B1764" s="3" t="s">
         <v>1825</v>
@@ -21903,7 +21906,7 @@
     </row>
     <row r="1765" spans="1:2">
       <c r="A1765" s="7" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="B1765" s="3" t="s">
         <v>1825</v>
@@ -21911,7 +21914,7 @@
     </row>
     <row r="1766" spans="1:2">
       <c r="A1766" s="7" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="B1766" s="3" t="s">
         <v>1825</v>
@@ -21919,7 +21922,7 @@
     </row>
     <row r="1767" spans="1:2">
       <c r="A1767" s="7" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="B1767" s="3" t="s">
         <v>1825</v>
@@ -21927,7 +21930,7 @@
     </row>
     <row r="1768" spans="1:2">
       <c r="A1768" s="7" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B1768" s="3" t="s">
         <v>1825</v>
@@ -21935,23 +21938,23 @@
     </row>
     <row r="1769" spans="1:2">
       <c r="A1769" s="7" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="B1769" s="3" t="s">
         <v>1825</v>
       </c>
     </row>
     <row r="1770" spans="1:2">
-      <c r="A1770" s="9" t="s">
-        <v>1857</v>
+      <c r="A1770" s="7" t="s">
+        <v>1856</v>
       </c>
       <c r="B1770" s="3" t="s">
         <v>1825</v>
       </c>
     </row>
     <row r="1771" spans="1:2">
-      <c r="A1771" s="7" t="s">
-        <v>1858</v>
+      <c r="A1771" s="9" t="s">
+        <v>1857</v>
       </c>
       <c r="B1771" s="3" t="s">
         <v>1825</v>
@@ -21959,7 +21962,7 @@
     </row>
     <row r="1772" spans="1:2">
       <c r="A1772" s="7" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="B1772" s="3" t="s">
         <v>1825</v>
@@ -21967,7 +21970,7 @@
     </row>
     <row r="1773" spans="1:2">
       <c r="A1773" s="7" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="B1773" s="3" t="s">
         <v>1825</v>
@@ -21975,23 +21978,23 @@
     </row>
     <row r="1774" spans="1:2">
       <c r="A1774" s="7" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="B1774" s="3" t="s">
         <v>1825</v>
       </c>
     </row>
     <row r="1775" spans="1:2">
-      <c r="A1775" s="10" t="s">
-        <v>1862</v>
+      <c r="A1775" s="7" t="s">
+        <v>1861</v>
       </c>
       <c r="B1775" s="3" t="s">
         <v>1825</v>
       </c>
     </row>
     <row r="1776" spans="1:2">
-      <c r="A1776" s="7" t="s">
-        <v>1863</v>
+      <c r="A1776" s="10" t="s">
+        <v>1862</v>
       </c>
       <c r="B1776" s="3" t="s">
         <v>1825</v>
@@ -21999,7 +22002,7 @@
     </row>
     <row r="1777" spans="1:2">
       <c r="A1777" s="7" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="B1777" s="3" t="s">
         <v>1825</v>
@@ -22007,7 +22010,7 @@
     </row>
     <row r="1778" spans="1:2">
       <c r="A1778" s="7" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="B1778" s="3" t="s">
         <v>1825</v>
@@ -22015,7 +22018,7 @@
     </row>
     <row r="1779" spans="1:2">
       <c r="A1779" s="7" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="B1779" s="3" t="s">
         <v>1825</v>
@@ -22023,7 +22026,7 @@
     </row>
     <row r="1780" spans="1:2">
       <c r="A1780" s="7" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="B1780" s="3" t="s">
         <v>1825</v>
@@ -22031,7 +22034,7 @@
     </row>
     <row r="1781" spans="1:2">
       <c r="A1781" s="7" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="B1781" s="3" t="s">
         <v>1825</v>
@@ -22039,7 +22042,7 @@
     </row>
     <row r="1782" spans="1:2">
       <c r="A1782" s="7" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="B1782" s="3" t="s">
         <v>1825</v>
@@ -22047,7 +22050,7 @@
     </row>
     <row r="1783" spans="1:2">
       <c r="A1783" s="7" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="B1783" s="3" t="s">
         <v>1825</v>
@@ -22055,7 +22058,7 @@
     </row>
     <row r="1784" spans="1:2">
       <c r="A1784" s="7" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="B1784" s="3" t="s">
         <v>1825</v>
@@ -22063,7 +22066,7 @@
     </row>
     <row r="1785" spans="1:2">
       <c r="A1785" s="7" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="B1785" s="3" t="s">
         <v>1825</v>
@@ -22071,15 +22074,15 @@
     </row>
     <row r="1786" spans="1:2">
       <c r="A1786" s="7" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="B1786" s="3" t="s">
-        <v>1874</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1787" spans="1:2">
       <c r="A1787" s="7" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="B1787" s="3" t="s">
         <v>1874</v>
@@ -22087,7 +22090,7 @@
     </row>
     <row r="1788" spans="1:2">
       <c r="A1788" s="7" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="B1788" s="3" t="s">
         <v>1874</v>
@@ -22095,111 +22098,111 @@
     </row>
     <row r="1789" spans="1:2">
       <c r="A1789" s="7" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="B1789" s="3" t="s">
-        <v>1878</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1790" spans="1:2">
       <c r="A1790" s="7" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="B1790" s="3" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="1791" spans="1:2">
       <c r="A1791" s="7" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="B1791" s="3" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1792" spans="1:2">
       <c r="A1792" s="7" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="B1792" s="3" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="1793" spans="1:2">
       <c r="A1793" s="7" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="B1793" s="3" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="1794" spans="1:2">
       <c r="A1794" s="7" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B1794" s="3" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:2">
+      <c r="A1795" s="7" t="s">
         <v>1887</v>
-      </c>
-      <c r="B1794" s="3" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="1795" spans="1:2">
-      <c r="A1795" s="10" t="s">
-        <v>1889</v>
       </c>
       <c r="B1795" s="3" t="s">
         <v>1888</v>
       </c>
     </row>
     <row r="1796" spans="1:2">
-      <c r="A1796" s="7" t="s">
-        <v>1890</v>
+      <c r="A1796" s="10" t="s">
+        <v>1889</v>
       </c>
       <c r="B1796" s="3" t="s">
-        <v>1891</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="1797" spans="1:2">
       <c r="A1797" s="7" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="B1797" s="3" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1798" spans="1:2">
       <c r="A1798" s="7" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="B1798" s="3" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="1799" spans="1:2">
       <c r="A1799" s="7" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B1799" s="3" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:2">
+      <c r="A1800" s="7" t="s">
         <v>1896</v>
       </c>
-      <c r="B1799" s="3" t="s">
+      <c r="B1800" s="3" t="s">
         <v>1897</v>
       </c>
     </row>
-    <row r="1800" spans="1:2">
-      <c r="A1800" s="10" t="s">
+    <row r="1801" spans="1:2">
+      <c r="A1801" s="10" t="s">
         <v>1898</v>
       </c>
-      <c r="B1800" s="3" t="s">
+      <c r="B1801" s="3" t="s">
         <v>1899</v>
-      </c>
-    </row>
-    <row r="1801" spans="1:2">
-      <c r="A1801" s="7" t="s">
-        <v>1900</v>
-      </c>
-      <c r="B1801" s="3" t="s">
-        <v>1901</v>
       </c>
     </row>
     <row r="1802" spans="1:2">
       <c r="A1802" s="7" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="B1802" s="3" t="s">
         <v>1901</v>
@@ -22207,7 +22210,7 @@
     </row>
     <row r="1803" spans="1:2">
       <c r="A1803" s="7" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B1803" s="3" t="s">
         <v>1901</v>
@@ -22215,7 +22218,7 @@
     </row>
     <row r="1804" spans="1:2">
       <c r="A1804" s="7" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="B1804" s="3" t="s">
         <v>1901</v>
@@ -22223,7 +22226,7 @@
     </row>
     <row r="1805" spans="1:2">
       <c r="A1805" s="7" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B1805" s="3" t="s">
         <v>1901</v>
@@ -22231,23 +22234,23 @@
     </row>
     <row r="1806" spans="1:2">
       <c r="A1806" s="7" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B1806" s="3" t="s">
         <v>1901</v>
       </c>
     </row>
     <row r="1807" spans="1:2">
-      <c r="A1807" s="9" t="s">
-        <v>1907</v>
+      <c r="A1807" s="7" t="s">
+        <v>1906</v>
       </c>
       <c r="B1807" s="3" t="s">
         <v>1901</v>
       </c>
     </row>
     <row r="1808" spans="1:2">
-      <c r="A1808" s="7" t="s">
-        <v>1908</v>
+      <c r="A1808" s="9" t="s">
+        <v>1907</v>
       </c>
       <c r="B1808" s="3" t="s">
         <v>1901</v>
@@ -22255,7 +22258,7 @@
     </row>
     <row r="1809" spans="1:2">
       <c r="A1809" s="7" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="B1809" s="3" t="s">
         <v>1901</v>
@@ -22263,7 +22266,7 @@
     </row>
     <row r="1810" spans="1:2">
       <c r="A1810" s="7" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B1810" s="3" t="s">
         <v>1901</v>
@@ -22271,7 +22274,7 @@
     </row>
     <row r="1811" spans="1:2">
       <c r="A1811" s="7" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B1811" s="3" t="s">
         <v>1901</v>
@@ -22279,7 +22282,7 @@
     </row>
     <row r="1812" spans="1:2">
       <c r="A1812" s="7" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="B1812" s="3" t="s">
         <v>1901</v>
@@ -22287,7 +22290,7 @@
     </row>
     <row r="1813" spans="1:2">
       <c r="A1813" s="7" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="B1813" s="3" t="s">
         <v>1901</v>
@@ -22295,7 +22298,7 @@
     </row>
     <row r="1814" spans="1:2">
       <c r="A1814" s="7" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B1814" s="3" t="s">
         <v>1901</v>
@@ -22303,7 +22306,7 @@
     </row>
     <row r="1815" spans="1:2">
       <c r="A1815" s="7" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B1815" s="3" t="s">
         <v>1901</v>
@@ -22311,7 +22314,7 @@
     </row>
     <row r="1816" spans="1:2">
       <c r="A1816" s="7" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="B1816" s="3" t="s">
         <v>1901</v>
@@ -22319,7 +22322,7 @@
     </row>
     <row r="1817" spans="1:2">
       <c r="A1817" s="7" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="B1817" s="3" t="s">
         <v>1901</v>
@@ -22327,39 +22330,39 @@
     </row>
     <row r="1818" spans="1:2">
       <c r="A1818" s="7" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="B1818" s="3" t="s">
-        <v>1919</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="1819" spans="1:2">
       <c r="A1819" s="7" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="B1819" s="3" t="s">
         <v>1919</v>
       </c>
     </row>
     <row r="1820" spans="1:2">
-      <c r="A1820" s="9" t="s">
-        <v>1921</v>
+      <c r="A1820" s="7" t="s">
+        <v>1920</v>
       </c>
       <c r="B1820" s="3" t="s">
         <v>1919</v>
       </c>
     </row>
     <row r="1821" spans="1:2">
-      <c r="A1821" s="4" t="s">
-        <v>1922</v>
+      <c r="A1821" s="9" t="s">
+        <v>1921</v>
       </c>
       <c r="B1821" s="3" t="s">
         <v>1919</v>
       </c>
     </row>
     <row r="1822" spans="1:2">
-      <c r="A1822" s="7" t="s">
-        <v>1923</v>
+      <c r="A1822" s="4" t="s">
+        <v>1922</v>
       </c>
       <c r="B1822" s="3" t="s">
         <v>1919</v>
@@ -22367,7 +22370,7 @@
     </row>
     <row r="1823" spans="1:2">
       <c r="A1823" s="7" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="B1823" s="3" t="s">
         <v>1919</v>
@@ -22375,7 +22378,7 @@
     </row>
     <row r="1824" spans="1:2">
       <c r="A1824" s="7" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="B1824" s="3" t="s">
         <v>1919</v>
@@ -22383,7 +22386,7 @@
     </row>
     <row r="1825" spans="1:2">
       <c r="A1825" s="7" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="B1825" s="3" t="s">
         <v>1919</v>
@@ -22391,7 +22394,7 @@
     </row>
     <row r="1826" spans="1:2">
       <c r="A1826" s="7" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="B1826" s="3" t="s">
         <v>1919</v>
@@ -22399,7 +22402,7 @@
     </row>
     <row r="1827" spans="1:2">
       <c r="A1827" s="7" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="B1827" s="3" t="s">
         <v>1919</v>
@@ -22407,15 +22410,15 @@
     </row>
     <row r="1828" spans="1:2">
       <c r="A1828" s="7" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="B1828" s="3" t="s">
-        <v>1930</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="1829" spans="1:2">
       <c r="A1829" s="7" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="B1829" s="3" t="s">
         <v>1930</v>
@@ -22423,38 +22426,46 @@
     </row>
     <row r="1830" spans="1:2">
       <c r="A1830" s="7" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="B1830" s="3" t="s">
-        <v>1933</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1831" spans="1:2">
       <c r="A1831" s="7" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="B1831" s="3" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1832" spans="1:2">
       <c r="A1832" s="7" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="B1832" s="3" t="s">
         <v>1935</v>
       </c>
     </row>
     <row r="1833" spans="1:2">
-      <c r="A1833" s="14" t="s">
+      <c r="A1833" s="7" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B1833" s="3" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:2">
+      <c r="A1834" s="14" t="s">
         <v>1937</v>
       </c>
-      <c r="B1833" s="3" t="s">
+      <c r="B1834" s="3" t="s">
         <v>1938</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A1833">
+  <conditionalFormatting sqref="A2:A1065 A1067:A1834">
     <cfRule type="duplicateValues" dxfId="0" priority="80"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Koding\tool-fcost\masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARISAFARI\Works\Project Applications\tool-fcost\masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD67A39-8DAE-4496-B444-D5DAA856388E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -26,12 +25,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">action!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">defect_category!$A$1:$D$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4653" uniqueCount="2385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4724" uniqueCount="2385">
   <si>
     <t>part_used</t>
   </si>
@@ -6792,18 +6791,6 @@
     <t>VERIFIED_OK</t>
   </si>
   <si>
-    <t>symptom_alias</t>
-  </si>
-  <si>
-    <t>symptom_canonical</t>
-  </si>
-  <si>
-    <t>repair_alias</t>
-  </si>
-  <si>
-    <t>repair_canonical</t>
-  </si>
-  <si>
     <t>EXS|EXTRNAL|EXTERNAL</t>
   </si>
   <si>
@@ -7186,12 +7173,24 @@
   </si>
   <si>
     <t>9TAHN7000CE002</t>
+  </si>
+  <si>
+    <t>alias</t>
+  </si>
+  <si>
+    <t>canonical</t>
+  </si>
+  <si>
+    <t>scope</t>
+  </si>
+  <si>
+    <t>both</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###"/>
   </numFmts>
@@ -7463,16 +7462,16 @@
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 3 14" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Normal 13 2 2 10 2 2 5 2 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 13 2 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 133 2 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 195" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Normal 2 2 7 2 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal 315" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Normal 80" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 10 3 14" xfId="7"/>
+    <cellStyle name="Normal 13 2 2 10 2 2 5 2 2 2 2" xfId="3"/>
+    <cellStyle name="Normal 13 2 2 2" xfId="4"/>
+    <cellStyle name="Normal 133 2 2" xfId="6"/>
+    <cellStyle name="Normal 195" xfId="8"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 2 2" xfId="10"/>
+    <cellStyle name="Normal 2 2 7 2 2 2" xfId="5"/>
+    <cellStyle name="Normal 315" xfId="9"/>
+    <cellStyle name="Normal 80" xfId="1"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -7760,7 +7759,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T1834"/>
   <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="12.75"/>
   <cols>
@@ -16304,7 +16303,7 @@
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" s="4" t="s">
-        <v>2384</v>
+        <v>2380</v>
       </c>
       <c r="B1066" s="3" t="s">
         <v>989</v>
@@ -22474,7 +22473,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T1971"/>
   <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="12.75"/>
   <cols>
@@ -30675,7 +30674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -31636,7 +31635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -31689,7 +31688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -31735,7 +31734,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -32112,10 +32111,10 @@
       </c>
       <c r="D19"/>
       <c r="E19" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
       <c r="F19" t="s">
-        <v>2364</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -32130,7 +32129,7 @@
       </c>
       <c r="D20"/>
       <c r="E20" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
       <c r="F20" t="s">
         <v>2155</v>
@@ -32147,7 +32146,7 @@
         <v>2137</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>2375</v>
+        <v>2371</v>
       </c>
       <c r="F21" t="s">
         <v>2158</v>
@@ -32413,7 +32412,7 @@
         <v>2137</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>2380</v>
+        <v>2376</v>
       </c>
       <c r="F37" t="s">
         <v>2151</v>
@@ -32430,7 +32429,7 @@
         <v>2137</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>2373</v>
+        <v>2369</v>
       </c>
       <c r="F38" t="s">
         <v>2151</v>
@@ -32447,7 +32446,7 @@
         <v>2137</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>2379</v>
+        <v>2375</v>
       </c>
       <c r="F39" t="s">
         <v>2151</v>
@@ -32583,7 +32582,7 @@
         <v>2137</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>2374</v>
+        <v>2370</v>
       </c>
       <c r="F47" t="s">
         <v>2149</v>
@@ -32702,7 +32701,7 @@
         <v>2137</v>
       </c>
       <c r="E54" s="32" t="s">
-        <v>2383</v>
+        <v>2379</v>
       </c>
       <c r="F54" t="s">
         <v>2149</v>
@@ -32804,7 +32803,7 @@
         <v>2137</v>
       </c>
       <c r="E60" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
       <c r="F60" t="s">
         <v>2196</v>
@@ -32855,7 +32854,7 @@
         <v>2137</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>2381</v>
+        <v>2377</v>
       </c>
       <c r="F63" t="s">
         <v>2142</v>
@@ -32991,7 +32990,7 @@
         <v>2137</v>
       </c>
       <c r="E71" s="32" t="s">
-        <v>2371</v>
+        <v>2367</v>
       </c>
       <c r="F71" t="s">
         <v>2144</v>
@@ -33042,7 +33041,7 @@
         <v>2137</v>
       </c>
       <c r="E74" t="s">
-        <v>2368</v>
+        <v>2364</v>
       </c>
       <c r="F74" t="s">
         <v>2166</v>
@@ -33423,13 +33422,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -34039,8 +34038,8 @@
       <c r="D43" s="29"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000006000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D43">
+  <autoFilter ref="A1:D1">
+    <sortState ref="A2:D43">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
@@ -34049,582 +34048,831 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D56"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="89.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="84.140625" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="104.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>2253</v>
+        <v>2381</v>
       </c>
       <c r="B1" t="s">
-        <v>2254</v>
+        <v>2382</v>
       </c>
       <c r="C1" t="s">
-        <v>2255</v>
+        <v>2383</v>
       </c>
       <c r="D1" t="s">
-        <v>2256</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2261</v>
+        <v>2257</v>
       </c>
       <c r="B2" t="s">
         <v>2067</v>
       </c>
       <c r="C2" t="s">
-        <v>2378</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2258</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2337</v>
+        <v>2333</v>
       </c>
       <c r="B3" t="s">
-        <v>2260</v>
+        <v>2256</v>
       </c>
       <c r="C3" t="s">
-        <v>2324</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2259</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2359</v>
+        <v>2355</v>
       </c>
       <c r="B4" t="s">
-        <v>2330</v>
+        <v>2326</v>
       </c>
       <c r="C4" t="s">
-        <v>2337</v>
-      </c>
-      <c r="D4" t="s">
-        <v>2260</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2269</v>
+        <v>2265</v>
       </c>
       <c r="B5" t="s">
         <v>2028</v>
       </c>
       <c r="C5" t="s">
-        <v>2257</v>
-      </c>
-      <c r="D5" t="s">
-        <v>2361</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2270</v>
+        <v>2266</v>
       </c>
       <c r="B6" t="s">
-        <v>2271</v>
+        <v>2267</v>
       </c>
       <c r="C6" t="s">
-        <v>2340</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2262</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="B7" t="s">
-        <v>2277</v>
+        <v>2273</v>
       </c>
       <c r="C7" t="s">
-        <v>2369</v>
-      </c>
-      <c r="D7" t="s">
-        <v>2263</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="B8" t="s">
-        <v>2342</v>
+        <v>2338</v>
       </c>
       <c r="C8" t="s">
-        <v>2264</v>
-      </c>
-      <c r="D8" t="s">
-        <v>2265</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2343</v>
+        <v>2339</v>
       </c>
       <c r="B9" t="s">
-        <v>2277</v>
+        <v>2273</v>
       </c>
       <c r="C9" t="s">
-        <v>2266</v>
-      </c>
-      <c r="D9" t="s">
-        <v>2273</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2270</v>
+        <v>2266</v>
       </c>
       <c r="B10" t="s">
-        <v>2271</v>
+        <v>2267</v>
       </c>
       <c r="C10" t="s">
-        <v>2307</v>
-      </c>
-      <c r="D10" t="s">
-        <v>2267</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2336</v>
+        <v>2332</v>
       </c>
       <c r="B11" t="s">
-        <v>2335</v>
+        <v>2331</v>
       </c>
       <c r="C11" t="s">
-        <v>2268</v>
-      </c>
-      <c r="D11" t="s">
-        <v>2028</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2344</v>
+        <v>2340</v>
       </c>
       <c r="B12" t="s">
-        <v>2345</v>
+        <v>2341</v>
       </c>
       <c r="C12" t="s">
-        <v>2270</v>
-      </c>
-      <c r="D12" t="s">
-        <v>2271</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="31" t="s">
-        <v>2346</v>
+        <v>2342</v>
       </c>
       <c r="B13" t="s">
         <v>2089</v>
       </c>
       <c r="C13" t="s">
-        <v>2365</v>
-      </c>
-      <c r="D13" t="s">
-        <v>2236</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2347</v>
+        <v>2343</v>
       </c>
       <c r="B14" t="s">
-        <v>2348</v>
+        <v>2344</v>
       </c>
       <c r="C14" t="s">
-        <v>2272</v>
-      </c>
-      <c r="D14" t="s">
-        <v>989</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2349</v>
+        <v>2345</v>
       </c>
       <c r="B15" t="s">
-        <v>2350</v>
+        <v>2346</v>
       </c>
       <c r="C15" t="s">
-        <v>2274</v>
-      </c>
-      <c r="D15" t="s">
-        <v>2263</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="31" t="s">
+        <v>2347</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>2348</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2350</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>2351</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B18" t="s">
         <v>2352</v>
       </c>
-      <c r="C16" t="s">
-        <v>2275</v>
-      </c>
-      <c r="D16" t="s">
-        <v>2262</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
+      <c r="C18" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B19" t="s">
         <v>2353</v>
       </c>
-      <c r="B17" t="s">
-        <v>2354</v>
-      </c>
-      <c r="C17" t="s">
-        <v>2276</v>
-      </c>
-      <c r="D17" t="s">
-        <v>2277</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>2355</v>
-      </c>
-      <c r="B18" t="s">
-        <v>2356</v>
-      </c>
-      <c r="C18" t="s">
-        <v>2278</v>
-      </c>
-      <c r="D18" t="s">
-        <v>2279</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>2358</v>
-      </c>
-      <c r="B19" t="s">
-        <v>2357</v>
-      </c>
       <c r="C19" t="s">
-        <v>2280</v>
-      </c>
-      <c r="D19" t="s">
-        <v>2281</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>2250</v>
       </c>
       <c r="B20" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2254</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2255</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2357</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>2336</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2261</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2269</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2267</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2236</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B32" t="s">
+        <v>989</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>2271</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2275</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2277</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>2281</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2282</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>2287</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B45" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>2290</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2294</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>2368</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>2301</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2297</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2282</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B53" t="s">
+        <v>2300</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>2305</v>
+      </c>
+      <c r="B54" t="s">
+        <v>2304</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>2334</v>
+      </c>
+      <c r="B55" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>2306</v>
+      </c>
+      <c r="B56" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B57" t="s">
+        <v>2309</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>2310</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2311</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>2312</v>
+      </c>
+      <c r="B59" t="s">
+        <v>2313</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>2356</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>2321</v>
+      </c>
+      <c r="B64" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B66" t="s">
+        <v>2067</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B67" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C67" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>2327</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>2329</v>
+      </c>
+      <c r="B69" t="s">
+        <v>2330</v>
+      </c>
+      <c r="C69" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>2332</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2331</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>2335</v>
+      </c>
+      <c r="B71" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
         <v>2362</v>
       </c>
-      <c r="C20" t="s">
-        <v>2282</v>
-      </c>
-      <c r="D20" t="s">
-        <v>2283</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="C21" t="s">
-        <v>2284</v>
-      </c>
-      <c r="D21" t="s">
-        <v>2283</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="C22" t="s">
-        <v>2285</v>
-      </c>
-      <c r="D22" t="s">
-        <v>2286</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="C23" t="s">
-        <v>2287</v>
-      </c>
-      <c r="D23" t="s">
-        <v>2283</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="C24" t="s">
-        <v>2306</v>
-      </c>
-      <c r="D24" t="s">
-        <v>2288</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="C25" t="s">
-        <v>2289</v>
-      </c>
-      <c r="D25" t="s">
-        <v>2290</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="C26" t="s">
-        <v>2291</v>
-      </c>
-      <c r="D26" t="s">
-        <v>2263</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="C27" t="s">
-        <v>2292</v>
-      </c>
-      <c r="D27" t="s">
-        <v>2293</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="C28" t="s">
-        <v>2294</v>
-      </c>
-      <c r="D28" t="s">
-        <v>2295</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="C29" t="s">
-        <v>2296</v>
-      </c>
-      <c r="D29" t="s">
-        <v>2283</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="C30" t="s">
-        <v>2297</v>
-      </c>
-      <c r="D30" t="s">
-        <v>2298</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="C31" t="s">
+      <c r="B72" t="s">
+        <v>2363</v>
+      </c>
+      <c r="C72" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B73" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
         <v>2372</v>
       </c>
-      <c r="D31" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="C32" t="s">
-        <v>2299</v>
-      </c>
-      <c r="D32" t="s">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="33" spans="3:4">
-      <c r="C33" t="s">
-        <v>2305</v>
-      </c>
-      <c r="D33" t="s">
-        <v>2301</v>
-      </c>
-    </row>
-    <row r="34" spans="3:4">
-      <c r="C34" t="s">
-        <v>2302</v>
-      </c>
-      <c r="D34" t="s">
-        <v>2286</v>
-      </c>
-    </row>
-    <row r="35" spans="3:4">
-      <c r="C35" t="s">
-        <v>2303</v>
-      </c>
-      <c r="D35" t="s">
-        <v>2304</v>
-      </c>
-    </row>
-    <row r="36" spans="3:4">
-      <c r="C36" t="s">
-        <v>2309</v>
-      </c>
-      <c r="D36" t="s">
-        <v>2308</v>
-      </c>
-    </row>
-    <row r="37" spans="3:4">
-      <c r="C37" t="s">
-        <v>2338</v>
-      </c>
-      <c r="D37" t="s">
-        <v>2166</v>
-      </c>
-    </row>
-    <row r="38" spans="3:4">
-      <c r="C38" t="s">
-        <v>2310</v>
-      </c>
-      <c r="D38" t="s">
-        <v>2311</v>
-      </c>
-    </row>
-    <row r="39" spans="3:4">
-      <c r="C39" t="s">
-        <v>2312</v>
-      </c>
-      <c r="D39" t="s">
-        <v>2313</v>
-      </c>
-    </row>
-    <row r="40" spans="3:4">
-      <c r="C40" t="s">
-        <v>2314</v>
-      </c>
-      <c r="D40" t="s">
-        <v>2315</v>
-      </c>
-    </row>
-    <row r="41" spans="3:4">
-      <c r="C41" t="s">
-        <v>2316</v>
-      </c>
-      <c r="D41" t="s">
-        <v>2317</v>
-      </c>
-    </row>
-    <row r="42" spans="3:4">
-      <c r="C42" t="s">
-        <v>2360</v>
-      </c>
-      <c r="D42" t="s">
-        <v>2318</v>
-      </c>
-    </row>
-    <row r="43" spans="3:4">
-      <c r="C43" t="s">
-        <v>2319</v>
-      </c>
-      <c r="D43" t="s">
-        <v>2320</v>
-      </c>
-    </row>
-    <row r="44" spans="3:4">
-      <c r="C44" t="s">
-        <v>2321</v>
-      </c>
-      <c r="D44" t="s">
-        <v>2322</v>
-      </c>
-    </row>
-    <row r="45" spans="3:4">
-      <c r="C45" t="s">
-        <v>2332</v>
-      </c>
-      <c r="D45" t="s">
-        <v>2323</v>
-      </c>
-    </row>
-    <row r="46" spans="3:4">
-      <c r="C46" t="s">
-        <v>2325</v>
-      </c>
-      <c r="D46" t="s">
-        <v>2029</v>
-      </c>
-    </row>
-    <row r="47" spans="3:4">
-      <c r="C47" t="s">
-        <v>2326</v>
-      </c>
-      <c r="D47" t="s">
-        <v>2327</v>
-      </c>
-    </row>
-    <row r="48" spans="3:4">
-      <c r="C48" t="s">
-        <v>2328</v>
-      </c>
-      <c r="D48" t="s">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="49" spans="3:4">
-      <c r="C49" t="s">
-        <v>2329</v>
-      </c>
-      <c r="D49" t="s">
-        <v>2330</v>
-      </c>
-    </row>
-    <row r="50" spans="3:4">
-      <c r="C50" t="s">
-        <v>2331</v>
-      </c>
-      <c r="D50" t="s">
-        <v>2283</v>
-      </c>
-    </row>
-    <row r="51" spans="3:4">
-      <c r="C51" t="s">
-        <v>2333</v>
-      </c>
-      <c r="D51" t="s">
-        <v>2334</v>
-      </c>
-    </row>
-    <row r="52" spans="3:4">
-      <c r="C52" t="s">
-        <v>2336</v>
-      </c>
-      <c r="D52" t="s">
-        <v>2335</v>
-      </c>
-    </row>
-    <row r="53" spans="3:4">
-      <c r="C53" t="s">
-        <v>2339</v>
-      </c>
-      <c r="D53" t="s">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="54" spans="3:4">
-      <c r="C54" t="s">
-        <v>2366</v>
-      </c>
-      <c r="D54" t="s">
-        <v>2367</v>
-      </c>
-    </row>
-    <row r="55" spans="3:4">
-      <c r="C55" t="s">
-        <v>2370</v>
-      </c>
-      <c r="D55" t="s">
-        <v>2283</v>
-      </c>
-    </row>
-    <row r="56" spans="3:4">
-      <c r="C56" t="s">
-        <v>2376</v>
-      </c>
-      <c r="D56" t="s">
-        <v>2377</v>
+      <c r="B74" t="s">
+        <v>2373</v>
+      </c>
+      <c r="C74" t="s">
+        <v>2384</v>
       </c>
     </row>
   </sheetData>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4724" uniqueCount="2385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4731" uniqueCount="2386">
   <si>
     <t>part_used</t>
   </si>
@@ -6134,9 +6134,6 @@
     <t>migrated from plain contains; source=X ADA GAMBAR</t>
   </si>
   <si>
-    <t>NO DISPLAY|STANDBY|GAMBAR GELAP|GAMBAR TDK KELUAR</t>
-  </si>
-  <si>
     <t>migrated from plain contains; source=NO DISPLAY</t>
   </si>
   <si>
@@ -6146,9 +6143,6 @@
     <t>migrated from plain contains; source=MATI</t>
   </si>
   <si>
-    <t>HANYA SUARA</t>
-  </si>
-  <si>
     <t>migrated from plain contains; source=HANYA SUARA SAJA</t>
   </si>
   <si>
@@ -6197,9 +6191,6 @@
     <t>migrated from wildcard contains; source=*TIDAK BISA HIDUP*</t>
   </si>
   <si>
-    <t>BERGERAK</t>
-  </si>
-  <si>
     <t>migrated from wildcard contains; source=*BERGERAK*</t>
   </si>
   <si>
@@ -6995,9 +6986,6 @@
     <t>GT|GNT|GNTI</t>
   </si>
   <si>
-    <t>BLAND</t>
-  </si>
-  <si>
     <t>DITAR IK</t>
   </si>
   <si>
@@ -7031,9 +7019,6 @@
     <t>CHANEL|CHENEL</t>
   </si>
   <si>
-    <t>X ADA GAMBAR|TIDAK ADA GAMBAR|TDK ADA GAMBAR|TIDAK AD AGAMBAR|TIDAK AD GAMBAR|TDK ADA GMBR</t>
-  </si>
-  <si>
     <t>SETING|STEL</t>
   </si>
   <si>
@@ -7043,9 +7028,6 @@
     <t>UNIL|UNTIT</t>
   </si>
   <si>
-    <t>0AMBAR</t>
-  </si>
-  <si>
     <t>GAMBAR</t>
   </si>
   <si>
@@ -7185,6 +7167,27 @@
   </si>
   <si>
     <t>both</t>
+  </si>
+  <si>
+    <t>BLAND|BLAN</t>
+  </si>
+  <si>
+    <t>0AMBAR|GAMABAR|</t>
+  </si>
+  <si>
+    <t>HANYA SUARA|SUARA SAJA</t>
+  </si>
+  <si>
+    <t>SUARA SAJA</t>
+  </si>
+  <si>
+    <t>BERGERAK|LAYAR BEREMBUN|LAYAR BERGERAK</t>
+  </si>
+  <si>
+    <t>X ADA GAMBAR|TIDAK ADA GAMBAR|TDK ADA GAMBAR|TIDAK AD AGAMBAR|TIDAK AD GAMBAR|TDK ADA GMBR|GAMBAR TIDAK KELUAR|TIDAK AD AGMBR|LCD-PIC-C01-GAMBAR TIDAK KELUAR</t>
+  </si>
+  <si>
+    <t>NO DISPLAY|STANDBY|GAMBAR GELAP|GAMBAR TDK KELUAR|GELAP|GAMBAR TIDAK KELUAR</t>
   </si>
 </sst>
 </file>
@@ -16303,7 +16306,7 @@
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" s="4" t="s">
-        <v>2380</v>
+        <v>2374</v>
       </c>
       <c r="B1066" s="3" t="s">
         <v>989</v>
@@ -30675,7 +30678,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -30857,13 +30860,13 @@
         <v>2020</v>
       </c>
       <c r="D9" t="s">
-        <v>2034</v>
+        <v>2385</v>
       </c>
       <c r="E9" t="s">
         <v>2029</v>
       </c>
       <c r="F9" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -30877,13 +30880,13 @@
         <v>2027</v>
       </c>
       <c r="D10" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E10" t="s">
         <v>2029</v>
       </c>
       <c r="F10" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -30897,13 +30900,13 @@
         <v>2020</v>
       </c>
       <c r="D11" t="s">
-        <v>2038</v>
+        <v>2382</v>
       </c>
       <c r="E11" t="s">
         <v>2029</v>
       </c>
       <c r="F11" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -30917,13 +30920,13 @@
         <v>2020</v>
       </c>
       <c r="D12" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2039</v>
+      </c>
+      <c r="F12" t="s">
         <v>2040</v>
-      </c>
-      <c r="E12" t="s">
-        <v>2041</v>
-      </c>
-      <c r="F12" t="s">
-        <v>2042</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -30937,13 +30940,13 @@
         <v>2020</v>
       </c>
       <c r="D13" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="E13" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="F13" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -30957,13 +30960,13 @@
         <v>2027</v>
       </c>
       <c r="D14" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F14" t="s">
         <v>2045</v>
-      </c>
-      <c r="E14" t="s">
-        <v>2046</v>
-      </c>
-      <c r="F14" t="s">
-        <v>2047</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -30977,13 +30980,13 @@
         <v>2027</v>
       </c>
       <c r="D15" t="s">
+        <v>2044</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F15" t="s">
         <v>2046</v>
-      </c>
-      <c r="E15" t="s">
-        <v>2046</v>
-      </c>
-      <c r="F15" t="s">
-        <v>2048</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -30997,13 +31000,13 @@
         <v>2027</v>
       </c>
       <c r="D16" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="E16" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="F16" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -31017,13 +31020,13 @@
         <v>2027</v>
       </c>
       <c r="D17" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="E17" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="F17" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -31037,13 +31040,13 @@
         <v>2027</v>
       </c>
       <c r="D18" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="E18" t="s">
         <v>2022</v>
       </c>
       <c r="F18" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -31054,16 +31057,16 @@
         <v>989</v>
       </c>
       <c r="C19" t="s">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="D19" t="s">
-        <v>2055</v>
+        <v>2383</v>
       </c>
       <c r="E19" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="F19" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -31077,13 +31080,13 @@
         <v>2020</v>
       </c>
       <c r="D20" t="s">
-        <v>2057</v>
+        <v>2054</v>
       </c>
       <c r="E20" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
       <c r="F20" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -31097,13 +31100,10 @@
         <v>2020</v>
       </c>
       <c r="D21" t="s">
-        <v>2060</v>
+        <v>2111</v>
       </c>
       <c r="E21" t="s">
-        <v>2061</v>
-      </c>
-      <c r="F21" t="s">
-        <v>2062</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -31114,16 +31114,16 @@
         <v>989</v>
       </c>
       <c r="C22" t="s">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="D22" t="s">
-        <v>2063</v>
+        <v>2057</v>
       </c>
       <c r="E22" t="s">
-        <v>2064</v>
+        <v>2058</v>
       </c>
       <c r="F22" t="s">
-        <v>2065</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -31131,19 +31131,19 @@
         <v>220</v>
       </c>
       <c r="B23" t="s">
-        <v>459</v>
+        <v>989</v>
       </c>
       <c r="C23" t="s">
-        <v>2020</v>
+        <v>2027</v>
       </c>
       <c r="D23" t="s">
-        <v>2066</v>
+        <v>2060</v>
       </c>
       <c r="E23" t="s">
-        <v>2067</v>
+        <v>2061</v>
       </c>
       <c r="F23" t="s">
-        <v>2068</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -31157,13 +31157,13 @@
         <v>2020</v>
       </c>
       <c r="D24" t="s">
-        <v>2069</v>
+        <v>2063</v>
       </c>
       <c r="E24" t="s">
-        <v>2022</v>
+        <v>2064</v>
       </c>
       <c r="F24" t="s">
-        <v>2070</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -31177,13 +31177,13 @@
         <v>2020</v>
       </c>
       <c r="D25" t="s">
-        <v>2071</v>
+        <v>2066</v>
       </c>
       <c r="E25" t="s">
         <v>2022</v>
       </c>
       <c r="F25" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -31197,13 +31197,13 @@
         <v>2020</v>
       </c>
       <c r="D26" t="s">
-        <v>2073</v>
+        <v>2068</v>
       </c>
       <c r="E26" t="s">
-        <v>2074</v>
+        <v>2022</v>
       </c>
       <c r="F26" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -31217,13 +31217,13 @@
         <v>2020</v>
       </c>
       <c r="D27" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="E27" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="F27" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -31234,16 +31234,16 @@
         <v>459</v>
       </c>
       <c r="C28" t="s">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="D28" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="E28" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="F28" t="s">
-        <v>2081</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -31254,16 +31254,16 @@
         <v>459</v>
       </c>
       <c r="C29" t="s">
-        <v>2020</v>
+        <v>2027</v>
       </c>
       <c r="D29" t="s">
-        <v>2082</v>
+        <v>2076</v>
       </c>
       <c r="E29" t="s">
-        <v>2083</v>
+        <v>2077</v>
       </c>
       <c r="F29" t="s">
-        <v>2084</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -31277,13 +31277,13 @@
         <v>2020</v>
       </c>
       <c r="D30" t="s">
-        <v>2085</v>
+        <v>2079</v>
       </c>
       <c r="E30" t="s">
-        <v>2086</v>
+        <v>2080</v>
       </c>
       <c r="F30" t="s">
-        <v>2087</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -31294,16 +31294,16 @@
         <v>459</v>
       </c>
       <c r="C31" t="s">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="D31" t="s">
-        <v>2088</v>
+        <v>2082</v>
       </c>
       <c r="E31" t="s">
-        <v>2089</v>
+        <v>2083</v>
       </c>
       <c r="F31" t="s">
-        <v>2090</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -31314,16 +31314,16 @@
         <v>459</v>
       </c>
       <c r="C32" t="s">
-        <v>2020</v>
+        <v>2027</v>
       </c>
       <c r="D32" t="s">
-        <v>2091</v>
+        <v>2085</v>
       </c>
       <c r="E32" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
       <c r="F32" t="s">
-        <v>2092</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -31334,16 +31334,16 @@
         <v>459</v>
       </c>
       <c r="C33" t="s">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="D33" t="s">
-        <v>2093</v>
+        <v>2088</v>
       </c>
       <c r="E33" t="s">
-        <v>2094</v>
+        <v>2086</v>
       </c>
       <c r="F33" t="s">
-        <v>2095</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -31354,16 +31354,16 @@
         <v>459</v>
       </c>
       <c r="C34" t="s">
-        <v>2020</v>
+        <v>2027</v>
       </c>
       <c r="D34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
       <c r="E34" t="s">
-        <v>2097</v>
+        <v>2091</v>
       </c>
       <c r="F34" t="s">
-        <v>2098</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -31374,16 +31374,16 @@
         <v>459</v>
       </c>
       <c r="C35" t="s">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="D35" t="s">
-        <v>2099</v>
+        <v>2093</v>
       </c>
       <c r="E35" t="s">
-        <v>2100</v>
+        <v>2094</v>
       </c>
       <c r="F35" t="s">
-        <v>2101</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -31397,13 +31397,13 @@
         <v>2027</v>
       </c>
       <c r="D36" t="s">
-        <v>2102</v>
+        <v>2096</v>
       </c>
       <c r="E36" t="s">
-        <v>2103</v>
+        <v>2097</v>
       </c>
       <c r="F36" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -31411,19 +31411,19 @@
         <v>360</v>
       </c>
       <c r="B37" t="s">
-        <v>1659</v>
+        <v>459</v>
       </c>
       <c r="C37" t="s">
-        <v>2020</v>
+        <v>2027</v>
       </c>
       <c r="D37" t="s">
-        <v>2105</v>
+        <v>2099</v>
       </c>
       <c r="E37" t="s">
-        <v>2106</v>
+        <v>2100</v>
       </c>
       <c r="F37" t="s">
-        <v>2107</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -31431,19 +31431,19 @@
         <v>370</v>
       </c>
       <c r="B38" t="s">
-        <v>989</v>
+        <v>1659</v>
       </c>
       <c r="C38" t="s">
         <v>2020</v>
       </c>
       <c r="D38" t="s">
-        <v>2108</v>
+        <v>2102</v>
       </c>
       <c r="E38" t="s">
-        <v>2029</v>
+        <v>2103</v>
       </c>
       <c r="F38" t="s">
-        <v>2109</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -31451,36 +31451,36 @@
         <v>380</v>
       </c>
       <c r="B39" t="s">
-        <v>1731</v>
+        <v>989</v>
       </c>
       <c r="C39" t="s">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="D39" t="s">
-        <v>2110</v>
+        <v>2105</v>
       </c>
       <c r="E39" t="s">
-        <v>2100</v>
+        <v>2029</v>
+      </c>
+      <c r="F39" t="s">
+        <v>2106</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
         <v>390</v>
       </c>
-      <c r="B40" s="31" t="s">
-        <v>214</v>
+      <c r="B40" t="s">
+        <v>1731</v>
       </c>
       <c r="C40" t="s">
-        <v>2020</v>
+        <v>2027</v>
       </c>
       <c r="D40" t="s">
-        <v>2111</v>
+        <v>2107</v>
       </c>
       <c r="E40" t="s">
-        <v>2067</v>
-      </c>
-      <c r="F40" t="s">
-        <v>2068</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -31494,30 +31494,33 @@
         <v>2020</v>
       </c>
       <c r="D41" t="s">
-        <v>2069</v>
+        <v>2108</v>
       </c>
       <c r="E41" t="s">
-        <v>2022</v>
+        <v>2064</v>
       </c>
       <c r="F41" t="s">
-        <v>2070</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
         <v>410</v>
       </c>
-      <c r="B42" t="s">
-        <v>459</v>
+      <c r="B42" s="31" t="s">
+        <v>214</v>
       </c>
       <c r="C42" t="s">
         <v>2020</v>
       </c>
-      <c r="D42" s="31" t="s">
-        <v>2112</v>
+      <c r="D42" t="s">
+        <v>2066</v>
       </c>
       <c r="E42" t="s">
-        <v>2074</v>
+        <v>2022</v>
+      </c>
+      <c r="F42" t="s">
+        <v>2067</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -31525,16 +31528,16 @@
         <v>420</v>
       </c>
       <c r="B43" t="s">
-        <v>345</v>
+        <v>459</v>
       </c>
       <c r="C43" t="s">
         <v>2020</v>
       </c>
       <c r="D43" s="31" t="s">
-        <v>2113</v>
+        <v>2109</v>
       </c>
       <c r="E43" t="s">
-        <v>2086</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -31545,33 +31548,30 @@
         <v>345</v>
       </c>
       <c r="C44" t="s">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="D44" s="31" t="s">
-        <v>2114</v>
+        <v>2110</v>
       </c>
       <c r="E44" t="s">
-        <v>2115</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
         <v>440</v>
       </c>
-      <c r="B45" s="31" t="s">
-        <v>214</v>
+      <c r="B45" t="s">
+        <v>345</v>
       </c>
       <c r="C45" t="s">
-        <v>2020</v>
-      </c>
-      <c r="D45" t="s">
-        <v>2032</v>
+        <v>2027</v>
+      </c>
+      <c r="D45" s="31" t="s">
+        <v>2111</v>
       </c>
       <c r="E45" t="s">
-        <v>2029</v>
-      </c>
-      <c r="F45" t="s">
-        <v>2033</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -31582,13 +31582,16 @@
         <v>214</v>
       </c>
       <c r="C46" t="s">
-        <v>2027</v>
-      </c>
-      <c r="D46" s="31" t="s">
-        <v>2116</v>
+        <v>2020</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2032</v>
       </c>
       <c r="E46" t="s">
-        <v>2115</v>
+        <v>2029</v>
+      </c>
+      <c r="F46" t="s">
+        <v>2033</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -31596,19 +31599,16 @@
         <v>460</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>1815</v>
+        <v>214</v>
       </c>
       <c r="C47" t="s">
-        <v>2020</v>
-      </c>
-      <c r="D47" t="s">
-        <v>2024</v>
+        <v>2027</v>
+      </c>
+      <c r="D47" s="31" t="s">
+        <v>2113</v>
       </c>
       <c r="E47" t="s">
-        <v>2025</v>
-      </c>
-      <c r="F47" t="s">
-        <v>2026</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -31622,10 +31622,30 @@
         <v>2020</v>
       </c>
       <c r="D48" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2025</v>
+      </c>
+      <c r="F48" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>480</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D49" t="s">
         <v>2032</v>
       </c>
-      <c r="E48" t="s">
-        <v>2086</v>
+      <c r="E49" t="s">
+        <v>2083</v>
       </c>
     </row>
   </sheetData>
@@ -31644,42 +31664,42 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="22" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>2118</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="23" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="23" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>2122</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="23" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="24" t="s">
-        <v>2125</v>
+        <v>2122</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
     </row>
   </sheetData>
@@ -31698,34 +31718,34 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="22" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="23" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>2130</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="23" t="s">
-        <v>2131</v>
+        <v>2128</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>2130</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="23" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>2130</v>
+        <v>2127</v>
       </c>
     </row>
   </sheetData>
@@ -31753,19 +31773,19 @@
         <v>2015</v>
       </c>
       <c r="B1" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
       <c r="E1" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
       <c r="F1" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -31776,13 +31796,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E2" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="F2" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -31796,13 +31816,13 @@
         <v>1815</v>
       </c>
       <c r="D3" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E3" t="s">
         <v>2137</v>
       </c>
-      <c r="E3" t="s">
-        <v>2140</v>
-      </c>
       <c r="F3" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -31813,13 +31833,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E4" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="F4" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -31830,13 +31850,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E5" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="F5" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -31850,13 +31870,13 @@
         <v>1428</v>
       </c>
       <c r="D6" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E6" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="F6" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -31870,13 +31890,13 @@
         <v>989</v>
       </c>
       <c r="D7" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E7" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="F7" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -31890,13 +31910,13 @@
         <v>459</v>
       </c>
       <c r="D8" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E8" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="F8" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -31910,13 +31930,13 @@
         <v>1659</v>
       </c>
       <c r="D9" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E9" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="F9" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -31930,13 +31950,13 @@
         <v>1397</v>
       </c>
       <c r="D10" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E10" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="F10" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -31950,13 +31970,13 @@
         <v>214</v>
       </c>
       <c r="D11" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E11" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="F11" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -31970,13 +31990,13 @@
         <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E12" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="F12" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -31990,13 +32010,13 @@
         <v>345</v>
       </c>
       <c r="D13" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E13" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="F13" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -32010,13 +32030,13 @@
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E14" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="F14" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -32030,13 +32050,13 @@
         <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E15" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="F15" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -32050,13 +32070,13 @@
         <v>128</v>
       </c>
       <c r="D16" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E16" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="F16" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -32070,13 +32090,13 @@
         <v>1731</v>
       </c>
       <c r="D17" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E17" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="F17" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -32090,13 +32110,13 @@
         <v>1825</v>
       </c>
       <c r="D18" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E18" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="F18" t="s">
-        <v>2157</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -32111,10 +32131,10 @@
       </c>
       <c r="D19"/>
       <c r="E19" t="s">
-        <v>2359</v>
+        <v>2353</v>
       </c>
       <c r="F19" t="s">
-        <v>2360</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -32129,10 +32149,10 @@
       </c>
       <c r="D20"/>
       <c r="E20" t="s">
-        <v>2359</v>
+        <v>2353</v>
       </c>
       <c r="F20" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -32143,13 +32163,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>2371</v>
+        <v>2365</v>
       </c>
       <c r="F21" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -32160,13 +32180,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E22" t="s">
-        <v>2159</v>
+        <v>2156</v>
       </c>
       <c r="F22" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -32177,13 +32197,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E23" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
       <c r="F23" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -32194,13 +32214,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E24" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
       <c r="F24" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -32211,13 +32231,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E25" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
       <c r="F25" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -32228,13 +32248,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E26" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="F26" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -32245,13 +32265,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E27" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="F27" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -32262,13 +32282,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
       <c r="F28" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -32279,10 +32299,10 @@
         <v>1</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>2171</v>
+        <v>2168</v>
       </c>
       <c r="F29" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -32296,10 +32316,10 @@
         <v>2029</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
       <c r="F30" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -32310,10 +32330,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="F31" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -32324,13 +32344,13 @@
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E32" t="s">
-        <v>2174</v>
+        <v>2171</v>
       </c>
       <c r="F32" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -32341,13 +32361,13 @@
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E33" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
       <c r="F33" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -32358,13 +32378,13 @@
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E34" t="s">
-        <v>2176</v>
+        <v>2173</v>
       </c>
       <c r="F34" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -32375,13 +32395,13 @@
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E35" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
       <c r="F35" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -32392,13 +32412,13 @@
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E36" t="s">
-        <v>2178</v>
+        <v>2175</v>
       </c>
       <c r="F36" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -32409,13 +32429,13 @@
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>2376</v>
+        <v>2370</v>
       </c>
       <c r="F37" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -32426,13 +32446,13 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>2369</v>
+        <v>2363</v>
       </c>
       <c r="F38" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -32443,13 +32463,13 @@
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>2375</v>
+        <v>2369</v>
       </c>
       <c r="F39" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -32460,13 +32480,13 @@
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E40" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
       <c r="F40" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -32477,13 +32497,13 @@
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E41" t="s">
-        <v>2180</v>
+        <v>2177</v>
       </c>
       <c r="F41" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -32494,13 +32514,13 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E42" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
       <c r="F42" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -32511,13 +32531,13 @@
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E43" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
       <c r="F43" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -32528,13 +32548,13 @@
         <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E44" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
       <c r="F44" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -32545,13 +32565,13 @@
         <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E45" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="F45" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -32562,13 +32582,13 @@
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E46" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
       <c r="F46" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -32579,13 +32599,13 @@
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>2370</v>
+        <v>2364</v>
       </c>
       <c r="F47" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -32596,13 +32616,13 @@
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E48" t="s">
-        <v>2187</v>
+        <v>2184</v>
       </c>
       <c r="F48" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -32613,13 +32633,13 @@
         <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E49" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
       <c r="F49" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -32630,13 +32650,13 @@
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E50" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="F50" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -32647,13 +32667,13 @@
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E51" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="F51" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -32664,13 +32684,13 @@
         <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E52" t="s">
-        <v>2191</v>
+        <v>2188</v>
       </c>
       <c r="F52" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -32681,13 +32701,13 @@
         <v>1</v>
       </c>
       <c r="D53" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E53" t="s">
-        <v>2192</v>
+        <v>2189</v>
       </c>
       <c r="F53" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -32698,13 +32718,13 @@
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E54" s="32" t="s">
-        <v>2379</v>
+        <v>2373</v>
       </c>
       <c r="F54" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -32715,13 +32735,13 @@
         <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E55" t="s">
-        <v>2193</v>
+        <v>2190</v>
       </c>
       <c r="F55" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -32732,13 +32752,13 @@
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E56" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="F56" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -32749,13 +32769,13 @@
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E57" t="s">
-        <v>2194</v>
+        <v>2191</v>
       </c>
       <c r="F57" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -32766,13 +32786,13 @@
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E58" t="s">
-        <v>2195</v>
+        <v>2192</v>
       </c>
       <c r="F58" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -32783,13 +32803,13 @@
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E59" t="s">
-        <v>2194</v>
+        <v>2191</v>
       </c>
       <c r="F59" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -32800,13 +32820,13 @@
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E60" t="s">
-        <v>2378</v>
+        <v>2372</v>
       </c>
       <c r="F60" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -32817,13 +32837,13 @@
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E61" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
       <c r="F61" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -32834,13 +32854,13 @@
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E62" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="F62" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -32851,13 +32871,13 @@
         <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>2377</v>
+        <v>2371</v>
       </c>
       <c r="F63" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -32868,13 +32888,13 @@
         <v>1</v>
       </c>
       <c r="D64" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E64" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
       <c r="F64" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -32885,13 +32905,13 @@
         <v>1</v>
       </c>
       <c r="D65" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E65" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
       <c r="F65" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -32902,13 +32922,13 @@
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E66" t="s">
-        <v>2201</v>
+        <v>2198</v>
       </c>
       <c r="F66" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -32919,13 +32939,13 @@
         <v>1</v>
       </c>
       <c r="D67" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E67" t="s">
-        <v>2202</v>
+        <v>2199</v>
       </c>
       <c r="F67" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -32936,13 +32956,13 @@
         <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E68" t="s">
-        <v>2203</v>
+        <v>2200</v>
       </c>
       <c r="F68" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -32953,13 +32973,13 @@
         <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E69" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="F69" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -32970,13 +32990,13 @@
         <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E70" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="F70" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -32987,13 +33007,13 @@
         <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E71" s="32" t="s">
-        <v>2367</v>
+        <v>2361</v>
       </c>
       <c r="F71" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -33004,13 +33024,13 @@
         <v>1</v>
       </c>
       <c r="D72" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E72" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="F72" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -33021,13 +33041,13 @@
         <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E73" t="s">
-        <v>2206</v>
+        <v>2203</v>
       </c>
       <c r="F73" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -33038,13 +33058,13 @@
         <v>1</v>
       </c>
       <c r="D74" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E74" t="s">
-        <v>2364</v>
+        <v>2358</v>
       </c>
       <c r="F74" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -33055,13 +33075,13 @@
         <v>1</v>
       </c>
       <c r="D75" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E75" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
       <c r="F75" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -33072,13 +33092,13 @@
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E76" t="s">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="F76" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -33089,13 +33109,13 @@
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E77" t="s">
-        <v>2208</v>
+        <v>2205</v>
       </c>
       <c r="F77" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -33106,13 +33126,13 @@
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E78" t="s">
-        <v>2209</v>
+        <v>2206</v>
       </c>
       <c r="F78" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -33123,13 +33143,13 @@
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E79" t="s">
-        <v>2210</v>
+        <v>2207</v>
       </c>
       <c r="F79" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -33140,13 +33160,13 @@
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E80" t="s">
-        <v>2211</v>
+        <v>2208</v>
       </c>
       <c r="F80" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -33157,13 +33177,13 @@
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E81" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
       <c r="F81" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -33174,13 +33194,13 @@
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E82" t="s">
-        <v>2213</v>
+        <v>2210</v>
       </c>
       <c r="F82" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -33191,13 +33211,13 @@
         <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E83" t="s">
-        <v>2159</v>
+        <v>2156</v>
       </c>
       <c r="F83" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -33208,13 +33228,13 @@
         <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E84" t="s">
-        <v>2214</v>
+        <v>2211</v>
       </c>
       <c r="F84" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -33225,13 +33245,13 @@
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E85" t="s">
-        <v>2215</v>
+        <v>2212</v>
       </c>
       <c r="F85" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -33242,13 +33262,13 @@
         <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E86" t="s">
-        <v>2216</v>
+        <v>2213</v>
       </c>
       <c r="F86" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -33259,13 +33279,13 @@
         <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E87" t="s">
-        <v>2214</v>
+        <v>2211</v>
       </c>
       <c r="F87" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -33276,13 +33296,13 @@
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E88" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
       <c r="F88" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -33293,13 +33313,13 @@
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E89" t="s">
-        <v>2217</v>
+        <v>2214</v>
       </c>
       <c r="F89" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -33310,13 +33330,13 @@
         <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E90" t="s">
-        <v>2218</v>
+        <v>2215</v>
       </c>
       <c r="F90" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -33327,13 +33347,13 @@
         <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E91" t="s">
-        <v>2219</v>
+        <v>2216</v>
       </c>
       <c r="F91" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -33344,13 +33364,13 @@
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E92" t="s">
-        <v>2220</v>
+        <v>2217</v>
       </c>
       <c r="F92" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -33361,13 +33381,13 @@
         <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E93" t="s">
-        <v>2221</v>
+        <v>2218</v>
       </c>
       <c r="F93" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -33378,13 +33398,13 @@
         <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E94" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="F94" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -33395,13 +33415,13 @@
         <v>1</v>
       </c>
       <c r="D95" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E95" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="F95" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -33412,13 +33432,13 @@
         <v>1</v>
       </c>
       <c r="D96" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E96" t="s">
-        <v>2226</v>
+        <v>2223</v>
       </c>
       <c r="F96" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
     </row>
   </sheetData>
@@ -33441,69 +33461,69 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="26" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D1" s="26" t="s">
         <v>2227</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>2228</v>
-      </c>
-      <c r="C1" s="26" t="s">
-        <v>2229</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>2230</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="29" t="s">
-        <v>2231</v>
+        <v>2228</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="29" t="s">
-        <v>2233</v>
+        <v>2230</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="28" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="29" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
       <c r="D5" s="29">
         <v>13</v>
@@ -33511,27 +33531,27 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="28" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="28" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="D7" s="29">
         <v>50</v>
@@ -33539,10 +33559,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="28" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>964</v>
@@ -33553,10 +33573,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="30" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>964</v>
@@ -33567,10 +33587,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="28" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>964</v>
@@ -33581,10 +33601,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="28" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C11" s="29" t="s">
         <v>964</v>
@@ -33595,10 +33615,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="29" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C12" s="29" t="s">
         <v>964</v>
@@ -33609,10 +33629,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="29" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C13" s="29" t="s">
         <v>964</v>
@@ -33623,10 +33643,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="28" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C14" s="29" t="s">
         <v>964</v>
@@ -33637,10 +33657,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="28" t="s">
-        <v>2242</v>
+        <v>2239</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C15" s="29" t="s">
         <v>964</v>
@@ -33651,10 +33671,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="28" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C16" s="29" t="s">
         <v>459</v>
@@ -33665,10 +33685,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="28" t="s">
-        <v>2243</v>
+        <v>2240</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C17" s="29" t="s">
         <v>989</v>
@@ -33679,10 +33699,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="30" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C18" s="29" t="s">
         <v>1428</v>
@@ -33693,10 +33713,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="28" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C19" s="28" t="s">
         <v>964</v>
@@ -33707,10 +33727,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="30" t="s">
-        <v>2244</v>
+        <v>2241</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C20" s="29" t="s">
         <v>964</v>
@@ -33721,10 +33741,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="29" t="s">
-        <v>2245</v>
+        <v>2242</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C21" s="29" t="s">
         <v>964</v>
@@ -33735,10 +33755,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="29" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C22" s="29" t="s">
         <v>964</v>
@@ -33749,10 +33769,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="28" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C23" s="29" t="s">
         <v>964</v>
@@ -33763,10 +33783,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="29" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C24" s="29" t="s">
         <v>964</v>
@@ -33777,10 +33797,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="28" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C25" s="29" t="s">
         <v>964</v>
@@ -33791,10 +33811,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="28" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C26" s="29" t="s">
         <v>459</v>
@@ -33805,10 +33825,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="28" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C27" s="29" t="s">
         <v>989</v>
@@ -33819,13 +33839,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="30" t="s">
-        <v>2247</v>
+        <v>2244</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="D28" s="29">
         <v>0</v>
@@ -33833,10 +33853,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="30" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C29" s="29" t="s">
         <v>1428</v>
@@ -33847,10 +33867,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="28" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C30" s="28" t="s">
         <v>964</v>
@@ -33861,10 +33881,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="29" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
       <c r="B31" s="29" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C31" s="29" t="s">
         <v>964</v>
@@ -33875,10 +33895,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="28" t="s">
-        <v>2248</v>
+        <v>2245</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C32" s="28" t="s">
         <v>964</v>
@@ -33889,10 +33909,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="29" t="s">
-        <v>2157</v>
+        <v>2154</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C33" s="29" t="s">
         <v>964</v>
@@ -33903,10 +33923,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="29" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C34" s="29" t="s">
         <v>964</v>
@@ -33917,13 +33937,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="29" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="D35" s="29">
         <v>12</v>
@@ -33931,13 +33951,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="29" t="s">
-        <v>2250</v>
+        <v>2247</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>2250</v>
+        <v>2247</v>
       </c>
       <c r="D36" s="29">
         <v>14</v>
@@ -33945,13 +33965,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="30" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
       <c r="B37" s="29" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="D37" s="29">
         <v>0</v>
@@ -33959,13 +33979,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="28" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="D38" s="29">
         <v>51</v>
@@ -33973,13 +33993,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="29" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
       <c r="D39" s="29">
         <v>11</v>
@@ -33987,27 +34007,27 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="28" t="s">
-        <v>2252</v>
+        <v>2249</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="28" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="D41" s="29">
         <v>0</v>
@@ -34015,10 +34035,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="29" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C42" s="29" t="s">
         <v>964</v>
@@ -34027,10 +34047,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="29" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C43" s="29" t="s">
         <v>964</v>
@@ -34049,24 +34069,24 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="84.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="106.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.85546875" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>2381</v>
+        <v>2375</v>
       </c>
       <c r="B1" t="s">
-        <v>2382</v>
+        <v>2376</v>
       </c>
       <c r="C1" t="s">
-        <v>2383</v>
+        <v>2377</v>
       </c>
       <c r="D1" t="s">
         <v>2019</v>
@@ -34074,805 +34094,816 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2257</v>
+        <v>2254</v>
       </c>
       <c r="B2" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="C2" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2333</v>
+        <v>2384</v>
       </c>
       <c r="B3" t="s">
-        <v>2256</v>
+        <v>2253</v>
       </c>
       <c r="C3" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2355</v>
+        <v>2349</v>
       </c>
       <c r="B4" t="s">
-        <v>2326</v>
+        <v>2322</v>
       </c>
       <c r="C4" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="B5" t="s">
         <v>2028</v>
       </c>
       <c r="C5" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B6" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="C6" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="B7" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="C7" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2337</v>
+        <v>2380</v>
       </c>
       <c r="B8" t="s">
-        <v>2338</v>
+        <v>2332</v>
       </c>
       <c r="C8" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2339</v>
+        <v>2333</v>
       </c>
       <c r="B9" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="C9" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B10" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="C10" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2332</v>
+        <v>2328</v>
       </c>
       <c r="B11" t="s">
-        <v>2331</v>
+        <v>2327</v>
       </c>
       <c r="C11" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2340</v>
+        <v>2334</v>
       </c>
       <c r="B12" t="s">
-        <v>2341</v>
+        <v>2335</v>
       </c>
       <c r="C12" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="31" t="s">
-        <v>2342</v>
+        <v>2336</v>
       </c>
       <c r="B13" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
       <c r="C13" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2343</v>
+        <v>2337</v>
       </c>
       <c r="B14" t="s">
-        <v>2344</v>
+        <v>2338</v>
       </c>
       <c r="C14" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2345</v>
+        <v>2339</v>
       </c>
       <c r="B15" t="s">
-        <v>2346</v>
+        <v>2340</v>
       </c>
       <c r="C15" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="31" t="s">
-        <v>2347</v>
+        <v>2341</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>2348</v>
+        <v>2342</v>
       </c>
       <c r="C16" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>2349</v>
+        <v>2343</v>
       </c>
       <c r="B17" t="s">
-        <v>2350</v>
+        <v>2344</v>
       </c>
       <c r="C17" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>2351</v>
+        <v>2345</v>
       </c>
       <c r="B18" t="s">
-        <v>2352</v>
+        <v>2346</v>
       </c>
       <c r="C18" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>2354</v>
+        <v>2348</v>
       </c>
       <c r="B19" t="s">
-        <v>2353</v>
+        <v>2347</v>
       </c>
       <c r="C19" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>2250</v>
+        <v>2247</v>
       </c>
       <c r="B20" t="s">
-        <v>2358</v>
+        <v>2352</v>
       </c>
       <c r="C20" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>2374</v>
+        <v>2368</v>
       </c>
       <c r="B21" t="s">
-        <v>2254</v>
+        <v>2251</v>
       </c>
       <c r="C21" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>2320</v>
+        <v>2317</v>
       </c>
       <c r="B22" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="C22" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>2253</v>
+        <v>2250</v>
       </c>
       <c r="B23" t="s">
-        <v>2357</v>
+        <v>2351</v>
       </c>
       <c r="C23" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>2336</v>
+        <v>2331</v>
       </c>
       <c r="B24" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="C24" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>2365</v>
+        <v>2359</v>
       </c>
       <c r="B25" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
       <c r="C25" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>2260</v>
+        <v>2257</v>
       </c>
       <c r="B26" t="s">
-        <v>2261</v>
+        <v>2258</v>
       </c>
       <c r="C26" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>2262</v>
+        <v>2259</v>
       </c>
       <c r="B27" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="C27" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="B28" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="C28" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="B29" t="s">
         <v>2028</v>
       </c>
       <c r="C29" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B30" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="C30" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>2361</v>
+        <v>2355</v>
       </c>
       <c r="B31" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="C31" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="B32" t="s">
         <v>989</v>
       </c>
       <c r="C32" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="B33" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
       <c r="C33" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="B34" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="C34" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="B35" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="C35" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="B36" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
       <c r="C36" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
       <c r="B37" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="C37" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>2278</v>
+        <v>2275</v>
       </c>
       <c r="B38" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="C38" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="B39" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="C39" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="B40" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="C40" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="B41" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="C41" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="B42" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="C42" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="B43" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="C43" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="B44" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
       <c r="C44" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="B45" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="C45" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
       <c r="B46" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="C46" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="B47" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="C47" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="B48" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="C48" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>2368</v>
+        <v>2362</v>
       </c>
       <c r="B49" t="s">
         <v>1888</v>
       </c>
       <c r="C49" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="B50" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="C50" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="B51" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
       <c r="C51" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="B52" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="C52" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="B53" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="C53" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="B54" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="C54" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>2334</v>
+        <v>2329</v>
       </c>
       <c r="B55" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C55" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="B56" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="C56" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="B57" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="C57" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>2310</v>
+        <v>2307</v>
       </c>
       <c r="B58" t="s">
-        <v>2311</v>
+        <v>2308</v>
       </c>
       <c r="C58" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>2312</v>
+        <v>2309</v>
       </c>
       <c r="B59" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="C59" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>2356</v>
+        <v>2350</v>
       </c>
       <c r="B60" t="s">
-        <v>2314</v>
+        <v>2311</v>
       </c>
       <c r="C60" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>2315</v>
+        <v>2312</v>
       </c>
       <c r="B61" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="C61" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>2317</v>
+        <v>2314</v>
       </c>
       <c r="B62" t="s">
-        <v>2318</v>
+        <v>2315</v>
       </c>
       <c r="C62" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>2328</v>
+        <v>2324</v>
       </c>
       <c r="B63" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="C63" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>2321</v>
+        <v>2379</v>
       </c>
       <c r="B64" t="s">
         <v>2029</v>
       </c>
       <c r="C64" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
       <c r="B65" t="s">
-        <v>2323</v>
+        <v>2319</v>
       </c>
       <c r="C65" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>2324</v>
+        <v>2320</v>
       </c>
       <c r="B66" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="C66" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>2325</v>
+        <v>2321</v>
       </c>
       <c r="B67" t="s">
-        <v>2326</v>
+        <v>2322</v>
       </c>
       <c r="C67" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>2327</v>
+        <v>2323</v>
       </c>
       <c r="B68" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="C68" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>2329</v>
+        <v>2325</v>
       </c>
       <c r="B69" t="s">
-        <v>2330</v>
+        <v>2326</v>
       </c>
       <c r="C69" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>2332</v>
+        <v>2328</v>
       </c>
       <c r="B70" t="s">
-        <v>2331</v>
+        <v>2327</v>
       </c>
       <c r="C70" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>2335</v>
+        <v>2330</v>
       </c>
       <c r="B71" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="C71" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>2362</v>
+        <v>2356</v>
       </c>
       <c r="B72" t="s">
-        <v>2363</v>
+        <v>2357</v>
       </c>
       <c r="C72" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>2366</v>
+        <v>2360</v>
       </c>
       <c r="B73" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="C73" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>2372</v>
+        <v>2366</v>
       </c>
       <c r="B74" t="s">
-        <v>2373</v>
+        <v>2367</v>
       </c>
       <c r="C74" t="s">
-        <v>2384</v>
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B75" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2378</v>
       </c>
     </row>
   </sheetData>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Koding\tool-fcost\masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARISAFARI\Works\Project Applications\tool-fcost\masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1332D24D-101B-4C37-82BC-567689E71700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -32,12 +31,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">part_list!$A$1:$B$1834</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">symptom!$A$1:$F$41</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4769" uniqueCount="2457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4851" uniqueCount="2483">
   <si>
     <t>part_used</t>
   </si>
@@ -6303,9 +6302,6 @@
     <t>action</t>
   </si>
   <si>
-    <t>ext|external|cairan|cleaning|semut|kotor|bersih|bersihkan|kardus rusak</t>
-  </si>
-  <si>
     <t>EXTERNAL</t>
   </si>
   <si>
@@ -6315,9 +6311,6 @@
     <t>CANCEL</t>
   </si>
   <si>
-    <t>cek normal|cek ok|unit cek ok|normal|fungsi ok|test fungsi|cek fungsi ok|cek unit|reposisi antena|antena</t>
-  </si>
-  <si>
     <t>USER</t>
   </si>
   <si>
@@ -6345,9 +6338,6 @@
     <t>FACTORY_RESET</t>
   </si>
   <si>
-    <t>setting|set up data|reset program|reset pabrik|stel ulang program|restart program|program ulang|reset unit|unit reset|reset ulang|riset program|data error-reset</t>
-  </si>
-  <si>
     <t>SETTING</t>
   </si>
   <si>
@@ -7408,12 +7398,99 @@
   </si>
   <si>
     <t>perbaikan remote|repair remote|resolder ulang sensor|remote</t>
+  </si>
+  <si>
+    <t>cek normal|cek ok|unit cek ok|normal|fungsi ok|test fungsi|cek fungsi ok|cek unit|reposisi antena|antena|DITEST OK</t>
+  </si>
+  <si>
+    <t>RESOLDER IC3101|RESOLDER IC7891|IC3101</t>
+  </si>
+  <si>
+    <t>lvds</t>
+  </si>
+  <si>
+    <t>setting|set up data|reset program|reset pabrik|stel ulang program|restart program|program ulang|reset unit|unit reset|reset ulang|riset program|data error-reset|RESTAR PROGRAM|RESET-ULANG|RESET MENU|RESET DATA|INSTALL ULANG</t>
+  </si>
+  <si>
+    <t>GANTI MAINBOARD|TU1102</t>
+  </si>
+  <si>
+    <t>PETIR</t>
+  </si>
+  <si>
+    <t>service power|repair power|repair regulator|repair modul|resolder power|resolder blok power|resolder modul power|resoldering modul|resoldering psu|resoldering|perbaikan power|perbaikan modul power|perbaiki power|ganti d1012|ganti dioda|REPAIR PCB|POWER</t>
+  </si>
+  <si>
+    <t>service main|repair main|repair main unit|repair pwb main|repair pwb|resolder main|resoldering main|resoldering mb|resolder ic7801|resolder ic memory|d7801|resolder blok main|resolder pwb|resolder pcb main|perbaikan main|perbaiki main|solder main|flash eprom|tuner|rusak main|REPAIR-MAIN</t>
+  </si>
+  <si>
+    <t>ext|external|cairan|cleaning|semut|kotor|bersih|bersihkan|kardus rusak|EKSTERNAL</t>
+  </si>
+  <si>
+    <t>RESOLDER R323|RESOLDER DIODA|Q4</t>
+  </si>
+  <si>
+    <t>COVER|FRAME</t>
+  </si>
+  <si>
+    <t>BACKLIGHT|BACK LIGHT|BACKLIG|LAMPU BACKLIG|LED BACKLIGHT|SOCKET BACKLIGHT|PANEL BACKLIGHT</t>
+  </si>
+  <si>
+    <t>LCD-PW|MATI TOTAL|MATI STANDBY|MATI-MATI|MATI$|STANDBY|POWER TIDAK FUNGSI</t>
+  </si>
+  <si>
+    <t>FUSE|DIODA|VARISTOR|CAPACITOR|TRANSISTOR|THERMOSTAT|Q702|Q4|REGULATOR|MODUL INVERTER|POWER|PWB RUSAK|RESOLDER MODUL|REPAIR MODUL</t>
+  </si>
+  <si>
+    <t>MAIN UNIT|MAINBOARD|MAIN-RUSAK|DIODA MAIN|IC MEMORY|COAX|AUDIO OUT|KABEL RCA|MICROPHONE|CONNECTOR AUDIO</t>
+  </si>
+  <si>
+    <t>TCON|TIKON</t>
+  </si>
+  <si>
+    <t>REPAIR_TCON_UNIT</t>
+  </si>
+  <si>
+    <t>REMOTE|REMOT|REMOTRE|DIREMOT|SENSOR ERROR|TIDAK RESPON.*REMOT</t>
+  </si>
+  <si>
+    <t>SENSOR IR|IR SENSOR|MODUL IR|SOCKET IR|REPAIR SENSOR IR|RESOLDER MODUL IR</t>
+  </si>
+  <si>
+    <t>KNOP|SWITCH POWE|TOMBOL</t>
+  </si>
+  <si>
+    <t>AC CORD|KABEL POWER</t>
+  </si>
+  <si>
+    <t>LUDS|LVDS|REPOSISI SOKET</t>
+  </si>
+  <si>
+    <t>RESET|SET ULANG|PENGATURAN PABRIK|CARI SIARAN|INSTAL ULANG|INSTALL ULANG|RESTART UNIT|RESTART|NO CHANGEL|CONNECTING ULANG|WIFI|INTERNET</t>
+  </si>
+  <si>
+    <t>FACTOYY|FACTORY</t>
+  </si>
+  <si>
+    <t>SUBT|SUBTITUSI|SUBSTITUSI|TKR|TUKAR|PENARIKAN DAN PENGANTARAN</t>
+  </si>
+  <si>
+    <t>CLAIM|KLAIM|GARANSI|TGG ACC|MAU DISERVICE|MAU TKR|CEK INFORMASI|DIKERJAKN KONS SENDIRI|DIKERJAKAN KONS SENDIRI</t>
+  </si>
+  <si>
+    <t>SEMUT|KENA SEMUT|BAUT KAKI PATAH|KOROSIF|RENGGANG</t>
+  </si>
+  <si>
+    <t>KOROSIF|BERSIHKAN SHEET|KOTOR|RENGGANG|LEPAS-BAUT|BAUT-PATAH|PASANG ULANG|PSNG ULANG</t>
+  </si>
+  <si>
+    <t>CEK FNGSI|CEK UNIT|CEK-UNIT|CEK FUNGSI|TES FUNGSI|OKE|OK</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="10">
     <font>
       <sz val="11"/>
@@ -7470,13 +7547,15 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7486,6 +7565,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -7526,7 +7611,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7538,19 +7623,23 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 3 14" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Normal 13 2 2 10 2 2 5 2 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 13 2 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 133 2 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 195" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Normal 2 2 7 2 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal 315" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Normal 80" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 10 3 14" xfId="7"/>
+    <cellStyle name="Normal 13 2 2 10 2 2 5 2 2 2 2" xfId="3"/>
+    <cellStyle name="Normal 13 2 2 2" xfId="4"/>
+    <cellStyle name="Normal 133 2 2" xfId="6"/>
+    <cellStyle name="Normal 195" xfId="8"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 2 2" xfId="10"/>
+    <cellStyle name="Normal 2 2 7 2 2 2" xfId="5"/>
+    <cellStyle name="Normal 315" xfId="9"/>
+    <cellStyle name="Normal 80" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -7827,7 +7916,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B1834"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -22508,13 +22597,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1834" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:B1834"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -23091,13 +23180,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B71" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:B71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -23140,13 +23229,13 @@
         <v>2021</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -23160,13 +23249,13 @@
         <v>2021</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -23180,13 +23269,13 @@
         <v>2021</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -23200,13 +23289,13 @@
         <v>2021</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -23220,13 +23309,13 @@
         <v>2021</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -23240,13 +23329,13 @@
         <v>2021</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -23260,13 +23349,13 @@
         <v>2021</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -23280,13 +23369,13 @@
         <v>2021</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -23300,13 +23389,13 @@
         <v>2021</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2440</v>
+        <v>2437</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>2362</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -23320,13 +23409,13 @@
         <v>2021</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2436</v>
+        <v>2433</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>2363</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -23346,7 +23435,7 @@
         <v>2027</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>2364</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -23366,7 +23455,7 @@
         <v>2029</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>2365</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -23386,7 +23475,7 @@
         <v>2031</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>2366</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -23406,7 +23495,7 @@
         <v>2033</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>2367</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -23420,7 +23509,7 @@
         <v>2021</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2441</v>
+        <v>2438</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>2034</v>
@@ -23440,13 +23529,13 @@
         <v>2021</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2368</v>
+        <v>2365</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>2036</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>2369</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -23460,13 +23549,13 @@
         <v>2021</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2370</v>
+        <v>2367</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>2371</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -23480,13 +23569,13 @@
         <v>2021</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2372</v>
+        <v>2369</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>2037</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>2373</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -23500,7 +23589,7 @@
         <v>2021</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2447</v>
+        <v>2444</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>2036</v>
@@ -23526,7 +23615,7 @@
         <v>2040</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>2375</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -23560,13 +23649,13 @@
         <v>2021</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2376</v>
+        <v>2373</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>2044</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>2377</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -23580,13 +23669,13 @@
         <v>2021</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>2448</v>
+        <v>2445</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>2378</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -23600,7 +23689,7 @@
         <v>2021</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2446</v>
+        <v>2443</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>2045</v>
@@ -23640,7 +23729,7 @@
         <v>2021</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>2379</v>
+        <v>2376</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>2050</v>
@@ -23700,7 +23789,7 @@
         <v>2021</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>2449</v>
+        <v>2446</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>2058</v>
@@ -23726,7 +23815,7 @@
         <v>2036</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>2380</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -23740,7 +23829,7 @@
         <v>2021</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2381</v>
+        <v>2378</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>2061</v>
@@ -23766,7 +23855,7 @@
         <v>2053</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -23800,13 +23889,13 @@
         <v>2021</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>2372</v>
+        <v>2369</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>2037</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>2383</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -23820,13 +23909,13 @@
         <v>2021</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>2384</v>
+        <v>2381</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>2058</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>2385</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -23840,7 +23929,7 @@
         <v>2021</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>2379</v>
+        <v>2376</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>2050</v>
@@ -23860,13 +23949,13 @@
         <v>2021</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>2386</v>
+        <v>2383</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>2044</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>2387</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -23918,13 +24007,13 @@
         <v>2021</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>2388</v>
+        <v>2385</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>2389</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -23936,13 +24025,13 @@
         <v>2021</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>2433</v>
+        <v>2430</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>2390</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -23954,13 +24043,13 @@
         <v>2021</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>2432</v>
+        <v>2429</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>2044</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>2391</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -23972,13 +24061,13 @@
         <v>2021</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>2392</v>
+        <v>2389</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>2033</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>2393</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -23990,13 +24079,13 @@
         <v>2021</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>2394</v>
+        <v>2391</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>2061</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>2395</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -24008,13 +24097,13 @@
         <v>2021</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2396</v>
+        <v>2393</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>2053</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>2397</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -24026,13 +24115,13 @@
         <v>2021</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>2455</v>
+        <v>2452</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>2045</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>2398</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -24044,13 +24133,13 @@
         <v>2021</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>2399</v>
+        <v>2396</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>2037</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>2400</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -24062,13 +24151,13 @@
         <v>2021</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>2401</v>
+        <v>2398</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>2402</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -24080,13 +24169,13 @@
         <v>2021</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>2403</v>
+        <v>2400</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>2029</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>2404</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -24098,13 +24187,13 @@
         <v>2021</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>2405</v>
+        <v>2402</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>2406</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -24116,13 +24205,13 @@
         <v>2021</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>2407</v>
+        <v>2404</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>2056</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>2408</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -24134,13 +24223,13 @@
         <v>2021</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>2409</v>
+        <v>2406</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>2036</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>2410</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -24154,13 +24243,13 @@
         <v>2021</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>2411</v>
+        <v>2408</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>2412</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -24174,13 +24263,13 @@
         <v>2021</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>2413</v>
+        <v>2410</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>2027</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>2414</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -24194,13 +24283,13 @@
         <v>2021</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>2415</v>
+        <v>2412</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>2416</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -24212,13 +24301,13 @@
         <v>2021</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>2417</v>
+        <v>2414</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>2418</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -24230,13 +24319,13 @@
         <v>2021</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>2419</v>
+        <v>2416</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>2420</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -24248,13 +24337,13 @@
         <v>2021</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>2421</v>
+        <v>2418</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>2036</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>2422</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -24266,13 +24355,13 @@
         <v>2021</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>2423</v>
+        <v>2420</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>2058</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>2424</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -24284,13 +24373,13 @@
         <v>2021</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>2425</v>
+        <v>2422</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>2044</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>2426</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -24304,13 +24393,13 @@
         <v>2021</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>2427</v>
+        <v>2424</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>2036</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>2428</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -24324,13 +24413,13 @@
         <v>2021</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>2429</v>
+        <v>2426</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>2044</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>2430</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -24344,7 +24433,7 @@
         <v>2021</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>2374</v>
+        <v>2371</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>2036</v>
@@ -24364,7 +24453,7 @@
         <v>2021</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>2374</v>
+        <v>2371</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>2036</v>
@@ -24384,7 +24473,7 @@
         <v>2021</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>2374</v>
+        <v>2371</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>2036</v>
@@ -24404,7 +24493,7 @@
         <v>2021</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>2374</v>
+        <v>2371</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>2036</v>
@@ -24447,7 +24536,7 @@
         <v>2060</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>2439</v>
+        <v>2436</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>2038</v>
@@ -24461,7 +24550,7 @@
         <v>2021</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>2374</v>
+        <v>2371</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>2036</v>
@@ -24496,10 +24585,10 @@
         <v>2021</v>
       </c>
       <c r="D72" t="s">
-        <v>2434</v>
+        <v>2431</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>2435</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -24513,10 +24602,10 @@
         <v>2021</v>
       </c>
       <c r="D73" t="s">
-        <v>2437</v>
+        <v>2434</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -24528,7 +24617,7 @@
         <v>2021</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2438</v>
+        <v>2435</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>2058</v>
@@ -24545,13 +24634,13 @@
         <v>2021</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>2444</v>
+        <v>2441</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>2058</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>2383</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -24565,7 +24654,7 @@
         <v>2021</v>
       </c>
       <c r="D76" t="s">
-        <v>2445</v>
+        <v>2442</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>2050</v>
@@ -24582,10 +24671,10 @@
         <v>2021</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>2451</v>
+        <v>2448</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>2452</v>
+        <v>2449</v>
       </c>
       <c r="F77" s="3"/>
     </row>
@@ -24597,20 +24686,20 @@
         <v>2021</v>
       </c>
       <c r="D78" t="s">
-        <v>2453</v>
+        <v>2450</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>2454</v>
+        <v>2451</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F41" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:F41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -24657,13 +24746,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:B5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -24704,14 +24793,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B4" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:B4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -24753,10 +24842,10 @@
         <v>2060</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>2462</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>2088</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>2089</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -24771,13 +24860,13 @@
         <v>2060</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>2089</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>2090</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:6" ht="30">
       <c r="A4" s="1">
         <v>30</v>
       </c>
@@ -24789,10 +24878,10 @@
         <v>2060</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2092</v>
+        <v>2454</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -24807,10 +24896,10 @@
         <v>2060</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -24825,10 +24914,10 @@
         <v>2060</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -24843,10 +24932,10 @@
         <v>2060</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -24861,13 +24950,13 @@
         <v>2060</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>2101</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="30">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="45">
       <c r="A9" s="1">
         <v>80</v>
       </c>
@@ -24879,10 +24968,10 @@
         <v>2060</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2102</v>
+        <v>2457</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -24899,10 +24988,10 @@
         <v>2060</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -24919,10 +25008,10 @@
         <v>2060</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -24939,10 +25028,10 @@
         <v>2060</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>2108</v>
+        <v>2105</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -24959,10 +25048,10 @@
         <v>2060</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2110</v>
+        <v>2107</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -24979,10 +25068,10 @@
         <v>2060</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>2112</v>
+        <v>2109</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -24999,10 +25088,10 @@
         <v>2060</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -25019,10 +25108,10 @@
         <v>2060</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -25039,10 +25128,10 @@
         <v>2060</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2118</v>
+        <v>2115</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -25059,10 +25148,10 @@
         <v>2060</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -25079,10 +25168,10 @@
         <v>2060</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -25099,10 +25188,10 @@
         <v>2060</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>2122</v>
+        <v>2119</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -25119,10 +25208,10 @@
         <v>2060</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>2125</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -25139,10 +25228,10 @@
         <v>2060</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="45">
@@ -25159,10 +25248,10 @@
         <v>2060</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="45">
@@ -25179,10 +25268,10 @@
         <v>2060</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>2130</v>
+        <v>2127</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>2131</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -25199,10 +25288,10 @@
         <v>2060</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -25219,10 +25308,10 @@
         <v>2060</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -25239,10 +25328,10 @@
         <v>2060</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -25259,10 +25348,10 @@
         <v>2060</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -25282,7 +25371,7 @@
         <v>2060</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -25302,7 +25391,7 @@
         <v>2060</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -25322,7 +25411,7 @@
         <v>2060</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -25342,7 +25431,7 @@
         <v>2060</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -25362,7 +25451,7 @@
         <v>2060</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>2131</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -25382,7 +25471,7 @@
         <v>2060</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -25402,7 +25491,7 @@
         <v>2060</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -25422,7 +25511,7 @@
         <v>2060</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -25442,7 +25531,7 @@
         <v>2060</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -25462,7 +25551,7 @@
         <v>2060</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -25482,7 +25571,7 @@
         <v>2060</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -25502,7 +25591,7 @@
         <v>2060</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -25522,7 +25611,7 @@
         <v>2060</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -25542,7 +25631,7 @@
         <v>2060</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>2125</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -25562,7 +25651,7 @@
         <v>2060</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -25577,13 +25666,13 @@
         <v>2060</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>2456</v>
+        <v>2453</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>2133</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="45">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="60">
       <c r="A45" s="1">
         <v>440</v>
       </c>
@@ -25595,10 +25684,10 @@
         <v>2060</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>2128</v>
+        <v>2461</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="45">
@@ -25613,20 +25702,502 @@
         <v>2060</v>
       </c>
       <c r="E46" s="1" t="s">
+        <v>2460</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="1">
+        <v>460</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E47" t="s">
+        <v>2455</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="1">
+        <v>470</v>
+      </c>
+      <c r="B48" s="1">
+        <v>1</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>2463</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="1">
+        <v>480</v>
+      </c>
+      <c r="B49" s="1">
+        <v>1</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2458</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="1">
+        <v>490</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>2456</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="1">
+        <v>500</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2464</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="1">
+        <v>510</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>2462</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="1">
+        <v>520</v>
+      </c>
+      <c r="B53" s="1">
+        <v>1</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1" t="s">
+        <v>2462</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="1">
+        <v>530</v>
+      </c>
+      <c r="B54" s="1">
+        <v>1</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2459</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="1">
+        <v>540</v>
+      </c>
+      <c r="B55" s="1">
+        <v>1</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2459</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="1">
+        <v>550</v>
+      </c>
+      <c r="B56" s="1">
+        <v>1</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E56" t="s">
+        <v>2188</v>
+      </c>
+      <c r="F56" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="5">
+        <v>560</v>
+      </c>
+      <c r="B57" s="5">
+        <v>1</v>
+      </c>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>2465</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="5">
+        <v>570</v>
+      </c>
+      <c r="B58" s="6">
+        <v>1</v>
+      </c>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6" t="s">
+        <v>2466</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="5">
+        <v>580</v>
+      </c>
+      <c r="B59" s="6">
+        <v>1</v>
+      </c>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>2467</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="5">
+        <v>590</v>
+      </c>
+      <c r="B60" s="6">
+        <v>1</v>
+      </c>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>2468</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="5">
+        <v>600</v>
+      </c>
+      <c r="B61" s="6">
+        <v>1</v>
+      </c>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>2469</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="5">
+        <v>610</v>
+      </c>
+      <c r="B62" s="6">
+        <v>1</v>
+      </c>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6" t="s">
+        <v>2471</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F62" s="6" t="s">
         <v>2130</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>2131</v>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="5">
+        <v>620</v>
+      </c>
+      <c r="B63" s="6">
+        <v>1</v>
+      </c>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>2472</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="5">
+        <v>630</v>
+      </c>
+      <c r="B64" s="6">
+        <v>1</v>
+      </c>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>2473</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="5">
+        <v>640</v>
+      </c>
+      <c r="B65" s="6">
+        <v>1</v>
+      </c>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>2474</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="5">
+        <v>650</v>
+      </c>
+      <c r="B66" s="6">
+        <v>1</v>
+      </c>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>2475</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="5">
+        <v>660</v>
+      </c>
+      <c r="B67" s="6">
+        <v>1</v>
+      </c>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>2476</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="5">
+        <v>670</v>
+      </c>
+      <c r="B68" s="6">
+        <v>1</v>
+      </c>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>2477</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="5">
+        <v>680</v>
+      </c>
+      <c r="B69" s="6">
+        <v>1</v>
+      </c>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="5">
+        <v>690</v>
+      </c>
+      <c r="B70" s="6">
+        <v>1</v>
+      </c>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>2479</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="5">
+        <v>700</v>
+      </c>
+      <c r="B71" s="6">
+        <v>1</v>
+      </c>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6" t="s">
+        <v>2480</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="5">
+        <v>710</v>
+      </c>
+      <c r="B72" s="6">
+        <v>1</v>
+      </c>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>2481</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="5">
+        <v>720</v>
+      </c>
+      <c r="B73" s="6">
+        <v>1</v>
+      </c>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>2482</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>2091</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F43" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -25638,584 +26209,584 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2138</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2139</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2140</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2141</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2157</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2159</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>459</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>989</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>2131</v>
+        <v>2128</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>1429</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2171</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2174</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2176</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>459</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>989</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2178</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30">
       <c r="A28" s="1" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>1429</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2180</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>2125</v>
+        <v>2122</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2187</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>2191</v>
+        <v>2188</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>2192</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2193</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>2194</v>
+        <v>2191</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>964</v>
@@ -26224,10 +26795,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>964</v>
@@ -26235,13 +26806,13 @@
       <c r="D43" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D43" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <autoFilter ref="A1:D43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -26253,13 +26824,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>2195</v>
+        <v>2192</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2020</v>
@@ -26267,7 +26838,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2037</v>
@@ -26276,110 +26847,110 @@
         <v>2019</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45">
       <c r="A3" s="1" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2201</v>
+        <v>2198</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2202</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>2431</v>
+        <v>2428</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2203</v>
+        <v>2200</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2206</v>
+        <v>2203</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2207</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>2208</v>
+        <v>2205</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2209</v>
+        <v>2206</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2210</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>2211</v>
+        <v>2208</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2213</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>2214</v>
+        <v>2211</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2215</v>
+        <v>2212</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2216</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2217</v>
+        <v>2214</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2218</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>2219</v>
+        <v>2216</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>2045</v>
@@ -26388,68 +26959,68 @@
         <v>2019</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2220</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>2221</v>
+        <v>2218</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2226</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>2227</v>
+        <v>2224</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2228</v>
+        <v>2225</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2229</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>2230</v>
+        <v>2227</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2231</v>
+        <v>2228</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>2233</v>
+        <v>2230</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>2023</v>
@@ -26458,624 +27029,624 @@
         <v>2019</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2242</v>
+        <v>2239</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2243</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>2244</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>2245</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>2246</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>2247</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>2248</v>
+        <v>2245</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2250</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2252</v>
+        <v>2249</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2253</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>2254</v>
+        <v>2251</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2256</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>2257</v>
+        <v>2254</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>2260</v>
+        <v>2257</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2261</v>
+        <v>2258</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2262</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>989</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>2278</v>
+        <v>2275</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="30">
       <c r="A33" s="1" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>1889</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>2310</v>
+        <v>2307</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>2311</v>
+        <v>2308</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>2312</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2314</v>
+        <v>2311</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>2315</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>2317</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
-        <v>2318</v>
+        <v>2315</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>2320</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
-        <v>2321</v>
+        <v>2318</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>2322</v>
+        <v>2319</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>2323</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>2324</v>
+        <v>2321</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>2325</v>
+        <v>2322</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>2326</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
-        <v>2327</v>
+        <v>2324</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>2328</v>
+        <v>2325</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>2329</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>2330</v>
+        <v>2327</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>2332</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1" t="s">
-        <v>2333</v>
+        <v>2330</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>2334</v>
+        <v>2331</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>2335</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1" t="s">
-        <v>2336</v>
+        <v>2333</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>2337</v>
+        <v>2334</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>2338</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
-        <v>2339</v>
+        <v>2336</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>2340</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1" t="s">
-        <v>2341</v>
+        <v>2338</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>2342</v>
+        <v>2339</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>2343</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>2450</v>
+        <v>2447</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>2344</v>
+        <v>2341</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>2345</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1" t="s">
-        <v>2346</v>
+        <v>2343</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>2347</v>
+        <v>2344</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>2348</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1" t="s">
-        <v>2349</v>
+        <v>2346</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>2350</v>
+        <v>2347</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>2351</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
-        <v>2352</v>
+        <v>2349</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>2353</v>
+        <v>2350</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>2355</v>
+        <v>2352</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>2356</v>
+        <v>2353</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>2357</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>2442</v>
+        <v>2439</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>2443</v>
+        <v>2440</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>2019</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D58" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <autoFilter ref="A1:D58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4851" uniqueCount="2483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4923" uniqueCount="2521">
   <si>
     <t>part_used</t>
   </si>
@@ -7485,6 +7485,120 @@
   </si>
   <si>
     <t>CEK FNGSI|CEK UNIT|CEK-UNIT|CEK FUNGSI|TES FUNGSI|OKE|OK</t>
+  </si>
+  <si>
+    <t>2TC45AD1X</t>
+  </si>
+  <si>
+    <t>2TC45AE1X</t>
+  </si>
+  <si>
+    <t>4TC50AH1X</t>
+  </si>
+  <si>
+    <t>4TC50DL1X</t>
+  </si>
+  <si>
+    <t>4TC50FJ1X</t>
+  </si>
+  <si>
+    <t>4TC55EJ2X</t>
+  </si>
+  <si>
+    <t>4TC55EK2X</t>
+  </si>
+  <si>
+    <t>4TC55FJ1X</t>
+  </si>
+  <si>
+    <t>4TC55FL1X</t>
+  </si>
+  <si>
+    <t>4TC55GN7000X</t>
+  </si>
+  <si>
+    <t>4TC60AH1X</t>
+  </si>
+  <si>
+    <t>4TC60BK1X</t>
+  </si>
+  <si>
+    <t>4TC60CH1X</t>
+  </si>
+  <si>
+    <t>4TC60CK1X</t>
+  </si>
+  <si>
+    <t>4TC60DK1X</t>
+  </si>
+  <si>
+    <t>4TC60DL1X</t>
+  </si>
+  <si>
+    <t>4TC65CK1X</t>
+  </si>
+  <si>
+    <t>4TC65DK1X</t>
+  </si>
+  <si>
+    <t>4TC65DL1X</t>
+  </si>
+  <si>
+    <t>4TC65FJ1X</t>
+  </si>
+  <si>
+    <t>4TC65FK1X</t>
+  </si>
+  <si>
+    <t>4TC65FL1X</t>
+  </si>
+  <si>
+    <t>4TC65GU8500X</t>
+  </si>
+  <si>
+    <t>4TC70AH1X</t>
+  </si>
+  <si>
+    <t>4TC70AL1X</t>
+  </si>
+  <si>
+    <t>4TC70BK1X</t>
+  </si>
+  <si>
+    <t>4TC70CK3X</t>
+  </si>
+  <si>
+    <t>4TC70DK1X</t>
+  </si>
+  <si>
+    <t>4TC70DL1X</t>
+  </si>
+  <si>
+    <t>4TC75EK2X</t>
+  </si>
+  <si>
+    <t>4TC75FJ1X</t>
+  </si>
+  <si>
+    <t>4TC85HN7000X</t>
+  </si>
+  <si>
+    <t>4TC98HN7000X</t>
+  </si>
+  <si>
+    <t>8TC70DW1X</t>
+  </si>
+  <si>
+    <t>LC32LE375X</t>
+  </si>
+  <si>
+    <t>LC40LE380X</t>
+  </si>
+  <si>
+    <t>SMM</t>
+  </si>
+  <si>
+    <t>AETECH</t>
   </si>
 </sst>
 </file>
@@ -22604,7 +22718,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -23179,8 +23293,295 @@
         <v>2014</v>
       </c>
     </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>2483</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>2485</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>2488</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>2489</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>2490</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>2493</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>2494</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>2497</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>2498</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>2500</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>2501</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>2503</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>2504</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>2505</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>2506</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>2507</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>2510</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>2511</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>2512</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>2514</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>2515</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>2516</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>2518</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>2519</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4923" uniqueCount="2521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4927" uniqueCount="2523">
   <si>
     <t>part_used</t>
   </si>
@@ -6116,9 +6116,6 @@
     <t>DISPLAY NG</t>
   </si>
   <si>
-    <t>bayang|berbayang|blur|buram|mura</t>
-  </si>
-  <si>
     <t>BLUR</t>
   </si>
   <si>
@@ -6413,9 +6410,6 @@
     <t>REPLACE SWITCH</t>
   </si>
   <si>
-    <t>service main|repair main|repair main unit|repair pwb main|repair pwb|resolder main|resoldering main|resoldering mb|resolder ic7801|resolder ic memory|resolder d7801|resolder blok main|resolder pwb|resolder pcb main|perbaikan main|perbaiki main|solder main|flash eprom|tuner|rusak main</t>
-  </si>
-  <si>
     <t>REPAIR_MAIN_UNIT</t>
   </si>
   <si>
@@ -7304,9 +7298,6 @@
     <t>Sample slow picture appears case.</t>
   </si>
   <si>
-    <t>colokan antena putus|antena putus</t>
-  </si>
-  <si>
     <t>Sample antenna connector/no-channel case.</t>
   </si>
   <si>
@@ -7328,18 +7319,12 @@
     <t>siaran|tidak ada siaran|tidak dapat siaran|no sinyal|tidak ada sinyal|tidak dapat remote|channel|sinyal</t>
   </si>
   <si>
-    <t>tak ada gambar|tidak ada gambar|no display|no picture|blank|layar blank|gambar tidak keluar|x gambar|gambar tidak ada|layat blank</t>
-  </si>
-  <si>
     <t>ADA BULATAN HITAM</t>
   </si>
   <si>
     <t>SPOT</t>
   </si>
   <si>
-    <t>goyang|bergelombang|delay|dominan|merah|putih|blue|warna|kualitas gambar|slow motion|gambar bermasalah|layar bermasalah|bergerak|berembun|BERMASALAH</t>
-  </si>
-  <si>
     <t>CEK FUNGSI</t>
   </si>
   <si>
@@ -7361,24 +7346,12 @@
     <t>BERMASALAH</t>
   </si>
   <si>
-    <t>LED KEDIP2|BERKEDIP|Kedip merah</t>
-  </si>
-  <si>
     <t>TIDAK BISA DI REMOTE</t>
   </si>
   <si>
-    <t>error|eror|netflix|software|aplikasi|app|youtube|SAFE MODE</t>
-  </si>
-  <si>
-    <t>mati total|matot|mati|tidak bisa hidup|tidak bisa nyala|tidak nyala|kena petir|listrik turun|SUSAH NYALA|TIDAK BISA DIHIDUPKAN</t>
-  </si>
-  <si>
     <t>tidak ada gambar|no picture|no display|layar blank|blank|Layar gelap|TIDAK BISA TV</t>
   </si>
   <si>
-    <t>gambar berganti sendiri|gambar blur|gambar klise|layar merah|gambar tidak baik|warna|GAMBAR TIDAK NORMAL|KEDIP|TAMPILAN DELAY|berkedip</t>
-  </si>
-  <si>
     <t>ANTHENA|ANTENE</t>
   </si>
   <si>
@@ -7388,9 +7361,6 @@
     <t>USB_NG</t>
   </si>
   <si>
-    <t>TIDAK BISA INTERNET</t>
-  </si>
-  <si>
     <t>INTERNET_NG</t>
   </si>
   <si>
@@ -7400,9 +7370,6 @@
     <t>perbaikan remote|repair remote|resolder ulang sensor|remote</t>
   </si>
   <si>
-    <t>cek normal|cek ok|unit cek ok|normal|fungsi ok|test fungsi|cek fungsi ok|cek unit|reposisi antena|antena|DITEST OK</t>
-  </si>
-  <si>
     <t>RESOLDER IC3101|RESOLDER IC7891|IC3101</t>
   </si>
   <si>
@@ -7424,9 +7391,6 @@
     <t>service main|repair main|repair main unit|repair pwb main|repair pwb|resolder main|resoldering main|resoldering mb|resolder ic7801|resolder ic memory|d7801|resolder blok main|resolder pwb|resolder pcb main|perbaikan main|perbaiki main|solder main|flash eprom|tuner|rusak main|REPAIR-MAIN</t>
   </si>
   <si>
-    <t>ext|external|cairan|cleaning|semut|kotor|bersih|bersihkan|kardus rusak|EKSTERNAL</t>
-  </si>
-  <si>
     <t>RESOLDER R323|RESOLDER DIODA|Q4</t>
   </si>
   <si>
@@ -7599,6 +7563,48 @@
   </si>
   <si>
     <t>AETECH</t>
+  </si>
+  <si>
+    <t>tak ada gambar|tidak ada gambar|no display|no picture|blank|layar blank|gambar tidak keluar|x gambar|gambar tidak ada|layat blank|gambar gelap</t>
+  </si>
+  <si>
+    <t>error|eror|netflix|software|aplikasi|app|youtube|SAFE MODE|Loading</t>
+  </si>
+  <si>
+    <t>ext|external|cairan|cleaning|semut|kotor|bersih|bersihkan|kardus rusak|EKSTERNAL|FAKTOR LUAR</t>
+  </si>
+  <si>
+    <t>LED KEDIP2|BERKEDIP|Kedip merah|REDUP SEBELAH</t>
+  </si>
+  <si>
+    <t>TIDAK BISA WIFI</t>
+  </si>
+  <si>
+    <t>colokan antena putus|antena putus|TIDAK BISA DIGITAL</t>
+  </si>
+  <si>
+    <t>TIDAK BISA INTERNET|KERUSAKAN INTERNET</t>
+  </si>
+  <si>
+    <t>goyang|bergelombang|delay|dominan|merah|putih|blue|warna|kualitas gambar|slow motion|gambar bermasalah|layar bermasalah|bergerak|berembun|BERMASALAH|</t>
+  </si>
+  <si>
+    <t>gambar berganti sendiri|gambar blur|gambar klise|layar merah|gambar tidak baik|warna|GAMBAR TIDAK NORMAL|KEDIP|TAMPILAN DELAY|berkedip|GAMBAR BERBAYANG</t>
+  </si>
+  <si>
+    <t>bayang|berbayang|blur|buram|mura|BUREM|GAMBAR TIDAK JELAS</t>
+  </si>
+  <si>
+    <t>mati total|matot|mati|tidak bisa hidup|tidak bisa nyala|tidak nyala|kena petir|listrik turun|SUSAH NYALA|TIDAK BISA DIHIDUPKAN|KORSLET</t>
+  </si>
+  <si>
+    <t>tidak ada gambar|no display|no picture|blank|gambar gelap|gambar tidak keluar|gelap|x ada gambar|layar blank|LAYAR HITAM</t>
+  </si>
+  <si>
+    <t>service main|repair main|repair main unit|repair pwb main|repair pwb|resolder main|resoldering main|resoldering mb|resolder ic7801|resolder ic memory|resolder d7801|resolder blok main|resolder pwb|resolder pcb main|perbaikan main|perbaiki main|solder main|flash eprom|tuner|rusak main|USB TIDAK BISA</t>
+  </si>
+  <si>
+    <t>cek normal|cek ok|unit cek ok|normal|fungsi ok|test fungsi|cek fungsi ok|cek unit|reposisi antena|antena|DITEST OK|TIDAK ADA KERUSAKAN</t>
   </si>
 </sst>
 </file>
@@ -7725,7 +7731,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7736,11 +7742,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -23295,255 +23306,255 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>2483</v>
+        <v>2471</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>2484</v>
+        <v>2472</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>2485</v>
+        <v>2473</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>2486</v>
+        <v>2474</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>2487</v>
+        <v>2475</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>2488</v>
+        <v>2476</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>2520</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>2489</v>
+        <v>2477</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>2520</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>2490</v>
+        <v>2478</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>2491</v>
+        <v>2479</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>2492</v>
+        <v>2480</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>2493</v>
+        <v>2481</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>2494</v>
+        <v>2482</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>2495</v>
+        <v>2483</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>2496</v>
+        <v>2484</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>2497</v>
+        <v>2485</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>2498</v>
+        <v>2486</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>2499</v>
+        <v>2487</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>2500</v>
+        <v>2488</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>2501</v>
+        <v>2489</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>2502</v>
+        <v>2490</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>2503</v>
+        <v>2491</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>2504</v>
+        <v>2492</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>2505</v>
+        <v>2493</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>2506</v>
+        <v>2494</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>2507</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>2519</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>2508</v>
+        <v>2496</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>2509</v>
+        <v>2497</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>2510</v>
+        <v>2498</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>2511</v>
+        <v>2499</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>2512</v>
+        <v>2500</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>2520</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>2513</v>
+        <v>2501</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>2514</v>
+        <v>2502</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>1943</v>
@@ -23551,7 +23562,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>2515</v>
+        <v>2503</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>1943</v>
@@ -23559,26 +23570,26 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>2516</v>
+        <v>2504</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>2517</v>
+        <v>2505</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>2518</v>
+        <v>2506</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>2519</v>
+        <v>2507</v>
       </c>
     </row>
   </sheetData>
@@ -23588,13 +23599,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="90" customWidth="1"/>
+    <col min="4" max="4" width="158.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="70" customWidth="1"/>
   </cols>
@@ -23621,107 +23632,104 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>989</v>
+        <v>720</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2059</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>2355</v>
+      <c r="D2" t="s">
+        <v>2429</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>2022</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>2356</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3">
-        <v>20</v>
+        <v>390</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>345</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2355</v>
+        <v>2066</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>2022</v>
+        <v>2035</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>2356</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3">
-        <v>30</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>214</v>
+        <v>630</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2355</v>
+        <v>2369</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>2022</v>
+        <v>2035</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>2356</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3">
-        <v>40</v>
+        <v>360</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1816</v>
+        <v>128</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2355</v>
+        <v>2374</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>2022</v>
+        <v>2049</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>2356</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3">
-        <v>50</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>989</v>
+        <v>640</v>
+      </c>
+      <c r="B6" t="s">
+        <v>128</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2357</v>
+        <v>2369</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>2023</v>
+        <v>2035</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>2358</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>214</v>
@@ -23730,238 +23738,235 @@
         <v>2021</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2357</v>
+        <v>2353</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>345</v>
+        <v>214</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1816</v>
+        <v>214</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2357</v>
+        <v>2367</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>2024</v>
+        <v>2036</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>2358</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3">
-        <v>90</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>989</v>
+        <v>650</v>
+      </c>
+      <c r="B10" t="s">
+        <v>214</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2437</v>
+        <v>2369</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>2023</v>
+        <v>2035</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>2359</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3">
-        <v>100</v>
+        <v>740</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>989</v>
+        <v>214</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2433</v>
+        <v>2512</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>2025</v>
+        <v>2057</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>2360</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3">
-        <v>110</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>989</v>
+        <v>750</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>322</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>2026</v>
+      <c r="D12" t="s">
+        <v>2436</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>2027</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>2361</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>989</v>
+        <v>345</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2028</v>
+        <v>2353</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>2029</v>
+        <v>2022</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>2362</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>989</v>
+        <v>345</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2030</v>
+        <v>2355</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>2031</v>
+        <v>2024</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>2363</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3">
-        <v>140</v>
+        <v>330</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>989</v>
+        <v>345</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>2031</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>2032</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>2033</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>2364</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3">
-        <v>150</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>989</v>
+        <v>660</v>
+      </c>
+      <c r="B16" t="s">
+        <v>345</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2438</v>
+        <v>2369</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>989</v>
+        <v>459</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>2036</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>989</v>
+        <v>459</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2367</v>
+        <v>2519</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>2023</v>
+        <v>2035</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>2368</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>459</v>
@@ -23970,10 +23975,10 @@
         <v>2021</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2369</v>
+        <v>2038</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>2370</v>
@@ -23981,7 +23986,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>459</v>
@@ -23990,18 +23995,18 @@
         <v>2021</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2444</v>
+        <v>2040</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>2036</v>
+        <v>2041</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>2038</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>459</v>
@@ -24010,10 +24015,10 @@
         <v>2021</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2039</v>
+        <v>2371</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>2372</v>
@@ -24021,7 +24026,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>459</v>
@@ -24030,18 +24035,18 @@
         <v>2021</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2041</v>
+        <v>2437</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>2042</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>2043</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>459</v>
@@ -24050,18 +24055,18 @@
         <v>2021</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2373</v>
+        <v>2510</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>2044</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>2374</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>459</v>
@@ -24070,18 +24075,18 @@
         <v>2021</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>2445</v>
+        <v>2046</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>2024</v>
+        <v>2047</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>2375</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>459</v>
@@ -24090,18 +24095,18 @@
         <v>2021</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2443</v>
+        <v>2374</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>2045</v>
+        <v>2049</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>2046</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="3">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>459</v>
@@ -24110,18 +24115,18 @@
         <v>2021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2047</v>
+        <v>2051</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>2048</v>
+        <v>2052</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>2049</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>459</v>
@@ -24130,18 +24135,18 @@
         <v>2021</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>2376</v>
+        <v>2054</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>2050</v>
+        <v>2055</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>2051</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>459</v>
@@ -24150,18 +24155,18 @@
         <v>2021</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>2052</v>
+        <v>2517</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>2054</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3">
-        <v>280</v>
+        <v>760</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>459</v>
@@ -24170,18 +24175,16 @@
         <v>2021</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>2055</v>
+        <v>2439</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>2056</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>2057</v>
-      </c>
+        <v>2440</v>
+      </c>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="3">
-        <v>290</v>
+        <v>780</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>459</v>
@@ -24189,453 +24192,474 @@
       <c r="C30" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>2446</v>
+      <c r="D30" t="s">
+        <v>2513</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>2059</v>
-      </c>
+        <v>2441</v>
+      </c>
+      <c r="F30" s="3"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="3">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1429</v>
+        <v>989</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>2060</v>
+        <v>2353</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>2036</v>
+        <v>2022</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>2377</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="3">
-        <v>310</v>
+        <v>50</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>1660</v>
+        <v>989</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2378</v>
+        <v>2520</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>2061</v>
+        <v>2023</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>2062</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="3">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>1732</v>
+        <v>989</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>2060</v>
+        <v>2432</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>2053</v>
+        <v>2023</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>2379</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="3">
-        <v>330</v>
+        <v>100</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>345</v>
+        <v>989</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>2032</v>
+        <v>2516</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>2033</v>
+        <v>2025</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>2063</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3">
-        <v>340</v>
+        <v>110</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>214</v>
+        <v>989</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>2369</v>
+        <v>2518</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>2037</v>
+        <v>2026</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>2380</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>1826</v>
+        <v>989</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>2381</v>
+        <v>2027</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>2058</v>
+        <v>2028</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>2382</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="3">
-        <v>360</v>
+        <v>130</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>128</v>
+        <v>989</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>2376</v>
+        <v>2029</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>2064</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="3">
-        <v>370</v>
+        <v>140</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>1889</v>
+        <v>989</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>2383</v>
+        <v>2031</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>2044</v>
+        <v>2032</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>2384</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="3">
-        <v>380</v>
+        <v>150</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1811</v>
+        <v>989</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>2065</v>
+        <v>2433</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>2056</v>
+        <v>2033</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>2066</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="3">
-        <v>390</v>
+        <v>160</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>3</v>
+        <v>989</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>2067</v>
+        <v>2363</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>2068</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="3">
-        <v>400</v>
-      </c>
-      <c r="B41" s="3"/>
+        <v>170</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>989</v>
+      </c>
       <c r="C41" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>2385</v>
+        <v>2365</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>2386</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="3">
-        <v>410</v>
-      </c>
-      <c r="B42" s="3"/>
+        <v>710</v>
+      </c>
+      <c r="B42" t="s">
+        <v>989</v>
+      </c>
       <c r="C42" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>2430</v>
+      <c r="D42" t="s">
+        <v>2427</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>2024</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>2387</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="3">
-        <v>420</v>
-      </c>
-      <c r="B43" s="3"/>
+        <v>670</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1398</v>
+      </c>
       <c r="C43" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>2429</v>
+        <v>2059</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>2044</v>
+        <v>2035</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>2388</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="3">
-        <v>430</v>
-      </c>
-      <c r="B44" s="3"/>
+        <v>300</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>1429</v>
+      </c>
       <c r="C44" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>2389</v>
+        <v>2059</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>2390</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="3">
-        <v>440</v>
-      </c>
-      <c r="B45" s="3"/>
+        <v>310</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>1660</v>
+      </c>
       <c r="C45" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>2391</v>
+        <v>2376</v>
       </c>
       <c r="E45" s="3" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>2061</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>2392</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3">
-        <v>450</v>
-      </c>
-      <c r="B46" s="3"/>
+        <v>680</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1660</v>
+      </c>
       <c r="C46" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2393</v>
+        <v>2059</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>2053</v>
+        <v>2431</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>2394</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3">
-        <v>460</v>
-      </c>
-      <c r="B47" s="3"/>
+        <v>320</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>1732</v>
+      </c>
       <c r="C47" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>2452</v>
+        <v>2059</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>2045</v>
+        <v>2052</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>2395</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3">
-        <v>470</v>
-      </c>
-      <c r="B48" s="3"/>
+        <v>380</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>1811</v>
+      </c>
       <c r="C48" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>2396</v>
+        <v>2064</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>2037</v>
+        <v>2055</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>2397</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="3">
-        <v>480</v>
-      </c>
-      <c r="B49" s="3"/>
+        <v>620</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>1811</v>
+      </c>
       <c r="C49" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>2398</v>
+        <v>2423</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>2025</v>
+        <v>2043</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>2399</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="3">
-        <v>490</v>
-      </c>
-      <c r="B50" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C50" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>2400</v>
+        <v>2353</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>2029</v>
+        <v>2022</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>2401</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="3">
-        <v>500</v>
-      </c>
-      <c r="B51" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C51" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>2402</v>
+        <v>2355</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>2034</v>
+        <v>2024</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>2403</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="3">
-        <v>510</v>
-      </c>
-      <c r="B52" s="3"/>
+        <v>530</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C52" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>2056</v>
+        <v>2025</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="3">
-        <v>520</v>
-      </c>
-      <c r="B53" s="3"/>
+        <v>540</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C53" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>2036</v>
+        <v>2026</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="3">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>1816</v>
@@ -24644,18 +24668,18 @@
         <v>2021</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>2025</v>
+        <v>2033</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="3">
-        <v>540</v>
+        <v>610</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>1816</v>
@@ -24664,437 +24688,448 @@
         <v>2021</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>2410</v>
+        <v>2421</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>2027</v>
+        <v>2035</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>2411</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="3">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>1816</v>
+        <v>1826</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>2412</v>
+        <v>2379</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>2034</v>
+        <v>2057</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>2413</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="3">
-        <v>560</v>
-      </c>
-      <c r="B57" s="3"/>
+        <v>370</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>1889</v>
+      </c>
       <c r="C57" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>2414</v>
+        <v>2381</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>2024</v>
+        <v>2043</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>2415</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="3">
-        <v>570</v>
+        <v>400</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>2416</v>
+        <v>2383</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>2417</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="3">
-        <v>580</v>
+        <v>410</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>2418</v>
+        <v>2509</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>2036</v>
+        <v>2024</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>2419</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="3">
-        <v>590</v>
+        <v>420</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>2420</v>
+        <v>2426</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>2058</v>
+        <v>2043</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>2421</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="3">
-        <v>600</v>
+        <v>430</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>2422</v>
+        <v>2387</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>2044</v>
+        <v>2032</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>2423</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="3">
-        <v>610</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>1816</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="B62" s="3"/>
       <c r="C62" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>2424</v>
+        <v>2389</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>2036</v>
+        <v>2060</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>2425</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="3">
-        <v>620</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>1811</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="B63" s="3"/>
       <c r="C63" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>2426</v>
+        <v>2391</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>2044</v>
+        <v>2052</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>2427</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="3">
-        <v>630</v>
-      </c>
-      <c r="B64" t="s">
-        <v>90</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="B64" s="3"/>
       <c r="C64" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>2371</v>
+        <v>2442</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>2036</v>
+        <v>2044</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>2038</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="3">
-        <v>640</v>
-      </c>
-      <c r="B65" t="s">
-        <v>128</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="B65" s="3"/>
       <c r="C65" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>2371</v>
+        <v>2394</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>2036</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>2038</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="3">
-        <v>650</v>
-      </c>
-      <c r="B66" t="s">
-        <v>214</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="B66" s="3"/>
       <c r="C66" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>2371</v>
+        <v>2396</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>2036</v>
+        <v>2025</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>2038</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="3">
-        <v>660</v>
-      </c>
-      <c r="B67" t="s">
-        <v>345</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="B67" s="3"/>
       <c r="C67" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>2371</v>
+        <v>2398</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>2036</v>
+        <v>2028</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>2038</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="3">
-        <v>670</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1398</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="B68" s="3"/>
       <c r="C68" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>2060</v>
+        <v>2400</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>2038</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="3">
-        <v>680</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1660</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="B69" s="3"/>
       <c r="C69" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>2060</v>
+        <v>2402</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>2436</v>
+        <v>2055</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>2038</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="3">
-        <v>690</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="B70" s="9"/>
       <c r="C70" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>2371</v>
+        <v>2404</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>2038</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="3">
-        <v>700</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="B71" s="3"/>
       <c r="C71" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>2041</v>
+        <v>2412</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>2042</v>
-      </c>
-      <c r="F71" s="3"/>
+        <v>2024</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>2413</v>
+      </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="3">
-        <v>710</v>
-      </c>
-      <c r="B72" t="s">
-        <v>989</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="B72" s="3"/>
       <c r="C72" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D72" t="s">
-        <v>2431</v>
+      <c r="D72" s="3" t="s">
+        <v>2414</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>2432</v>
+        <v>2025</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>2415</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="3">
-        <v>720</v>
-      </c>
-      <c r="B73" t="s">
-        <v>2060</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="B73" s="3"/>
       <c r="C73" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D73" t="s">
-        <v>2434</v>
+      <c r="D73" s="3" t="s">
+        <v>2416</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>2091</v>
+        <v>2035</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>2417</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="3">
-        <v>730</v>
+        <v>590</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2435</v>
+        <v>2418</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>2058</v>
+        <v>2057</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>2419</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="3">
-        <v>740</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>214</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="B75" s="3"/>
       <c r="C75" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>2441</v>
+        <v>2514</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>2058</v>
+        <v>2043</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>2380</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="3">
-        <v>750</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>322</v>
-      </c>
+        <v>690</v>
+      </c>
+      <c r="B76" s="7"/>
       <c r="C76" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D76" t="s">
-        <v>2442</v>
+      <c r="D76" s="3" t="s">
+        <v>2369</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>2050</v>
+        <v>2035</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>2037</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="3">
-        <v>760</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>459</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="B77" s="8"/>
       <c r="C77" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>2448</v>
+        <v>2040</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>2449</v>
+        <v>2041</v>
       </c>
       <c r="F77" s="3"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="3">
-        <v>770</v>
-      </c>
+        <v>730</v>
+      </c>
+      <c r="B78" s="3"/>
       <c r="C78" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D78" t="s">
-        <v>2450</v>
+      <c r="D78" s="3" t="s">
+        <v>2430</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>2451</v>
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="3">
+        <v>770</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D79" t="s">
+        <v>2515</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>2441</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F41"/>
+  <autoFilter ref="A1:F41">
+    <sortState ref="A2:F79">
+      <sortCondition ref="B1:B41"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25110,40 +25145,40 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2069</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2070</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2071</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2072</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2073</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2074</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>2075</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2076</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
     </row>
   </sheetData>
@@ -25163,34 +25198,34 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2078</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2079</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2080</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2081</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
     </row>
   </sheetData>
@@ -25216,188 +25251,204 @@
         <v>2016</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>2084</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2085</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>2086</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2087</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>1826</v>
+      </c>
       <c r="D2" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2462</v>
+        <v>2120</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>2088</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1">
-        <v>20</v>
+        <v>410</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>1826</v>
+      </c>
       <c r="D3" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2089</v>
+        <v>2059</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="30">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>1811</v>
+      </c>
       <c r="D4" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2454</v>
+        <v>2122</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>2091</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1">
-        <v>40</v>
+        <v>420</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>1811</v>
+      </c>
       <c r="D5" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2092</v>
+        <v>2059</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>2093</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>1732</v>
+      </c>
       <c r="D6" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>2094</v>
+        <v>2118</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>2095</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>1732</v>
+      </c>
       <c r="D7" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2096</v>
+        <v>2059</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>2097</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1">
-        <v>70</v>
+        <v>240</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>1660</v>
+      </c>
       <c r="D8" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>2098</v>
+        <v>2127</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>2099</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="45">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>1660</v>
+      </c>
       <c r="D9" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2457</v>
+        <v>2106</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>2100</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1">
-        <v>90</v>
+        <v>310</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>989</v>
+        <v>1660</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>2101</v>
+        <v>2059</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>2102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="45">
       <c r="A11" s="1">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
@@ -25406,1193 +25457,1181 @@
         <v>1429</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2103</v>
+        <v>2125</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>2104</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>459</v>
+        <v>1429</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1">
-        <v>120</v>
+        <v>280</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1660</v>
+        <v>1429</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2107</v>
+        <v>2059</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>2108</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1">
-        <v>130</v>
+        <v>320</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>214</v>
+        <v>1398</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>2109</v>
+        <v>2059</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>2110</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>345</v>
+        <v>989</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2111</v>
+        <v>2100</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>2112</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>90</v>
+        <v>989</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>2113</v>
+        <v>2059</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="60">
       <c r="A17" s="1">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3</v>
+        <v>459</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2115</v>
+        <v>2521</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>2116</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>128</v>
+        <v>459</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>2117</v>
+        <v>2104</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>2118</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>322</v>
+        <v>459</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2117</v>
+        <v>2059</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>2118</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1732</v>
+        <v>345</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>2119</v>
+        <v>2129</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>2120</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1826</v>
+        <v>345</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2121</v>
+        <v>2110</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>2122</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1">
-        <v>210</v>
+        <v>350</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1811</v>
+        <v>345</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>2123</v>
+        <v>2059</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>2124</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="45">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="1">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="B23" s="1">
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>459</v>
+        <v>322</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>2125</v>
+        <v>2116</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="45">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1">
-        <v>230</v>
+        <v>390</v>
       </c>
       <c r="B24" s="1">
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1429</v>
+        <v>322</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>2127</v>
+        <v>2059</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>2128</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="B25" s="1">
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1660</v>
+        <v>214</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>2129</v>
+        <v>2108</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>2130</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1">
-        <v>250</v>
+        <v>330</v>
       </c>
       <c r="B26" s="1">
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>345</v>
+        <v>214</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>2131</v>
+        <v>2059</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>2132</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1">
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="B27" s="1">
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2133</v>
+        <v>2116</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>2134</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1">
-        <v>270</v>
+        <v>380</v>
       </c>
       <c r="B28" s="1">
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>2133</v>
+        <v>2059</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>2134</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="B29" s="1">
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1429</v>
+        <v>109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>2104</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>989</v>
+        <v>90</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>2060</v>
+        <v>2112</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>2102</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="B31" s="1">
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>459</v>
+        <v>90</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>2106</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="B32" s="1">
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1660</v>
+        <v>37</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>2060</v>
+        <v>2131</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>2108</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="B33" s="1">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1398</v>
+        <v>24</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>2060</v>
+        <v>2131</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>2128</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1">
-        <v>330</v>
+        <v>160</v>
       </c>
       <c r="B34" s="1">
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>214</v>
+        <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>2060</v>
+        <v>2114</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>2110</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="B35" s="1">
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>2126</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1">
-        <v>350</v>
+        <v>510</v>
       </c>
       <c r="B36" s="1">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>345</v>
+        <v>2059</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>2060</v>
+        <v>2511</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>2112</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1">
-        <v>360</v>
+        <v>520</v>
       </c>
       <c r="B37" s="1">
         <v>1</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>2060</v>
-      </c>
+        <v>2059</v>
+      </c>
+      <c r="D37" s="1"/>
       <c r="E37" s="1" t="s">
-        <v>2060</v>
+        <v>2511</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>2116</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="B38" s="1">
         <v>1</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>2060</v>
+        <v>2088</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>2114</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="1">
-        <v>380</v>
-      </c>
-      <c r="B39" s="1">
+      <c r="A39" s="4">
+        <v>690</v>
+      </c>
+      <c r="B39" s="5">
         <v>1</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>2060</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>2118</v>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>2467</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>2089</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1">
-        <v>390</v>
+        <v>50</v>
       </c>
       <c r="B40" s="1">
         <v>1</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>322</v>
-      </c>
+      <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>2060</v>
+        <v>2093</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>2118</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="B41" s="1">
         <v>1</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>1732</v>
-      </c>
+      <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>2060</v>
+        <v>2511</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>2120</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1">
-        <v>410</v>
+        <v>530</v>
       </c>
       <c r="B42" s="1">
         <v>1</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>1826</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>2060</v>
+      <c r="D42" t="s">
+        <v>2448</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>2122</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1">
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="B43" s="1">
         <v>1</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>1811</v>
-      </c>
       <c r="D43" s="1" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
+      </c>
+      <c r="E43" t="s">
+        <v>2448</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>2124</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="1">
-        <v>430</v>
-      </c>
-      <c r="B44" s="1">
+      <c r="A44" s="4">
+        <v>700</v>
+      </c>
+      <c r="B44" s="5">
         <v>1</v>
       </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>2453</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="60">
-      <c r="A45" s="1">
-        <v>440</v>
-      </c>
-      <c r="B45" s="1">
+      <c r="C44" s="5"/>
+      <c r="D44" s="5" t="s">
+        <v>2468</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="4">
+        <v>710</v>
+      </c>
+      <c r="B45" s="5">
         <v>1</v>
       </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>2461</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="45">
+      <c r="C45" s="5"/>
+      <c r="D45" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>2469</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" s="1">
-        <v>450</v>
+        <v>70</v>
       </c>
       <c r="B46" s="1">
         <v>1</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>2460</v>
+        <v>2097</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>2128</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="1">
-        <v>460</v>
-      </c>
-      <c r="B47" s="1">
+      <c r="A47" s="4">
+        <v>670</v>
+      </c>
+      <c r="B47" s="5">
         <v>1</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E47" t="s">
-        <v>2455</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>2126</v>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>2465</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>2098</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="1">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="B48" s="1">
         <v>1</v>
       </c>
+      <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>2463</v>
+        <v>2059</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2452</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>2128</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="1">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="B49" s="1">
         <v>1</v>
       </c>
+      <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E49" t="s">
-        <v>2458</v>
+        <v>2059</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>2445</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>2126</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="1">
-        <v>490</v>
-      </c>
-      <c r="B50" s="1">
+      <c r="A50" s="4">
+        <v>650</v>
+      </c>
+      <c r="B50" s="5">
         <v>1</v>
       </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>2456</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>2132</v>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>2463</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>2130</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="1">
-        <v>500</v>
-      </c>
-      <c r="B51" s="1">
+      <c r="A51" s="4">
+        <v>560</v>
+      </c>
+      <c r="B51" s="4">
         <v>1</v>
       </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E51" t="s">
-        <v>2464</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>2134</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="C51" s="4"/>
+      <c r="D51" s="4" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>2453</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="60">
       <c r="A52" s="1">
-        <v>510</v>
+        <v>440</v>
       </c>
       <c r="B52" s="1">
         <v>1</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>2060</v>
-      </c>
+      <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>2462</v>
+        <v>2450</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>2088</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
       <c r="B53" s="1">
         <v>1</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>2060</v>
-      </c>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1" t="s">
-        <v>2462</v>
+      <c r="D53" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E53" t="s">
+        <v>2444</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>2088</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="1">
-        <v>530</v>
+        <v>480</v>
       </c>
       <c r="B54" s="1">
         <v>1</v>
       </c>
-      <c r="D54" t="s">
-        <v>2459</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>2060</v>
+      <c r="D54" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E54" t="s">
+        <v>2447</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>2088</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="1">
-        <v>540</v>
-      </c>
-      <c r="B55" s="1">
+      <c r="A55" s="4">
+        <v>590</v>
+      </c>
+      <c r="B55" s="5">
         <v>1</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E55" t="s">
-        <v>2459</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>2088</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="C55" s="5"/>
+      <c r="D55" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>2456</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="45">
       <c r="A56" s="1">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="B56" s="1">
         <v>1</v>
       </c>
+      <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E56" t="s">
-        <v>2188</v>
-      </c>
-      <c r="F56" t="s">
-        <v>2188</v>
+        <v>2059</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>2449</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>2126</v>
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="5">
-        <v>560</v>
-      </c>
-      <c r="B57" s="5">
+      <c r="A57" s="1">
+        <v>470</v>
+      </c>
+      <c r="B57" s="1">
         <v>1</v>
       </c>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>2465</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>2157</v>
+      <c r="D57" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>2126</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="5">
+      <c r="A58" s="4">
         <v>570</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B58" s="5">
         <v>1</v>
       </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6" t="s">
+      <c r="C58" s="5"/>
+      <c r="D58" s="5" t="s">
+        <v>2454</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="4">
+        <v>580</v>
+      </c>
+      <c r="B59" s="5">
+        <v>1</v>
+      </c>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>2455</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="1">
+        <v>430</v>
+      </c>
+      <c r="B60" s="1">
+        <v>1</v>
+      </c>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>2443</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="4">
+        <v>610</v>
+      </c>
+      <c r="B61" s="5">
+        <v>1</v>
+      </c>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5" t="s">
+        <v>2459</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="4">
+        <v>620</v>
+      </c>
+      <c r="B62" s="5">
+        <v>1</v>
+      </c>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>2460</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="4">
+        <v>600</v>
+      </c>
+      <c r="B63" s="5">
+        <v>1</v>
+      </c>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>2457</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="4">
+        <v>630</v>
+      </c>
+      <c r="B64" s="5">
+        <v>1</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>2461</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="45">
+      <c r="A65" s="1">
+        <v>80</v>
+      </c>
+      <c r="B65" s="1">
+        <v>1</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>2446</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="4">
+        <v>660</v>
+      </c>
+      <c r="B66" s="5">
+        <v>1</v>
+      </c>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>2464</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="1">
+        <v>550</v>
+      </c>
+      <c r="B67" s="1">
+        <v>1</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E67" t="s">
+        <v>2186</v>
+      </c>
+      <c r="F67" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="4">
+        <v>680</v>
+      </c>
+      <c r="B68" s="5">
+        <v>1</v>
+      </c>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E68" s="5" t="s">
         <v>2466</v>
       </c>
-      <c r="E58" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="5">
-        <v>580</v>
-      </c>
-      <c r="B59" s="6">
+      <c r="F68" s="5" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="1">
+        <v>60</v>
+      </c>
+      <c r="B69" s="1">
         <v>1</v>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>2467</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="5">
-        <v>590</v>
-      </c>
-      <c r="B60" s="6">
+      <c r="C69" s="1"/>
+      <c r="D69" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="30">
+      <c r="A70" s="1">
+        <v>30</v>
+      </c>
+      <c r="B70" s="1">
         <v>1</v>
       </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>2468</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="5">
-        <v>600</v>
-      </c>
-      <c r="B61" s="6">
+      <c r="C70" s="1"/>
+      <c r="D70" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>2522</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="4">
+        <v>640</v>
+      </c>
+      <c r="B71" s="5">
         <v>1</v>
       </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>2469</v>
-      </c>
-      <c r="F61" s="6" t="s">
+      <c r="C71" s="5"/>
+      <c r="D71" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>2462</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="4">
+        <v>720</v>
+      </c>
+      <c r="B72" s="5">
+        <v>1</v>
+      </c>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E72" s="5" t="s">
         <v>2470</v>
       </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="5">
-        <v>610</v>
-      </c>
-      <c r="B62" s="6">
+      <c r="F72" s="5" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="1">
+        <v>40</v>
+      </c>
+      <c r="B73" s="1">
         <v>1</v>
       </c>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6" t="s">
-        <v>2471</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="5">
-        <v>620</v>
-      </c>
-      <c r="B63" s="6">
-        <v>1</v>
-      </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>2472</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="5">
-        <v>630</v>
-      </c>
-      <c r="B64" s="6">
-        <v>1</v>
-      </c>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>2473</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>2124</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="5">
-        <v>640</v>
-      </c>
-      <c r="B65" s="6">
-        <v>1</v>
-      </c>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>2474</v>
-      </c>
-      <c r="F65" s="6" t="s">
+      <c r="C73" s="1"/>
+      <c r="D73" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>2091</v>
       </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" s="5">
-        <v>650</v>
-      </c>
-      <c r="B66" s="6">
-        <v>1</v>
-      </c>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>2475</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>2132</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="5">
-        <v>660</v>
-      </c>
-      <c r="B67" s="6">
-        <v>1</v>
-      </c>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>2476</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" s="5">
-        <v>670</v>
-      </c>
-      <c r="B68" s="6">
-        <v>1</v>
-      </c>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>2477</v>
-      </c>
-      <c r="F68" s="6" t="s">
-        <v>2099</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" s="5">
-        <v>680</v>
-      </c>
-      <c r="B69" s="6">
-        <v>1</v>
-      </c>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>2478</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>2188</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" s="5">
-        <v>690</v>
-      </c>
-      <c r="B70" s="6">
-        <v>1</v>
-      </c>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>2479</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" s="5">
-        <v>700</v>
-      </c>
-      <c r="B71" s="6">
-        <v>1</v>
-      </c>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6" t="s">
-        <v>2480</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="F71" s="6" t="s">
-        <v>2088</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" s="5">
-        <v>710</v>
-      </c>
-      <c r="B72" s="6">
-        <v>1</v>
-      </c>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>2481</v>
-      </c>
-      <c r="F72" s="6" t="s">
-        <v>2088</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" s="5">
-        <v>720</v>
-      </c>
-      <c r="B73" s="6">
-        <v>1</v>
-      </c>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>2482</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>2091</v>
+      <c r="F73" s="1" t="s">
+        <v>2092</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F43"/>
+  <autoFilter ref="A1:F43">
+    <sortState ref="A2:F73">
+      <sortCondition descending="1" ref="C1:C43"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26610,584 +26649,584 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2135</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2136</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2137</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2138</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>2144</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>2145</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>2146</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>459</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>989</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>2128</v>
+        <v>2126</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>1429</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>459</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>989</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30">
       <c r="A28" s="1" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>1429</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>964</v>
@@ -27196,10 +27235,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>964</v>
@@ -27225,13 +27264,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2192</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2193</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2194</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2020</v>
@@ -27239,189 +27278,189 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45">
       <c r="A3" s="1" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>2428</v>
+        <v>2425</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>2023</v>
@@ -27430,617 +27469,617 @@
         <v>2019</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>2241</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>2242</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>2244</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>2245</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>2246</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>2247</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>2248</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>2249</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>2250</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>2250</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>2251</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>2252</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>2253</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>2254</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>2255</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>2256</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>2257</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>2258</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>2259</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>2260</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>2261</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>2262</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>2263</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>2264</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>2265</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>2266</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>2267</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>2268</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>2271</v>
+        <v>2269</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>989</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2272</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>2273</v>
+        <v>2271</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2274</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>2275</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>2276</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>2277</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>2277</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>2278</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>2279</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>2280</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="30">
       <c r="A33" s="1" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>2280</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>2281</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>2282</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>2283</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>2284</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>2285</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>2286</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>2287</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>2288</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>2289</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>2290</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>2291</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>2292</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>2293</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>2294</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>2295</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>2296</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>2297</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>2298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>1889</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>2300</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>2301</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>2302</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>2303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>2303</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>2304</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>2305</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>2306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
+        <v>2305</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>2306</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>2307</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>2308</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>2309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>2309</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>2310</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>2311</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>2312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>2315</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>2316</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>2317</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
+        <v>2316</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>2317</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>2318</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>2319</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>2320</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>2320</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>2321</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>2322</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>2323</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>2324</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>2325</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>2326</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>2327</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>2328</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>2329</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>2330</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>2331</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>2332</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1" t="s">
+        <v>2331</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>2333</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>2334</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>2335</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>2337</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1" t="s">
+        <v>2336</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>2337</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>2338</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>2339</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>2340</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>2447</v>
+        <v>2438</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1" t="s">
+        <v>2341</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>2342</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>2343</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>2344</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>2345</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1" t="s">
+        <v>2344</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>2346</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>2347</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>2348</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
+        <v>2347</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>2348</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>2349</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>2350</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>2351</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
+        <v>2350</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>2351</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>2352</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>2353</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>2354</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>2439</v>
+        <v>2434</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>2440</v>
+        <v>2435</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>2019</v>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARISAFARI\Works\Project Applications\tool-fcost\masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Koding\tool-fcost\masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DE972C-D48D-422D-92E8-183C47B625F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -7586,9 +7587,6 @@
     <t>TIDAK BISA INTERNET|KERUSAKAN INTERNET</t>
   </si>
   <si>
-    <t>goyang|bergelombang|delay|dominan|merah|putih|blue|warna|kualitas gambar|slow motion|gambar bermasalah|layar bermasalah|bergerak|berembun|BERMASALAH|</t>
-  </si>
-  <si>
     <t>gambar berganti sendiri|gambar blur|gambar klise|layar merah|gambar tidak baik|warna|GAMBAR TIDAK NORMAL|KEDIP|TAMPILAN DELAY|berkedip|GAMBAR BERBAYANG</t>
   </si>
   <si>
@@ -7605,12 +7603,15 @@
   </si>
   <si>
     <t>cek normal|cek ok|unit cek ok|normal|fungsi ok|test fungsi|cek fungsi ok|cek unit|reposisi antena|antena|DITEST OK|TIDAK ADA KERUSAKAN</t>
+  </si>
+  <si>
+    <t>goyang|bergelombang|delay|dominan|merah|putih|blue|warna|kualitas gambar|slow motion|gambar bermasalah|layar bermasalah|bergerak|berembun|BERMASALAH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="10">
     <font>
       <sz val="11"/>
@@ -7731,7 +7732,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7746,25 +7747,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 3 14" xfId="7"/>
-    <cellStyle name="Normal 13 2 2 10 2 2 5 2 2 2 2" xfId="3"/>
-    <cellStyle name="Normal 13 2 2 2" xfId="4"/>
-    <cellStyle name="Normal 133 2 2" xfId="6"/>
-    <cellStyle name="Normal 195" xfId="8"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 2" xfId="10"/>
-    <cellStyle name="Normal 2 2 7 2 2 2" xfId="5"/>
-    <cellStyle name="Normal 315" xfId="9"/>
-    <cellStyle name="Normal 80" xfId="1"/>
+    <cellStyle name="Normal 10 3 14" xfId="7" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 13 2 2 10 2 2 5 2 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 13 2 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 133 2 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 195" xfId="8" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Normal 2 2 7 2 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Normal 315" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Normal 80" xfId="1" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8041,7 +8038,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B1834"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -22722,13 +22719,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1834"/>
+  <autoFilter ref="A1:B1834" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -23598,7 +23595,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -23955,7 +23952,7 @@
         <v>2021</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>2035</v>
@@ -24155,7 +24152,7 @@
         <v>2021</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>2057</v>
@@ -24231,7 +24228,7 @@
         <v>2021</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>2023</v>
@@ -24271,7 +24268,7 @@
         <v>2021</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>2516</v>
+        <v>2522</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>2025</v>
@@ -24291,7 +24288,7 @@
         <v>2021</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>2026</v>
@@ -24957,7 +24954,7 @@
       <c r="A70" s="3">
         <v>520</v>
       </c>
-      <c r="B70" s="9"/>
+      <c r="B70" s="3"/>
       <c r="C70" s="3" t="s">
         <v>2021</v>
       </c>
@@ -25083,7 +25080,6 @@
       <c r="A77" s="3">
         <v>700</v>
       </c>
-      <c r="B77" s="8"/>
       <c r="C77" s="3" t="s">
         <v>2021</v>
       </c>
@@ -25125,8 +25121,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F41">
-    <sortState ref="A2:F79">
+  <autoFilter ref="A1:F41" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F79">
       <sortCondition ref="B1:B41"/>
     </sortState>
   </autoFilter>
@@ -25135,7 +25131,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -25182,13 +25178,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5"/>
+  <autoFilter ref="A1:B5" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -25229,13 +25225,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B4"/>
+  <autoFilter ref="A1:B4" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -25580,7 +25576,7 @@
         <v>2059</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>2124</v>
@@ -26566,7 +26562,7 @@
         <v>2059</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>2090</v>
@@ -26627,8 +26623,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F43">
-    <sortState ref="A2:F73">
+  <autoFilter ref="A1:F43" xr:uid="{00000000-0009-0000-0000-000005000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F73">
       <sortCondition descending="1" ref="C1:C43"/>
     </sortState>
   </autoFilter>
@@ -26637,7 +26633,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -27246,13 +27242,13 @@
       <c r="D43" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D43"/>
+  <autoFilter ref="A1:D43" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -28086,7 +28082,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D58"/>
+  <autoFilter ref="A1:D58" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Koding\tool-fcost\masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARISAFARI\Works\Project Applications\tool-fcost\masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DE972C-D48D-422D-92E8-183C47B625F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4927" uniqueCount="2523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4931" uniqueCount="2525">
   <si>
     <t>part_used</t>
   </si>
@@ -7606,13 +7605,19 @@
   </si>
   <si>
     <t>goyang|bergelombang|delay|dominan|merah|putih|blue|warna|kualitas gambar|slow motion|gambar bermasalah|layar bermasalah|bergerak|berembun|BERMASALAH</t>
+  </si>
+  <si>
+    <t>4TC75GU8500X</t>
+  </si>
+  <si>
+    <t>4TC85HU8500X</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7675,8 +7680,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7692,6 +7701,11 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -7732,7 +7746,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7749,19 +7763,20 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 3 14" xfId="7" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 13 2 2 10 2 2 5 2 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 13 2 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 133 2 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 195" xfId="8" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Normal 2 2 7 2 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Normal 315" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Normal 80" xfId="1" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Normal 10 3 14" xfId="7"/>
+    <cellStyle name="Normal 13 2 2 10 2 2 5 2 2 2 2" xfId="3"/>
+    <cellStyle name="Normal 13 2 2 2" xfId="4"/>
+    <cellStyle name="Normal 133 2 2" xfId="6"/>
+    <cellStyle name="Normal 195" xfId="8"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 2 2" xfId="10"/>
+    <cellStyle name="Normal 2 2 7 2 2 2" xfId="5"/>
+    <cellStyle name="Normal 315" xfId="9"/>
+    <cellStyle name="Normal 80" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8038,7 +8053,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B1834"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -22719,14 +22734,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1834" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:B1834"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B107"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -23589,13 +23604,29 @@
         <v>2507</v>
       </c>
     </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="8" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="8" t="s">
+        <v>2524</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>2507</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -25121,8 +25152,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F41" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F79">
+  <autoFilter ref="A1:F41">
+    <sortState ref="A2:F79">
       <sortCondition ref="B1:B41"/>
     </sortState>
   </autoFilter>
@@ -25131,7 +25162,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -25178,13 +25209,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:B5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -25225,13 +25256,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B4" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:B4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -26623,8 +26654,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F43" xr:uid="{00000000-0009-0000-0000-000005000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F73">
+  <autoFilter ref="A1:F43">
+    <sortState ref="A2:F73">
       <sortCondition descending="1" ref="C1:C43"/>
     </sortState>
   </autoFilter>
@@ -26633,7 +26664,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -27242,13 +27273,13 @@
       <c r="D43" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D43" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <autoFilter ref="A1:D43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -28082,7 +28113,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D58" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <autoFilter ref="A1:D58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4931" uniqueCount="2525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4937" uniqueCount="2528">
   <si>
     <t>part_used</t>
   </si>
@@ -7611,6 +7611,15 @@
   </si>
   <si>
     <t>4TC85HU8500X</t>
+  </si>
+  <si>
+    <t>4TC65HN7000I</t>
+  </si>
+  <si>
+    <t>4TC65HU8500I</t>
+  </si>
+  <si>
+    <t>4TC75HN7000I</t>
   </si>
 </sst>
 </file>
@@ -22741,7 +22750,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -23618,6 +23627,30 @@
       </c>
       <c r="B109" s="1" t="s">
         <v>2507</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>2525</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>1943</v>
       </c>
     </row>
   </sheetData>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -22,21 +22,21 @@
     <sheet name="comment_synonyms" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">action!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">action!$A$1:$F$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">branch!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">comment_synonyms!$A$1:$D$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">comment_synonyms!$A$1:$D$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">defect_category!$A$1:$D$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">factory!$A$1:$B$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">panel_usage!$A$1:$B$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">part_list!$A$1:$B$1834</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">symptom!$A$1:$F$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">symptom!$A$1:$F$47</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4937" uniqueCount="2528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5000" uniqueCount="2552">
   <si>
     <t>part_used</t>
   </si>
@@ -6125,9 +6125,6 @@
     <t>DOT</t>
   </si>
   <si>
-    <t>setengah|sebelah|half</t>
-  </si>
-  <si>
     <t>HALF</t>
   </si>
   <si>
@@ -6647,18 +6644,12 @@
     <t>No-channel phrase aliases.</t>
   </si>
   <si>
-    <t>0AMBAR|GAMABAR</t>
-  </si>
-  <si>
     <t>GAMBAR</t>
   </si>
   <si>
     <t>Gambar typo cleanup.</t>
   </si>
   <si>
-    <t>]IDAK|TDK</t>
-  </si>
-  <si>
     <t>TIDAK</t>
   </si>
   <si>
@@ -6722,9 +6713,6 @@
     <t>Boot-loop typo cleanup.</t>
   </si>
   <si>
-    <t>BLAND|BLAN</t>
-  </si>
-  <si>
     <t>Blank typo cleanup.</t>
   </si>
   <si>
@@ -6821,9 +6809,6 @@
     <t>Lampu typo cleanup.</t>
   </si>
   <si>
-    <t>MB</t>
-  </si>
-  <si>
     <t>MAIN BOARD</t>
   </si>
   <si>
@@ -7127,9 +7112,6 @@
     <t>Blinking/flicker display.</t>
   </si>
   <si>
-    <t>mati total|matot|mati|tidak bisa hidup|tidak bisa nyala|tidak nyala</t>
-  </si>
-  <si>
     <t>Panel reported as total off/no power.</t>
   </si>
   <si>
@@ -7319,9 +7301,6 @@
     <t>siaran|tidak ada siaran|tidak dapat siaran|no sinyal|tidak ada sinyal|tidak dapat remote|channel|sinyal</t>
   </si>
   <si>
-    <t>ADA BULATAN HITAM</t>
-  </si>
-  <si>
     <t>SPOT</t>
   </si>
   <si>
@@ -7334,9 +7313,6 @@
     <t>REMOTE_NG</t>
   </si>
   <si>
-    <t>tidak ada siaran|tidak ada channel|no channel|channel|sinyal|signal|siaran|STANDBY</t>
-  </si>
-  <si>
     <t>pecah|retak|broken|rusak panel|glass|PANEL RUSAK</t>
   </si>
   <si>
@@ -7349,9 +7325,6 @@
     <t>TIDAK BISA DI REMOTE</t>
   </si>
   <si>
-    <t>tidak ada gambar|no picture|no display|layar blank|blank|Layar gelap|TIDAK BISA TV</t>
-  </si>
-  <si>
     <t>ANTHENA|ANTENE</t>
   </si>
   <si>
@@ -7568,9 +7541,6 @@
     <t>tak ada gambar|tidak ada gambar|no display|no picture|blank|layar blank|gambar tidak keluar|x gambar|gambar tidak ada|layat blank|gambar gelap</t>
   </si>
   <si>
-    <t>error|eror|netflix|software|aplikasi|app|youtube|SAFE MODE|Loading</t>
-  </si>
-  <si>
     <t>ext|external|cairan|cleaning|semut|kotor|bersih|bersihkan|kardus rusak|EKSTERNAL|FAKTOR LUAR</t>
   </si>
   <si>
@@ -7592,9 +7562,6 @@
     <t>bayang|berbayang|blur|buram|mura|BUREM|GAMBAR TIDAK JELAS</t>
   </si>
   <si>
-    <t>mati total|matot|mati|tidak bisa hidup|tidak bisa nyala|tidak nyala|kena petir|listrik turun|SUSAH NYALA|TIDAK BISA DIHIDUPKAN|KORSLET</t>
-  </si>
-  <si>
     <t>tidak ada gambar|no display|no picture|blank|gambar gelap|gambar tidak keluar|gelap|x ada gambar|layar blank|LAYAR HITAM</t>
   </si>
   <si>
@@ -7604,9 +7571,6 @@
     <t>cek normal|cek ok|unit cek ok|normal|fungsi ok|test fungsi|cek fungsi ok|cek unit|reposisi antena|antena|DITEST OK|TIDAK ADA KERUSAKAN</t>
   </si>
   <si>
-    <t>goyang|bergelombang|delay|dominan|merah|putih|blue|warna|kualitas gambar|slow motion|gambar bermasalah|layar bermasalah|bergerak|berembun|BERMASALAH</t>
-  </si>
-  <si>
     <t>4TC75GU8500X</t>
   </si>
   <si>
@@ -7620,13 +7584,121 @@
   </si>
   <si>
     <t>4TC75HN7000I</t>
+  </si>
+  <si>
+    <t>4TC75HJ6000IG</t>
+  </si>
+  <si>
+    <t>BLAND|BLAN|BALNK|BLLANK</t>
+  </si>
+  <si>
+    <t>BERGAIRS</t>
+  </si>
+  <si>
+    <t>BERGARIS</t>
+  </si>
+  <si>
+    <t>setengah|sebelah|half|SEPARUH</t>
+  </si>
+  <si>
+    <t>LAYAR REDUP</t>
+  </si>
+  <si>
+    <t>DARK</t>
+  </si>
+  <si>
+    <t>ADA BULATAN HITAM|TITIK BOLA|BERCAK</t>
+  </si>
+  <si>
+    <t>goyang|bergelombang|delay|dominan|merah|putih|blue|warna|kualitas gambar|slow motion|gambar bermasalah|layar bermasalah|bergerak|berembun|BERMASALAH|KLISE|BERGETAR</t>
+  </si>
+  <si>
+    <t>]IDAK|TDK|TIDKA</t>
+  </si>
+  <si>
+    <t>L99|LAYAR KUNING|LAYAR ERROR</t>
+  </si>
+  <si>
+    <t>tidak ada siaran|tidak ada channel|no channel|channel|sinyal|signal|siaran|STANDBY|TIDAK MENYALA|TIDAK BISA DINYALAKAN|GAMBAR HILANG</t>
+  </si>
+  <si>
+    <t>ANJLOK</t>
+  </si>
+  <si>
+    <t>TURUN</t>
+  </si>
+  <si>
+    <t>REDUP</t>
+  </si>
+  <si>
+    <t>MATI</t>
+  </si>
+  <si>
+    <t>WIFI_NG</t>
+  </si>
+  <si>
+    <t>error|eror|netflix|software|aplikasi|app|youtube|SAFE MODE|Loading|TULISAN MODE</t>
+  </si>
+  <si>
+    <t>HIDUP</t>
+  </si>
+  <si>
+    <t>BLUETOOTH</t>
+  </si>
+  <si>
+    <t>BLUETOOTH_NG</t>
+  </si>
+  <si>
+    <t>mati total|matot|mati|tidak bisa hidup|tidak bisa nyala|tidak nyala|kena petir|listrik turun|SUSAH NYALA|TIDAK BISA DIHIDUPKAN|KORSLET|MCB MEMBALIK|KONSLET</t>
+  </si>
+  <si>
+    <t>0AMBAR|GAMABAR|GBR|GAMABR</t>
+  </si>
+  <si>
+    <t>DINYALAKAN|MENYALA</t>
+  </si>
+  <si>
+    <t>AFDA</t>
+  </si>
+  <si>
+    <t>ADA</t>
+  </si>
+  <si>
+    <t>MB|MAINBOAR</t>
+  </si>
+  <si>
+    <t>WIFI|INTERNET</t>
+  </si>
+  <si>
+    <t>MATO|13TI</t>
+  </si>
+  <si>
+    <t>A99|NO POWER|TIDAK hidup|MAIN BOARD RUSAK</t>
+  </si>
+  <si>
+    <t>tidak ada gambar|no picture|no display|layar blank|blank|Layar gelap|TIDAK BISA TV|GAMBAR GELAP|gambar hitam|GAMBAR TIDAK KELUAR|LAYAR TIDAK MUNCUL</t>
+  </si>
+  <si>
+    <t>mati total|matot|mati|tidak bisa hidup|tidak bisa nyala|tidak nyala|TIDAK HIDUP</t>
+  </si>
+  <si>
+    <t>9RATLA980WJZZ</t>
+  </si>
+  <si>
+    <t>9RATLA985WJZZ</t>
+  </si>
+  <si>
+    <t>9TAHL6500CP006</t>
+  </si>
+  <si>
+    <t>REPLACE_SWITCH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7681,6 +7753,11 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -7755,7 +7832,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7770,9 +7847,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8063,7 +8150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1834"/>
+  <dimension ref="A1:B1837"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -22742,6 +22829,30 @@
         <v>1939</v>
       </c>
     </row>
+    <row r="1835" spans="1:2">
+      <c r="A1835" s="11" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B1835" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:2">
+      <c r="A1836" s="11" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B1836" s="12" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:2">
+      <c r="A1837" s="11" t="s">
+        <v>2550</v>
+      </c>
+      <c r="B1837" s="1" t="s">
+        <v>1826</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B1834"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22750,7 +22861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -23327,255 +23438,255 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>2471</v>
+        <v>2462</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>2472</v>
+        <v>2463</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>2473</v>
+        <v>2464</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>2474</v>
+        <v>2465</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>2475</v>
+        <v>2466</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>2476</v>
+        <v>2467</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>2508</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>2477</v>
+        <v>2468</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>2508</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>2478</v>
+        <v>2469</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>2479</v>
+        <v>2470</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>2480</v>
+        <v>2471</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>2481</v>
+        <v>2472</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>2482</v>
+        <v>2473</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>2483</v>
+        <v>2474</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>2484</v>
+        <v>2475</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>2485</v>
+        <v>2476</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>2486</v>
+        <v>2477</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>2487</v>
+        <v>2478</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>2488</v>
+        <v>2479</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>2489</v>
+        <v>2480</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>2490</v>
+        <v>2481</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>2491</v>
+        <v>2482</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>2492</v>
+        <v>2483</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>2493</v>
+        <v>2484</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>2494</v>
+        <v>2485</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>2495</v>
+        <v>2486</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>2496</v>
+        <v>2487</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>2497</v>
+        <v>2488</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
+        <v>2489</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>2498</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>2507</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>2499</v>
+        <v>2490</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>2500</v>
+        <v>2491</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>2508</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>2501</v>
+        <v>2492</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>2502</v>
+        <v>2493</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>1943</v>
@@ -23583,7 +23694,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>2503</v>
+        <v>2494</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>1943</v>
@@ -23591,47 +23702,47 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>2504</v>
+        <v>2495</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>2505</v>
+        <v>2496</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>2506</v>
+        <v>2497</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="8" t="s">
-        <v>2523</v>
+      <c r="A108" s="6" t="s">
+        <v>2511</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="8" t="s">
-        <v>2524</v>
+      <c r="A109" s="6" t="s">
+        <v>2512</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>2507</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>2525</v>
+        <v>2513</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>1943</v>
@@ -23639,7 +23750,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>2526</v>
+        <v>2514</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>1943</v>
@@ -23647,9 +23758,17 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>2527</v>
+        <v>2515</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>2516</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>1943</v>
       </c>
     </row>
@@ -23660,7 +23779,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -23693,104 +23812,107 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3">
-        <v>720</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2059</v>
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>989</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D2" t="s">
-        <v>2429</v>
+      <c r="D2" s="3" t="s">
+        <v>2348</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>2090</v>
+        <v>2022</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>2349</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>3</v>
+        <v>345</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2066</v>
+        <v>2348</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>2035</v>
+        <v>2022</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>2067</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3">
-        <v>630</v>
-      </c>
-      <c r="B4" t="s">
-        <v>90</v>
+        <v>30</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2369</v>
+        <v>2348</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>2035</v>
+        <v>2022</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>2037</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3">
-        <v>360</v>
+        <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>128</v>
+        <v>1816</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2374</v>
+        <v>2348</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>2049</v>
+        <v>2022</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>2063</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3">
-        <v>640</v>
-      </c>
-      <c r="B6" t="s">
-        <v>128</v>
+        <v>50</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>989</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2369</v>
+        <v>2508</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>2035</v>
+        <v>2023</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>2037</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>214</v>
@@ -23799,127 +23921,130 @@
         <v>2021</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2353</v>
+        <v>2350</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>214</v>
+        <v>345</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2355</v>
+        <v>2350</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>2356</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3">
-        <v>340</v>
+        <v>80</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>214</v>
+        <v>1816</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2367</v>
+        <v>2350</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>2036</v>
+        <v>2024</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>2378</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3">
-        <v>650</v>
-      </c>
-      <c r="B10" t="s">
-        <v>214</v>
+        <v>90</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>989</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2369</v>
+        <v>2527</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>2035</v>
+        <v>2023</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>2037</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3">
-        <v>740</v>
+        <v>100</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>214</v>
+        <v>989</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2512</v>
+        <v>2524</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>2057</v>
+        <v>2025</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>2378</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3">
-        <v>750</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>322</v>
+        <v>101</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>989</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D12" t="s">
-        <v>2436</v>
+      <c r="D12" s="3" t="s">
+        <v>2526</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>2049</v>
+        <v>2025</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>2353</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>345</v>
+        <v>989</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2353</v>
+        <v>2507</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>2354</v>
@@ -23927,127 +24052,127 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>345</v>
+        <v>989</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>2028</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>2355</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>2024</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>2356</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3">
-        <v>330</v>
+        <v>130</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>345</v>
+        <v>989</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2031</v>
+        <v>2520</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>2032</v>
+        <v>2029</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>2062</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3">
-        <v>660</v>
-      </c>
-      <c r="B16" t="s">
-        <v>345</v>
+        <v>140</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>989</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2369</v>
+        <v>2030</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>2035</v>
+        <v>2031</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>2037</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>459</v>
+        <v>989</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2367</v>
+        <v>2425</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>2036</v>
+        <v>2032</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>2368</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>459</v>
+        <v>989</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2518</v>
+        <v>2547</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>2037</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>459</v>
+        <v>989</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2038</v>
+        <v>2359</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>2039</v>
+        <v>2023</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>2370</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>459</v>
@@ -24056,18 +24181,18 @@
         <v>2021</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2040</v>
+        <v>2361</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>2041</v>
+        <v>2035</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>2042</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>459</v>
@@ -24076,18 +24201,18 @@
         <v>2021</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2371</v>
+        <v>2537</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>2043</v>
+        <v>2034</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>2372</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3">
-        <v>230</v>
+        <v>191</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>459</v>
@@ -24095,19 +24220,19 @@
       <c r="C22" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>2437</v>
+      <c r="D22" s="10" t="s">
+        <v>2545</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>2024</v>
+        <v>2034</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>2373</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>459</v>
@@ -24116,18 +24241,18 @@
         <v>2021</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2510</v>
+        <v>2037</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>2044</v>
+        <v>2038</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>2045</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>459</v>
@@ -24136,18 +24261,18 @@
         <v>2021</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>2046</v>
+        <v>2039</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>2047</v>
+        <v>2040</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>2048</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>459</v>
@@ -24156,18 +24281,18 @@
         <v>2021</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2374</v>
+        <v>2365</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>2049</v>
+        <v>2042</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>2050</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="3">
-        <v>270</v>
+        <v>221</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>459</v>
@@ -24176,18 +24301,16 @@
         <v>2021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2051</v>
+        <v>2543</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>2052</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>2053</v>
-      </c>
+        <v>2532</v>
+      </c>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3">
-        <v>280</v>
+        <v>222</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>459</v>
@@ -24196,18 +24319,16 @@
         <v>2021</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>2054</v>
+        <v>2535</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>2055</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>2056</v>
-      </c>
+        <v>2536</v>
+      </c>
+      <c r="F27" s="3"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>459</v>
@@ -24216,18 +24337,18 @@
         <v>2021</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>2516</v>
+        <v>2546</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>2057</v>
+        <v>2024</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>2058</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3">
-        <v>760</v>
+        <v>231</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>459</v>
@@ -24236,16 +24357,16 @@
         <v>2021</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>2439</v>
+        <v>2530</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>2440</v>
+        <v>2522</v>
       </c>
       <c r="F29" s="3"/>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="3">
-        <v>780</v>
+        <v>240</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>459</v>
@@ -24253,873 +24374,876 @@
       <c r="C30" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D30" t="s">
-        <v>2513</v>
+      <c r="D30" s="3" t="s">
+        <v>2533</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>2441</v>
-      </c>
-      <c r="F30" s="3"/>
+        <v>2043</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>2044</v>
+      </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="3">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>989</v>
+        <v>459</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>2353</v>
+        <v>2045</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>2022</v>
+        <v>2046</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>2354</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="3">
-        <v>50</v>
+        <v>260</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>989</v>
+        <v>459</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2519</v>
+        <v>2368</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>2023</v>
+        <v>2048</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>2356</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="3">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>989</v>
+        <v>459</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>2432</v>
+        <v>2050</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>2023</v>
+        <v>2051</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>2357</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="3">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>989</v>
+        <v>459</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>2522</v>
+        <v>2053</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>2025</v>
+        <v>2054</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>2358</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3">
-        <v>110</v>
+        <v>290</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>989</v>
+        <v>459</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>2517</v>
+        <v>2506</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>2026</v>
+        <v>2056</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>2359</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3">
-        <v>120</v>
+        <v>291</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>989</v>
+        <v>459</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>2027</v>
+        <v>2519</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>2028</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>2360</v>
-      </c>
+        <v>2056</v>
+      </c>
+      <c r="F36" s="3"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="3">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>989</v>
+        <v>1429</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>2029</v>
+        <v>2058</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>2030</v>
+        <v>2034</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>2361</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="3">
-        <v>140</v>
+        <v>310</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>989</v>
+        <v>1660</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>2031</v>
+        <v>2370</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>2032</v>
+        <v>2059</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>2362</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="3">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>989</v>
+        <v>1732</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>2433</v>
+        <v>2058</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>2033</v>
+        <v>2051</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>2034</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="3">
-        <v>160</v>
+        <v>330</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>989</v>
+        <v>345</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>2363</v>
+        <v>2030</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>2035</v>
+        <v>2031</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>2364</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="3">
-        <v>170</v>
+        <v>340</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>989</v>
+        <v>214</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>2365</v>
+        <v>2361</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>2023</v>
+        <v>2035</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>2366</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="3">
-        <v>710</v>
-      </c>
-      <c r="B42" t="s">
-        <v>989</v>
+        <v>350</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>1826</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D42" t="s">
-        <v>2427</v>
+      <c r="D42" s="3" t="s">
+        <v>2373</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>2428</v>
+        <v>2056</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>2374</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="3">
-        <v>670</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1398</v>
+        <v>360</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>2059</v>
+        <v>2368</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>2035</v>
+        <v>2048</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>2037</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="3">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>1429</v>
+        <v>1889</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>2059</v>
+        <v>2375</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>2035</v>
+        <v>2042</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="3">
-        <v>310</v>
+        <v>380</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1660</v>
+        <v>1811</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>2376</v>
+        <v>2063</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>2060</v>
+        <v>2054</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3">
-        <v>680</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1660</v>
+        <v>390</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>2431</v>
+        <v>2034</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>2037</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3">
-        <v>320</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>1732</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="B47" s="3"/>
       <c r="C47" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>2059</v>
+        <v>2377</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>2052</v>
+        <v>2022</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3">
-        <v>380</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>1811</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="B48" s="3"/>
       <c r="C48" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>2064</v>
+        <v>2500</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>2055</v>
+        <v>2024</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>2065</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="3">
-        <v>620</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>1811</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="B49" s="3"/>
       <c r="C49" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>2423</v>
+        <v>2420</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>2424</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="3">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>1816</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="B50" s="3"/>
       <c r="C50" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>2353</v>
+        <v>2381</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>2022</v>
+        <v>2031</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>2354</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="3">
-        <v>80</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>1816</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="B51" s="3"/>
       <c r="C51" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>2355</v>
+        <v>2383</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>2024</v>
+        <v>2059</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>2356</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="3">
-        <v>530</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>1816</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="B52" s="3"/>
       <c r="C52" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>2406</v>
+        <v>2385</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>2025</v>
+        <v>2051</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>2407</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="3">
-        <v>540</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>1816</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="B53" s="3"/>
       <c r="C53" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>2408</v>
+        <v>2433</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>2026</v>
+        <v>2043</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>2409</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="3">
-        <v>550</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>1816</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="B54" s="3"/>
       <c r="C54" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>2410</v>
+        <v>2388</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>2411</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="3">
-        <v>610</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>1816</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="B55" s="3"/>
       <c r="C55" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>2421</v>
+        <v>2390</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>2035</v>
+        <v>2025</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>2422</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="3">
-        <v>350</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>1826</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="B56" s="3"/>
       <c r="C56" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>2379</v>
+        <v>2392</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>2057</v>
+        <v>2028</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>2380</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="3">
-        <v>370</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>1889</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="B57" s="3"/>
       <c r="C57" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>2381</v>
+        <v>2394</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>2043</v>
+        <v>2032</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>2382</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="3">
-        <v>400</v>
+        <v>510</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>2383</v>
+        <v>2396</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>2022</v>
+        <v>2054</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>2384</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="3">
-        <v>410</v>
+        <v>520</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>2509</v>
+        <v>2398</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>2024</v>
+        <v>2034</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>2385</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="3">
-        <v>420</v>
-      </c>
-      <c r="B60" s="3"/>
+        <v>530</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C60" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>2426</v>
+        <v>2400</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>2043</v>
+        <v>2025</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>2386</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="3">
-        <v>430</v>
-      </c>
-      <c r="B61" s="3"/>
+        <v>540</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C61" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>2387</v>
+        <v>2402</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>2032</v>
+        <v>2026</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>2388</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="3">
-        <v>440</v>
-      </c>
-      <c r="B62" s="3"/>
+        <v>550</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C62" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>2389</v>
+        <v>2404</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>2060</v>
+        <v>2032</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>2390</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="3">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>2391</v>
+        <v>2406</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>2052</v>
+        <v>2024</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>2392</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="3">
-        <v>460</v>
+        <v>570</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>2442</v>
+        <v>2408</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>2044</v>
+        <v>2025</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>2393</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="3">
-        <v>470</v>
+        <v>580</v>
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>2394</v>
+        <v>2410</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>2395</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="3">
-        <v>480</v>
+        <v>590</v>
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>2396</v>
+        <v>2412</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>2025</v>
+        <v>2056</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>2397</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="3">
-        <v>490</v>
+        <v>600</v>
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>2398</v>
+        <v>2504</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>2028</v>
+        <v>2042</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>2399</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="3">
-        <v>500</v>
-      </c>
-      <c r="B68" s="3"/>
+        <v>610</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C68" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>2400</v>
+        <v>2415</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>2401</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="3">
-        <v>510</v>
-      </c>
-      <c r="B69" s="3"/>
+        <v>620</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>1811</v>
+      </c>
       <c r="C69" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>2402</v>
+        <v>2417</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>2055</v>
+        <v>2042</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>2403</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="3">
-        <v>520</v>
-      </c>
-      <c r="B70" s="3"/>
+        <v>630</v>
+      </c>
+      <c r="B70" t="s">
+        <v>90</v>
+      </c>
       <c r="C70" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>2404</v>
+        <v>2363</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>2405</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="3">
-        <v>560</v>
-      </c>
-      <c r="B71" s="3"/>
+        <v>640</v>
+      </c>
+      <c r="B71" t="s">
+        <v>128</v>
+      </c>
       <c r="C71" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>2412</v>
+        <v>2363</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>2024</v>
+        <v>2034</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>2413</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="3">
-        <v>570</v>
-      </c>
-      <c r="B72" s="3"/>
+        <v>650</v>
+      </c>
+      <c r="B72" t="s">
+        <v>214</v>
+      </c>
       <c r="C72" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>2414</v>
+        <v>2363</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>2025</v>
+        <v>2034</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>2415</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="3">
-        <v>580</v>
-      </c>
-      <c r="B73" s="3"/>
+        <v>660</v>
+      </c>
+      <c r="B73" t="s">
+        <v>345</v>
+      </c>
       <c r="C73" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>2416</v>
+        <v>2363</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>2417</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="3">
-        <v>590</v>
-      </c>
-      <c r="B74" s="3"/>
+        <v>670</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1398</v>
+      </c>
       <c r="C74" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2418</v>
+        <v>2058</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>2057</v>
+        <v>2034</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>2419</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="3">
-        <v>600</v>
-      </c>
-      <c r="B75" s="3"/>
+        <v>680</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1660</v>
+      </c>
       <c r="C75" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>2514</v>
+        <v>2058</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>2043</v>
+        <v>2424</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>2420</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -25131,13 +25255,13 @@
         <v>2021</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>2369</v>
+        <v>2363</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -25148,46 +25272,173 @@
         <v>2021</v>
       </c>
       <c r="D77" s="3" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>2040</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>2041</v>
       </c>
       <c r="F77" s="3"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="3">
-        <v>730</v>
-      </c>
-      <c r="B78" s="3"/>
+        <v>710</v>
+      </c>
+      <c r="B78" t="s">
+        <v>989</v>
+      </c>
       <c r="C78" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>2430</v>
+      <c r="D78" t="s">
+        <v>2523</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>2057</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="3">
-        <v>770</v>
+        <v>711</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>989</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D79" t="s">
-        <v>2515</v>
+      <c r="D79" s="3" t="s">
+        <v>2521</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>2441</v>
-      </c>
+        <v>2522</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="3">
+        <v>720</v>
+      </c>
+      <c r="B80" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D80" t="s">
+        <v>2422</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="3">
+        <v>730</v>
+      </c>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>2423</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="3">
+        <v>740</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>2056</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="3">
+        <v>750</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D83" t="s">
+        <v>2428</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="3">
+        <v>760</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>2431</v>
+      </c>
+      <c r="F84" s="3"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="3">
+        <v>770</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D85" t="s">
+        <v>2505</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="3">
+        <v>780</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D86" t="s">
+        <v>2503</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>2432</v>
+      </c>
+      <c r="F86" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F41">
-    <sortState ref="A2:F79">
-      <sortCondition ref="B1:B41"/>
+  <autoFilter ref="A1:F47">
+    <sortState ref="A2:F81">
+      <sortCondition ref="A1:A42"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25205,40 +25456,40 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2068</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2069</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2070</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2071</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2072</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2073</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>2074</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2075</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
     </row>
   </sheetData>
@@ -25258,34 +25509,34 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2077</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2078</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2079</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2080</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
   </sheetData>
@@ -25296,7 +25547,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -25311,204 +25562,188 @@
         <v>2016</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>2083</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2084</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>2085</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2086</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>1826</v>
-      </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2120</v>
+        <v>2501</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>2121</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1826</v>
-      </c>
+      <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2059</v>
+        <v>2087</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>2121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30">
       <c r="A4" s="1">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>1811</v>
-      </c>
+      <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2122</v>
+        <v>2510</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>2123</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1">
-        <v>420</v>
+        <v>40</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>1811</v>
-      </c>
+      <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2059</v>
+        <v>2090</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>2123</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>1732</v>
-      </c>
+      <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>2118</v>
+        <v>2092</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>2119</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>1732</v>
-      </c>
+      <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2059</v>
+        <v>2094</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>2119</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>1660</v>
-      </c>
+      <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>2127</v>
+        <v>2096</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="45">
       <c r="A9" s="1">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>1660</v>
-      </c>
+      <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2106</v>
+        <v>2437</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>2107</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1">
-        <v>310</v>
+        <v>90</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1660</v>
+        <v>989</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>2059</v>
+        <v>2099</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>2107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="45">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
@@ -25517,1179 +25752,1231 @@
         <v>1429</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2125</v>
+        <v>2101</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>2126</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1429</v>
+        <v>459</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1429</v>
+        <v>459</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2059</v>
+        <v>2501</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>2103</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1398</v>
+        <v>1660</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>2059</v>
+        <v>2105</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>2126</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>989</v>
+        <v>214</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2100</v>
+        <v>2107</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>2101</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>989</v>
+        <v>345</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>2059</v>
+        <v>2109</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>2101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="60">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>459</v>
+        <v>90</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2520</v>
+        <v>2111</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>2124</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>459</v>
+        <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>2104</v>
+        <v>2113</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>2105</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1">
-        <v>300</v>
+        <v>170</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>459</v>
+        <v>128</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2059</v>
+        <v>2115</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>2105</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>2129</v>
+        <v>2115</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>2130</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>345</v>
+        <v>1732</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2110</v>
+        <v>2117</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>2111</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>345</v>
+        <v>1826</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>2059</v>
+        <v>2119</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>2111</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="B23" s="1">
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>322</v>
+        <v>1811</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>2116</v>
+        <v>2121</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>2117</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="60">
       <c r="A24" s="1">
-        <v>390</v>
+        <v>220</v>
       </c>
       <c r="B24" s="1">
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>322</v>
+        <v>459</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>2059</v>
+        <v>2509</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>2117</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="45">
       <c r="A25" s="1">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="B25" s="1">
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>214</v>
+        <v>1429</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>2108</v>
+        <v>2124</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>2109</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1">
-        <v>330</v>
+        <v>240</v>
       </c>
       <c r="B26" s="1">
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>214</v>
+        <v>1660</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>2059</v>
+        <v>2126</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>2109</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="B27" s="1">
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>128</v>
+        <v>345</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2116</v>
+        <v>2128</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>2117</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="B28" s="1">
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>128</v>
+        <v>37</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>2059</v>
+        <v>2130</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>2117</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1">
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="B29" s="1">
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>2059</v>
+        <v>2130</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>90</v>
+        <v>1429</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>2112</v>
+        <v>2058</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>2113</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1">
-        <v>370</v>
+        <v>290</v>
       </c>
       <c r="B31" s="1">
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>90</v>
+        <v>989</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>2113</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="B32" s="1">
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>37</v>
+        <v>459</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>2131</v>
+        <v>2058</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>2132</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="B33" s="1">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>24</v>
+        <v>1660</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>2131</v>
+        <v>2058</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>2132</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="B34" s="1">
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>3</v>
+        <v>1398</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>2114</v>
+        <v>2058</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>2115</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="B35" s="1">
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>3</v>
+        <v>214</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>2115</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1">
-        <v>510</v>
+        <v>340</v>
       </c>
       <c r="B36" s="1">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2059</v>
+        <v>109</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>2511</v>
+        <v>2058</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>2087</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1">
-        <v>520</v>
+        <v>350</v>
       </c>
       <c r="B37" s="1">
         <v>1</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>2059</v>
-      </c>
-      <c r="D37" s="1"/>
+        <v>345</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>2058</v>
+      </c>
       <c r="E37" s="1" t="s">
-        <v>2511</v>
+        <v>2058</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>2087</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1">
-        <v>20</v>
+        <v>360</v>
       </c>
       <c r="B38" s="1">
         <v>1</v>
       </c>
-      <c r="C38" s="1"/>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="D38" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>2088</v>
+        <v>2058</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>2089</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="4">
-        <v>690</v>
-      </c>
-      <c r="B39" s="5">
+      <c r="A39" s="1">
+        <v>370</v>
+      </c>
+      <c r="B39" s="1">
         <v>1</v>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>2467</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>2089</v>
+      <c r="C39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>2112</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1">
-        <v>50</v>
+        <v>380</v>
       </c>
       <c r="B40" s="1">
         <v>1</v>
       </c>
-      <c r="C40" s="1"/>
+      <c r="C40" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="D40" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>2093</v>
+        <v>2058</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>2094</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1">
-        <v>10</v>
+        <v>390</v>
       </c>
       <c r="B41" s="1">
         <v>1</v>
       </c>
-      <c r="C41" s="1"/>
+      <c r="C41" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="D41" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>2511</v>
+        <v>2058</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>2087</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1">
-        <v>530</v>
+        <v>400</v>
       </c>
       <c r="B42" s="1">
         <v>1</v>
       </c>
-      <c r="D42" t="s">
-        <v>2448</v>
+      <c r="C42" s="1" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>2058</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>2087</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1">
-        <v>540</v>
+        <v>410</v>
       </c>
       <c r="B43" s="1">
         <v>1</v>
       </c>
+      <c r="C43" s="1" t="s">
+        <v>1826</v>
+      </c>
       <c r="D43" s="1" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E43" t="s">
-        <v>2448</v>
+        <v>2058</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>2058</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>2087</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="4">
-        <v>700</v>
-      </c>
-      <c r="B44" s="5">
+      <c r="A44" s="1">
+        <v>420</v>
+      </c>
+      <c r="B44" s="1">
         <v>1</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5" t="s">
-        <v>2468</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>2059</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>2087</v>
+      <c r="C44" s="1" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>2551</v>
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="4">
-        <v>710</v>
-      </c>
-      <c r="B45" s="5">
+      <c r="A45" s="1">
+        <v>430</v>
+      </c>
+      <c r="B45" s="1">
         <v>1</v>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>2469</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>2087</v>
+      <c r="C45" s="11" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>2180</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1">
-        <v>70</v>
+        <v>440</v>
       </c>
       <c r="B46" s="1">
         <v>1</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>2097</v>
+        <v>2434</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="4">
-        <v>670</v>
-      </c>
-      <c r="B47" s="5">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="60">
+      <c r="A47" s="1">
+        <v>450</v>
+      </c>
+      <c r="B47" s="1">
         <v>1</v>
       </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>2465</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="1"/>
+      <c r="D47" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>2441</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="45">
       <c r="A48" s="1">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="B48" s="1">
         <v>1</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E48" t="s">
-        <v>2452</v>
+        <v>2058</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>2440</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>2132</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="1">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="B49" s="1">
         <v>1</v>
       </c>
-      <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>2445</v>
+        <v>2058</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2435</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>2130</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="4">
-        <v>650</v>
-      </c>
-      <c r="B50" s="5">
+      <c r="A50" s="1">
+        <v>480</v>
+      </c>
+      <c r="B50" s="1">
         <v>1</v>
       </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>2463</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>2130</v>
+      <c r="D50" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>2442</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>2125</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="4">
-        <v>560</v>
-      </c>
-      <c r="B51" s="4">
+      <c r="A51" s="1">
+        <v>490</v>
+      </c>
+      <c r="B51" s="1">
         <v>1</v>
       </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>2453</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>2155</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="60">
+      <c r="D51" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2438</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="1">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="B52" s="1">
         <v>1</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>2450</v>
+        <v>2436</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>2124</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="1">
-        <v>460</v>
+        <v>510</v>
       </c>
       <c r="B53" s="1">
         <v>1</v>
       </c>
+      <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E53" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>2124</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
       <c r="B54" s="1">
         <v>1</v>
       </c>
+      <c r="C54" s="1" t="s">
+        <v>2058</v>
+      </c>
       <c r="D54" s="1" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E54" t="s">
-        <v>2447</v>
+        <v>2058</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>2501</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>2124</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="4">
-        <v>590</v>
-      </c>
-      <c r="B55" s="5">
+      <c r="A55" s="1">
+        <v>530</v>
+      </c>
+      <c r="B55" s="1">
         <v>1</v>
       </c>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>2456</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>2124</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="45">
+      <c r="C55" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>2501</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" s="1">
-        <v>450</v>
+        <v>540</v>
       </c>
       <c r="B56" s="1">
         <v>1</v>
       </c>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1" t="s">
-        <v>2059</v>
+      <c r="D56" t="s">
+        <v>2439</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>2449</v>
+        <v>2058</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>2126</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="1">
-        <v>470</v>
+        <v>550</v>
       </c>
       <c r="B57" s="1">
         <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>2451</v>
+        <v>2058</v>
+      </c>
+      <c r="E57" t="s">
+        <v>2439</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>2126</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="4">
-        <v>570</v>
-      </c>
-      <c r="B58" s="5">
+        <v>560</v>
+      </c>
+      <c r="B58" s="4">
         <v>1</v>
       </c>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5" t="s">
-        <v>2454</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>2059</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>2126</v>
+      <c r="D58" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E58" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F58" t="s">
+        <v>2185</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="4">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="B59" s="5">
         <v>1</v>
       </c>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>2455</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>2126</v>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>2444</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>2154</v>
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="1">
-        <v>430</v>
-      </c>
-      <c r="B60" s="1">
+      <c r="A60" s="4">
+        <v>580</v>
+      </c>
+      <c r="B60" s="5">
         <v>1</v>
       </c>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>2443</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>2128</v>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5" t="s">
+        <v>2445</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>2058</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>2125</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="4">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="B61" s="5">
         <v>1</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5" t="s">
-        <v>2459</v>
+        <v>2058</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>2059</v>
+        <v>2446</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="4">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="B62" s="5">
         <v>1</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="5" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>2460</v>
+        <v>2447</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>2128</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="4">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="B63" s="5">
         <v>1</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>2457</v>
+        <v>2448</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>2458</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="4">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="B64" s="5">
         <v>1</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5" t="s">
-        <v>2059</v>
+        <v>2450</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>2461</v>
+        <v>2058</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>2123</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="45">
-      <c r="A65" s="1">
-        <v>80</v>
-      </c>
-      <c r="B65" s="1">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="4">
+        <v>630</v>
+      </c>
+      <c r="B65" s="5">
         <v>1</v>
       </c>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>2446</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>2099</v>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>2451</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>2127</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="4">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="B66" s="5">
         <v>1</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>2464</v>
+        <v>2452</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>2099</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="1">
-        <v>550</v>
-      </c>
-      <c r="B67" s="1">
+      <c r="A67" s="4">
+        <v>650</v>
+      </c>
+      <c r="B67" s="5">
         <v>1</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E67" t="s">
-        <v>2186</v>
-      </c>
-      <c r="F67" t="s">
-        <v>2186</v>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>2453</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>2089</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="4">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="B68" s="5">
         <v>1</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>2466</v>
+        <v>2454</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>2186</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="1">
-        <v>60</v>
-      </c>
-      <c r="B69" s="1">
+      <c r="A69" s="4">
+        <v>670</v>
+      </c>
+      <c r="B69" s="5">
         <v>1</v>
       </c>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>2095</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>2096</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="30">
-      <c r="A70" s="1">
-        <v>30</v>
-      </c>
-      <c r="B70" s="1">
+      <c r="C69" s="5"/>
+      <c r="D69" s="5" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>2455</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="4">
+        <v>680</v>
+      </c>
+      <c r="B70" s="5">
         <v>1</v>
       </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>2521</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>2090</v>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>2456</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>2097</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="4">
-        <v>640</v>
+        <v>690</v>
       </c>
       <c r="B71" s="5">
         <v>1</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="5" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>2462</v>
+        <v>2457</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>2090</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="4">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="B72" s="5">
         <v>1</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="5" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>2470</v>
+        <v>2458</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="1">
-        <v>40</v>
-      </c>
-      <c r="B73" s="1">
+      <c r="A73" s="4">
+        <v>710</v>
+      </c>
+      <c r="B73" s="5">
         <v>1</v>
       </c>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1" t="s">
-        <v>2059</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>2091</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>2092</v>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5" t="s">
+        <v>2459</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>2058</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="4">
+        <v>720</v>
+      </c>
+      <c r="B74" s="5">
+        <v>1</v>
+      </c>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>2460</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="C75" s="5"/>
+      <c r="D75" s="5" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>2461</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>2089</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F43">
-    <sortState ref="A2:F73">
-      <sortCondition descending="1" ref="C1:C43"/>
+  <autoFilter ref="A1:F44">
+    <sortState ref="A2:F74">
+      <sortCondition ref="A1:A44"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26709,584 +26996,584 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2133</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2134</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2135</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2136</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2137</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>2138</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>2140</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>2094</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>2141</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>2142</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>2143</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>2144</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>459</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>2159</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>2142</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>2160</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>1429</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>459</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>989</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30">
       <c r="A28" s="1" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>1429</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>2183</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>2184</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>2140</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>2184</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>2185</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>2142</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>2143</v>
-      </c>
       <c r="D38" s="1" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>964</v>
@@ -27295,10 +27582,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>964</v>
@@ -27313,7 +27600,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="78" customWidth="1"/>
@@ -27324,13 +27611,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2190</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2191</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2192</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2020</v>
@@ -27338,815 +27625,875 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45">
       <c r="A3" s="1" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2195</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2196</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>2425</v>
+        <v>2419</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>2200</v>
+        <v>2544</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2201</v>
+        <v>2531</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2019</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>2202</v>
-      </c>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>2203</v>
+        <v>2199</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2204</v>
+        <v>2200</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2205</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>2206</v>
+        <v>2538</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2207</v>
+        <v>2202</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2208</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>2209</v>
+        <v>2525</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2210</v>
+        <v>2204</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2211</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>2184</v>
+        <v>2206</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2212</v>
+        <v>2207</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2213</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>2214</v>
+        <v>2540</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2044</v>
+        <v>2541</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2019</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>2215</v>
-      </c>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>2216</v>
+        <v>2183</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2217</v>
+        <v>2209</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2218</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>2219</v>
+      <c r="A12" t="s">
+        <v>2539</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2220</v>
+        <v>2534</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>2019</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>2221</v>
-      </c>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>2222</v>
+      <c r="A13" t="s">
+        <v>2518</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2223</v>
+        <v>2519</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>2019</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>2224</v>
-      </c>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>2225</v>
+        <v>2211</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2226</v>
+        <v>2043</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2227</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>2228</v>
+        <v>2528</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2023</v>
+        <v>2529</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2019</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>2229</v>
-      </c>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>2230</v>
+        <v>2213</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2231</v>
+        <v>2214</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2232</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>2233</v>
+        <v>2216</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2234</v>
+        <v>2217</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2235</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>2236</v>
+        <v>2219</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2237</v>
+        <v>2220</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2238</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>2239</v>
+        <v>2222</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2240</v>
+        <v>2223</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2241</v>
+        <v>2019</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2242</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>2243</v>
+        <v>2517</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2244</v>
+        <v>2023</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2241</v>
+        <v>2019</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2245</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2246</v>
+        <v>2226</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2247</v>
+        <v>2227</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2241</v>
+        <v>2019</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2248</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>2249</v>
+        <v>2229</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2250</v>
+        <v>2230</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2241</v>
+        <v>2019</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2251</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>2252</v>
+        <v>2232</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2253</v>
+        <v>2233</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2241</v>
+        <v>2019</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2254</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>2255</v>
+        <v>2235</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2256</v>
+        <v>2236</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2257</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>2258</v>
+        <v>2239</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2259</v>
+        <v>2240</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>2241</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>2260</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>2261</v>
+        <v>2242</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2262</v>
+        <v>2243</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2263</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>2264</v>
+        <v>2245</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2265</v>
+        <v>2246</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2266</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>2267</v>
+        <v>2248</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2143</v>
+        <v>2249</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2268</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>2269</v>
+        <v>2251</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>989</v>
+        <v>2252</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2270</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>2271</v>
+        <v>2254</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2272</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>2273</v>
+        <v>2542</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>2274</v>
+        <v>2257</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2275</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2276</v>
+        <v>2259</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>2277</v>
+        <v>2260</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2278</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="30">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>2279</v>
+        <v>2262</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>2280</v>
+        <v>2142</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2281</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>2282</v>
+        <v>2264</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>2283</v>
+        <v>989</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2284</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>2285</v>
+        <v>2266</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2286</v>
+        <v>2249</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2287</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>2288</v>
+        <v>2268</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2289</v>
+        <v>2269</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2290</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>2291</v>
+        <v>2271</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2292</v>
+        <v>2272</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2293</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="30">
       <c r="A38" s="1" t="s">
-        <v>2294</v>
+        <v>2274</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2295</v>
+        <v>2275</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>2296</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>2297</v>
+        <v>2277</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1889</v>
+        <v>2278</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2298</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>2299</v>
+        <v>2280</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2300</v>
+        <v>2281</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2301</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>2302</v>
+        <v>2283</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>2303</v>
+        <v>2284</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2304</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>2305</v>
+        <v>2286</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>2306</v>
+        <v>2287</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>2307</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2308</v>
+        <v>2289</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2309</v>
+        <v>2290</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>2310</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>2311</v>
+        <v>2292</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>2099</v>
+        <v>1889</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>2312</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
-        <v>2313</v>
+        <v>2294</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>2314</v>
+        <v>2295</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>2315</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
-        <v>2316</v>
+        <v>2297</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>2317</v>
+        <v>2298</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>2318</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>2319</v>
+        <v>2300</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>2320</v>
+        <v>2301</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>2321</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
-        <v>2322</v>
+        <v>2303</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>2323</v>
+        <v>2304</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>2324</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>2325</v>
+        <v>2306</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>2326</v>
+        <v>2098</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>2327</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1" t="s">
-        <v>2328</v>
+        <v>2308</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>2329</v>
+        <v>2309</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>2330</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1" t="s">
-        <v>2331</v>
+        <v>2311</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>2332</v>
+        <v>2312</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>2333</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
-        <v>2334</v>
+        <v>2314</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>2096</v>
+        <v>2315</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>2335</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1" t="s">
-        <v>2336</v>
+        <v>2317</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>2337</v>
+        <v>2318</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>2338</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>2438</v>
+        <v>2320</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>2339</v>
+        <v>2321</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>2340</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1" t="s">
-        <v>2341</v>
+        <v>2323</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>2342</v>
+        <v>2324</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>2343</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1" t="s">
-        <v>2344</v>
+        <v>2326</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>2345</v>
+        <v>2327</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>2346</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
-        <v>2347</v>
+        <v>2329</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>2348</v>
+        <v>2095</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>2349</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>2350</v>
+        <v>2331</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>2351</v>
+        <v>2332</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>2352</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" t="s">
-        <v>2434</v>
+      <c r="A59" s="1" t="s">
+        <v>2429</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>2435</v>
+        <v>2334</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="1" t="s">
+        <v>2336</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>2337</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="1" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="1" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>2346</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>2427</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>2019</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D58"/>
+  <autoFilter ref="A1:D63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -7771,7 +7771,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7781,12 +7781,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -7832,7 +7826,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7843,11 +7837,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -7856,10 +7846,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22830,7 +22825,7 @@
       </c>
     </row>
     <row r="1835" spans="1:2">
-      <c r="A1835" s="11" t="s">
+      <c r="A1835" s="9" t="s">
         <v>2548</v>
       </c>
       <c r="B1835" s="1" t="s">
@@ -22838,15 +22833,15 @@
       </c>
     </row>
     <row r="1836" spans="1:2">
-      <c r="A1836" s="11" t="s">
+      <c r="A1836" s="9" t="s">
         <v>2549</v>
       </c>
-      <c r="B1836" s="12" t="s">
+      <c r="B1836" s="10" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="1837" spans="1:2">
-      <c r="A1837" s="11" t="s">
+      <c r="A1837" s="9" t="s">
         <v>2550</v>
       </c>
       <c r="B1837" s="1" t="s">
@@ -23725,7 +23720,7 @@
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="4" t="s">
         <v>2511</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -23733,7 +23728,7 @@
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="4" t="s">
         <v>2512</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -24220,7 +24215,7 @@
       <c r="C22" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="8" t="s">
         <v>2545</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -25250,7 +25245,7 @@
       <c r="A76" s="3">
         <v>690</v>
       </c>
-      <c r="B76" s="7"/>
+      <c r="B76" s="5"/>
       <c r="C76" s="3" t="s">
         <v>2021</v>
       </c>
@@ -25372,7 +25367,7 @@
       <c r="A83" s="3">
         <v>750</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="7" t="s">
         <v>322</v>
       </c>
       <c r="C83" s="3" t="s">
@@ -25389,7 +25384,7 @@
       <c r="A84" s="3">
         <v>760</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="6" t="s">
         <v>459</v>
       </c>
       <c r="C84" s="3" t="s">
@@ -25547,7 +25542,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -25557,7 +25552,7 @@
     <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>2016</v>
       </c>
@@ -25577,7 +25572,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>10</v>
       </c>
@@ -25595,1383 +25590,1601 @@
         <v>2086</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1">
+    <row r="3" spans="1:8">
+      <c r="A3" s="11">
         <v>20</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="11">
         <v>1</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="11"/>
+      <c r="D3" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="11" t="s">
         <v>2087</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="11" t="s">
         <v>2088</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="30">
-      <c r="A4" s="1">
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+    </row>
+    <row r="4" spans="1:8" ht="30">
+      <c r="A4" s="11">
         <v>30</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="11"/>
+      <c r="D4" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="11" t="s">
         <v>2510</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="11" t="s">
         <v>2089</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1">
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="11">
         <v>40</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="11"/>
+      <c r="D5" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="11" t="s">
         <v>2090</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="11" t="s">
         <v>2091</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1">
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="11">
         <v>50</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="11">
         <v>1</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="11"/>
+      <c r="D6" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="11" t="s">
         <v>2092</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="11" t="s">
         <v>2093</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1">
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="11">
         <v>60</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="11">
         <v>1</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="11"/>
+      <c r="D7" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="11" t="s">
         <v>2094</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="11" t="s">
         <v>2095</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1">
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="11">
         <v>70</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="11">
         <v>1</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="C8" s="11"/>
+      <c r="D8" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="11" t="s">
         <v>2096</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="11" t="s">
         <v>2097</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="45">
-      <c r="A9" s="1">
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+    </row>
+    <row r="9" spans="1:8" ht="45">
+      <c r="A9" s="11">
         <v>80</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="11">
         <v>1</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1" t="s">
+      <c r="C9" s="11"/>
+      <c r="D9" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="11" t="s">
         <v>2437</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="11" t="s">
         <v>2098</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1">
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="11">
         <v>90</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="11">
         <v>1</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="C10" s="11" t="s">
+        <v>989</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="11" t="s">
         <v>2099</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="11" t="s">
         <v>2100</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1">
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="11">
         <v>100</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="11">
         <v>1</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="11" t="s">
         <v>1429</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="11" t="s">
         <v>2101</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="11" t="s">
         <v>2102</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1">
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="11">
         <v>110</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="11">
         <v>1</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="C12" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="11" t="s">
         <v>2103</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="11" t="s">
         <v>2104</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="1">
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="11">
         <v>111</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="11">
         <v>1</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="11" t="s">
         <v>2501</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="11" t="s">
         <v>2086</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="1">
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="11">
         <v>120</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="11">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="11" t="s">
         <v>1660</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="11" t="s">
         <v>2105</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="11" t="s">
         <v>2106</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1">
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="11">
         <v>130</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="11">
         <v>1</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="11" t="s">
         <v>2107</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="11" t="s">
         <v>2108</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="1">
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="11">
         <v>140</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="11">
         <v>1</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="11" t="s">
         <v>2109</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="11" t="s">
         <v>2110</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="1">
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="11">
         <v>150</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="11">
         <v>1</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="11" t="s">
         <v>2111</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="11" t="s">
         <v>2112</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="1">
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="11">
         <v>160</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="11">
         <v>1</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="11" t="s">
         <v>2113</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="11" t="s">
         <v>2114</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="1">
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="11">
         <v>170</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="11">
         <v>1</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="11" t="s">
         <v>2115</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="11" t="s">
         <v>2116</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="1">
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="11">
         <v>180</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="11">
         <v>1</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="11" t="s">
         <v>2115</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="11" t="s">
         <v>2116</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="1">
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="11">
         <v>190</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="11">
         <v>1</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="11" t="s">
         <v>1732</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="11" t="s">
         <v>2117</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="11" t="s">
         <v>2118</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="1">
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="11">
         <v>200</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="11">
         <v>1</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="11" t="s">
         <v>1826</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="11" t="s">
         <v>2119</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="11" t="s">
         <v>2120</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="1">
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="11">
         <v>210</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="11">
         <v>1</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="11" t="s">
         <v>1811</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="11" t="s">
         <v>2121</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="11" t="s">
         <v>2122</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="60">
-      <c r="A24" s="1">
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+    </row>
+    <row r="24" spans="1:8" ht="60">
+      <c r="A24" s="11">
         <v>220</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="11">
         <v>1</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="C24" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="11" t="s">
         <v>2509</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="11" t="s">
         <v>2123</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="45">
-      <c r="A25" s="1">
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" spans="1:8" ht="45">
+      <c r="A25" s="11">
         <v>230</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="11">
         <v>1</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="11" t="s">
         <v>1429</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="11" t="s">
         <v>2124</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="11" t="s">
         <v>2125</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="1">
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="11">
         <v>240</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="11">
         <v>1</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="11" t="s">
         <v>1660</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="11" t="s">
         <v>2126</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="11" t="s">
         <v>2127</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="1">
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="11">
         <v>250</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="11">
         <v>1</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="11" t="s">
         <v>2128</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="11" t="s">
         <v>2129</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="1">
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="11">
         <v>260</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="11">
         <v>1</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="11" t="s">
         <v>2130</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="11" t="s">
         <v>2131</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="1">
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="11">
         <v>270</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="11">
         <v>1</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="11" t="s">
         <v>2130</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="11" t="s">
         <v>2131</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="1">
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="11">
         <v>280</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="11">
         <v>1</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="11" t="s">
         <v>1429</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="11" t="s">
         <v>2102</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="1">
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="11">
         <v>290</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="11">
         <v>1</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="D31" s="1" t="s">
+      <c r="C31" s="11" t="s">
+        <v>989</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="11" t="s">
         <v>2100</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="1">
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="11">
         <v>300</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="11">
         <v>1</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="C32" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="11" t="s">
         <v>2104</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="1">
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="11">
         <v>310</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="11">
         <v>1</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="11" t="s">
         <v>1660</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="11" t="s">
         <v>2106</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="1">
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="11">
         <v>320</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="11">
         <v>1</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="11" t="s">
         <v>1398</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="11" t="s">
         <v>2125</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="1">
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="11">
         <v>330</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="11">
         <v>1</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="11" t="s">
         <v>2108</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="1">
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="11">
         <v>340</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="11">
         <v>1</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="11" t="s">
         <v>2123</v>
       </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="1">
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="11">
         <v>350</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="11">
         <v>1</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="11" t="s">
         <v>2110</v>
       </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="1">
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="11">
         <v>360</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="11">
         <v>1</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="11" t="s">
         <v>2114</v>
       </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="1">
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="11">
         <v>370</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="11">
         <v>1</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="11" t="s">
         <v>2112</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="1">
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="11">
         <v>380</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="11">
         <v>1</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="11" t="s">
         <v>2116</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="1">
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="11">
         <v>390</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="11">
         <v>1</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="11" t="s">
         <v>2116</v>
       </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="1">
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="11">
         <v>400</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="11">
         <v>1</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="11" t="s">
         <v>1732</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="11" t="s">
         <v>2118</v>
       </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="1">
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="11">
         <v>410</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="11">
         <v>1</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="11" t="s">
         <v>1826</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="11" t="s">
         <v>2120</v>
       </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="1">
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="11">
         <v>420</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="11">
         <v>1</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="11" t="s">
         <v>1811</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="11" t="s">
         <v>2551</v>
       </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="1">
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="11">
         <v>430</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="11">
         <v>1</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="13" t="s">
         <v>1902</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="11" t="s">
         <v>2180</v>
       </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="1">
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="11">
         <v>440</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="11">
         <v>1</v>
       </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1" t="s">
+      <c r="C46" s="11"/>
+      <c r="D46" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="11" t="s">
         <v>2434</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="11" t="s">
         <v>2127</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="60">
-      <c r="A47" s="1">
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+    </row>
+    <row r="47" spans="1:8" ht="60">
+      <c r="A47" s="11">
         <v>450</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="11">
         <v>1</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1" t="s">
+      <c r="C47" s="11"/>
+      <c r="D47" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="11" t="s">
         <v>2441</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="11" t="s">
         <v>2123</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="45">
-      <c r="A48" s="1">
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+    </row>
+    <row r="48" spans="1:8" ht="45">
+      <c r="A48" s="11">
         <v>460</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="11">
         <v>1</v>
       </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1" t="s">
+      <c r="C48" s="11"/>
+      <c r="D48" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="11" t="s">
         <v>2440</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="11" t="s">
         <v>2125</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="1">
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="11">
         <v>470</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="11">
         <v>1</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="C49" s="12"/>
+      <c r="D49" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="12" t="s">
         <v>2435</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="11" t="s">
         <v>2123</v>
       </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="1">
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="11">
         <v>480</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="11">
         <v>1</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="C50" s="12"/>
+      <c r="D50" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="11" t="s">
         <v>2442</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="11" t="s">
         <v>2125</v>
       </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="1">
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="11">
         <v>490</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="11">
         <v>1</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="C51" s="12"/>
+      <c r="D51" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="12" t="s">
         <v>2438</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="11" t="s">
         <v>2123</v>
       </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="1">
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="11">
         <v>500</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="11">
         <v>1</v>
       </c>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1" t="s">
+      <c r="C52" s="11"/>
+      <c r="D52" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="11" t="s">
         <v>2436</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="11" t="s">
         <v>2129</v>
       </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="1">
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="11">
         <v>510</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="11">
         <v>1</v>
       </c>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1" t="s">
+      <c r="C53" s="11"/>
+      <c r="D53" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="12" t="s">
         <v>2443</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="11" t="s">
         <v>2131</v>
       </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="1">
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="11">
         <v>520</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="11">
         <v>1</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="11" t="s">
         <v>2501</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="11" t="s">
         <v>2086</v>
       </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="1">
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="11">
         <v>530</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="11">
         <v>1</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="11" t="s">
         <v>2501</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="11" t="s">
         <v>2086</v>
       </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="1">
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="11">
         <v>540</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="11">
         <v>1</v>
       </c>
-      <c r="D56" t="s">
+      <c r="C56" s="12"/>
+      <c r="D56" s="12" t="s">
         <v>2439</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="11" t="s">
         <v>2086</v>
       </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="1">
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="11">
         <v>550</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="11">
         <v>1</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="C57" s="12"/>
+      <c r="D57" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="12" t="s">
         <v>2439</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="11" t="s">
         <v>2086</v>
       </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="4">
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="11">
         <v>560</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="11">
         <v>1</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="C58" s="12"/>
+      <c r="D58" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="12" t="s">
         <v>2185</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="12" t="s">
         <v>2185</v>
       </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="4">
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="11">
         <v>570</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59" s="12">
         <v>1</v>
       </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4" t="s">
+      <c r="C59" s="11"/>
+      <c r="D59" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="11" t="s">
         <v>2444</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="F59" s="11" t="s">
         <v>2154</v>
       </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="4">
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="11">
         <v>580</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B60" s="12">
         <v>1</v>
       </c>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5" t="s">
+      <c r="C60" s="12"/>
+      <c r="D60" s="12" t="s">
         <v>2445</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E60" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="F60" s="12" t="s">
         <v>2125</v>
       </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="4">
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="11">
         <v>590</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B61" s="12">
         <v>1</v>
       </c>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5" t="s">
+      <c r="C61" s="12"/>
+      <c r="D61" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" s="12" t="s">
         <v>2446</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="F61" s="12" t="s">
         <v>2125</v>
       </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="4">
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="11">
         <v>600</v>
       </c>
-      <c r="B62" s="5">
+      <c r="B62" s="12">
         <v>1</v>
       </c>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5" t="s">
+      <c r="C62" s="12"/>
+      <c r="D62" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="E62" s="12" t="s">
         <v>2447</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" s="12" t="s">
         <v>2123</v>
       </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="4">
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="11">
         <v>610</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B63" s="12">
         <v>1</v>
       </c>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5" t="s">
+      <c r="C63" s="12"/>
+      <c r="D63" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E63" s="12" t="s">
         <v>2448</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="F63" s="12" t="s">
         <v>2449</v>
       </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="4">
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="11">
         <v>620</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B64" s="12">
         <v>1</v>
       </c>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5" t="s">
+      <c r="C64" s="12"/>
+      <c r="D64" s="12" t="s">
         <v>2450</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="F64" s="12" t="s">
         <v>2127</v>
       </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="4">
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="11">
         <v>630</v>
       </c>
-      <c r="B65" s="5">
+      <c r="B65" s="12">
         <v>1</v>
       </c>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5" t="s">
+      <c r="C65" s="12"/>
+      <c r="D65" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E65" s="12" t="s">
         <v>2451</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="F65" s="12" t="s">
         <v>2127</v>
       </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" s="4">
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="11">
         <v>640</v>
       </c>
-      <c r="B66" s="5">
+      <c r="B66" s="12">
         <v>1</v>
       </c>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5" t="s">
+      <c r="C66" s="12"/>
+      <c r="D66" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E66" s="12" t="s">
         <v>2452</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="F66" s="12" t="s">
         <v>2122</v>
       </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="4">
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="11">
         <v>650</v>
       </c>
-      <c r="B67" s="5">
+      <c r="B67" s="12">
         <v>1</v>
       </c>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5" t="s">
+      <c r="C67" s="12"/>
+      <c r="D67" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="E67" s="12" t="s">
         <v>2453</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="F67" s="12" t="s">
         <v>2089</v>
       </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" s="4">
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="11">
         <v>660</v>
       </c>
-      <c r="B68" s="5">
+      <c r="B68" s="12">
         <v>1</v>
       </c>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5" t="s">
+      <c r="C68" s="12"/>
+      <c r="D68" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="E68" s="12" t="s">
         <v>2454</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="F68" s="12" t="s">
         <v>2129</v>
       </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" s="4">
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="11">
         <v>670</v>
       </c>
-      <c r="B69" s="5">
+      <c r="B69" s="12">
         <v>1</v>
       </c>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5" t="s">
+      <c r="C69" s="12"/>
+      <c r="D69" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E69" s="12" t="s">
         <v>2455</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="F69" s="12" t="s">
         <v>2098</v>
       </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" s="4">
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="11">
         <v>680</v>
       </c>
-      <c r="B70" s="5">
+      <c r="B70" s="12">
         <v>1</v>
       </c>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5" t="s">
+      <c r="C70" s="12"/>
+      <c r="D70" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="E70" s="12" t="s">
         <v>2456</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="F70" s="12" t="s">
         <v>2097</v>
       </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" s="4">
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="11">
         <v>690</v>
       </c>
-      <c r="B71" s="5">
+      <c r="B71" s="12">
         <v>1</v>
       </c>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5" t="s">
+      <c r="C71" s="12"/>
+      <c r="D71" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E71" s="12" t="s">
         <v>2457</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="F71" s="12" t="s">
         <v>2185</v>
       </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" s="4">
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="11">
         <v>700</v>
       </c>
-      <c r="B72" s="5">
+      <c r="B72" s="12">
         <v>1</v>
       </c>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5" t="s">
+      <c r="C72" s="12"/>
+      <c r="D72" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="E72" s="12" t="s">
         <v>2458</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="F72" s="12" t="s">
         <v>2088</v>
       </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" s="4">
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="11">
         <v>710</v>
       </c>
-      <c r="B73" s="5">
+      <c r="B73" s="12">
         <v>1</v>
       </c>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5" t="s">
+      <c r="C73" s="12"/>
+      <c r="D73" s="12" t="s">
         <v>2459</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="E73" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="F73" s="12" t="s">
         <v>2086</v>
       </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" s="4">
+      <c r="G73" s="12"/>
+      <c r="H73" s="12"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="11">
         <v>720</v>
       </c>
-      <c r="B74" s="5">
+      <c r="B74" s="12">
         <v>1</v>
       </c>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5" t="s">
+      <c r="C74" s="12"/>
+      <c r="D74" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" s="12" t="s">
         <v>2460</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="12" t="s">
         <v>2086</v>
       </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="C75" s="5"/>
-      <c r="D75" s="5" t="s">
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="11">
+        <v>730</v>
+      </c>
+      <c r="B75" s="12">
+        <v>1</v>
+      </c>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12" t="s">
         <v>2058</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="E75" s="12" t="s">
         <v>2461</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="12" t="s">
         <v>2089</v>
       </c>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="12"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="12"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="12"/>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="12"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12"/>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="12"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
+      <c r="H79" s="12"/>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="12"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+      <c r="H80" s="12"/>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="12"/>
+      <c r="B81" s="12"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+      <c r="H81" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F44">

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -22,21 +22,21 @@
     <sheet name="comment_synonyms" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">action!$A$1:$F$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">action!$A$1:$F$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">branch!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">comment_synonyms!$A$1:$D$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">comment_synonyms!$A$1:$D$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">defect_category!$A$1:$D$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">factory!$A$1:$B$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">panel_usage!$A$1:$B$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">part_list!$A$1:$B$1834</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">symptom!$A$1:$F$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">symptom!$A$1:$F$91</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5000" uniqueCount="2552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5058" uniqueCount="2562">
   <si>
     <t>part_used</t>
   </si>
@@ -6149,9 +6149,6 @@
     <t>No power / total off.</t>
   </si>
   <si>
-    <t>logo|booting|boot loop|google|freeze|restart</t>
-  </si>
-  <si>
     <t>LOGO_FREEZE</t>
   </si>
   <si>
@@ -6308,9 +6305,6 @@
     <t>USER</t>
   </si>
   <si>
-    <t>bawa|zy|z1|ditarik|tarik|kirim|ws|carry|to ws|diantar</t>
-  </si>
-  <si>
     <t>ZY</t>
   </si>
   <si>
@@ -6614,9 +6608,6 @@
     <t>scope</t>
   </si>
   <si>
-    <t>STANDY BY|STANBY|STAND BY|STANBAY|STBY</t>
-  </si>
-  <si>
     <t>Typos/variants normalized before symptom matching.</t>
   </si>
   <si>
@@ -6896,9 +6887,6 @@
     <t>Service mode typo cleanup.</t>
   </si>
   <si>
-    <t>SREVICE</t>
-  </si>
-  <si>
     <t>SERVICE</t>
   </si>
   <si>
@@ -7268,15 +7256,9 @@
     <t>Sample blank-part contamination/display case.</t>
   </si>
   <si>
-    <t>main unit rusak|unit rusak</t>
-  </si>
-  <si>
     <t>Sample blank-part main/unit rusak case.</t>
   </si>
   <si>
-    <t>lama keluar gambarnya|lama keluar gambar</t>
-  </si>
-  <si>
     <t>Sample slow picture appears case.</t>
   </si>
   <si>
@@ -7298,9 +7280,6 @@
     <t>MATOT|MATOL|MATOLA|ATI TOTAL|MT|TIDAK BISA HIDUP</t>
   </si>
   <si>
-    <t>siaran|tidak ada siaran|tidak dapat siaran|no sinyal|tidak ada sinyal|tidak dapat remote|channel|sinyal</t>
-  </si>
-  <si>
     <t>SPOT</t>
   </si>
   <si>
@@ -7313,9 +7292,6 @@
     <t>REMOTE_NG</t>
   </si>
   <si>
-    <t>pecah|retak|broken|rusak panel|glass|PANEL RUSAK</t>
-  </si>
-  <si>
     <t>BEMASALAH</t>
   </si>
   <si>
@@ -7337,9 +7313,6 @@
     <t>INTERNET_NG</t>
   </si>
   <si>
-    <t>error|app|aplikasi|google voice|wifi|tidak bisa tambah aplikasi|tidak konek|stop logo|logo|youtube</t>
-  </si>
-  <si>
     <t>perbaikan remote|repair remote|resolder ulang sensor|remote</t>
   </si>
   <si>
@@ -7403,9 +7376,6 @@
     <t>LUDS|LVDS|REPOSISI SOKET</t>
   </si>
   <si>
-    <t>RESET|SET ULANG|PENGATURAN PABRIK|CARI SIARAN|INSTAL ULANG|INSTALL ULANG|RESTART UNIT|RESTART|NO CHANGEL|CONNECTING ULANG|WIFI|INTERNET</t>
-  </si>
-  <si>
     <t>FACTOYY|FACTORY</t>
   </si>
   <si>
@@ -7544,18 +7514,9 @@
     <t>ext|external|cairan|cleaning|semut|kotor|bersih|bersihkan|kardus rusak|EKSTERNAL|FAKTOR LUAR</t>
   </si>
   <si>
-    <t>LED KEDIP2|BERKEDIP|Kedip merah|REDUP SEBELAH</t>
-  </si>
-  <si>
     <t>TIDAK BISA WIFI</t>
   </si>
   <si>
-    <t>colokan antena putus|antena putus|TIDAK BISA DIGITAL</t>
-  </si>
-  <si>
-    <t>TIDAK BISA INTERNET|KERUSAKAN INTERNET</t>
-  </si>
-  <si>
     <t>gambar berganti sendiri|gambar blur|gambar klise|layar merah|gambar tidak baik|warna|GAMBAR TIDAK NORMAL|KEDIP|TAMPILAN DELAY|berkedip|GAMBAR BERBAYANG</t>
   </si>
   <si>
@@ -7616,9 +7577,6 @@
     <t>]IDAK|TDK|TIDKA</t>
   </si>
   <si>
-    <t>L99|LAYAR KUNING|LAYAR ERROR</t>
-  </si>
-  <si>
     <t>tidak ada siaran|tidak ada channel|no channel|channel|sinyal|signal|siaran|STANDBY|TIDAK MENYALA|TIDAK BISA DINYALAKAN|GAMBAR HILANG</t>
   </si>
   <si>
@@ -7637,9 +7595,6 @@
     <t>WIFI_NG</t>
   </si>
   <si>
-    <t>error|eror|netflix|software|aplikasi|app|youtube|SAFE MODE|Loading|TULISAN MODE</t>
-  </si>
-  <si>
     <t>HIDUP</t>
   </si>
   <si>
@@ -7670,15 +7625,9 @@
     <t>WIFI|INTERNET</t>
   </si>
   <si>
-    <t>MATO|13TI</t>
-  </si>
-  <si>
     <t>A99|NO POWER|TIDAK hidup|MAIN BOARD RUSAK</t>
   </si>
   <si>
-    <t>tidak ada gambar|no picture|no display|layar blank|blank|Layar gelap|TIDAK BISA TV|GAMBAR GELAP|gambar hitam|GAMBAR TIDAK KELUAR|LAYAR TIDAK MUNCUL</t>
-  </si>
-  <si>
     <t>mati total|matot|mati|tidak bisa hidup|tidak bisa nyala|tidak nyala|TIDAK HIDUP</t>
   </si>
   <si>
@@ -7692,6 +7641,87 @@
   </si>
   <si>
     <t>REPLACE_SWITCH</t>
+  </si>
+  <si>
+    <t>taransfer</t>
+  </si>
+  <si>
+    <t>TRANSFER</t>
+  </si>
+  <si>
+    <t>RESET|SET ULANG|PENGATURAN PABRIK|CARI SIARAN|INSTAL ULANG|INSTALL ULANG|RESTART UNIT|RESTART|NO CHANGEL|CONNECTING ULANG|WIFI|INTERNET|Searching ulang</t>
+  </si>
+  <si>
+    <t>SERICE</t>
+  </si>
+  <si>
+    <t>SREVICE|SERICE</t>
+  </si>
+  <si>
+    <t>bawa|zy|z1|ditarik|tarik|kirim|ws|carry|to ws|diantar|TRANSFER</t>
+  </si>
+  <si>
+    <t>SUBTITUSI|SUBS</t>
+  </si>
+  <si>
+    <t>SUBSTIUSI</t>
+  </si>
+  <si>
+    <t>MATO|13TI|WATI</t>
+  </si>
+  <si>
+    <t>TIDAK SIMPAN SIARAN</t>
+  </si>
+  <si>
+    <t>TIDAK BISA MATI</t>
+  </si>
+  <si>
+    <t>LOGO</t>
+  </si>
+  <si>
+    <t>error|eror|netflix|software|aplikasi|app|youtube|SAFE MODE|Loading|TULISAN MODE|LOADING</t>
+  </si>
+  <si>
+    <t>colokan antena putus|antena putus|TIDAK BISA DIGITAL|PENERIMAAN</t>
+  </si>
+  <si>
+    <t>lama keluar gambarnya|lama keluar gambar|GAMBAR TIDAK BAGUS|LAYAR HIJAU</t>
+  </si>
+  <si>
+    <t>pecah|retak|broken|rusak panel|glass|PANEL RUSAK|TIDAK DINGIN</t>
+  </si>
+  <si>
+    <t>error|app|aplikasi|google voice|wifi|tidak bisa tambah aplikasi|tidak konek|stop logo|logo|youtube|TIDAK BISA PROGRAM|SETELAN TIDAK TERSIMPAN|NYALA LAMA|TIDAK DAPAT MASUK KE MENU</t>
+  </si>
+  <si>
+    <t>siaran|tidak ada siaran|tidak dapat siaran|no sinyal|tidak ada sinyal|tidak dapat remote|channel|sinyal|TV DIGITAL</t>
+  </si>
+  <si>
+    <t>main unit rusak|unit rusak|SUSAH DI NYALAKAN|TIDAK MAU HIDUP|TIDAK HIDUP|TIDAK BISA ON</t>
+  </si>
+  <si>
+    <t>INTERNET</t>
+  </si>
+  <si>
+    <t>tidak ada gambar|no picture|no display|layar blank|blank|Layar gelap|TIDAK BISA TV|GAMBAR GELAP|gambar hitam|GAMBAR TIDAK KELUAR|LAYAR TIDAK MUNCUL|POLOS</t>
+  </si>
+  <si>
+    <t>logo|booting|boot loop|google|freeze|restart|ANDROID</t>
+  </si>
+  <si>
+    <t>STANDY BY|STANBY|STAND BY|STANBAY|STBY|STABY(B)|STADNBY</t>
+  </si>
+  <si>
+    <t>indikator|protect|proteksi|KEDIP</t>
+  </si>
+  <si>
+    <t>L99|LAYAR KUNING|LAYAR ERROR|GERAKAN LAMBAT|Z99|LAYAR TIDAK BAGUS</t>
+  </si>
+  <si>
+    <t>LED KEDIP2|BERKEDIP|Kedip merah|REDUP SEBELAH|MERAH</t>
+  </si>
+  <si>
+    <t>BERGARIS|Tampilan tidak normal|KUNING</t>
   </si>
 </sst>
 </file>
@@ -7826,7 +7856,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7838,11 +7868,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -7854,7 +7882,17 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22825,24 +22863,24 @@
       </c>
     </row>
     <row r="1835" spans="1:2">
-      <c r="A1835" s="9" t="s">
-        <v>2548</v>
+      <c r="A1835" s="7" t="s">
+        <v>2531</v>
       </c>
       <c r="B1835" s="1" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="1836" spans="1:2">
-      <c r="A1836" s="9" t="s">
-        <v>2549</v>
-      </c>
-      <c r="B1836" s="10" t="s">
+      <c r="A1836" s="7" t="s">
+        <v>2532</v>
+      </c>
+      <c r="B1836" s="8" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="1837" spans="1:2">
-      <c r="A1837" s="9" t="s">
-        <v>2550</v>
+      <c r="A1837" s="7" t="s">
+        <v>2533</v>
       </c>
       <c r="B1837" s="1" t="s">
         <v>1826</v>
@@ -23433,255 +23471,255 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>2462</v>
+        <v>2452</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>2463</v>
+        <v>2453</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>2464</v>
+        <v>2454</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>2465</v>
+        <v>2455</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>2466</v>
+        <v>2456</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>2467</v>
+        <v>2457</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>2499</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>2468</v>
+        <v>2458</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>2499</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>2469</v>
+        <v>2459</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>2471</v>
+        <v>2461</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>2472</v>
+        <v>2462</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>2473</v>
+        <v>2463</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>2474</v>
+        <v>2464</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>2475</v>
+        <v>2465</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>2476</v>
+        <v>2466</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>2477</v>
+        <v>2467</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>2478</v>
+        <v>2468</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>2479</v>
+        <v>2469</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>2481</v>
+        <v>2471</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>2482</v>
+        <v>2472</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>2483</v>
+        <v>2473</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>2484</v>
+        <v>2474</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>2485</v>
+        <v>2475</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>2486</v>
+        <v>2476</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>2487</v>
+        <v>2477</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>2488</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>2498</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>2489</v>
+        <v>2479</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>2490</v>
+        <v>2480</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>2491</v>
+        <v>2481</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>2499</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>2492</v>
+        <v>2482</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>2493</v>
+        <v>2483</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>1943</v>
@@ -23689,7 +23727,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>2494</v>
+        <v>2484</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>1943</v>
@@ -23697,47 +23735,47 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>2495</v>
+        <v>2485</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>2496</v>
+        <v>2486</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>2497</v>
+        <v>2487</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="4" t="s">
-        <v>2511</v>
+        <v>2498</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="4" t="s">
-        <v>2512</v>
+        <v>2499</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>2498</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>2513</v>
+        <v>2500</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>1943</v>
@@ -23745,7 +23783,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>2514</v>
+        <v>2501</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>1943</v>
@@ -23753,7 +23791,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>2515</v>
+        <v>2502</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>1943</v>
@@ -23761,7 +23799,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>2516</v>
+        <v>2503</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>1943</v>
@@ -23774,7 +23812,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -23807,416 +23845,400 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>989</v>
+        <v>750</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2057</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>2348</v>
+      <c r="D2" t="s">
+        <v>2415</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>2022</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>2349</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3">
-        <v>20</v>
+        <v>390</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>345</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2348</v>
+        <v>2064</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>2022</v>
+        <v>2034</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>2349</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3">
-        <v>30</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>214</v>
+        <v>650</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2348</v>
+        <v>2192</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>2022</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>2349</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3">
-        <v>40</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>1816</v>
+        <v>640</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2348</v>
+        <v>2359</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>2022</v>
+        <v>2034</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>2349</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3">
-        <v>50</v>
+        <v>401</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>989</v>
+        <v>109</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2508</v>
+        <v>2545</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>2023</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>2351</v>
-      </c>
+        <v>2042</v>
+      </c>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3">
-        <v>60</v>
+        <v>402</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>214</v>
+        <v>109</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2350</v>
+        <v>2546</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>2023</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>2351</v>
-      </c>
+        <v>2037</v>
+      </c>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3">
-        <v>70</v>
+        <v>400</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>345</v>
+        <v>109</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2350</v>
+        <v>2544</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>2024</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>2351</v>
-      </c>
+        <v>2041</v>
+      </c>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3">
-        <v>80</v>
+        <v>403</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1816</v>
+        <v>109</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2350</v>
+        <v>2490</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>2024</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>2351</v>
-      </c>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3">
-        <v>90</v>
+        <v>360</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>989</v>
+        <v>128</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2527</v>
+        <v>2364</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>2023</v>
+        <v>2047</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>2352</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3">
-        <v>100</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>989</v>
+        <v>660</v>
+      </c>
+      <c r="B11" t="s">
+        <v>128</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2524</v>
+        <v>2359</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>2025</v>
+        <v>2034</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>2353</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>989</v>
+        <v>214</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2526</v>
+        <v>2346</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>2353</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>989</v>
+        <v>214</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2507</v>
+        <v>2344</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>2354</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3">
-        <v>120</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>989</v>
+        <v>770</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2027</v>
+        <v>2560</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>2028</v>
+        <v>2055</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>2355</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3">
-        <v>130</v>
+        <v>31</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>989</v>
+        <v>214</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2520</v>
+        <v>2558</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>2029</v>
+        <v>2045</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>2356</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3">
-        <v>140</v>
+        <v>340</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>989</v>
+        <v>214</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2030</v>
+        <v>2357</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>2031</v>
+        <v>2035</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>2357</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3">
-        <v>150</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>989</v>
+        <v>670</v>
+      </c>
+      <c r="B17" t="s">
+        <v>214</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2425</v>
+        <v>2359</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3">
-        <v>160</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>989</v>
+        <v>780</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>322</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>2547</v>
+      <c r="D18" t="s">
+        <v>2420</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>2034</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>2358</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3">
-        <v>170</v>
+        <v>330</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>989</v>
+        <v>345</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2359</v>
+        <v>2030</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>2023</v>
+        <v>2031</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>2360</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>459</v>
+        <v>345</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2361</v>
+        <v>2344</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>2035</v>
+        <v>2022</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>2362</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>459</v>
+        <v>345</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2537</v>
+        <v>2346</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>2034</v>
+        <v>2024</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>2036</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3">
-        <v>191</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>459</v>
+        <v>680</v>
+      </c>
+      <c r="B22" t="s">
+        <v>345</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>2545</v>
+      <c r="D22" s="3" t="s">
+        <v>2359</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>2034</v>
@@ -24227,7 +24249,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>459</v>
@@ -24236,18 +24258,16 @@
         <v>2021</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2037</v>
+        <v>2520</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>2038</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>2364</v>
-      </c>
+        <v>2521</v>
+      </c>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>459</v>
@@ -24256,18 +24276,18 @@
         <v>2021</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>2039</v>
+        <v>2052</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>2040</v>
+        <v>2053</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>2041</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>459</v>
@@ -24276,18 +24296,16 @@
         <v>2021</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2365</v>
+        <v>2516</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>2042</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>2366</v>
-      </c>
+        <v>2509</v>
+      </c>
+      <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="3">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>459</v>
@@ -24296,16 +24314,18 @@
         <v>2021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2543</v>
+        <v>2547</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>2532</v>
-      </c>
-      <c r="F26" s="3"/>
+        <v>2042</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>2043</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>459</v>
@@ -24314,16 +24334,18 @@
         <v>2021</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>2535</v>
+        <v>2038</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>2536</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>2039</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>2040</v>
+      </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3">
-        <v>230</v>
+        <v>810</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>459</v>
@@ -24331,19 +24353,17 @@
       <c r="C28" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>2546</v>
+      <c r="D28" t="s">
+        <v>2492</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>2024</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>2367</v>
-      </c>
+        <v>2424</v>
+      </c>
+      <c r="F28" s="3"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>459</v>
@@ -24352,16 +24372,18 @@
         <v>2021</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>2530</v>
+        <v>2556</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>2522</v>
-      </c>
-      <c r="F29" s="3"/>
+        <v>2037</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>2360</v>
+      </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="3">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>459</v>
@@ -24370,18 +24392,18 @@
         <v>2021</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>2533</v>
+        <v>2361</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>2044</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="3">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>459</v>
@@ -24390,18 +24412,18 @@
         <v>2021</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>2045</v>
+        <v>2555</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>2046</v>
+        <v>2024</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>2047</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="3">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>459</v>
@@ -24410,18 +24432,18 @@
         <v>2021</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2368</v>
+        <v>2493</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>2048</v>
+        <v>2055</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>2049</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="3">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>459</v>
@@ -24430,18 +24452,16 @@
         <v>2021</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>2050</v>
+        <v>2561</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>2051</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>2052</v>
-      </c>
+        <v>2055</v>
+      </c>
+      <c r="F33" s="3"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="3">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>459</v>
@@ -24450,18 +24470,18 @@
         <v>2021</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>2053</v>
+        <v>2044</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>2054</v>
+        <v>2045</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>2055</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>459</v>
@@ -24470,18 +24490,18 @@
         <v>2021</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>2506</v>
+        <v>2364</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>2056</v>
+        <v>2047</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>2057</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>459</v>
@@ -24490,600 +24510,631 @@
         <v>2021</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>2519</v>
+        <v>2049</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>2056</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>2050</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>2051</v>
+      </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="3">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1429</v>
+        <v>459</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>2058</v>
+        <v>2357</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>2369</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="3">
-        <v>310</v>
+        <v>190</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>1660</v>
+        <v>459</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>2370</v>
+        <v>2522</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>2059</v>
+        <v>2034</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>2060</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="3">
-        <v>320</v>
+        <v>191</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1732</v>
+        <v>459</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>2058</v>
+      <c r="D39" s="6" t="s">
+        <v>2529</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>2051</v>
+        <v>2034</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>2371</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="3">
-        <v>330</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>345</v>
+        <v>790</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>459</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>2030</v>
+        <v>2422</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>2031</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>2061</v>
-      </c>
+        <v>2423</v>
+      </c>
+      <c r="F40" s="3"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="3">
-        <v>340</v>
+        <v>221</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>214</v>
+        <v>459</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>2361</v>
+        <v>2528</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>2035</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>2372</v>
-      </c>
+        <v>2518</v>
+      </c>
+      <c r="F41" s="3"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="3">
-        <v>350</v>
+        <v>50</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>1826</v>
+        <v>989</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>2373</v>
+        <v>2495</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>2056</v>
+        <v>2023</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>2374</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="3">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>128</v>
+        <v>989</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>2368</v>
+        <v>2513</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>2048</v>
+        <v>2023</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>2062</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="3">
-        <v>370</v>
+        <v>170</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>1889</v>
+        <v>989</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>2375</v>
+        <v>2355</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>2042</v>
+        <v>2023</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>2376</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="3">
-        <v>380</v>
+        <v>140</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1811</v>
+        <v>989</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>2063</v>
+        <v>2030</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>2054</v>
+        <v>2031</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>2064</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>3</v>
+        <v>989</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2065</v>
+        <v>2494</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>2034</v>
+        <v>2026</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>2066</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3">
-        <v>400</v>
-      </c>
-      <c r="B47" s="3"/>
+        <v>150</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>989</v>
+      </c>
       <c r="C47" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>2377</v>
+        <v>2550</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>2022</v>
+        <v>2032</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>2378</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3">
-        <v>410</v>
-      </c>
-      <c r="B48" s="3"/>
+        <v>740</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>989</v>
+      </c>
       <c r="C48" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>2500</v>
+        <v>2508</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>2024</v>
+        <v>2509</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>2379</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="3">
-        <v>420</v>
-      </c>
-      <c r="B49" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>989</v>
+      </c>
       <c r="C49" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>2420</v>
+        <v>2511</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>2042</v>
+        <v>2025</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>2380</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="3">
-        <v>430</v>
-      </c>
-      <c r="B50" s="3"/>
+        <v>101</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>989</v>
+      </c>
       <c r="C50" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>2381</v>
+        <v>2559</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>2031</v>
+        <v>2025</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>2382</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="3">
-        <v>440</v>
-      </c>
-      <c r="B51" s="3"/>
+        <v>120</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>989</v>
+      </c>
       <c r="C51" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>2383</v>
+        <v>2027</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>2059</v>
+        <v>2028</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>2384</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="3">
-        <v>450</v>
-      </c>
-      <c r="B52" s="3"/>
+        <v>130</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>989</v>
+      </c>
       <c r="C52" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>2385</v>
+        <v>2507</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>2051</v>
+        <v>2029</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>2386</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="3">
-        <v>460</v>
-      </c>
-      <c r="B53" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>989</v>
+      </c>
       <c r="C53" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>2433</v>
+        <v>2344</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>2043</v>
+        <v>2022</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>2387</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="3">
-        <v>470</v>
-      </c>
-      <c r="B54" s="3"/>
+        <v>730</v>
+      </c>
+      <c r="B54" t="s">
+        <v>989</v>
+      </c>
       <c r="C54" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>2388</v>
+      <c r="D54" t="s">
+        <v>2510</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>2035</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>2389</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="3">
-        <v>480</v>
-      </c>
-      <c r="B55" s="3"/>
+        <v>160</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>989</v>
+      </c>
       <c r="C55" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>2390</v>
+        <v>2530</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>2025</v>
+        <v>2034</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>2391</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="3">
-        <v>490</v>
-      </c>
-      <c r="B56" s="3"/>
+        <v>690</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1398</v>
+      </c>
       <c r="C56" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>2392</v>
+        <v>2057</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>2028</v>
+        <v>2034</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>2393</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="3">
-        <v>500</v>
-      </c>
-      <c r="B57" s="3"/>
+        <v>300</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>1429</v>
+      </c>
       <c r="C57" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>2394</v>
+        <v>2057</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>2395</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="3">
-        <v>510</v>
-      </c>
-      <c r="B58" s="3"/>
+        <v>310</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>1660</v>
+      </c>
       <c r="C58" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>2396</v>
+        <v>2366</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>2054</v>
+        <v>2058</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>2397</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="3">
-        <v>520</v>
-      </c>
-      <c r="B59" s="3"/>
+        <v>700</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1660</v>
+      </c>
       <c r="C59" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>2398</v>
+        <v>2057</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>2034</v>
+        <v>2417</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>2399</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="3">
-        <v>530</v>
+        <v>320</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>1816</v>
+        <v>1732</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>2400</v>
+        <v>2057</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>2025</v>
+        <v>2050</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>2401</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="3">
-        <v>540</v>
+        <v>380</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>1816</v>
+        <v>1811</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>2402</v>
+        <v>2062</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>2026</v>
+        <v>2053</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>2403</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="3">
-        <v>550</v>
+        <v>630</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>1816</v>
+        <v>1811</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>2404</v>
+        <v>2411</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>2032</v>
+        <v>2041</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>2405</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="3">
-        <v>560</v>
-      </c>
-      <c r="B63" s="3"/>
+        <v>550</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C63" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>2406</v>
+        <v>2398</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>2407</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="3">
-        <v>570</v>
-      </c>
-      <c r="B64" s="3"/>
+        <v>560</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C64" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>2408</v>
+        <v>2400</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>2025</v>
+        <v>2032</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>2409</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="3">
-        <v>580</v>
-      </c>
-      <c r="B65" s="3"/>
+        <v>540</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C65" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>2410</v>
+        <v>2396</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>2034</v>
+        <v>2025</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>2411</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="3">
-        <v>590</v>
-      </c>
-      <c r="B66" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C66" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>2412</v>
+        <v>2344</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>2056</v>
+        <v>2022</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>2413</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="3">
-        <v>600</v>
-      </c>
-      <c r="B67" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C67" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>2504</v>
+        <v>2346</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>2042</v>
+        <v>2024</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>2414</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="3">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>1816</v>
@@ -25092,351 +25143,536 @@
         <v>2021</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>2415</v>
+        <v>2409</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>2416</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="3">
-        <v>620</v>
+        <v>350</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1811</v>
+        <v>1826</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>2417</v>
+        <v>2369</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>2042</v>
+        <v>2055</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>2418</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="3">
-        <v>630</v>
-      </c>
-      <c r="B70" t="s">
-        <v>90</v>
+        <v>351</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>1826</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>2363</v>
+        <v>2517</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>2036</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="3">
-        <v>640</v>
-      </c>
-      <c r="B71" t="s">
-        <v>128</v>
+        <v>370</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>1889</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>2363</v>
+        <v>2371</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>2034</v>
+        <v>2041</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>2036</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="3">
-        <v>650</v>
-      </c>
-      <c r="B72" t="s">
-        <v>214</v>
+        <v>222</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>1902</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>2363</v>
+        <v>2528</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>2034</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>2036</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="3">
-        <v>660</v>
-      </c>
-      <c r="B73" t="s">
-        <v>345</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="B73" s="3"/>
       <c r="C73" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>2363</v>
+        <v>2377</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>2034</v>
+        <v>2031</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>2036</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="3">
-        <v>670</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1398</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="B74" s="3"/>
       <c r="C74" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2058</v>
+        <v>2520</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>2034</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>2036</v>
-      </c>
+        <v>2521</v>
+      </c>
+      <c r="F74" s="3"/>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="3">
-        <v>680</v>
-      </c>
-      <c r="B75" t="s">
-        <v>1660</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="B75" s="3"/>
       <c r="C75" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>2058</v>
+        <v>2390</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>2424</v>
+        <v>2032</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>2036</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="3">
-        <v>690</v>
-      </c>
-      <c r="B76" s="5"/>
+        <v>520</v>
+      </c>
+      <c r="B76" s="3"/>
       <c r="C76" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>2363</v>
+        <v>2392</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>2034</v>
+        <v>2053</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>2036</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="3">
-        <v>700</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="B77" s="3"/>
       <c r="C77" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>2039</v>
+        <v>2386</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>2040</v>
-      </c>
-      <c r="F77" s="3"/>
+        <v>2025</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>2387</v>
+      </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="3">
-        <v>710</v>
-      </c>
-      <c r="B78" t="s">
-        <v>989</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="B78" s="3"/>
       <c r="C78" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D78" t="s">
-        <v>2523</v>
+      <c r="D78" s="3" t="s">
+        <v>2404</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>2421</v>
+        <v>2025</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>2405</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="3">
-        <v>711</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>989</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="B79" s="3"/>
       <c r="C79" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>2521</v>
+        <v>2388</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>2522</v>
+        <v>2028</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>2360</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="3">
-        <v>720</v>
-      </c>
-      <c r="B80" t="s">
-        <v>2058</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="B80" s="3"/>
       <c r="C80" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D80" t="s">
-        <v>2422</v>
+      <c r="D80" s="3" t="s">
+        <v>2551</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>2089</v>
+        <v>2042</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>2383</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="3">
-        <v>730</v>
+        <v>471</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>2423</v>
+        <v>2547</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>2056</v>
+        <v>2042</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>2383</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="3">
-        <v>740</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>214</v>
+        <v>720</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>2502</v>
+        <v>2038</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>2056</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>2372</v>
-      </c>
+        <v>2039</v>
+      </c>
+      <c r="F82" s="3"/>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="3">
-        <v>750</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>322</v>
+        <v>800</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D83" t="s">
-        <v>2428</v>
+        <v>2554</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>2048</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="3">
-        <v>760</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>459</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="B84" s="3"/>
       <c r="C84" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>2430</v>
+        <v>2373</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>2431</v>
-      </c>
-      <c r="F84" s="3"/>
+        <v>2022</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>2374</v>
+      </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="3">
-        <v>770</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="B85" s="3"/>
       <c r="C85" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D85" t="s">
-        <v>2505</v>
+      <c r="D85" s="3" t="s">
+        <v>2552</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>2432</v>
+        <v>2041</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>2376</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="3">
-        <v>780</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>459</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="B86" s="3"/>
       <c r="C86" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D86" t="s">
-        <v>2503</v>
+      <c r="D86" s="3" t="s">
+        <v>2548</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>2432</v>
-      </c>
-      <c r="F86" s="3"/>
+        <v>2041</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="3">
+        <v>420</v>
+      </c>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>2490</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>2024</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="3">
+        <v>570</v>
+      </c>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>2402</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>2024</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="3">
+        <v>600</v>
+      </c>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>2549</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>2055</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="3">
+        <v>760</v>
+      </c>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>2416</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="3">
+        <v>450</v>
+      </c>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>2058</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="3">
+        <v>460</v>
+      </c>
+      <c r="B92" s="17"/>
+      <c r="C92" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>2381</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>2050</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="3">
+        <v>480</v>
+      </c>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>2384</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>2035</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="3">
+        <v>530</v>
+      </c>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>2394</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="3">
+        <v>590</v>
+      </c>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>2553</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="3">
+        <v>710</v>
+      </c>
+      <c r="B96" s="16"/>
+      <c r="C96" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>2359</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="3">
+        <v>791</v>
+      </c>
+      <c r="B97" s="5"/>
+      <c r="C97" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>2422</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>2423</v>
+      </c>
+      <c r="F97" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F47">
-    <sortState ref="A2:F81">
-      <sortCondition ref="A1:A42"/>
+  <autoFilter ref="A1:F91">
+    <sortState ref="A2:F97">
+      <sortCondition ref="B1:B91"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -25451,40 +25687,40 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2067</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2068</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2069</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2070</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2071</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2072</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>2073</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2074</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
     </row>
   </sheetData>
@@ -25504,34 +25740,34 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2076</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2077</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2078</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2079</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
   </sheetData>
@@ -25542,12 +25778,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.7109375" customWidth="1"/>
     <col min="5" max="5" width="100" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
@@ -25557,1639 +25793,1679 @@
         <v>2016</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2083</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>2084</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="9">
+        <v>20</v>
+      </c>
+      <c r="B2" s="9">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="9">
+        <v>700</v>
+      </c>
+      <c r="B3" s="10">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>2448</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="9">
+        <v>50</v>
+      </c>
+      <c r="B4" s="9">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>2090</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>2091</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>2491</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>2085</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1">
-        <v>10</v>
-      </c>
-      <c r="B2" s="1">
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>2086</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="11">
-        <v>20</v>
-      </c>
-      <c r="B3" s="11">
+      <c r="C6" s="11" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>2491</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="9">
+        <v>111</v>
+      </c>
+      <c r="B7" s="9">
         <v>1</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>2087</v>
-      </c>
-      <c r="F3" s="11" t="s">
+      <c r="C7" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>2491</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="9">
+        <v>520</v>
+      </c>
+      <c r="B8" s="9">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>2491</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="9">
+        <v>530</v>
+      </c>
+      <c r="B9" s="9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>2491</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="9">
+        <v>540</v>
+      </c>
+      <c r="B10" s="9">
+        <v>1</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="9">
+        <v>550</v>
+      </c>
+      <c r="B11" s="9">
+        <v>1</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>2430</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="9">
+        <v>710</v>
+      </c>
+      <c r="B12" s="10">
+        <v>1</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10" t="s">
+        <v>2449</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="9">
+        <v>720</v>
+      </c>
+      <c r="B13" s="10">
+        <v>1</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>2450</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>2085</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="9">
+        <v>70</v>
+      </c>
+      <c r="B14" s="9">
+        <v>1</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>2094</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>2095</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="9">
+        <v>680</v>
+      </c>
+      <c r="B15" s="10">
+        <v>1</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>2446</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>2095</v>
+      </c>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="9">
+        <v>260</v>
+      </c>
+      <c r="B16" s="9">
+        <v>1</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>2128</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>2129</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="9">
+        <v>270</v>
+      </c>
+      <c r="B17" s="9">
+        <v>1</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>2128</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>2129</v>
+      </c>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="9">
+        <v>510</v>
+      </c>
+      <c r="B18" s="9">
+        <v>1</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>2434</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>2129</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="9">
+        <v>250</v>
+      </c>
+      <c r="B19" s="9">
+        <v>1</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>2126</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>2127</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="9">
+        <v>500</v>
+      </c>
+      <c r="B20" s="9">
+        <v>1</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>2427</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>2127</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="9">
+        <v>660</v>
+      </c>
+      <c r="B21" s="10">
+        <v>1</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>2445</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>2127</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="9">
+        <v>570</v>
+      </c>
+      <c r="B22" s="10">
+        <v>1</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>2435</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>2152</v>
+      </c>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+    </row>
+    <row r="23" spans="1:8" ht="60">
+      <c r="A23" s="9">
+        <v>220</v>
+      </c>
+      <c r="B23" s="9">
+        <v>1</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>2496</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>2121</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="9">
+        <v>340</v>
+      </c>
+      <c r="B24" s="9">
+        <v>1</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>2121</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+    </row>
+    <row r="25" spans="1:8" ht="60">
+      <c r="A25" s="9">
+        <v>450</v>
+      </c>
+      <c r="B25" s="9">
+        <v>1</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>2432</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>2121</v>
+      </c>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="9">
+        <v>470</v>
+      </c>
+      <c r="B26" s="9">
+        <v>1</v>
+      </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>2426</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>2121</v>
+      </c>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="9">
+        <v>490</v>
+      </c>
+      <c r="B27" s="9">
+        <v>1</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>2429</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>2121</v>
+      </c>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="9">
+        <v>600</v>
+      </c>
+      <c r="B28" s="10">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>2438</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>2121</v>
+      </c>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+    </row>
+    <row r="29" spans="1:8" ht="45">
+      <c r="A29" s="9">
+        <v>230</v>
+      </c>
+      <c r="B29" s="9">
+        <v>1</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>2123</v>
+      </c>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="9">
+        <v>320</v>
+      </c>
+      <c r="B30" s="9">
+        <v>1</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>2123</v>
+      </c>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+    </row>
+    <row r="31" spans="1:8" ht="45">
+      <c r="A31" s="9">
+        <v>460</v>
+      </c>
+      <c r="B31" s="9">
+        <v>1</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>2431</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>2123</v>
+      </c>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="9">
+        <v>480</v>
+      </c>
+      <c r="B32" s="9">
+        <v>1</v>
+      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>2433</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>2123</v>
+      </c>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="9">
+        <v>580</v>
+      </c>
+      <c r="B33" s="10">
+        <v>1</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10" t="s">
+        <v>2436</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>2123</v>
+      </c>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="9">
+        <v>590</v>
+      </c>
+      <c r="B34" s="10">
+        <v>1</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>2123</v>
+      </c>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="9">
+        <v>240</v>
+      </c>
+      <c r="B35" s="9">
+        <v>1</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>2124</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>2125</v>
+      </c>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="9">
+        <v>440</v>
+      </c>
+      <c r="B36" s="9">
+        <v>1</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>2425</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>2125</v>
+      </c>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="9">
+        <v>620</v>
+      </c>
+      <c r="B37" s="10">
+        <v>1</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10" t="s">
+        <v>2441</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>2125</v>
+      </c>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="9">
+        <v>630</v>
+      </c>
+      <c r="B38" s="10">
+        <v>1</v>
+      </c>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>2442</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>2125</v>
+      </c>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="9">
+        <v>610</v>
+      </c>
+      <c r="B39" s="10">
+        <v>1</v>
+      </c>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>2439</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>2440</v>
+      </c>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="9">
+        <v>210</v>
+      </c>
+      <c r="B40" s="9">
+        <v>1</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>2119</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>2120</v>
+      </c>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="9">
+        <v>640</v>
+      </c>
+      <c r="B41" s="10">
+        <v>1</v>
+      </c>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>2443</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>2120</v>
+      </c>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="9">
+        <v>160</v>
+      </c>
+      <c r="B42" s="9">
+        <v>1</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>2111</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>2112</v>
+      </c>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="9">
+        <v>360</v>
+      </c>
+      <c r="B43" s="9">
+        <v>1</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>2112</v>
+      </c>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="9">
+        <v>150</v>
+      </c>
+      <c r="B44" s="9">
+        <v>1</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>2109</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>2110</v>
+      </c>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="9">
+        <v>370</v>
+      </c>
+      <c r="B45" s="9">
+        <v>1</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>2110</v>
+      </c>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="9">
+        <v>170</v>
+      </c>
+      <c r="B46" s="9">
+        <v>1</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>2113</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>2114</v>
+      </c>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="9">
+        <v>180</v>
+      </c>
+      <c r="B47" s="9">
+        <v>1</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>2113</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>2114</v>
+      </c>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="9">
+        <v>380</v>
+      </c>
+      <c r="B48" s="9">
+        <v>1</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>2114</v>
+      </c>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="9">
+        <v>390</v>
+      </c>
+      <c r="B49" s="9">
+        <v>1</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>2114</v>
+      </c>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="9">
+        <v>130</v>
+      </c>
+      <c r="B50" s="9">
+        <v>1</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>2105</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>2106</v>
+      </c>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="9">
+        <v>330</v>
+      </c>
+      <c r="B51" s="9">
+        <v>1</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>2106</v>
+      </c>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="9">
+        <v>140</v>
+      </c>
+      <c r="B52" s="9">
+        <v>1</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>2107</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>2108</v>
+      </c>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="9">
+        <v>350</v>
+      </c>
+      <c r="B53" s="9">
+        <v>1</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>2108</v>
+      </c>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="9">
+        <v>110</v>
+      </c>
+      <c r="B54" s="9">
+        <v>1</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>2101</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>2102</v>
+      </c>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="9">
+        <v>300</v>
+      </c>
+      <c r="B55" s="9">
+        <v>1</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>2102</v>
+      </c>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="9">
+        <v>90</v>
+      </c>
+      <c r="B56" s="9">
+        <v>1</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>989</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>2097</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>2098</v>
+      </c>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="9">
+        <v>91</v>
+      </c>
+      <c r="B57" s="9">
+        <v>1</v>
+      </c>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>2097</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>2098</v>
+      </c>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="9">
+        <v>290</v>
+      </c>
+      <c r="B58" s="9">
+        <v>1</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>989</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>2098</v>
+      </c>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="9">
+        <v>100</v>
+      </c>
+      <c r="B59" s="9">
+        <v>1</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>2099</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="9">
+        <v>280</v>
+      </c>
+      <c r="B60" s="9">
+        <v>1</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>2100</v>
+      </c>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="9">
+        <v>120</v>
+      </c>
+      <c r="B61" s="9">
+        <v>1</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>2103</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>2104</v>
+      </c>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="9">
+        <v>310</v>
+      </c>
+      <c r="B62" s="9">
+        <v>1</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>2104</v>
+      </c>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="9">
+        <v>190</v>
+      </c>
+      <c r="B63" s="9">
+        <v>1</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>2115</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>2116</v>
+      </c>
+      <c r="G63" s="10"/>
+      <c r="H63" s="10"/>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="9">
+        <v>400</v>
+      </c>
+      <c r="B64" s="9">
+        <v>1</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>2116</v>
+      </c>
+      <c r="G64" s="10"/>
+      <c r="H64" s="10"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="9">
+        <v>420</v>
+      </c>
+      <c r="B65" s="9">
+        <v>1</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>2534</v>
+      </c>
+      <c r="G65" s="10"/>
+      <c r="H65" s="10"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="9">
+        <v>200</v>
+      </c>
+      <c r="B66" s="9">
+        <v>1</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>2117</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>2118</v>
+      </c>
+      <c r="G66" s="10"/>
+      <c r="H66" s="10"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="9">
+        <v>410</v>
+      </c>
+      <c r="B67" s="9">
+        <v>1</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>2118</v>
+      </c>
+      <c r="G67" s="10"/>
+      <c r="H67" s="10"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="9">
+        <v>430</v>
+      </c>
+      <c r="B68" s="9">
+        <v>1</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>2178</v>
+      </c>
+      <c r="G68" s="10"/>
+      <c r="H68" s="10"/>
+    </row>
+    <row r="69" spans="1:8" ht="45">
+      <c r="A69" s="9">
+        <v>80</v>
+      </c>
+      <c r="B69" s="9">
+        <v>1</v>
+      </c>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>2428</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>2096</v>
+      </c>
+      <c r="G69" s="10"/>
+      <c r="H69" s="10"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="9">
+        <v>670</v>
+      </c>
+      <c r="B70" s="10">
+        <v>1</v>
+      </c>
+      <c r="C70" s="10"/>
+      <c r="D70" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>2537</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>2096</v>
+      </c>
+      <c r="G70" s="10"/>
+      <c r="H70" s="10"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="9">
+        <v>560</v>
+      </c>
+      <c r="B71" s="9">
+        <v>1</v>
+      </c>
+      <c r="C71" s="10"/>
+      <c r="D71" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>2541</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G71" s="10"/>
+      <c r="H71" s="10"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="9">
+        <v>690</v>
+      </c>
+      <c r="B72" s="10">
+        <v>1</v>
+      </c>
+      <c r="C72" s="10"/>
+      <c r="D72" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G72" s="10"/>
+      <c r="H72" s="10"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="9">
+        <v>60</v>
+      </c>
+      <c r="B73" s="9">
+        <v>1</v>
+      </c>
+      <c r="C73" s="8"/>
+      <c r="D73" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>2092</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>2093</v>
+      </c>
+      <c r="G73" s="10"/>
+      <c r="H73" s="10"/>
+    </row>
+    <row r="74" spans="1:8" ht="30">
+      <c r="A74" s="9">
+        <v>30</v>
+      </c>
+      <c r="B74" s="9">
+        <v>1</v>
+      </c>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>2497</v>
+      </c>
+      <c r="F74" s="9" t="s">
         <v>2088</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-    </row>
-    <row r="4" spans="1:8" ht="30">
-      <c r="A4" s="11">
-        <v>30</v>
-      </c>
-      <c r="B4" s="11">
+      <c r="G74" s="10"/>
+      <c r="H74" s="10"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="9">
+        <v>650</v>
+      </c>
+      <c r="B75" s="10">
         <v>1</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>2510</v>
-      </c>
-      <c r="F4" s="11" t="s">
+      <c r="C75" s="10"/>
+      <c r="D75" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>2444</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>2088</v>
+      </c>
+      <c r="G75" s="10"/>
+      <c r="H75" s="10"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="9">
+        <v>730</v>
+      </c>
+      <c r="B76" s="10">
+        <v>1</v>
+      </c>
+      <c r="C76" s="10"/>
+      <c r="D76" s="10" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>2451</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>2088</v>
+      </c>
+      <c r="G76" s="10"/>
+      <c r="H76" s="10"/>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="9">
+        <v>40</v>
+      </c>
+      <c r="B77" s="9">
+        <v>1</v>
+      </c>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>2540</v>
+      </c>
+      <c r="F77" s="9" t="s">
         <v>2089</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="11">
-        <v>40</v>
-      </c>
-      <c r="B5" s="11">
-        <v>1</v>
-      </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>2090</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>2091</v>
-      </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="11">
-        <v>50</v>
-      </c>
-      <c r="B6" s="11">
-        <v>1</v>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>2092</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>2093</v>
-      </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="11">
-        <v>60</v>
-      </c>
-      <c r="B7" s="11">
-        <v>1</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>2094</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>2095</v>
-      </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="11">
-        <v>70</v>
-      </c>
-      <c r="B8" s="11">
-        <v>1</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>2096</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>2097</v>
-      </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-    </row>
-    <row r="9" spans="1:8" ht="45">
-      <c r="A9" s="11">
-        <v>80</v>
-      </c>
-      <c r="B9" s="11">
-        <v>1</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>2437</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>2098</v>
-      </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="11">
-        <v>90</v>
-      </c>
-      <c r="B10" s="11">
-        <v>1</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>989</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>2099</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>2100</v>
-      </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="11">
-        <v>100</v>
-      </c>
-      <c r="B11" s="11">
-        <v>1</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>1429</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>2101</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>2102</v>
-      </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="11">
-        <v>110</v>
-      </c>
-      <c r="B12" s="11">
-        <v>1</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>2103</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>2104</v>
-      </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="11">
-        <v>111</v>
-      </c>
-      <c r="B13" s="11">
-        <v>1</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="11">
-        <v>120</v>
-      </c>
-      <c r="B14" s="11">
-        <v>1</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>1660</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>2105</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>2106</v>
-      </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="11">
-        <v>130</v>
-      </c>
-      <c r="B15" s="11">
-        <v>1</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>2107</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>2108</v>
-      </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="11">
-        <v>140</v>
-      </c>
-      <c r="B16" s="11">
-        <v>1</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>2109</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>2110</v>
-      </c>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="11">
-        <v>150</v>
-      </c>
-      <c r="B17" s="11">
-        <v>1</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>2111</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>2112</v>
-      </c>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="11">
-        <v>160</v>
-      </c>
-      <c r="B18" s="11">
-        <v>1</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>2113</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>2114</v>
-      </c>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="11">
-        <v>170</v>
-      </c>
-      <c r="B19" s="11">
-        <v>1</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>2115</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>2116</v>
-      </c>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="11">
-        <v>180</v>
-      </c>
-      <c r="B20" s="11">
-        <v>1</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>2115</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>2116</v>
-      </c>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="11">
-        <v>190</v>
-      </c>
-      <c r="B21" s="11">
-        <v>1</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>1732</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>2117</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>2118</v>
-      </c>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="11">
-        <v>200</v>
-      </c>
-      <c r="B22" s="11">
-        <v>1</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>1826</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>2119</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>2120</v>
-      </c>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="11">
-        <v>210</v>
-      </c>
-      <c r="B23" s="11">
-        <v>1</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>1811</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>2121</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>2122</v>
-      </c>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-    </row>
-    <row r="24" spans="1:8" ht="60">
-      <c r="A24" s="11">
-        <v>220</v>
-      </c>
-      <c r="B24" s="11">
-        <v>1</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>2509</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>2123</v>
-      </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-    </row>
-    <row r="25" spans="1:8" ht="45">
-      <c r="A25" s="11">
-        <v>230</v>
-      </c>
-      <c r="B25" s="11">
-        <v>1</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>1429</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>2124</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>2125</v>
-      </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="11">
-        <v>240</v>
-      </c>
-      <c r="B26" s="11">
-        <v>1</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>1660</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>2126</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>2127</v>
-      </c>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="11">
-        <v>250</v>
-      </c>
-      <c r="B27" s="11">
-        <v>1</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>2128</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>2129</v>
-      </c>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="11">
-        <v>260</v>
-      </c>
-      <c r="B28" s="11">
-        <v>1</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>2130</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>2131</v>
-      </c>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="11">
-        <v>270</v>
-      </c>
-      <c r="B29" s="11">
-        <v>1</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>2130</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>2131</v>
-      </c>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="11">
-        <v>280</v>
-      </c>
-      <c r="B30" s="11">
-        <v>1</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>1429</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>2102</v>
-      </c>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="11">
-        <v>290</v>
-      </c>
-      <c r="B31" s="11">
-        <v>1</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>989</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>2100</v>
-      </c>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="11">
-        <v>300</v>
-      </c>
-      <c r="B32" s="11">
-        <v>1</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>2104</v>
-      </c>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="11">
-        <v>310</v>
-      </c>
-      <c r="B33" s="11">
-        <v>1</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>1660</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>2106</v>
-      </c>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="11">
-        <v>320</v>
-      </c>
-      <c r="B34" s="11">
-        <v>1</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>1398</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>2125</v>
-      </c>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="11">
-        <v>330</v>
-      </c>
-      <c r="B35" s="11">
-        <v>1</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>2108</v>
-      </c>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="11">
-        <v>340</v>
-      </c>
-      <c r="B36" s="11">
-        <v>1</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>2123</v>
-      </c>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="11">
-        <v>350</v>
-      </c>
-      <c r="B37" s="11">
-        <v>1</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>2110</v>
-      </c>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="11">
-        <v>360</v>
-      </c>
-      <c r="B38" s="11">
-        <v>1</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>2114</v>
-      </c>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="11">
-        <v>370</v>
-      </c>
-      <c r="B39" s="11">
-        <v>1</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>2112</v>
-      </c>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="11">
-        <v>380</v>
-      </c>
-      <c r="B40" s="11">
-        <v>1</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>2116</v>
-      </c>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="11">
-        <v>390</v>
-      </c>
-      <c r="B41" s="11">
-        <v>1</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>2116</v>
-      </c>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="11">
-        <v>400</v>
-      </c>
-      <c r="B42" s="11">
-        <v>1</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>1732</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>2118</v>
-      </c>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="11">
-        <v>410</v>
-      </c>
-      <c r="B43" s="11">
-        <v>1</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>1826</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>2120</v>
-      </c>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="11">
-        <v>420</v>
-      </c>
-      <c r="B44" s="11">
-        <v>1</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>1811</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>2551</v>
-      </c>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="11">
-        <v>430</v>
-      </c>
-      <c r="B45" s="11">
-        <v>1</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>1902</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>2180</v>
-      </c>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="11">
-        <v>440</v>
-      </c>
-      <c r="B46" s="11">
-        <v>1</v>
-      </c>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>2434</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>2127</v>
-      </c>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-    </row>
-    <row r="47" spans="1:8" ht="60">
-      <c r="A47" s="11">
-        <v>450</v>
-      </c>
-      <c r="B47" s="11">
-        <v>1</v>
-      </c>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>2441</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>2123</v>
-      </c>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-    </row>
-    <row r="48" spans="1:8" ht="45">
-      <c r="A48" s="11">
-        <v>460</v>
-      </c>
-      <c r="B48" s="11">
-        <v>1</v>
-      </c>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>2440</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>2125</v>
-      </c>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="11">
-        <v>470</v>
-      </c>
-      <c r="B49" s="11">
-        <v>1</v>
-      </c>
-      <c r="C49" s="12"/>
-      <c r="D49" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>2435</v>
-      </c>
-      <c r="F49" s="11" t="s">
-        <v>2123</v>
-      </c>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="11">
-        <v>480</v>
-      </c>
-      <c r="B50" s="11">
-        <v>1</v>
-      </c>
-      <c r="C50" s="12"/>
-      <c r="D50" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>2442</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>2125</v>
-      </c>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="11">
-        <v>490</v>
-      </c>
-      <c r="B51" s="11">
-        <v>1</v>
-      </c>
-      <c r="C51" s="12"/>
-      <c r="D51" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>2438</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>2123</v>
-      </c>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="11">
-        <v>500</v>
-      </c>
-      <c r="B52" s="11">
-        <v>1</v>
-      </c>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>2436</v>
-      </c>
-      <c r="F52" s="11" t="s">
-        <v>2129</v>
-      </c>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="11">
-        <v>510</v>
-      </c>
-      <c r="B53" s="11">
-        <v>1</v>
-      </c>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>2443</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>2131</v>
-      </c>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="11">
-        <v>520</v>
-      </c>
-      <c r="B54" s="11">
-        <v>1</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="11">
-        <v>530</v>
-      </c>
-      <c r="B55" s="11">
-        <v>1</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="11">
-        <v>540</v>
-      </c>
-      <c r="B56" s="11">
-        <v>1</v>
-      </c>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12" t="s">
-        <v>2439</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F56" s="11" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="11">
-        <v>550</v>
-      </c>
-      <c r="B57" s="11">
-        <v>1</v>
-      </c>
-      <c r="C57" s="12"/>
-      <c r="D57" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>2439</v>
-      </c>
-      <c r="F57" s="11" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="11">
-        <v>560</v>
-      </c>
-      <c r="B58" s="11">
-        <v>1</v>
-      </c>
-      <c r="C58" s="12"/>
-      <c r="D58" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>2185</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>2185</v>
-      </c>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="11">
-        <v>570</v>
-      </c>
-      <c r="B59" s="12">
-        <v>1</v>
-      </c>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E59" s="11" t="s">
-        <v>2444</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>2154</v>
-      </c>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="11">
-        <v>580</v>
-      </c>
-      <c r="B60" s="12">
-        <v>1</v>
-      </c>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12" t="s">
-        <v>2445</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>2125</v>
-      </c>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="11">
-        <v>590</v>
-      </c>
-      <c r="B61" s="12">
-        <v>1</v>
-      </c>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>2446</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>2125</v>
-      </c>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="11">
-        <v>600</v>
-      </c>
-      <c r="B62" s="12">
-        <v>1</v>
-      </c>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>2447</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>2123</v>
-      </c>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="11">
-        <v>610</v>
-      </c>
-      <c r="B63" s="12">
-        <v>1</v>
-      </c>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>2448</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>2449</v>
-      </c>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12"/>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="11">
-        <v>620</v>
-      </c>
-      <c r="B64" s="12">
-        <v>1</v>
-      </c>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12" t="s">
-        <v>2450</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>2127</v>
-      </c>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12"/>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="11">
-        <v>630</v>
-      </c>
-      <c r="B65" s="12">
-        <v>1</v>
-      </c>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>2451</v>
-      </c>
-      <c r="F65" s="12" t="s">
-        <v>2127</v>
-      </c>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12"/>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="11">
-        <v>640</v>
-      </c>
-      <c r="B66" s="12">
-        <v>1</v>
-      </c>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>2452</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>2122</v>
-      </c>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="11">
-        <v>650</v>
-      </c>
-      <c r="B67" s="12">
-        <v>1</v>
-      </c>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>2453</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>2089</v>
-      </c>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12"/>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="11">
-        <v>660</v>
-      </c>
-      <c r="B68" s="12">
-        <v>1</v>
-      </c>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>2454</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>2129</v>
-      </c>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12"/>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="11">
-        <v>670</v>
-      </c>
-      <c r="B69" s="12">
-        <v>1</v>
-      </c>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>2455</v>
-      </c>
-      <c r="F69" s="12" t="s">
-        <v>2098</v>
-      </c>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12"/>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="11">
-        <v>680</v>
-      </c>
-      <c r="B70" s="12">
-        <v>1</v>
-      </c>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E70" s="12" t="s">
-        <v>2456</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>2097</v>
-      </c>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12"/>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="11">
-        <v>690</v>
-      </c>
-      <c r="B71" s="12">
-        <v>1</v>
-      </c>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E71" s="12" t="s">
-        <v>2457</v>
-      </c>
-      <c r="F71" s="12" t="s">
-        <v>2185</v>
-      </c>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12"/>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="11">
-        <v>700</v>
-      </c>
-      <c r="B72" s="12">
-        <v>1</v>
-      </c>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E72" s="12" t="s">
-        <v>2458</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>2088</v>
-      </c>
-      <c r="G72" s="12"/>
-      <c r="H72" s="12"/>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="11">
-        <v>710</v>
-      </c>
-      <c r="B73" s="12">
-        <v>1</v>
-      </c>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12" t="s">
-        <v>2459</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F73" s="12" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G73" s="12"/>
-      <c r="H73" s="12"/>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="11">
-        <v>720</v>
-      </c>
-      <c r="B74" s="12">
-        <v>1</v>
-      </c>
-      <c r="C74" s="12"/>
-      <c r="D74" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>2460</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>2086</v>
-      </c>
-      <c r="G74" s="12"/>
-      <c r="H74" s="12"/>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="11">
-        <v>730</v>
-      </c>
-      <c r="B75" s="12">
-        <v>1</v>
-      </c>
-      <c r="C75" s="12"/>
-      <c r="D75" s="12" t="s">
-        <v>2058</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>2461</v>
-      </c>
-      <c r="F75" s="12" t="s">
-        <v>2089</v>
-      </c>
-      <c r="G75" s="12"/>
-      <c r="H75" s="12"/>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="12"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="12"/>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="12"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="12"/>
-      <c r="D77" s="12"/>
-      <c r="E77" s="12"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="12"/>
+      <c r="G77" s="10"/>
+      <c r="H77" s="10"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="12"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="12"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="12"/>
+      <c r="A78" s="10"/>
+      <c r="B78" s="10"/>
+      <c r="C78" s="10"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="10"/>
+      <c r="F78" s="10"/>
+      <c r="G78" s="10"/>
+      <c r="H78" s="10"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="12"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="12"/>
-      <c r="E79" s="12"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="12"/>
+      <c r="A79" s="10"/>
+      <c r="B79" s="10"/>
+      <c r="C79" s="10"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="10"/>
+      <c r="G79" s="10"/>
+      <c r="H79" s="10"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="12"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="12"/>
-      <c r="E80" s="12"/>
-      <c r="F80" s="12"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="12"/>
+      <c r="A80" s="10"/>
+      <c r="B80" s="10"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="10"/>
+      <c r="G80" s="10"/>
+      <c r="H80" s="10"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="12"/>
-      <c r="B81" s="12"/>
-      <c r="C81" s="12"/>
-      <c r="D81" s="12"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="12"/>
+      <c r="A81" s="10"/>
+      <c r="B81" s="10"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10"/>
+      <c r="G81" s="10"/>
+      <c r="H81" s="10"/>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="10"/>
+      <c r="B82" s="10"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="10"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="10"/>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="10"/>
+      <c r="B83" s="10"/>
+      <c r="C83" s="10"/>
+      <c r="D83" s="10"/>
+      <c r="E83" s="10"/>
+      <c r="F83" s="10"/>
+      <c r="G83" s="10"/>
+      <c r="H83" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F44">
-    <sortState ref="A2:F74">
-      <sortCondition ref="A1:A44"/>
+  <autoFilter ref="A1:F46">
+    <sortState ref="A2:F77">
+      <sortCondition ref="F1:F46"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27209,584 +27485,584 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2132</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2133</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2134</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2135</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>2141</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>2142</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>2143</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>2131</v>
+        <v>2129</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>2123</v>
+        <v>2121</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>459</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>989</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>1429</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>459</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>989</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30">
       <c r="A28" s="1" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>1429</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>964</v>
@@ -27795,10 +28071,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>964</v>
@@ -27813,7 +28089,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="78" customWidth="1"/>
@@ -27822,23 +28098,23 @@
     <col min="4" max="4" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2188</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2189</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2190</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2191</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2020</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>2192</v>
+        <v>2557</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2035</v>
@@ -27847,866 +28123,892 @@
         <v>2019</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="45">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="45">
       <c r="A3" s="1" t="s">
-        <v>2194</v>
+        <v>2191</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2195</v>
+        <v>2192</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2196</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>2419</v>
+        <v>2413</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2198</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2531</v>
+        <v>2517</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>2538</v>
+        <v>2523</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2202</v>
+        <v>2199</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2203</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>2525</v>
+        <v>2512</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2205</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>2206</v>
+        <v>2203</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>2540</v>
+        <v>2525</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2541</v>
+        <v>2526</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2209</v>
+        <v>2206</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>2207</v>
+      </c>
+      <c r="F11" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>2539</v>
+        <v>2524</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2534</v>
+        <v>2519</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>2518</v>
+        <v>2505</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2519</v>
+        <v>2506</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>2211</v>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>2535</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2043</v>
+        <v>2536</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>2212</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>2234</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>2528</v>
+        <v>2208</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2529</v>
+        <v>2042</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2019</v>
       </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="D15" s="1" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>2213</v>
+        <v>2514</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2214</v>
+        <v>2515</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2019</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>2215</v>
-      </c>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>2216</v>
+        <v>2210</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2217</v>
+        <v>2211</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2218</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>2219</v>
+        <v>2213</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2220</v>
+        <v>2214</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2221</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>2222</v>
+        <v>2216</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2223</v>
+        <v>2217</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2224</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>2517</v>
+        <v>2219</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2023</v>
+        <v>2220</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2225</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2226</v>
+        <v>2504</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2227</v>
+        <v>2023</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2228</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>2229</v>
+        <v>2223</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2230</v>
+        <v>2224</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2231</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>2232</v>
+        <v>2226</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2233</v>
+        <v>2227</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2234</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>2235</v>
+        <v>2229</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2236</v>
+        <v>2230</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2237</v>
+        <v>2019</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2238</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>2239</v>
+        <v>2232</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2240</v>
+        <v>2233</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2241</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>2242</v>
+        <v>2236</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2243</v>
+        <v>2237</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2244</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2246</v>
+        <v>2240</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2247</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>2248</v>
+        <v>2242</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2249</v>
+        <v>2243</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2250</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>2251</v>
+        <v>2245</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2252</v>
+        <v>2246</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2253</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>2254</v>
+        <v>2248</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2255</v>
+        <v>2249</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2256</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>2542</v>
+        <v>2251</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2258</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2259</v>
+        <v>2527</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>2260</v>
+        <v>2254</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2261</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>2262</v>
+        <v>2256</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>2142</v>
+        <v>2257</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2263</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>2264</v>
+        <v>2259</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>989</v>
+        <v>2140</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2265</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>2266</v>
+        <v>2261</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2249</v>
+        <v>989</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2267</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>2268</v>
+        <v>2263</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2269</v>
+        <v>2246</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2270</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>2269</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="30">
+      <c r="A39" s="1" t="s">
         <v>2271</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>2272</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>2237</v>
-      </c>
-      <c r="D37" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>2273</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="30">
-      <c r="A38" s="1" t="s">
-        <v>2274</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>2275</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>2237</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>2276</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
-        <v>2277</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>2278</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>2237</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>2279</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>2280</v>
+        <v>2274</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2281</v>
+        <v>2275</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2282</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>2283</v>
+        <v>2277</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>2284</v>
+        <v>2278</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2285</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>2286</v>
+        <v>2280</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>2287</v>
+        <v>2281</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>2288</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2289</v>
+        <v>2539</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2290</v>
+        <v>2283</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>2291</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>2292</v>
+        <v>2285</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1889</v>
+        <v>2286</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>2293</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
-        <v>2294</v>
+        <v>2288</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>2295</v>
+        <v>1889</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>2296</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
-        <v>2297</v>
+        <v>2290</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>2298</v>
+        <v>2291</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>2299</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>2300</v>
+        <v>2293</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>2301</v>
+        <v>2294</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>2302</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
-        <v>2303</v>
+        <v>2296</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>2304</v>
+        <v>2297</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>2305</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>2306</v>
+        <v>2299</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>2098</v>
+        <v>2300</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>2307</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1" t="s">
-        <v>2308</v>
+        <v>2302</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>2309</v>
+        <v>2096</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>2310</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1" t="s">
-        <v>2311</v>
+        <v>2304</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>2312</v>
+        <v>2305</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>2313</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
-        <v>2314</v>
+        <v>2307</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>2315</v>
+        <v>2308</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>2316</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1" t="s">
-        <v>2317</v>
+        <v>2310</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>2318</v>
+        <v>2311</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>2319</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>2320</v>
+        <v>2313</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>2321</v>
+        <v>2314</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>2322</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1" t="s">
-        <v>2323</v>
+        <v>2316</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>2324</v>
+        <v>2317</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>2325</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1" t="s">
-        <v>2326</v>
+        <v>2319</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>2327</v>
+        <v>2320</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>2328</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
-        <v>2329</v>
+        <v>2322</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>2095</v>
+        <v>2323</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>2330</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>2331</v>
+        <v>2325</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>2332</v>
+        <v>2093</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>2333</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1" t="s">
-        <v>2429</v>
+        <v>2327</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>2334</v>
+        <v>2328</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>2335</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>2336</v>
+        <v>2421</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>2337</v>
+        <v>2330</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>2338</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1" t="s">
-        <v>2339</v>
+        <v>2332</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>2340</v>
+        <v>2333</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>2341</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="1" t="s">
-        <v>2342</v>
+        <v>2335</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>2343</v>
+        <v>2336</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>2344</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="1" t="s">
-        <v>2345</v>
+        <v>2338</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>2346</v>
+        <v>2339</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>2347</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" t="s">
-        <v>2426</v>
+      <c r="A64" s="1" t="s">
+        <v>2341</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>2427</v>
+        <v>2342</v>
       </c>
       <c r="C64" s="1" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>2419</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>2019</v>
       </c>
     </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>2234</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D63"/>
+  <autoFilter ref="A1:D64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5058" uniqueCount="2562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5074" uniqueCount="2570">
   <si>
     <t>part_used</t>
   </si>
@@ -7722,6 +7722,30 @@
   </si>
   <si>
     <t>BERGARIS|Tampilan tidak normal|KUNING</t>
+  </si>
+  <si>
+    <t>2TC24CB3IBK</t>
+  </si>
+  <si>
+    <t>2TC40AE1IAM</t>
+  </si>
+  <si>
+    <t>LC24SA4000I</t>
+  </si>
+  <si>
+    <t>LC29LE507I</t>
+  </si>
+  <si>
+    <t>LC32LE295I</t>
+  </si>
+  <si>
+    <t>LC32SA4101IWH</t>
+  </si>
+  <si>
+    <t>LC40LE185IWH</t>
+  </si>
+  <si>
+    <t>LC40SA5100I</t>
   </si>
 </sst>
 </file>
@@ -7856,7 +7880,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7867,7 +7891,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -7893,6 +7916,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22863,7 +22890,7 @@
       </c>
     </row>
     <row r="1835" spans="1:2">
-      <c r="A1835" s="7" t="s">
+      <c r="A1835" s="6" t="s">
         <v>2531</v>
       </c>
       <c r="B1835" s="1" t="s">
@@ -22871,15 +22898,15 @@
       </c>
     </row>
     <row r="1836" spans="1:2">
-      <c r="A1836" s="7" t="s">
+      <c r="A1836" s="6" t="s">
         <v>2532</v>
       </c>
-      <c r="B1836" s="8" t="s">
+      <c r="B1836" s="7" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="1837" spans="1:2">
-      <c r="A1837" s="7" t="s">
+      <c r="A1837" s="6" t="s">
         <v>2533</v>
       </c>
       <c r="B1837" s="1" t="s">
@@ -22894,7 +22921,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -22910,903 +22937,968 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="17" t="s">
         <v>1942</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="17" t="s">
         <v>1944</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="17" t="s">
         <v>1945</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="17" t="s">
         <v>1946</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="17" t="s">
         <v>1947</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="17" t="s">
         <v>1948</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="17" t="s">
         <v>1949</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="17" t="s">
         <v>1950</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="17" t="s">
         <v>1951</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="17" t="s">
         <v>1952</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="17" t="s">
         <v>1953</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="17" t="s">
         <v>1954</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="17" t="s">
         <v>1955</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="17" t="s">
         <v>1956</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="17" t="s">
         <v>1957</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="17" t="s">
         <v>1956</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="17" t="s">
         <v>1958</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="17" t="s">
         <v>1956</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="17" t="s">
         <v>1959</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="17" t="s">
         <v>1956</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="17" t="s">
         <v>1960</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="17" t="s">
         <v>1962</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="17" t="s">
         <v>1963</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="17" t="s">
         <v>1964</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="17" t="s">
         <v>1965</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="17" t="s">
         <v>1966</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="17" t="s">
         <v>1967</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="17" t="s">
         <v>1968</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="17" t="s">
         <v>1969</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="17" t="s">
         <v>1970</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="17" t="s">
         <v>1971</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="17" t="s">
         <v>1972</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="17" t="s">
         <v>1973</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="17" t="s">
         <v>1974</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="17" t="s">
         <v>1975</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="17" t="s">
         <v>1976</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="17" t="s">
         <v>1977</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="17" t="s">
         <v>1978</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="17" t="s">
         <v>1979</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="17" t="s">
         <v>1980</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="17" t="s">
         <v>1981</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="17" t="s">
         <v>1982</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="17" t="s">
         <v>1983</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="17" t="s">
         <v>1984</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="17" t="s">
         <v>1985</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="17" t="s">
         <v>1986</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="17" t="s">
         <v>1987</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="17" t="s">
         <v>1988</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="17" t="s">
         <v>1989</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="17" t="s">
         <v>1990</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="17" t="s">
         <v>1991</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="17" t="s">
         <v>1992</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="17" t="s">
         <v>1993</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="17" t="s">
         <v>1994</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="17" t="s">
         <v>1995</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="17" t="s">
         <v>1996</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="17" t="s">
         <v>1997</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="17" t="s">
         <v>1998</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="17" t="s">
         <v>1999</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="17" t="s">
         <v>2000</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="17" t="s">
         <v>2001</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="17" t="s">
         <v>2002</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="17" t="s">
         <v>2003</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="17" t="s">
         <v>2004</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="17" t="s">
         <v>2005</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="17" t="s">
         <v>2006</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="17" t="s">
         <v>2007</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="17" t="s">
         <v>2008</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="17" t="s">
         <v>2009</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="17" t="s">
         <v>2010</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="17" t="s">
         <v>2011</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="17" t="s">
         <v>2012</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="17" t="s">
         <v>1961</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="17" t="s">
         <v>2013</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="17" t="s">
         <v>2014</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="17" t="s">
         <v>2015</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="17" t="s">
         <v>2014</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" t="s">
+      <c r="A72" s="15" t="s">
         <v>2452</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" t="s">
+      <c r="A73" s="15" t="s">
         <v>2453</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" t="s">
+      <c r="A74" s="15" t="s">
         <v>2454</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" t="s">
+      <c r="A75" s="15" t="s">
         <v>2455</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" t="s">
+      <c r="A76" s="15" t="s">
         <v>2456</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" t="s">
+      <c r="A77" s="15" t="s">
         <v>2457</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="17" t="s">
         <v>2489</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" t="s">
+      <c r="A78" s="15" t="s">
         <v>2458</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="17" t="s">
         <v>2489</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" t="s">
+      <c r="A79" s="15" t="s">
         <v>2459</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" t="s">
+      <c r="A80" s="15" t="s">
         <v>2460</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" t="s">
+      <c r="A81" s="15" t="s">
         <v>2461</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" t="s">
+      <c r="A82" s="15" t="s">
         <v>2462</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" t="s">
+      <c r="A83" s="15" t="s">
         <v>2463</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" t="s">
+      <c r="A84" s="15" t="s">
         <v>2464</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" t="s">
+      <c r="A85" s="15" t="s">
         <v>2465</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" t="s">
+      <c r="A86" s="15" t="s">
         <v>2466</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" t="s">
+      <c r="A87" s="15" t="s">
         <v>2467</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" t="s">
+      <c r="A88" s="15" t="s">
         <v>2468</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" t="s">
+      <c r="A89" s="15" t="s">
         <v>2469</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" t="s">
+      <c r="A90" s="15" t="s">
         <v>2470</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" t="s">
+      <c r="A91" s="15" t="s">
         <v>2471</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" t="s">
+      <c r="A92" s="15" t="s">
         <v>2472</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" t="s">
+      <c r="A93" s="15" t="s">
         <v>2473</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" t="s">
+      <c r="A94" s="15" t="s">
         <v>2474</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" t="s">
+      <c r="A95" s="15" t="s">
         <v>2475</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" t="s">
+      <c r="A96" s="15" t="s">
         <v>2476</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" t="s">
+      <c r="A97" s="15" t="s">
         <v>2477</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" t="s">
+      <c r="A98" s="15" t="s">
         <v>2478</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" t="s">
+      <c r="A99" s="15" t="s">
         <v>2479</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" t="s">
+      <c r="A100" s="15" t="s">
         <v>2480</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" t="s">
+      <c r="A101" s="15" t="s">
         <v>2481</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="17" t="s">
         <v>2489</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" t="s">
+      <c r="A102" s="15" t="s">
         <v>2482</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" t="s">
+      <c r="A103" s="15" t="s">
         <v>2483</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" t="s">
+      <c r="A104" s="15" t="s">
         <v>2484</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B104" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" t="s">
+      <c r="A105" s="15" t="s">
         <v>2485</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B105" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" t="s">
+      <c r="A106" s="15" t="s">
         <v>2486</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B106" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" t="s">
+      <c r="A107" s="15" t="s">
         <v>2487</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B107" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="18" t="s">
         <v>2498</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B108" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="18" t="s">
         <v>2499</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B109" s="17" t="s">
         <v>2488</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" t="s">
+      <c r="A110" s="15" t="s">
         <v>2500</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B110" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" t="s">
+      <c r="A111" s="15" t="s">
         <v>2501</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B111" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" t="s">
+      <c r="A112" s="15" t="s">
         <v>2502</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B112" s="17" t="s">
         <v>1943</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" t="s">
+      <c r="A113" s="15" t="s">
         <v>2503</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B113" s="17" t="s">
         <v>1943</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="12" t="s">
+        <v>2562</v>
+      </c>
+      <c r="B114" s="17" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="12" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B115" s="17" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="12" t="s">
+        <v>2564</v>
+      </c>
+      <c r="B116" s="17" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="12" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B117" s="17" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="12" t="s">
+        <v>2566</v>
+      </c>
+      <c r="B118" s="17" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="12" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B119" s="17" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="12" t="s">
+        <v>2568</v>
+      </c>
+      <c r="B120" s="17" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="12" t="s">
+        <v>2569</v>
+      </c>
+      <c r="B121" s="17" t="s">
+        <v>1961</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -24074,7 +24166,7 @@
       <c r="A14" s="3">
         <v>770</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>214</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -24154,7 +24246,7 @@
       <c r="A18" s="3">
         <v>780</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="14" t="s">
         <v>322</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -24569,7 +24661,7 @@
       <c r="C39" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="5" t="s">
         <v>2529</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -24583,7 +24675,7 @@
       <c r="A40" s="3">
         <v>790</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>459</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -25563,7 +25655,7 @@
       <c r="A92" s="3">
         <v>460</v>
       </c>
-      <c r="B92" s="17"/>
+      <c r="B92" s="16"/>
       <c r="C92" s="3" t="s">
         <v>2021</v>
       </c>
@@ -25635,7 +25727,7 @@
       <c r="A96" s="3">
         <v>710</v>
       </c>
-      <c r="B96" s="16"/>
+      <c r="B96" s="15"/>
       <c r="C96" s="3" t="s">
         <v>2021</v>
       </c>
@@ -25653,7 +25745,7 @@
       <c r="A97" s="3">
         <v>791</v>
       </c>
-      <c r="B97" s="5"/>
+      <c r="B97" s="4"/>
       <c r="C97" s="3" t="s">
         <v>2021</v>
       </c>
@@ -25809,60 +25901,60 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="9">
+      <c r="A2" s="8">
         <v>20</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="8">
         <v>1</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>2086</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>2087</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>700</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <v>1</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="11"/>
+      <c r="D3" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>2448</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>2087</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>50</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>1</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>2090</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>2091</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
@@ -25881,8 +25973,8 @@
       <c r="F5" s="1" t="s">
         <v>2085</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
@@ -25891,7 +25983,7 @@
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>1816</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -25903,1564 +25995,1564 @@
       <c r="F6" s="1" t="s">
         <v>2085</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>111</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <v>1</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="C7" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>2491</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>2085</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>520</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <v>1</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>2491</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>2085</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>530</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <v>1</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>2491</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>2085</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>540</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="8">
         <v>1</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10" t="s">
+      <c r="C10" s="9"/>
+      <c r="D10" s="9" t="s">
         <v>2430</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>2085</v>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>550</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="8">
         <v>1</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="9" t="s">
+      <c r="C11" s="9"/>
+      <c r="D11" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>2430</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="8" t="s">
         <v>2085</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>710</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>1</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10" t="s">
+      <c r="C12" s="9"/>
+      <c r="D12" s="9" t="s">
         <v>2449</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>2085</v>
       </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>720</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>1</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10" t="s">
+      <c r="C13" s="9"/>
+      <c r="D13" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>2450</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>2085</v>
       </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>70</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <v>1</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9" t="s">
+      <c r="C14" s="8"/>
+      <c r="D14" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="8" t="s">
         <v>2094</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="8" t="s">
         <v>2095</v>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>680</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>1</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10" t="s">
+      <c r="C15" s="9"/>
+      <c r="D15" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>2446</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="9" t="s">
         <v>2095</v>
       </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>260</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="8">
         <v>1</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>2128</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>2129</v>
       </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>270</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="8">
         <v>1</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="8" t="s">
         <v>2128</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>2129</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="9">
+      <c r="A18" s="8">
         <v>510</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="8">
         <v>1</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9" t="s">
+      <c r="C18" s="8"/>
+      <c r="D18" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
         <v>2434</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="8" t="s">
         <v>2129</v>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="9">
+      <c r="A19" s="8">
         <v>250</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="8">
         <v>1</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="8" t="s">
         <v>2126</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="8" t="s">
         <v>2127</v>
       </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="9">
+      <c r="A20" s="8">
         <v>500</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="8">
         <v>1</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9" t="s">
+      <c r="C20" s="8"/>
+      <c r="D20" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="8" t="s">
         <v>2427</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="8" t="s">
         <v>2127</v>
       </c>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="9">
+      <c r="A21" s="8">
         <v>660</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>1</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10" t="s">
+      <c r="C21" s="9"/>
+      <c r="D21" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="9" t="s">
         <v>2445</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="9" t="s">
         <v>2127</v>
       </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="9">
+      <c r="A22" s="8">
         <v>570</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>1</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9" t="s">
+      <c r="C22" s="8"/>
+      <c r="D22" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="8" t="s">
         <v>2435</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="8" t="s">
         <v>2152</v>
       </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
     </row>
     <row r="23" spans="1:8" ht="60">
-      <c r="A23" s="9">
+      <c r="A23" s="8">
         <v>220</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="8">
         <v>1</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="D23" s="9" t="s">
+      <c r="C23" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>2496</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="8" t="s">
         <v>2121</v>
       </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="9">
+      <c r="A24" s="8">
         <v>340</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="8">
         <v>1</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="8" t="s">
         <v>2121</v>
       </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
     </row>
     <row r="25" spans="1:8" ht="60">
-      <c r="A25" s="9">
+      <c r="A25" s="8">
         <v>450</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="8">
         <v>1</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9" t="s">
+      <c r="C25" s="8"/>
+      <c r="D25" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="8" t="s">
         <v>2432</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="8" t="s">
         <v>2121</v>
       </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="9">
+      <c r="A26" s="8">
         <v>470</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="8">
         <v>1</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="9" t="s">
+      <c r="C26" s="9"/>
+      <c r="D26" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="9" t="s">
         <v>2426</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="8" t="s">
         <v>2121</v>
       </c>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="9">
+      <c r="A27" s="8">
         <v>490</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="8">
         <v>1</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="9" t="s">
+      <c r="C27" s="9"/>
+      <c r="D27" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="9" t="s">
         <v>2429</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="8" t="s">
         <v>2121</v>
       </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="9">
+      <c r="A28" s="8">
         <v>600</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="9">
         <v>1</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10" t="s">
+      <c r="C28" s="9"/>
+      <c r="D28" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="9" t="s">
         <v>2438</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="9" t="s">
         <v>2121</v>
       </c>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
     </row>
     <row r="29" spans="1:8" ht="45">
-      <c r="A29" s="9">
+      <c r="A29" s="8">
         <v>230</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="8">
         <v>1</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>1429</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="8" t="s">
         <v>2122</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="8" t="s">
         <v>2123</v>
       </c>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="9">
+      <c r="A30" s="8">
         <v>320</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="8">
         <v>1</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="8" t="s">
         <v>1398</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="8" t="s">
         <v>2123</v>
       </c>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
     </row>
     <row r="31" spans="1:8" ht="45">
-      <c r="A31" s="9">
+      <c r="A31" s="8">
         <v>460</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="8">
         <v>1</v>
       </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9" t="s">
+      <c r="C31" s="8"/>
+      <c r="D31" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="8" t="s">
         <v>2431</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="8" t="s">
         <v>2123</v>
       </c>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="9">
+      <c r="A32" s="8">
         <v>480</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="8">
         <v>1</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="9" t="s">
+      <c r="C32" s="9"/>
+      <c r="D32" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="8" t="s">
         <v>2433</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="8" t="s">
         <v>2123</v>
       </c>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="9">
+      <c r="A33" s="8">
         <v>580</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="9">
         <v>1</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10" t="s">
+      <c r="C33" s="9"/>
+      <c r="D33" s="9" t="s">
         <v>2436</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="9" t="s">
         <v>2123</v>
       </c>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="9">
+      <c r="A34" s="8">
         <v>590</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="9">
         <v>1</v>
       </c>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10" t="s">
+      <c r="C34" s="9"/>
+      <c r="D34" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="9" t="s">
         <v>2437</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="9" t="s">
         <v>2123</v>
       </c>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="9">
+      <c r="A35" s="8">
         <v>240</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="8">
         <v>1</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="8" t="s">
         <v>1660</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="8" t="s">
         <v>2124</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="8" t="s">
         <v>2125</v>
       </c>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="9">
+      <c r="A36" s="8">
         <v>440</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="8">
         <v>1</v>
       </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9" t="s">
+      <c r="C36" s="8"/>
+      <c r="D36" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="8" t="s">
         <v>2425</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="8" t="s">
         <v>2125</v>
       </c>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="9">
+      <c r="A37" s="8">
         <v>620</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="9">
         <v>1</v>
       </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10" t="s">
+      <c r="C37" s="9"/>
+      <c r="D37" s="9" t="s">
         <v>2441</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="9" t="s">
         <v>2125</v>
       </c>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="9">
+      <c r="A38" s="8">
         <v>630</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="9">
         <v>1</v>
       </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10" t="s">
+      <c r="C38" s="9"/>
+      <c r="D38" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="9" t="s">
         <v>2442</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="9" t="s">
         <v>2125</v>
       </c>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="9">
+      <c r="A39" s="8">
         <v>610</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="9">
         <v>1</v>
       </c>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10" t="s">
+      <c r="C39" s="9"/>
+      <c r="D39" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="9" t="s">
         <v>2439</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="9" t="s">
         <v>2440</v>
       </c>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="9">
+      <c r="A40" s="8">
         <v>210</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="8">
         <v>1</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="8" t="s">
         <v>1811</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" s="8" t="s">
         <v>2119</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="8" t="s">
         <v>2120</v>
       </c>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="9">
+      <c r="A41" s="8">
         <v>640</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="9">
         <v>1</v>
       </c>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10" t="s">
+      <c r="C41" s="9"/>
+      <c r="D41" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="9" t="s">
         <v>2443</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="9" t="s">
         <v>2120</v>
       </c>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="9">
+      <c r="A42" s="8">
         <v>160</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="8">
         <v>1</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="8" t="s">
         <v>2111</v>
       </c>
-      <c r="F42" s="9" t="s">
+      <c r="F42" s="8" t="s">
         <v>2112</v>
       </c>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="9">
+      <c r="A43" s="8">
         <v>360</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43" s="8">
         <v>1</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F43" s="8" t="s">
         <v>2112</v>
       </c>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="9">
+      <c r="A44" s="8">
         <v>150</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B44" s="8">
         <v>1</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="8" t="s">
         <v>2109</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F44" s="8" t="s">
         <v>2110</v>
       </c>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="9">
+      <c r="A45" s="8">
         <v>370</v>
       </c>
-      <c r="B45" s="9">
+      <c r="B45" s="8">
         <v>1</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="8" t="s">
         <v>2110</v>
       </c>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="9">
+      <c r="A46" s="8">
         <v>170</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="8">
         <v>1</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E46" s="8" t="s">
         <v>2113</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="F46" s="8" t="s">
         <v>2114</v>
       </c>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="9">
+      <c r="A47" s="8">
         <v>180</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="8">
         <v>1</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="E47" s="8" t="s">
         <v>2113</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="8" t="s">
         <v>2114</v>
       </c>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="9">
+      <c r="A48" s="8">
         <v>380</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="8">
         <v>1</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E48" s="9" t="s">
+      <c r="E48" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="F48" s="8" t="s">
         <v>2114</v>
       </c>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="9">
+      <c r="A49" s="8">
         <v>390</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B49" s="8">
         <v>1</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="E49" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="F49" s="8" t="s">
         <v>2114</v>
       </c>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="9">
+      <c r="A50" s="8">
         <v>130</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50" s="8">
         <v>1</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" s="8" t="s">
         <v>2105</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="F50" s="8" t="s">
         <v>2106</v>
       </c>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="9">
+      <c r="A51" s="8">
         <v>330</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="8">
         <v>1</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D51" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E51" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" s="8" t="s">
         <v>2106</v>
       </c>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="9">
+      <c r="A52" s="8">
         <v>140</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52" s="8">
         <v>1</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" s="8" t="s">
         <v>2107</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" s="8" t="s">
         <v>2108</v>
       </c>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="9">
+      <c r="A53" s="8">
         <v>350</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53" s="8">
         <v>1</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F53" s="8" t="s">
         <v>2108</v>
       </c>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="9">
+      <c r="A54" s="8">
         <v>110</v>
       </c>
-      <c r="B54" s="9">
+      <c r="B54" s="8">
         <v>1</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="D54" s="9" t="s">
+      <c r="C54" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E54" s="9" t="s">
+      <c r="E54" s="8" t="s">
         <v>2101</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="F54" s="8" t="s">
         <v>2102</v>
       </c>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="9">
+      <c r="A55" s="8">
         <v>300</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="8">
         <v>1</v>
       </c>
-      <c r="C55" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="D55" s="9" t="s">
+      <c r="C55" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F55" s="8" t="s">
         <v>2102</v>
       </c>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="9">
+      <c r="A56" s="8">
         <v>90</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56" s="8">
         <v>1</v>
       </c>
-      <c r="C56" s="9" t="s">
-        <v>989</v>
-      </c>
-      <c r="D56" s="9" t="s">
+      <c r="C56" s="8" t="s">
+        <v>989</v>
+      </c>
+      <c r="D56" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E56" s="8" t="s">
         <v>2097</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="F56" s="8" t="s">
         <v>2098</v>
       </c>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="9">
+      <c r="A57" s="8">
         <v>91</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57" s="8">
         <v>1</v>
       </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9" t="s">
+      <c r="C57" s="8"/>
+      <c r="D57" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="8" t="s">
         <v>2097</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" s="8" t="s">
         <v>2098</v>
       </c>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="9">
+      <c r="A58" s="8">
         <v>290</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="8">
         <v>1</v>
       </c>
-      <c r="C58" s="9" t="s">
-        <v>989</v>
-      </c>
-      <c r="D58" s="9" t="s">
+      <c r="C58" s="8" t="s">
+        <v>989</v>
+      </c>
+      <c r="D58" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E58" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F58" s="9" t="s">
+      <c r="F58" s="8" t="s">
         <v>2098</v>
       </c>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="9">
+      <c r="A59" s="8">
         <v>100</v>
       </c>
-      <c r="B59" s="9">
+      <c r="B59" s="8">
         <v>1</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="8" t="s">
         <v>1429</v>
       </c>
-      <c r="D59" s="9" t="s">
+      <c r="D59" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="E59" s="8" t="s">
         <v>2099</v>
       </c>
-      <c r="F59" s="9" t="s">
+      <c r="F59" s="8" t="s">
         <v>2100</v>
       </c>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="9">
+      <c r="A60" s="8">
         <v>280</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="8">
         <v>1</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="8" t="s">
         <v>1429</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D60" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="E60" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="F60" s="8" t="s">
         <v>2100</v>
       </c>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="9">
+      <c r="A61" s="8">
         <v>120</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B61" s="8">
         <v>1</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="8" t="s">
         <v>1660</v>
       </c>
-      <c r="D61" s="9" t="s">
+      <c r="D61" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E61" s="9" t="s">
+      <c r="E61" s="8" t="s">
         <v>2103</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F61" s="8" t="s">
         <v>2104</v>
       </c>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="9">
+      <c r="A62" s="8">
         <v>310</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="8">
         <v>1</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="8" t="s">
         <v>1660</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E62" s="9" t="s">
+      <c r="E62" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F62" s="9" t="s">
+      <c r="F62" s="8" t="s">
         <v>2104</v>
       </c>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="9">
+      <c r="A63" s="8">
         <v>190</v>
       </c>
-      <c r="B63" s="9">
+      <c r="B63" s="8">
         <v>1</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C63" s="8" t="s">
         <v>1732</v>
       </c>
-      <c r="D63" s="9" t="s">
+      <c r="D63" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E63" s="9" t="s">
+      <c r="E63" s="8" t="s">
         <v>2115</v>
       </c>
-      <c r="F63" s="9" t="s">
+      <c r="F63" s="8" t="s">
         <v>2116</v>
       </c>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="9">
+      <c r="A64" s="8">
         <v>400</v>
       </c>
-      <c r="B64" s="9">
+      <c r="B64" s="8">
         <v>1</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="C64" s="8" t="s">
         <v>1732</v>
       </c>
-      <c r="D64" s="9" t="s">
+      <c r="D64" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E64" s="9" t="s">
+      <c r="E64" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F64" s="9" t="s">
+      <c r="F64" s="8" t="s">
         <v>2116</v>
       </c>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="9">
+      <c r="A65" s="8">
         <v>420</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65" s="8">
         <v>1</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" s="8" t="s">
         <v>1811</v>
       </c>
-      <c r="D65" s="9" t="s">
+      <c r="D65" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="E65" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F65" s="9" t="s">
+      <c r="F65" s="8" t="s">
         <v>2534</v>
       </c>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="9">
+      <c r="A66" s="8">
         <v>200</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="8">
         <v>1</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="C66" s="8" t="s">
         <v>1826</v>
       </c>
-      <c r="D66" s="9" t="s">
+      <c r="D66" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E66" s="9" t="s">
+      <c r="E66" s="8" t="s">
         <v>2117</v>
       </c>
-      <c r="F66" s="9" t="s">
+      <c r="F66" s="8" t="s">
         <v>2118</v>
       </c>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="9">
+      <c r="A67" s="8">
         <v>410</v>
       </c>
-      <c r="B67" s="9">
+      <c r="B67" s="8">
         <v>1</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C67" s="8" t="s">
         <v>1826</v>
       </c>
-      <c r="D67" s="9" t="s">
+      <c r="D67" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E67" s="9" t="s">
+      <c r="E67" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F67" s="9" t="s">
+      <c r="F67" s="8" t="s">
         <v>2118</v>
       </c>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="9">
+      <c r="A68" s="8">
         <v>430</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="8">
         <v>1</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="12" t="s">
         <v>1902</v>
       </c>
-      <c r="D68" s="9" t="s">
+      <c r="D68" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E68" s="9" t="s">
+      <c r="E68" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F68" s="9" t="s">
+      <c r="F68" s="8" t="s">
         <v>2178</v>
       </c>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
     </row>
     <row r="69" spans="1:8" ht="45">
-      <c r="A69" s="9">
+      <c r="A69" s="8">
         <v>80</v>
       </c>
-      <c r="B69" s="9">
+      <c r="B69" s="8">
         <v>1</v>
       </c>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9" t="s">
+      <c r="C69" s="8"/>
+      <c r="D69" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E69" s="9" t="s">
+      <c r="E69" s="8" t="s">
         <v>2428</v>
       </c>
-      <c r="F69" s="9" t="s">
+      <c r="F69" s="8" t="s">
         <v>2096</v>
       </c>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="9"/>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="9">
+      <c r="A70" s="8">
         <v>670</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B70" s="9">
         <v>1</v>
       </c>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10" t="s">
+      <c r="C70" s="9"/>
+      <c r="D70" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E70" s="10" t="s">
+      <c r="E70" s="9" t="s">
         <v>2537</v>
       </c>
-      <c r="F70" s="10" t="s">
+      <c r="F70" s="9" t="s">
         <v>2096</v>
       </c>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="9">
+      <c r="A71" s="8">
         <v>560</v>
       </c>
-      <c r="B71" s="9">
+      <c r="B71" s="8">
         <v>1</v>
       </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="9" t="s">
+      <c r="C71" s="9"/>
+      <c r="D71" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" s="9" t="s">
         <v>2541</v>
       </c>
-      <c r="F71" s="10" t="s">
+      <c r="F71" s="9" t="s">
         <v>2183</v>
       </c>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="9"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="9">
+      <c r="A72" s="8">
         <v>690</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B72" s="9">
         <v>1</v>
       </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="10" t="s">
+      <c r="C72" s="9"/>
+      <c r="D72" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="E72" s="9" t="s">
         <v>2447</v>
       </c>
-      <c r="F72" s="10" t="s">
+      <c r="F72" s="9" t="s">
         <v>2183</v>
       </c>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="9"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="9">
+      <c r="A73" s="8">
         <v>60</v>
       </c>
-      <c r="B73" s="9">
+      <c r="B73" s="8">
         <v>1</v>
       </c>
-      <c r="C73" s="8"/>
-      <c r="D73" s="9" t="s">
+      <c r="C73" s="7"/>
+      <c r="D73" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E73" s="9" t="s">
+      <c r="E73" s="8" t="s">
         <v>2092</v>
       </c>
-      <c r="F73" s="9" t="s">
+      <c r="F73" s="8" t="s">
         <v>2093</v>
       </c>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="9"/>
     </row>
     <row r="74" spans="1:8" ht="30">
-      <c r="A74" s="9">
+      <c r="A74" s="8">
         <v>30</v>
       </c>
-      <c r="B74" s="9">
+      <c r="B74" s="8">
         <v>1</v>
       </c>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9" t="s">
+      <c r="C74" s="8"/>
+      <c r="D74" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E74" s="9" t="s">
+      <c r="E74" s="8" t="s">
         <v>2497</v>
       </c>
-      <c r="F74" s="9" t="s">
+      <c r="F74" s="8" t="s">
         <v>2088</v>
       </c>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="9">
+      <c r="A75" s="8">
         <v>650</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="9">
         <v>1</v>
       </c>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10" t="s">
+      <c r="C75" s="9"/>
+      <c r="D75" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E75" s="9" t="s">
         <v>2444</v>
       </c>
-      <c r="F75" s="10" t="s">
+      <c r="F75" s="9" t="s">
         <v>2088</v>
       </c>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="9">
+      <c r="A76" s="8">
         <v>730</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="9">
         <v>1</v>
       </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10" t="s">
+      <c r="C76" s="9"/>
+      <c r="D76" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="E76" s="9" t="s">
         <v>2451</v>
       </c>
-      <c r="F76" s="10" t="s">
+      <c r="F76" s="9" t="s">
         <v>2088</v>
       </c>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="9">
+      <c r="A77" s="8">
         <v>40</v>
       </c>
-      <c r="B77" s="9">
+      <c r="B77" s="8">
         <v>1</v>
       </c>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9" t="s">
+      <c r="C77" s="8"/>
+      <c r="D77" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E77" s="9" t="s">
+      <c r="E77" s="8" t="s">
         <v>2540</v>
       </c>
-      <c r="F77" s="9" t="s">
+      <c r="F77" s="8" t="s">
         <v>2089</v>
       </c>
-      <c r="G77" s="10"/>
-      <c r="H77" s="10"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="10"/>
-      <c r="B78" s="10"/>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
+      <c r="A78" s="9"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="10"/>
-      <c r="B79" s="10"/>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="10"/>
-      <c r="H79" s="10"/>
+      <c r="A79" s="9"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="9"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="10"/>
-      <c r="B80" s="10"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="10"/>
+      <c r="A80" s="9"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="9"/>
+      <c r="H80" s="9"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="10"/>
-      <c r="B81" s="10"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="10"/>
-      <c r="H81" s="10"/>
+      <c r="A81" s="9"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
+      <c r="G81" s="9"/>
+      <c r="H81" s="9"/>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="10"/>
-      <c r="B82" s="10"/>
-      <c r="C82" s="10"/>
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="10"/>
-      <c r="H82" s="10"/>
+      <c r="A82" s="9"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="10"/>
-      <c r="B83" s="10"/>
-      <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
-      <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="10"/>
-      <c r="H83" s="10"/>
+      <c r="A83" s="9"/>
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9"/>
+      <c r="F83" s="9"/>
+      <c r="G83" s="9"/>
+      <c r="H83" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F46">

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">branch!$A$1:$B$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">comment_synonyms!$A$1:$D$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">defect_category!$A$1:$D$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">factory!$A$1:$B$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">factory!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">panel_usage!$A$1:$B$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">part_list!$A$1:$B$1834</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">symptom!$A$1:$F$91</definedName>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5074" uniqueCount="2570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5203" uniqueCount="2578">
   <si>
     <t>part_used</t>
   </si>
@@ -7746,6 +7746,30 @@
   </si>
   <si>
     <t>LC40SA5100I</t>
+  </si>
+  <si>
+    <t>series</t>
+  </si>
+  <si>
+    <t>2TC24CB3I</t>
+  </si>
+  <si>
+    <t>2TC32BB1I</t>
+  </si>
+  <si>
+    <t>2TC32BD1I</t>
+  </si>
+  <si>
+    <t>9TAHL6500IP004</t>
+  </si>
+  <si>
+    <t>RUNTKC242WJN1</t>
+  </si>
+  <si>
+    <t>PEVA-A042VDZZ</t>
+  </si>
+  <si>
+    <t>RSNSZA025QBZZ</t>
   </si>
 </sst>
 </file>
@@ -8210,7 +8234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1837"/>
+  <dimension ref="A1:B1841"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -22913,6 +22937,38 @@
         <v>1826</v>
       </c>
     </row>
+    <row r="1838" spans="1:2">
+      <c r="A1838" t="s">
+        <v>2574</v>
+      </c>
+      <c r="B1838" s="7" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:2">
+      <c r="A1839" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B1839" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:2">
+      <c r="A1840" t="s">
+        <v>2576</v>
+      </c>
+      <c r="B1840" s="7" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:2">
+      <c r="A1841" t="s">
+        <v>2577</v>
+      </c>
+      <c r="B1841" s="7" t="s">
+        <v>964</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B1834"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22921,982 +22977,1351 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B121"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>1940</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1941</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="17" t="s">
-        <v>1942</v>
+      <c r="C1" s="2" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="12" t="s">
+        <v>2562</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="17" t="s">
-        <v>1944</v>
+        <v>1960</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="17" t="s">
-        <v>1945</v>
+        <v>1962</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="17" t="s">
-        <v>1946</v>
+        <v>1963</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="17" t="s">
-        <v>1947</v>
+        <v>1964</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="17" t="s">
-        <v>1948</v>
+        <v>1965</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="17" t="s">
-        <v>1949</v>
+        <v>1966</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="17" t="s">
-        <v>1950</v>
+        <v>1967</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="17" t="s">
-        <v>1951</v>
+        <v>1968</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="17" t="s">
-        <v>1952</v>
+        <v>1969</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="17" t="s">
-        <v>1953</v>
+        <v>1970</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="17" t="s">
-        <v>1954</v>
+        <v>1971</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="17" t="s">
-        <v>1955</v>
+        <v>1972</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="17" t="s">
-        <v>1957</v>
+        <v>1973</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="17" t="s">
-        <v>1958</v>
+        <v>1974</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="17" t="s">
-        <v>1959</v>
+        <v>1975</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>1961</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="17" t="s">
-        <v>1960</v>
+        <v>1976</v>
       </c>
       <c r="B18" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="C18" s="17" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="17" t="s">
-        <v>1962</v>
+        <v>1977</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="C19" s="17" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="17" t="s">
-        <v>1963</v>
+        <v>1978</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="C20" s="17" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="17" t="s">
-        <v>1964</v>
+        <v>1979</v>
       </c>
       <c r="B21" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="C21" s="17" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="17" t="s">
-        <v>1965</v>
+        <v>2013</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>2014</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="17" t="s">
-        <v>1966</v>
+        <v>1942</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>1943</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>1967</v>
+        <v>1944</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>1943</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>1968</v>
+        <v>1980</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="17" t="s">
-        <v>1969</v>
+      <c r="C25" s="17" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="12" t="s">
+        <v>2563</v>
       </c>
       <c r="B26" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
+      <c r="C26" s="17" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="B27" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
+      <c r="C27" s="17" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="B28" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
+      <c r="C28" s="17" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>1972</v>
+        <v>1983</v>
       </c>
       <c r="B29" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="30" spans="1:2">
+      <c r="C29" s="17" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="17" t="s">
-        <v>1973</v>
+        <v>1984</v>
       </c>
       <c r="B30" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="31" spans="1:2">
+      <c r="C30" s="17" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="17" t="s">
-        <v>1974</v>
+        <v>1985</v>
       </c>
       <c r="B31" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="32" spans="1:2">
+      <c r="C31" s="17" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="17" t="s">
-        <v>1975</v>
+        <v>1986</v>
       </c>
       <c r="B32" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="33" spans="1:2">
+      <c r="C32" s="17" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="17" t="s">
-        <v>1976</v>
+        <v>1987</v>
       </c>
       <c r="B33" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="34" spans="1:2">
+      <c r="C33" s="17" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="17" t="s">
-        <v>1977</v>
+        <v>1988</v>
       </c>
       <c r="B34" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="35" spans="1:2">
+      <c r="C34" s="17" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="17" t="s">
-        <v>1978</v>
+        <v>1989</v>
       </c>
       <c r="B35" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="36" spans="1:2">
+      <c r="C35" s="17" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="17" t="s">
-        <v>1979</v>
+        <v>1990</v>
       </c>
       <c r="B36" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="37" spans="1:2">
+      <c r="C36" s="17" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="17" t="s">
-        <v>1980</v>
+        <v>2015</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>2014</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="17" t="s">
-        <v>1981</v>
+        <v>1991</v>
       </c>
       <c r="B38" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="17" t="s">
-        <v>1982</v>
+      <c r="C38" s="17" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="15" t="s">
+        <v>2452</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="17" t="s">
-        <v>1983</v>
+        <v>2488</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="15" t="s">
+        <v>2453</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>2488</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" s="17" t="s">
-        <v>1984</v>
+        <v>1992</v>
       </c>
       <c r="B41" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="42" spans="1:2">
+      <c r="C41" s="17" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" s="17" t="s">
-        <v>1985</v>
+        <v>1993</v>
       </c>
       <c r="B42" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="43" spans="1:2">
+      <c r="C42" s="17" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" s="17" t="s">
-        <v>1986</v>
+        <v>1994</v>
       </c>
       <c r="B43" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="44" spans="1:2">
+      <c r="C43" s="17" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" s="17" t="s">
-        <v>1987</v>
+        <v>1995</v>
       </c>
       <c r="B44" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="45" spans="1:2">
+      <c r="C44" s="17" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" s="17" t="s">
-        <v>1988</v>
+        <v>1996</v>
       </c>
       <c r="B45" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="46" spans="1:2">
+      <c r="C45" s="17" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" s="17" t="s">
-        <v>1989</v>
+        <v>1997</v>
       </c>
       <c r="B46" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="47" spans="1:2">
+      <c r="C46" s="17" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" s="17" t="s">
-        <v>1990</v>
+        <v>1998</v>
       </c>
       <c r="B47" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="48" spans="1:2">
+      <c r="C47" s="17" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" s="17" t="s">
-        <v>1991</v>
+        <v>1945</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="17" t="s">
-        <v>1992</v>
+        <v>1943</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="15" t="s">
+        <v>2454</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>2488</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" s="17" t="s">
-        <v>1993</v>
+        <v>1999</v>
       </c>
       <c r="B50" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="51" spans="1:2">
+      <c r="C50" s="17" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51" s="17" t="s">
-        <v>1994</v>
+        <v>2000</v>
       </c>
       <c r="B51" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="17" t="s">
-        <v>1995</v>
+      <c r="C51" s="17" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="15" t="s">
+        <v>2455</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>2488</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" s="17" t="s">
-        <v>1996</v>
+        <v>1955</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="17" t="s">
-        <v>1997</v>
+        <v>1956</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="15" t="s">
+        <v>2456</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>2488</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" s="17" t="s">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="B55" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="56" spans="1:2">
+      <c r="C55" s="17" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56" s="17" t="s">
-        <v>1999</v>
+        <v>1946</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>1943</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57" s="17" t="s">
-        <v>2000</v>
+        <v>1947</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="17" t="s">
-        <v>2001</v>
+        <v>1943</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="15" t="s">
+        <v>2457</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="17" t="s">
-        <v>2002</v>
+        <v>2489</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="15" t="s">
+        <v>2458</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>2489</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60" s="17" t="s">
-        <v>2003</v>
+        <v>1957</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="17" t="s">
-        <v>2004</v>
+        <v>1956</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="15" t="s">
+        <v>2459</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="17" t="s">
-        <v>2005</v>
+        <v>2488</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="15" t="s">
+        <v>2460</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="17" t="s">
-        <v>2006</v>
+        <v>2488</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="15" t="s">
+        <v>2461</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>2488</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64" s="17" t="s">
-        <v>2007</v>
+        <v>1948</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
+        <v>1943</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65" s="17" t="s">
-        <v>2008</v>
+        <v>1949</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>1943</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66" s="17" t="s">
-        <v>2009</v>
+        <v>1950</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="17" t="s">
-        <v>2010</v>
+        <v>1943</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="15" t="s">
+        <v>2462</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="17" t="s">
-        <v>2011</v>
+        <v>2488</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="15" t="s">
+        <v>2463</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="17" t="s">
-        <v>2012</v>
+        <v>2488</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="15" t="s">
+        <v>2464</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="17" t="s">
-        <v>2013</v>
+        <v>2488</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="15" t="s">
+        <v>2465</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="17" t="s">
-        <v>2015</v>
+        <v>2488</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="15" t="s">
+        <v>2466</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>2488</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72" s="15" t="s">
-        <v>2452</v>
+        <v>2467</v>
       </c>
       <c r="B72" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="73" spans="1:2">
+      <c r="C72" s="15" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73" s="15" t="s">
-        <v>2453</v>
+        <v>2468</v>
       </c>
       <c r="B73" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="74" spans="1:2">
+      <c r="C73" s="15" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74" s="15" t="s">
-        <v>2454</v>
+        <v>2469</v>
       </c>
       <c r="B74" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="75" spans="1:2">
+      <c r="C74" s="15" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75" s="15" t="s">
-        <v>2455</v>
+        <v>2470</v>
       </c>
       <c r="B75" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="15" t="s">
-        <v>2456</v>
+      <c r="C75" s="15" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="17" t="s">
+        <v>1958</v>
       </c>
       <c r="B76" s="17" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="15" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B77" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="15" t="s">
-        <v>2457</v>
-      </c>
-      <c r="B77" s="17" t="s">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
+      <c r="C77" s="15" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78" s="15" t="s">
-        <v>2458</v>
+        <v>2472</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>2488</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79" s="15" t="s">
-        <v>2459</v>
+        <v>2473</v>
       </c>
       <c r="B79" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="80" spans="1:2">
+      <c r="C79" s="15" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80" s="15" t="s">
-        <v>2460</v>
+        <v>2474</v>
       </c>
       <c r="B80" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="15" t="s">
-        <v>2461</v>
+      <c r="C80" s="15" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="17" t="s">
+        <v>1951</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="15" t="s">
-        <v>2462</v>
+        <v>1943</v>
+      </c>
+      <c r="C81" s="17" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="17" t="s">
+        <v>1952</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>1943</v>
+      </c>
+      <c r="C82" s="17" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83" s="15" t="s">
-        <v>2463</v>
+        <v>2500</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>1943</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84" s="15" t="s">
-        <v>2464</v>
+        <v>2501</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
+        <v>1943</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85" s="15" t="s">
-        <v>2465</v>
+        <v>2475</v>
       </c>
       <c r="B85" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="86" spans="1:2">
+      <c r="C85" s="15" t="s">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86" s="15" t="s">
-        <v>2466</v>
+        <v>2476</v>
       </c>
       <c r="B86" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="87" spans="1:2">
+      <c r="C86" s="15" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87" s="15" t="s">
-        <v>2467</v>
+        <v>2477</v>
       </c>
       <c r="B87" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="88" spans="1:2">
+      <c r="C87" s="15" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88" s="15" t="s">
-        <v>2468</v>
+        <v>2478</v>
       </c>
       <c r="B88" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="89" spans="1:2">
+      <c r="C88" s="15" t="s">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
       <c r="A89" s="15" t="s">
-        <v>2469</v>
+        <v>2479</v>
       </c>
       <c r="B89" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="90" spans="1:2">
+      <c r="C89" s="15" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
       <c r="A90" s="15" t="s">
-        <v>2470</v>
+        <v>2480</v>
       </c>
       <c r="B90" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="91" spans="1:2">
+      <c r="C90" s="15" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91" s="15" t="s">
-        <v>2471</v>
+        <v>2481</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" s="15" t="s">
-        <v>2472</v>
+        <v>2489</v>
+      </c>
+      <c r="C91" s="15" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="17" t="s">
+        <v>1959</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
+        <v>1956</v>
+      </c>
+      <c r="C92" s="17" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
       <c r="A93" s="15" t="s">
-        <v>2473</v>
+        <v>2482</v>
       </c>
       <c r="B93" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="15" t="s">
-        <v>2474</v>
+      <c r="C93" s="15" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="18" t="s">
+        <v>2498</v>
       </c>
       <c r="B94" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="15" t="s">
-        <v>2475</v>
+      <c r="C94" s="18" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="17" t="s">
+        <v>1953</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
+        <v>1943</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96" s="15" t="s">
-        <v>2476</v>
+        <v>2503</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" s="15" t="s">
-        <v>2477</v>
+        <v>1943</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="17" t="s">
+        <v>1954</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
+        <v>1943</v>
+      </c>
+      <c r="C97" s="17" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98" s="15" t="s">
-        <v>2478</v>
+        <v>2502</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
+        <v>1943</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99" s="15" t="s">
-        <v>2479</v>
+        <v>2483</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="15" t="s">
-        <v>2480</v>
+        <v>1943</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="18" t="s">
+        <v>2499</v>
       </c>
       <c r="B100" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="101" spans="1:2">
+      <c r="C100" s="18" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101" s="15" t="s">
-        <v>2481</v>
+        <v>2484</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
+        <v>1943</v>
+      </c>
+      <c r="C101" s="15" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102" s="15" t="s">
-        <v>2482</v>
+        <v>2485</v>
       </c>
       <c r="B102" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="15" t="s">
-        <v>2483</v>
+      <c r="C102" s="15" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="17" t="s">
+        <v>2002</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="15" t="s">
-        <v>2484</v>
+        <v>1961</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="12" t="s">
+        <v>2564</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="15" t="s">
-        <v>2485</v>
+        <v>1961</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="17" t="s">
+        <v>2003</v>
       </c>
       <c r="B105" s="17" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="12" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B106" s="17" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="17" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B107" s="17" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C107" s="17" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="17" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B108" s="17" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C108" s="17" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="12" t="s">
+        <v>2566</v>
+      </c>
+      <c r="B109" s="17" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="15" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B110" s="17" t="s">
         <v>2488</v>
       </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="15" t="s">
+      <c r="C110" s="15" t="s">
         <v>2486</v>
       </c>
-      <c r="B106" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="15" t="s">
-        <v>2487</v>
-      </c>
-      <c r="B107" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="18" t="s">
-        <v>2498</v>
-      </c>
-      <c r="B108" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="18" t="s">
-        <v>2499</v>
-      </c>
-      <c r="B109" s="17" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="15" t="s">
-        <v>2500</v>
-      </c>
-      <c r="B110" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="15" t="s">
-        <v>2501</v>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="17" t="s">
+        <v>2006</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="15" t="s">
-        <v>2502</v>
+        <v>1961</v>
+      </c>
+      <c r="C111" s="17" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="17" t="s">
+        <v>2007</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="15" t="s">
-        <v>2503</v>
+        <v>1961</v>
+      </c>
+      <c r="C112" s="17" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="12" t="s">
+        <v>2567</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="12" t="s">
-        <v>2562</v>
+        <v>1961</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="17" t="s">
+        <v>2008</v>
       </c>
       <c r="B114" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="12" t="s">
-        <v>2563</v>
+      <c r="C114" s="17" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="17" t="s">
+        <v>2009</v>
       </c>
       <c r="B115" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="12" t="s">
-        <v>2564</v>
+      <c r="C115" s="17" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="17" t="s">
+        <v>2010</v>
       </c>
       <c r="B116" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="12" t="s">
-        <v>2565</v>
+      <c r="C116" s="17" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="17" t="s">
+        <v>2011</v>
       </c>
       <c r="B117" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="118" spans="1:2">
+      <c r="C117" s="17" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
       <c r="A118" s="12" t="s">
-        <v>2566</v>
+        <v>2568</v>
       </c>
       <c r="B118" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="12" t="s">
-        <v>2567</v>
+      <c r="C118" s="12" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="15" t="s">
+        <v>2487</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
+        <v>2488</v>
+      </c>
+      <c r="C119" s="15" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
       <c r="A120" s="12" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="B120" s="17" t="s">
         <v>1961</v>
       </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="12" t="s">
+      <c r="C120" s="12" t="s">
         <v>2569</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="17" t="s">
+        <v>2012</v>
       </c>
       <c r="B121" s="17" t="s">
         <v>1961</v>
       </c>
+      <c r="C121" s="17" t="s">
+        <v>2012</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1">
+    <sortState ref="A2:C121">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="comment_synonyms" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">action!$A$1:$F$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">action!$A$1:$F$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">branch!$A$1:$B$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">comment_synonyms!$A$1:$D$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">defect_category!$A$1:$D$43</definedName>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5203" uniqueCount="2578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5216" uniqueCount="2576">
   <si>
     <t>part_used</t>
   </si>
@@ -6353,15 +6353,9 @@
     <t>REPLACE_REMOTE</t>
   </si>
   <si>
-    <t>ganti|replace|led bar</t>
-  </si>
-  <si>
     <t>REPLACE_LED_BAR</t>
   </si>
   <si>
-    <t>ganti|replace|lvds</t>
-  </si>
-  <si>
     <t>REPLACE_LVDS_WIRE</t>
   </si>
   <si>
@@ -7379,9 +7373,6 @@
     <t>FACTOYY|FACTORY</t>
   </si>
   <si>
-    <t>SUBT|SUBTITUSI|SUBSTITUSI|TKR|TUKAR|PENARIKAN DAN PENGANTARAN</t>
-  </si>
-  <si>
     <t>CLAIM|KLAIM|GARANSI|TGG ACC|MAU DISERVICE|MAU TKR|CEK INFORMASI|DIKERJAKN KONS SENDIRI|DIKERJAKAN KONS SENDIRI</t>
   </si>
   <si>
@@ -7661,12 +7652,6 @@
     <t>bawa|zy|z1|ditarik|tarik|kirim|ws|carry|to ws|diantar|TRANSFER</t>
   </si>
   <si>
-    <t>SUBTITUSI|SUBS</t>
-  </si>
-  <si>
-    <t>SUBSTIUSI</t>
-  </si>
-  <si>
     <t>MATO|13TI|WATI</t>
   </si>
   <si>
@@ -7770,6 +7755,15 @@
   </si>
   <si>
     <t>RSNSZA025QBZZ</t>
+  </si>
+  <si>
+    <t>SUBT|SUBTITUSI|SUBSTITUSI|TKR|TUKAR|PENARIKAN DAN PENGANTARAN|SUBS</t>
+  </si>
+  <si>
+    <t>SUBSTIUSI|SUBT|SUBTITUSI|SUBSTITUSI|TKR|TUKAR|PENARIKAN DAN PENGANTARAN|SUBS</t>
+  </si>
+  <si>
+    <t>ganti|replace|ir|sensor|LED IR</t>
   </si>
 </sst>
 </file>
@@ -7904,7 +7898,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7929,12 +7923,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -7944,6 +7933,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22915,7 +22906,7 @@
     </row>
     <row r="1835" spans="1:2">
       <c r="A1835" s="6" t="s">
-        <v>2531</v>
+        <v>2528</v>
       </c>
       <c r="B1835" s="1" t="s">
         <v>459</v>
@@ -22923,7 +22914,7 @@
     </row>
     <row r="1836" spans="1:2">
       <c r="A1836" s="6" t="s">
-        <v>2532</v>
+        <v>2529</v>
       </c>
       <c r="B1836" s="7" t="s">
         <v>459</v>
@@ -22931,7 +22922,7 @@
     </row>
     <row r="1837" spans="1:2">
       <c r="A1837" s="6" t="s">
-        <v>2533</v>
+        <v>2530</v>
       </c>
       <c r="B1837" s="1" t="s">
         <v>1826</v>
@@ -22939,7 +22930,7 @@
     </row>
     <row r="1838" spans="1:2">
       <c r="A1838" t="s">
-        <v>2574</v>
+        <v>2569</v>
       </c>
       <c r="B1838" s="7" t="s">
         <v>1429</v>
@@ -22947,7 +22938,7 @@
     </row>
     <row r="1839" spans="1:2">
       <c r="A1839" t="s">
-        <v>2575</v>
+        <v>2570</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>214</v>
@@ -22955,7 +22946,7 @@
     </row>
     <row r="1840" spans="1:2">
       <c r="A1840" t="s">
-        <v>2576</v>
+        <v>2571</v>
       </c>
       <c r="B1840" s="7" t="s">
         <v>964</v>
@@ -22963,7 +22954,7 @@
     </row>
     <row r="1841" spans="1:2">
       <c r="A1841" t="s">
-        <v>2577</v>
+        <v>2572</v>
       </c>
       <c r="B1841" s="7" t="s">
         <v>964</v>
@@ -22993,1326 +22984,1326 @@
         <v>1941</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2570</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="14" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="14" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="14" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="14" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="14" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="14" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="14" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="14" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="14" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="14" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="14" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="14" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="14" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="14" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="14" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="14" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="14" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="14" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="14" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="14" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="14" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="14" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="14" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="10" t="s">
+        <v>2558</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="14" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="14" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="14" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="14" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="14" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="14" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="14" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="14" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="14" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="14" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="14" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="14" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="12" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="12" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="14" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="14" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="14" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="14" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="14" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="14" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="14" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="14" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="12" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="14" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="14" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="12" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="14" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="12" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="14" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="14" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="14" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="12" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>2486</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="12" t="s">
+        <v>2455</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>2486</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="14" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="12" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="12" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="12" t="s">
+        <v>2458</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="14" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="14" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="12" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="12" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="12" t="s">
+        <v>2461</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="12" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="12" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="12" t="s">
+        <v>2464</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="12" t="s">
+        <v>2465</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="12" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="12" t="s">
+        <v>2467</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="14" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="12" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="12" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="12" t="s">
+        <v>2470</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="12" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="14" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="14" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="12" t="s">
+        <v>2497</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="12" t="s">
+        <v>2498</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="12" t="s">
+        <v>2472</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="12" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="12" t="s">
+        <v>2474</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="12" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="12" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="12" t="s">
+        <v>2477</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="12" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B91" s="14" t="s">
+        <v>2486</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="14" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C92" s="14" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="12" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="15" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="14" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="12" t="s">
+        <v>2500</v>
+      </c>
+      <c r="B96" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="14" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="12" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="12" t="s">
+        <v>2480</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="15" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="12" t="s">
+        <v>2481</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="12" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B102" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="14" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B103" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C103" s="14" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="10" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B104" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="14" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B105" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C105" s="14" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="10" t="s">
+        <v>2560</v>
+      </c>
+      <c r="B106" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="14" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B107" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="14" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B108" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="10" t="s">
+        <v>2561</v>
+      </c>
+      <c r="B109" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="12" t="s">
+        <v>2483</v>
+      </c>
+      <c r="B110" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="14" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B111" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C111" s="14" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="14" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B112" s="14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C112" s="14" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="10" t="s">
         <v>2562</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B113" s="14" t="s">
         <v>1961</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>2571</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="17" t="s">
-        <v>1960</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="C113" s="10" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="14" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B114" s="14" t="s">
         <v>1961</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="17" t="s">
-        <v>1962</v>
-      </c>
-      <c r="B4" s="17" t="s">
+      <c r="C114" s="14" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="14" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B115" s="14" t="s">
         <v>1961</v>
       </c>
-      <c r="C4" s="17" t="s">
-        <v>1962</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="17" t="s">
-        <v>1963</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="C115" s="14" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="14" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B116" s="14" t="s">
         <v>1961</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="17" t="s">
-        <v>1964</v>
-      </c>
-      <c r="B6" s="17" t="s">
+      <c r="C116" s="14" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="14" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B117" s="14" t="s">
         <v>1961</v>
       </c>
-      <c r="C6" s="17" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="17" t="s">
-        <v>1965</v>
-      </c>
-      <c r="B7" s="17" t="s">
+      <c r="C117" s="14" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="10" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B118" s="14" t="s">
         <v>1961</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>1966</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="17" t="s">
-        <v>1966</v>
-      </c>
-      <c r="B8" s="17" t="s">
+      <c r="C118" s="10" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="12" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B119" s="14" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="10" t="s">
+        <v>2564</v>
+      </c>
+      <c r="B120" s="14" t="s">
         <v>1961</v>
       </c>
-      <c r="C8" s="17" t="s">
-        <v>1966</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="17" t="s">
-        <v>1967</v>
-      </c>
-      <c r="B9" s="17" t="s">
+      <c r="C120" s="10" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="14" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B121" s="14" t="s">
         <v>1961</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>1967</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="17" t="s">
-        <v>1968</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>1968</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="17" t="s">
-        <v>1969</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>2572</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="17" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>2573</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="17" t="s">
-        <v>1971</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="17" t="s">
-        <v>1972</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="17" t="s">
-        <v>1973</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="17" t="s">
-        <v>1974</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="17" t="s">
-        <v>1975</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="17" t="s">
-        <v>1976</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="17" t="s">
-        <v>1977</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="17" t="s">
-        <v>1978</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="17" t="s">
-        <v>1979</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="17" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>2014</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="17" t="s">
-        <v>1942</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="17" t="s">
-        <v>1944</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="17" t="s">
-        <v>1980</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="12" t="s">
-        <v>2563</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="17" t="s">
-        <v>1981</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="17" t="s">
-        <v>1982</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>1982</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="17" t="s">
-        <v>1983</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>1983</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="17" t="s">
-        <v>1984</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>1984</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="17" t="s">
-        <v>1985</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>1984</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="17" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>1986</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="17" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>1987</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="17" t="s">
-        <v>1988</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>1987</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="17" t="s">
-        <v>1989</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>1989</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="17" t="s">
-        <v>1990</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="17" t="s">
-        <v>2015</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>2014</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="17" t="s">
-        <v>1991</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C38" s="17" t="s">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="15" t="s">
-        <v>2452</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>2452</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="15" t="s">
-        <v>2453</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>2453</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="17" t="s">
-        <v>1992</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="17" t="s">
-        <v>1993</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C42" s="17" t="s">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="17" t="s">
-        <v>1994</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="17" t="s">
-        <v>1995</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="17" t="s">
-        <v>1996</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="17" t="s">
-        <v>1997</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="17" t="s">
-        <v>1998</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C47" s="17" t="s">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="17" t="s">
-        <v>1945</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="15" t="s">
-        <v>2454</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C49" s="15" t="s">
-        <v>2454</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="17" t="s">
-        <v>1999</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="17" t="s">
-        <v>2000</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="15" t="s">
-        <v>2455</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>2455</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="17" t="s">
-        <v>1955</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>1956</v>
-      </c>
-      <c r="C53" s="17" t="s">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="15" t="s">
-        <v>2456</v>
-      </c>
-      <c r="B54" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>2456</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="17" t="s">
-        <v>2001</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C55" s="17" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="17" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B56" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C56" s="17" t="s">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="17" t="s">
-        <v>1947</v>
-      </c>
-      <c r="B57" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C57" s="17" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="15" t="s">
-        <v>2457</v>
-      </c>
-      <c r="B58" s="17" t="s">
-        <v>2489</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>2457</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="15" t="s">
-        <v>2458</v>
-      </c>
-      <c r="B59" s="17" t="s">
-        <v>2489</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>2458</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="17" t="s">
-        <v>1957</v>
-      </c>
-      <c r="B60" s="17" t="s">
-        <v>1956</v>
-      </c>
-      <c r="C60" s="17" t="s">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="15" t="s">
-        <v>2459</v>
-      </c>
-      <c r="B61" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C61" s="15" t="s">
-        <v>2459</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="15" t="s">
-        <v>2460</v>
-      </c>
-      <c r="B62" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>2460</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="15" t="s">
-        <v>2461</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C63" s="15" t="s">
-        <v>2461</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="17" t="s">
-        <v>1948</v>
-      </c>
-      <c r="B64" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C64" s="17" t="s">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="17" t="s">
-        <v>1949</v>
-      </c>
-      <c r="B65" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="17" t="s">
-        <v>1950</v>
-      </c>
-      <c r="B66" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C66" s="17" t="s">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="15" t="s">
-        <v>2462</v>
-      </c>
-      <c r="B67" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>2462</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="15" t="s">
-        <v>2463</v>
-      </c>
-      <c r="B68" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C68" s="15" t="s">
-        <v>2463</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="15" t="s">
-        <v>2464</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>2464</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="15" t="s">
-        <v>2465</v>
-      </c>
-      <c r="B70" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C70" s="15" t="s">
-        <v>2465</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="15" t="s">
-        <v>2466</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C71" s="15" t="s">
-        <v>2466</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="15" t="s">
-        <v>2467</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C72" s="15" t="s">
-        <v>2467</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="15" t="s">
-        <v>2468</v>
-      </c>
-      <c r="B73" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C73" s="15" t="s">
-        <v>2468</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="15" t="s">
-        <v>2469</v>
-      </c>
-      <c r="B74" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C74" s="15" t="s">
-        <v>2469</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="15" t="s">
-        <v>2470</v>
-      </c>
-      <c r="B75" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C75" s="15" t="s">
-        <v>2470</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="17" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B76" s="17" t="s">
-        <v>1956</v>
-      </c>
-      <c r="C76" s="17" t="s">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="15" t="s">
-        <v>2471</v>
-      </c>
-      <c r="B77" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C77" s="15" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="15" t="s">
-        <v>2472</v>
-      </c>
-      <c r="B78" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C78" s="15" t="s">
-        <v>2472</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="15" t="s">
-        <v>2473</v>
-      </c>
-      <c r="B79" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C79" s="15" t="s">
-        <v>2473</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="15" t="s">
-        <v>2474</v>
-      </c>
-      <c r="B80" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C80" s="15" t="s">
-        <v>2474</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="17" t="s">
-        <v>1951</v>
-      </c>
-      <c r="B81" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C81" s="17" t="s">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="17" t="s">
-        <v>1952</v>
-      </c>
-      <c r="B82" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C82" s="17" t="s">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="15" t="s">
-        <v>2500</v>
-      </c>
-      <c r="B83" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C83" s="15" t="s">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="15" t="s">
-        <v>2501</v>
-      </c>
-      <c r="B84" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C84" s="15" t="s">
-        <v>2501</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="15" t="s">
-        <v>2475</v>
-      </c>
-      <c r="B85" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C85" s="15" t="s">
-        <v>2475</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="15" t="s">
-        <v>2476</v>
-      </c>
-      <c r="B86" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C86" s="15" t="s">
-        <v>2476</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="15" t="s">
-        <v>2477</v>
-      </c>
-      <c r="B87" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C87" s="15" t="s">
-        <v>2477</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="15" t="s">
-        <v>2478</v>
-      </c>
-      <c r="B88" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C88" s="15" t="s">
-        <v>2478</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="15" t="s">
-        <v>2479</v>
-      </c>
-      <c r="B89" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C89" s="15" t="s">
-        <v>2479</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="15" t="s">
-        <v>2480</v>
-      </c>
-      <c r="B90" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C90" s="15" t="s">
-        <v>2480</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="15" t="s">
-        <v>2481</v>
-      </c>
-      <c r="B91" s="17" t="s">
-        <v>2489</v>
-      </c>
-      <c r="C91" s="15" t="s">
-        <v>2481</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="17" t="s">
-        <v>1959</v>
-      </c>
-      <c r="B92" s="17" t="s">
-        <v>1956</v>
-      </c>
-      <c r="C92" s="17" t="s">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="15" t="s">
-        <v>2482</v>
-      </c>
-      <c r="B93" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C93" s="15" t="s">
-        <v>2482</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="18" t="s">
-        <v>2498</v>
-      </c>
-      <c r="B94" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C94" s="18" t="s">
-        <v>2498</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="17" t="s">
-        <v>1953</v>
-      </c>
-      <c r="B95" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C95" s="17" t="s">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="15" t="s">
-        <v>2503</v>
-      </c>
-      <c r="B96" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C96" s="15" t="s">
-        <v>2503</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="17" t="s">
-        <v>1954</v>
-      </c>
-      <c r="B97" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C97" s="17" t="s">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="15" t="s">
-        <v>2502</v>
-      </c>
-      <c r="B98" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C98" s="15" t="s">
-        <v>2502</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="15" t="s">
-        <v>2483</v>
-      </c>
-      <c r="B99" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C99" s="15" t="s">
-        <v>2483</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="18" t="s">
-        <v>2499</v>
-      </c>
-      <c r="B100" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C100" s="18" t="s">
-        <v>2499</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="15" t="s">
-        <v>2484</v>
-      </c>
-      <c r="B101" s="17" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C101" s="15" t="s">
-        <v>2484</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="15" t="s">
-        <v>2485</v>
-      </c>
-      <c r="B102" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C102" s="15" t="s">
-        <v>2485</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" s="17" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B103" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C103" s="17" t="s">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" s="12" t="s">
-        <v>2564</v>
-      </c>
-      <c r="B104" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C104" s="12" t="s">
-        <v>2564</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="17" t="s">
-        <v>2003</v>
-      </c>
-      <c r="B105" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C105" s="17" t="s">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" s="12" t="s">
-        <v>2565</v>
-      </c>
-      <c r="B106" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C106" s="12" t="s">
-        <v>2565</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" s="17" t="s">
-        <v>2004</v>
-      </c>
-      <c r="B107" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C107" s="17" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" s="17" t="s">
-        <v>2005</v>
-      </c>
-      <c r="B108" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C108" s="17" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="12" t="s">
-        <v>2566</v>
-      </c>
-      <c r="B109" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C109" s="12" t="s">
-        <v>2566</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" s="15" t="s">
-        <v>2486</v>
-      </c>
-      <c r="B110" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C110" s="15" t="s">
-        <v>2486</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="17" t="s">
-        <v>2006</v>
-      </c>
-      <c r="B111" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C111" s="17" t="s">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="17" t="s">
-        <v>2007</v>
-      </c>
-      <c r="B112" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C112" s="17" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="12" t="s">
-        <v>2567</v>
-      </c>
-      <c r="B113" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C113" s="12" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="17" t="s">
-        <v>2008</v>
-      </c>
-      <c r="B114" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C114" s="17" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="17" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B115" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C115" s="17" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="17" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B116" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C116" s="17" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="17" t="s">
-        <v>2011</v>
-      </c>
-      <c r="B117" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C117" s="17" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="12" t="s">
-        <v>2568</v>
-      </c>
-      <c r="B118" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C118" s="12" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="15" t="s">
-        <v>2487</v>
-      </c>
-      <c r="B119" s="17" t="s">
-        <v>2488</v>
-      </c>
-      <c r="C119" s="15" t="s">
-        <v>2487</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="12" t="s">
-        <v>2569</v>
-      </c>
-      <c r="B120" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C120" s="12" t="s">
-        <v>2569</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="17" t="s">
-        <v>2012</v>
-      </c>
-      <c r="B121" s="17" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C121" s="17" t="s">
+      <c r="C121" s="14" t="s">
         <v>2012</v>
       </c>
     </row>
@@ -24371,7 +24362,7 @@
         <v>2021</v>
       </c>
       <c r="D2" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>2088</v>
@@ -24408,7 +24399,7 @@
         <v>2021</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>2024</v>
@@ -24426,7 +24417,7 @@
         <v>2021</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>2034</v>
@@ -24446,7 +24437,7 @@
         <v>2021</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2545</v>
+        <v>2540</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>2042</v>
@@ -24464,7 +24455,7 @@
         <v>2021</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2546</v>
+        <v>2541</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>2037</v>
@@ -24482,7 +24473,7 @@
         <v>2021</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2544</v>
+        <v>2539</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>2041</v>
@@ -24500,7 +24491,7 @@
         <v>2021</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2490</v>
+        <v>2487</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>2024</v>
@@ -24518,7 +24509,7 @@
         <v>2021</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>2047</v>
@@ -24538,7 +24529,7 @@
         <v>2021</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>2034</v>
@@ -24558,13 +24549,13 @@
         <v>2021</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -24578,13 +24569,13 @@
         <v>2021</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -24598,13 +24589,13 @@
         <v>2021</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2560</v>
+        <v>2555</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>2055</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -24618,7 +24609,7 @@
         <v>2021</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2558</v>
+        <v>2553</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>2045</v>
@@ -24638,13 +24629,13 @@
         <v>2021</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>2035</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -24658,7 +24649,7 @@
         <v>2021</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>2034</v>
@@ -24671,14 +24662,14 @@
       <c r="A18" s="3">
         <v>780</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="11" t="s">
         <v>322</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D18" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>2047</v>
@@ -24715,13 +24706,13 @@
         <v>2021</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -24735,13 +24726,13 @@
         <v>2021</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -24755,7 +24746,7 @@
         <v>2021</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>2034</v>
@@ -24775,10 +24766,10 @@
         <v>2021</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2520</v>
+        <v>2517</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>2521</v>
+        <v>2518</v>
       </c>
       <c r="F23" s="3"/>
     </row>
@@ -24813,10 +24804,10 @@
         <v>2021</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="F25" s="3"/>
     </row>
@@ -24831,7 +24822,7 @@
         <v>2021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2547</v>
+        <v>2542</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>2042</v>
@@ -24871,10 +24862,10 @@
         <v>2021</v>
       </c>
       <c r="D28" t="s">
-        <v>2492</v>
+        <v>2489</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="F28" s="3"/>
     </row>
@@ -24889,13 +24880,13 @@
         <v>2021</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>2556</v>
+        <v>2551</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>2037</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>2360</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -24909,13 +24900,13 @@
         <v>2021</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>2041</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -24929,13 +24920,13 @@
         <v>2021</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -24949,7 +24940,7 @@
         <v>2021</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2493</v>
+        <v>2490</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>2055</v>
@@ -24969,7 +24960,7 @@
         <v>2021</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>2561</v>
+        <v>2556</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>2055</v>
@@ -25007,7 +24998,7 @@
         <v>2021</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>2047</v>
@@ -25047,13 +25038,13 @@
         <v>2021</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>2035</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -25067,7 +25058,7 @@
         <v>2021</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>2522</v>
+        <v>2519</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>2034</v>
@@ -25087,7 +25078,7 @@
         <v>2021</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>2529</v>
+        <v>2526</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>2034</v>
@@ -25107,10 +25098,10 @@
         <v>2021</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
       <c r="F40" s="3"/>
     </row>
@@ -25125,10 +25116,10 @@
         <v>2021</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>2518</v>
+        <v>2515</v>
       </c>
       <c r="F41" s="3"/>
     </row>
@@ -25143,13 +25134,13 @@
         <v>2021</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>2495</v>
+        <v>2492</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -25163,13 +25154,13 @@
         <v>2021</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>2513</v>
+        <v>2510</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>2348</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -25183,13 +25174,13 @@
         <v>2021</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>2356</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -25209,7 +25200,7 @@
         <v>2031</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>2353</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -25223,13 +25214,13 @@
         <v>2021</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2494</v>
+        <v>2491</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>2026</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -25243,7 +25234,7 @@
         <v>2021</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>2032</v>
@@ -25263,13 +25254,13 @@
         <v>2021</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>2508</v>
+        <v>2505</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>2356</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -25283,13 +25274,13 @@
         <v>2021</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>2511</v>
+        <v>2508</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>2349</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -25303,13 +25294,13 @@
         <v>2021</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>2559</v>
+        <v>2554</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>2349</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -25329,7 +25320,7 @@
         <v>2028</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>2351</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -25343,13 +25334,13 @@
         <v>2021</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>2029</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>2352</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -25363,13 +25354,13 @@
         <v>2021</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -25383,10 +25374,10 @@
         <v>2021</v>
       </c>
       <c r="D54" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -25400,13 +25391,13 @@
         <v>2021</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>2530</v>
+        <v>2527</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>2354</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -25446,7 +25437,7 @@
         <v>2034</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -25460,7 +25451,7 @@
         <v>2021</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>2058</v>
@@ -25483,7 +25474,7 @@
         <v>2057</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>2036</v>
@@ -25506,7 +25497,7 @@
         <v>2050</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -25540,13 +25531,13 @@
         <v>2021</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>2041</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -25560,13 +25551,13 @@
         <v>2021</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>2026</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -25580,13 +25571,13 @@
         <v>2021</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>2032</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -25600,13 +25591,13 @@
         <v>2021</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -25620,13 +25611,13 @@
         <v>2021</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -25640,13 +25631,13 @@
         <v>2021</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -25660,13 +25651,13 @@
         <v>2021</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -25680,13 +25671,13 @@
         <v>2021</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>2055</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -25700,13 +25691,13 @@
         <v>2021</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>2517</v>
+        <v>2514</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -25720,13 +25711,13 @@
         <v>2021</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>2041</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -25740,10 +25731,10 @@
         <v>2021</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>2518</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -25755,13 +25746,13 @@
         <v>2021</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>2031</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -25773,10 +25764,10 @@
         <v>2021</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2520</v>
+        <v>2517</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>2521</v>
+        <v>2518</v>
       </c>
       <c r="F74" s="3"/>
     </row>
@@ -25789,13 +25780,13 @@
         <v>2021</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>2032</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -25807,13 +25798,13 @@
         <v>2021</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>2053</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -25825,13 +25816,13 @@
         <v>2021</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -25843,13 +25834,13 @@
         <v>2021</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -25861,13 +25852,13 @@
         <v>2021</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>2028</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -25879,13 +25870,13 @@
         <v>2021</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>2551</v>
+        <v>2546</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>2042</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -25897,13 +25888,13 @@
         <v>2021</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>2547</v>
+        <v>2542</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>2042</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -25929,10 +25920,10 @@
         <v>2021</v>
       </c>
       <c r="D83" t="s">
-        <v>2554</v>
+        <v>2549</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -25944,13 +25935,13 @@
         <v>2021</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -25962,13 +25953,13 @@
         <v>2021</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>2552</v>
+        <v>2547</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>2041</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -25980,13 +25971,13 @@
         <v>2021</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>2548</v>
+        <v>2543</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>2041</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -25998,13 +25989,13 @@
         <v>2021</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>2490</v>
+        <v>2487</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -26016,13 +26007,13 @@
         <v>2021</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -26034,13 +26025,13 @@
         <v>2021</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>2055</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -26052,7 +26043,7 @@
         <v>2021</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>2055</v>
@@ -26067,31 +26058,31 @@
         <v>2021</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>2058</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="3">
         <v>460</v>
       </c>
-      <c r="B92" s="16"/>
+      <c r="B92" s="13"/>
       <c r="C92" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>2050</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -26103,13 +26094,13 @@
         <v>2021</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>2035</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -26121,13 +26112,13 @@
         <v>2021</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -26139,25 +26130,25 @@
         <v>2021</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>2553</v>
+        <v>2548</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="3">
         <v>710</v>
       </c>
-      <c r="B96" s="15"/>
+      <c r="B96" s="12"/>
       <c r="C96" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>2034</v>
@@ -26175,10 +26166,10 @@
         <v>2021</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
       <c r="F97" s="3"/>
     </row>
@@ -26295,7 +26286,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -26326,76 +26317,80 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="8">
-        <v>20</v>
-      </c>
-      <c r="B2" s="8">
+      <c r="A2" s="1">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>2086</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>2087</v>
+      <c r="E2" s="1" t="s">
+        <v>2488</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>2085</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="8">
-        <v>700</v>
-      </c>
-      <c r="B3" s="9">
+      <c r="A3" s="1">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="6" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>2448</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>2087</v>
+      <c r="E3" s="1" t="s">
+        <v>2488</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2085</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="8">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B4" s="8">
         <v>1</v>
       </c>
-      <c r="C4" s="8"/>
+      <c r="C4" s="8" t="s">
+        <v>2057</v>
+      </c>
       <c r="D4" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>2090</v>
+        <v>2488</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>2091</v>
+        <v>2085</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1">
+        <v>13</v>
+      </c>
+      <c r="B5" s="8">
         <v>1</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>2491</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="E5" s="8" t="s">
+        <v>2488</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>2085</v>
       </c>
       <c r="G5" s="9"/>
@@ -26403,21 +26398,19 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1">
+        <v>14</v>
+      </c>
+      <c r="B6" s="8">
         <v>1</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>1816</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="9"/>
+      <c r="D6" s="9" t="s">
+        <v>2428</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>2491</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="8" t="s">
         <v>2085</v>
       </c>
       <c r="G6" s="9"/>
@@ -26425,19 +26418,17 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="8">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <v>1</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>459</v>
-      </c>
+      <c r="C7" s="9"/>
       <c r="D7" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>2491</v>
+      <c r="E7" s="9" t="s">
+        <v>2428</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>2085</v>
@@ -26446,44 +26437,40 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="8">
-        <v>520</v>
-      </c>
-      <c r="B8" s="8">
+      <c r="A8" s="1">
+        <v>16</v>
+      </c>
+      <c r="B8" s="9">
         <v>1</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="16"/>
+      <c r="D8" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>2057</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>2491</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>2085</v>
+      <c r="E8" s="9" t="s">
+        <v>2445</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>2087</v>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="8">
-        <v>530</v>
-      </c>
-      <c r="B9" s="8">
+      <c r="A9" s="1">
+        <v>17</v>
+      </c>
+      <c r="B9" s="9">
         <v>1</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9"/>
+      <c r="D9" s="9" t="s">
+        <v>2446</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>2057</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>2491</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>2085</v>
       </c>
       <c r="G9" s="9"/>
@@ -26491,57 +26478,61 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="8">
-        <v>540</v>
-      </c>
-      <c r="B10" s="8">
+        <v>18</v>
+      </c>
+      <c r="B10" s="9">
         <v>1</v>
       </c>
-      <c r="C10" s="9"/>
+      <c r="C10" s="9" t="s">
+        <v>2057</v>
+      </c>
       <c r="D10" s="9" t="s">
-        <v>2430</v>
-      </c>
-      <c r="E10" s="8" t="s">
+        <v>2446</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="9" t="s">
         <v>2085</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="8">
-        <v>550</v>
-      </c>
-      <c r="B11" s="8">
+      <c r="A11" s="1">
+        <v>19</v>
+      </c>
+      <c r="B11" s="9">
         <v>1</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>2057</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>2430</v>
-      </c>
-      <c r="F11" s="8" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>2085</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="8">
-        <v>710</v>
+      <c r="A12" s="1">
+        <v>20</v>
       </c>
       <c r="B12" s="9">
         <v>1</v>
       </c>
-      <c r="C12" s="9"/>
+      <c r="C12" s="6" t="s">
+        <v>109</v>
+      </c>
       <c r="D12" s="9" t="s">
-        <v>2449</v>
-      </c>
-      <c r="E12" s="9" t="s">
         <v>2057</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>2488</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>2085</v>
@@ -26551,111 +26542,113 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="8">
-        <v>720</v>
+        <v>21</v>
       </c>
       <c r="B13" s="9">
         <v>1</v>
       </c>
-      <c r="C13" s="9"/>
+      <c r="C13" s="6" t="s">
+        <v>109</v>
+      </c>
       <c r="D13" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>2450</v>
+      <c r="E13" s="8" t="s">
+        <v>2238</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>2085</v>
+        <v>2119</v>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="8">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="B14" s="8">
         <v>1</v>
       </c>
-      <c r="C14" s="8"/>
+      <c r="C14" s="8" t="s">
+        <v>2057</v>
+      </c>
       <c r="D14" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>2094</v>
+        <v>2086</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>2095</v>
+        <v>2087</v>
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" ht="30">
       <c r="A15" s="8">
-        <v>680</v>
-      </c>
-      <c r="B15" s="9">
+        <v>40</v>
+      </c>
+      <c r="B15" s="8">
         <v>1</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9" t="s">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>2446</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>2095</v>
+      <c r="E15" s="8" t="s">
+        <v>2494</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>2088</v>
       </c>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" ht="30">
       <c r="A16" s="8">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="B16" s="8">
         <v>1</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>37</v>
+        <v>2057</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>2128</v>
+        <v>2494</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>2129</v>
+        <v>2088</v>
       </c>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="8">
-        <v>270</v>
+        <v>50</v>
       </c>
       <c r="B17" s="8">
         <v>1</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="C17" s="8"/>
       <c r="D17" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>2128</v>
+        <v>2537</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>2129</v>
+        <v>2089</v>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="8">
-        <v>510</v>
+        <v>60</v>
       </c>
       <c r="B18" s="8">
         <v>1</v>
@@ -26664,40 +26657,38 @@
       <c r="D18" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>2434</v>
+      <c r="E18" s="8" t="s">
+        <v>2090</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>2129</v>
+        <v>2091</v>
       </c>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="8">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="B19" s="8">
         <v>1</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>345</v>
-      </c>
+      <c r="C19" s="7"/>
       <c r="D19" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>2126</v>
+        <v>2092</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>2127</v>
+        <v>2093</v>
       </c>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="8">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="B20" s="8">
         <v>1</v>
@@ -26707,477 +26698,503 @@
         <v>2057</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>2427</v>
+        <v>2094</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>2127</v>
+        <v>2095</v>
       </c>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" ht="45">
       <c r="A21" s="8">
-        <v>660</v>
-      </c>
-      <c r="B21" s="9">
+        <v>90</v>
+      </c>
+      <c r="B21" s="8">
         <v>1</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9" t="s">
+      <c r="C21" s="8"/>
+      <c r="D21" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>2445</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>2127</v>
+      <c r="E21" s="8" t="s">
+        <v>2426</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>2096</v>
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="8">
-        <v>570</v>
-      </c>
-      <c r="B22" s="9">
+        <v>100</v>
+      </c>
+      <c r="B22" s="8">
         <v>1</v>
       </c>
-      <c r="C22" s="8"/>
+      <c r="C22" s="8" t="s">
+        <v>989</v>
+      </c>
       <c r="D22" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>2435</v>
+        <v>2097</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>2152</v>
+        <v>2098</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
     </row>
-    <row r="23" spans="1:8" ht="60">
+    <row r="23" spans="1:8">
       <c r="A23" s="8">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="B23" s="8">
         <v>1</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>459</v>
-      </c>
+      <c r="C23" s="7"/>
       <c r="D23" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>2496</v>
+        <v>2097</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>2121</v>
+        <v>2098</v>
       </c>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="8">
-        <v>340</v>
+        <v>120</v>
       </c>
       <c r="B24" s="8">
         <v>1</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>109</v>
+        <v>1429</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>2057</v>
+        <v>2099</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>2121</v>
+        <v>2100</v>
       </c>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8" ht="60">
+    <row r="25" spans="1:8">
       <c r="A25" s="8">
-        <v>450</v>
+        <v>130</v>
       </c>
       <c r="B25" s="8">
         <v>1</v>
       </c>
-      <c r="C25" s="8"/>
+      <c r="C25" s="8" t="s">
+        <v>459</v>
+      </c>
       <c r="D25" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>2432</v>
+        <v>2101</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>2121</v>
+        <v>2102</v>
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="8">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="B26" s="8">
         <v>1</v>
       </c>
-      <c r="C26" s="9"/>
+      <c r="C26" s="8" t="s">
+        <v>459</v>
+      </c>
       <c r="D26" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>2426</v>
+      <c r="E26" s="8" t="s">
+        <v>2488</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>2121</v>
+        <v>2085</v>
       </c>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="8">
-        <v>490</v>
+        <v>150</v>
       </c>
       <c r="B27" s="8">
         <v>1</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="8" t="s">
+        <v>1660</v>
+      </c>
       <c r="D27" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>2429</v>
+      <c r="E27" s="8" t="s">
+        <v>2103</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>2121</v>
+        <v>2104</v>
       </c>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="8">
-        <v>600</v>
-      </c>
-      <c r="B28" s="9">
+        <v>160</v>
+      </c>
+      <c r="B28" s="8">
         <v>1</v>
       </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9" t="s">
+      <c r="C28" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>2438</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>2121</v>
+      <c r="E28" s="8" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>2105</v>
       </c>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8" ht="45">
+    <row r="29" spans="1:8">
       <c r="A29" s="8">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="B29" s="8">
         <v>1</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>1429</v>
+        <v>345</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>2122</v>
+        <v>2057</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>2123</v>
+        <v>2106</v>
       </c>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="8">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="B30" s="8">
         <v>1</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>1398</v>
+        <v>90</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>2057</v>
+        <v>2107</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>2123</v>
+        <v>2108</v>
       </c>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8" ht="45">
+    <row r="31" spans="1:8">
       <c r="A31" s="8">
-        <v>460</v>
+        <v>190</v>
       </c>
       <c r="B31" s="8">
         <v>1</v>
       </c>
-      <c r="C31" s="8"/>
+      <c r="C31" s="8" t="s">
+        <v>3</v>
+      </c>
       <c r="D31" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>2431</v>
+        <v>2109</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>2123</v>
+        <v>2110</v>
       </c>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="8">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="B32" s="8">
         <v>1</v>
       </c>
-      <c r="C32" s="9"/>
+      <c r="C32" s="8" t="s">
+        <v>128</v>
+      </c>
       <c r="D32" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>2433</v>
+        <v>2575</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>2123</v>
+        <v>2112</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="8">
-        <v>580</v>
-      </c>
-      <c r="B33" s="9">
+        <v>210</v>
+      </c>
+      <c r="B33" s="8">
         <v>1</v>
       </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9" t="s">
-        <v>2436</v>
-      </c>
-      <c r="E33" s="9" t="s">
+      <c r="C33" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>2123</v>
+      <c r="E33" s="8" t="s">
+        <v>2111</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>2112</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="8">
-        <v>590</v>
-      </c>
-      <c r="B34" s="9">
+        <v>220</v>
+      </c>
+      <c r="B34" s="8">
         <v>1</v>
       </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9" t="s">
+      <c r="C34" s="8" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E34" s="9" t="s">
-        <v>2437</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>2123</v>
+      <c r="E34" s="8" t="s">
+        <v>2113</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>2114</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="8">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B35" s="8">
         <v>1</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1660</v>
+        <v>1826</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>2124</v>
+        <v>2115</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>2125</v>
+        <v>2116</v>
       </c>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="8">
-        <v>440</v>
+        <v>240</v>
       </c>
       <c r="B36" s="8">
         <v>1</v>
       </c>
-      <c r="C36" s="8"/>
+      <c r="C36" s="8" t="s">
+        <v>1811</v>
+      </c>
       <c r="D36" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>2425</v>
+        <v>2117</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>2125</v>
+        <v>2118</v>
       </c>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" ht="60">
       <c r="A37" s="8">
-        <v>620</v>
-      </c>
-      <c r="B37" s="9">
+        <v>250</v>
+      </c>
+      <c r="B37" s="8">
         <v>1</v>
       </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9" t="s">
-        <v>2441</v>
-      </c>
-      <c r="E37" s="9" t="s">
+      <c r="C37" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>2125</v>
+      <c r="E37" s="8" t="s">
+        <v>2493</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>2119</v>
       </c>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" ht="45">
       <c r="A38" s="8">
-        <v>630</v>
-      </c>
-      <c r="B38" s="9">
+        <v>260</v>
+      </c>
+      <c r="B38" s="8">
         <v>1</v>
       </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9" t="s">
+      <c r="C38" s="8" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E38" s="9" t="s">
-        <v>2442</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>2125</v>
+      <c r="E38" s="8" t="s">
+        <v>2120</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>2121</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="8">
-        <v>610</v>
-      </c>
-      <c r="B39" s="9">
+        <v>270</v>
+      </c>
+      <c r="B39" s="8">
         <v>1</v>
       </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9" t="s">
+      <c r="C39" s="8" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E39" s="9" t="s">
-        <v>2439</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>2440</v>
+      <c r="E39" s="8" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>2123</v>
       </c>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="8">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="B40" s="8">
         <v>1</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>1811</v>
+        <v>345</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>2120</v>
+        <v>2125</v>
       </c>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="8">
-        <v>640</v>
-      </c>
-      <c r="B41" s="9">
+        <v>290</v>
+      </c>
+      <c r="B41" s="8">
         <v>1</v>
       </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9" t="s">
+      <c r="C41" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E41" s="9" t="s">
-        <v>2443</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>2120</v>
+      <c r="E41" s="8" t="s">
+        <v>2126</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>2127</v>
       </c>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="8">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="B42" s="8">
         <v>1</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>2111</v>
+        <v>2126</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>2112</v>
+        <v>2127</v>
       </c>
       <c r="G42" s="9"/>
       <c r="H42" s="9"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="8">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="B43" s="8">
         <v>1</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>3</v>
+        <v>1429</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>2057</v>
@@ -27186,42 +27203,42 @@
         <v>2057</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>2112</v>
+        <v>2100</v>
       </c>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="8">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="B44" s="8">
         <v>1</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>90</v>
+        <v>989</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>2109</v>
+        <v>2057</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>2110</v>
+        <v>2098</v>
       </c>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="8">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="B45" s="8">
         <v>1</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>90</v>
+        <v>459</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>2057</v>
@@ -27230,64 +27247,64 @@
         <v>2057</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>2110</v>
+        <v>2102</v>
       </c>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="8">
-        <v>170</v>
+        <v>340</v>
       </c>
       <c r="B46" s="8">
         <v>1</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>128</v>
+        <v>1660</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>2113</v>
+        <v>2057</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>2114</v>
+        <v>2104</v>
       </c>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="8">
-        <v>180</v>
+        <v>350</v>
       </c>
       <c r="B47" s="8">
         <v>1</v>
       </c>
-      <c r="C47" s="13" t="s">
-        <v>322</v>
+      <c r="C47" s="8" t="s">
+        <v>1398</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>2113</v>
+        <v>2057</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>2114</v>
+        <v>2121</v>
       </c>
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="8">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B48" s="8">
         <v>1</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>128</v>
+        <v>214</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>2057</v>
@@ -27296,20 +27313,20 @@
         <v>2057</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>2114</v>
+        <v>2105</v>
       </c>
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="8">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="B49" s="8">
         <v>1</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>322</v>
+      <c r="C49" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>2057</v>
@@ -27318,26 +27335,26 @@
         <v>2057</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>2114</v>
+        <v>2119</v>
       </c>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="8">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="B50" s="8">
         <v>1</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>214</v>
+        <v>345</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>2105</v>
+        <v>2057</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>2106</v>
@@ -27347,13 +27364,13 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="8">
-        <v>330</v>
+        <v>390</v>
       </c>
       <c r="B51" s="8">
         <v>1</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>214</v>
+        <v>3</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>2057</v>
@@ -27362,26 +27379,26 @@
         <v>2057</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>2106</v>
+        <v>2110</v>
       </c>
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="8">
-        <v>140</v>
+        <v>400</v>
       </c>
       <c r="B52" s="8">
         <v>1</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>345</v>
+        <v>90</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>2107</v>
+        <v>2057</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>2108</v>
@@ -27391,13 +27408,13 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="8">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="B53" s="8">
         <v>1</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>2057</v>
@@ -27406,42 +27423,42 @@
         <v>2057</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>2108</v>
+        <v>2112</v>
       </c>
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="8">
-        <v>110</v>
+        <v>420</v>
       </c>
       <c r="B54" s="8">
         <v>1</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>459</v>
+        <v>322</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>2101</v>
+        <v>2057</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="8">
-        <v>300</v>
+        <v>430</v>
       </c>
       <c r="B55" s="8">
         <v>1</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>459</v>
+        <v>1732</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>2057</v>
@@ -27450,62 +27467,64 @@
         <v>2057</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>2102</v>
+        <v>2114</v>
       </c>
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="8">
-        <v>90</v>
+        <v>440</v>
       </c>
       <c r="B56" s="8">
         <v>1</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>989</v>
+        <v>1826</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>2097</v>
+        <v>2057</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>2098</v>
+        <v>2116</v>
       </c>
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="8">
-        <v>91</v>
+        <v>450</v>
       </c>
       <c r="B57" s="8">
         <v>1</v>
       </c>
-      <c r="C57" s="8"/>
+      <c r="C57" s="8" t="s">
+        <v>1811</v>
+      </c>
       <c r="D57" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>2097</v>
+        <v>2057</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>2098</v>
+        <v>2531</v>
       </c>
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="8">
-        <v>290</v>
+        <v>460</v>
       </c>
       <c r="B58" s="8">
         <v>1</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>989</v>
+      <c r="C58" s="17" t="s">
+        <v>1902</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>2057</v>
@@ -27514,254 +27533,234 @@
         <v>2057</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>2098</v>
+        <v>2176</v>
       </c>
       <c r="G58" s="9"/>
       <c r="H58" s="9"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="8">
-        <v>100</v>
+        <v>470</v>
       </c>
       <c r="B59" s="8">
         <v>1</v>
       </c>
-      <c r="C59" s="8" t="s">
-        <v>1429</v>
-      </c>
+      <c r="C59" s="8"/>
       <c r="D59" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>2099</v>
+        <v>2423</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>2100</v>
+        <v>2123</v>
       </c>
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" ht="60">
       <c r="A60" s="8">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="B60" s="8">
         <v>1</v>
       </c>
-      <c r="C60" s="8" t="s">
-        <v>1429</v>
-      </c>
+      <c r="C60" s="8"/>
       <c r="D60" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>2057</v>
+        <v>2430</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>2100</v>
+        <v>2119</v>
       </c>
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" ht="45">
       <c r="A61" s="8">
-        <v>120</v>
+        <v>490</v>
       </c>
       <c r="B61" s="8">
         <v>1</v>
       </c>
-      <c r="C61" s="8" t="s">
-        <v>1660</v>
-      </c>
+      <c r="C61" s="8"/>
       <c r="D61" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>2103</v>
+        <v>2429</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>2104</v>
+        <v>2121</v>
       </c>
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="8">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="B62" s="8">
         <v>1</v>
       </c>
-      <c r="C62" s="8" t="s">
-        <v>1660</v>
-      </c>
+      <c r="C62" s="9"/>
       <c r="D62" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E62" s="8" t="s">
-        <v>2057</v>
+      <c r="E62" s="9" t="s">
+        <v>2424</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>2104</v>
+        <v>2119</v>
       </c>
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="8">
-        <v>190</v>
+        <v>510</v>
       </c>
       <c r="B63" s="8">
         <v>1</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>1732</v>
-      </c>
+      <c r="C63" s="9"/>
       <c r="D63" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>2115</v>
+        <v>2431</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>2116</v>
+        <v>2121</v>
       </c>
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="8">
-        <v>400</v>
+        <v>520</v>
       </c>
       <c r="B64" s="8">
         <v>1</v>
       </c>
-      <c r="C64" s="8" t="s">
-        <v>1732</v>
-      </c>
+      <c r="C64" s="9"/>
       <c r="D64" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E64" s="8" t="s">
-        <v>2057</v>
+      <c r="E64" s="9" t="s">
+        <v>2427</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="8">
-        <v>420</v>
+        <v>530</v>
       </c>
       <c r="B65" s="8">
         <v>1</v>
       </c>
-      <c r="C65" s="8" t="s">
-        <v>1811</v>
-      </c>
+      <c r="C65" s="8"/>
       <c r="D65" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>2057</v>
+        <v>2425</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>2534</v>
+        <v>2125</v>
       </c>
       <c r="G65" s="9"/>
       <c r="H65" s="9"/>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="8">
-        <v>200</v>
+        <v>540</v>
       </c>
       <c r="B66" s="8">
         <v>1</v>
       </c>
-      <c r="C66" s="8" t="s">
-        <v>1826</v>
-      </c>
+      <c r="C66" s="8"/>
       <c r="D66" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="E66" s="8" t="s">
-        <v>2117</v>
+      <c r="E66" s="9" t="s">
+        <v>2432</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>2118</v>
+        <v>2127</v>
       </c>
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="8">
-        <v>410</v>
-      </c>
-      <c r="B67" s="8">
+        <v>550</v>
+      </c>
+      <c r="B67" s="9">
         <v>1</v>
       </c>
-      <c r="C67" s="8" t="s">
-        <v>1826</v>
-      </c>
+      <c r="C67" s="8"/>
       <c r="D67" s="8" t="s">
         <v>2057</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>2057</v>
+        <v>2433</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>2118</v>
+        <v>2150</v>
       </c>
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="8">
-        <v>430</v>
-      </c>
-      <c r="B68" s="8">
+        <v>560</v>
+      </c>
+      <c r="B68" s="9">
         <v>1</v>
       </c>
-      <c r="C68" s="12" t="s">
-        <v>1902</v>
-      </c>
-      <c r="D68" s="8" t="s">
+      <c r="C68" s="9"/>
+      <c r="D68" s="9" t="s">
+        <v>2434</v>
+      </c>
+      <c r="E68" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E68" s="8" t="s">
-        <v>2057</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>2178</v>
+      <c r="F68" s="9" t="s">
+        <v>2121</v>
       </c>
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
     </row>
-    <row r="69" spans="1:8" ht="45">
+    <row r="69" spans="1:8">
       <c r="A69" s="8">
-        <v>80</v>
-      </c>
-      <c r="B69" s="8">
+        <v>570</v>
+      </c>
+      <c r="B69" s="9">
         <v>1</v>
       </c>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8" t="s">
+      <c r="C69" s="9"/>
+      <c r="D69" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E69" s="8" t="s">
-        <v>2428</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>2096</v>
+      <c r="E69" s="9" t="s">
+        <v>2435</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>2121</v>
       </c>
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="8">
-        <v>670</v>
+        <v>580</v>
       </c>
       <c r="B70" s="9">
         <v>1</v>
@@ -27771,97 +27770,97 @@
         <v>2057</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>2537</v>
+        <v>2436</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>2096</v>
+        <v>2119</v>
       </c>
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="8">
-        <v>560</v>
-      </c>
-      <c r="B71" s="8">
+        <v>590</v>
+      </c>
+      <c r="B71" s="9">
         <v>1</v>
       </c>
       <c r="C71" s="9"/>
-      <c r="D71" s="8" t="s">
+      <c r="D71" s="9" t="s">
         <v>2057</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>2541</v>
+        <v>2437</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>2183</v>
+        <v>2438</v>
       </c>
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="8">
-        <v>690</v>
+        <v>600</v>
       </c>
       <c r="B72" s="9">
         <v>1</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9" t="s">
+        <v>2439</v>
+      </c>
+      <c r="E72" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E72" s="9" t="s">
-        <v>2447</v>
-      </c>
       <c r="F72" s="9" t="s">
-        <v>2183</v>
+        <v>2123</v>
       </c>
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="8">
-        <v>60</v>
-      </c>
-      <c r="B73" s="8">
+        <v>610</v>
+      </c>
+      <c r="B73" s="9">
         <v>1</v>
       </c>
-      <c r="C73" s="7"/>
-      <c r="D73" s="8" t="s">
+      <c r="C73" s="9"/>
+      <c r="D73" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E73" s="8" t="s">
-        <v>2092</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>2093</v>
+      <c r="E73" s="9" t="s">
+        <v>2440</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>2123</v>
       </c>
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
     </row>
-    <row r="74" spans="1:8" ht="30">
+    <row r="74" spans="1:8">
       <c r="A74" s="8">
-        <v>30</v>
-      </c>
-      <c r="B74" s="8">
+        <v>620</v>
+      </c>
+      <c r="B74" s="9">
         <v>1</v>
       </c>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8" t="s">
+      <c r="C74" s="9"/>
+      <c r="D74" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E74" s="8" t="s">
-        <v>2497</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>2088</v>
+      <c r="E74" s="9" t="s">
+        <v>2441</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>2118</v>
       </c>
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="8">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="B75" s="9">
         <v>1</v>
@@ -27871,7 +27870,7 @@
         <v>2057</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>2088</v>
@@ -27881,7 +27880,7 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="8">
-        <v>730</v>
+        <v>640</v>
       </c>
       <c r="B76" s="9">
         <v>1</v>
@@ -27891,61 +27890,91 @@
         <v>2057</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>2451</v>
+        <v>2443</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>2088</v>
+        <v>2125</v>
       </c>
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="8">
-        <v>40</v>
-      </c>
-      <c r="B77" s="8">
+        <v>650</v>
+      </c>
+      <c r="B77" s="9">
         <v>1</v>
       </c>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8" t="s">
+      <c r="C77" s="9"/>
+      <c r="D77" s="9" t="s">
         <v>2057</v>
       </c>
-      <c r="E77" s="8" t="s">
-        <v>2540</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>2089</v>
+      <c r="E77" s="9" t="s">
+        <v>2534</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>2096</v>
       </c>
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="9"/>
-      <c r="B78" s="9"/>
+      <c r="A78" s="8">
+        <v>660</v>
+      </c>
+      <c r="B78" s="9">
+        <v>1</v>
+      </c>
       <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
+      <c r="D78" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>2444</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>2095</v>
+      </c>
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="9"/>
-      <c r="B79" s="9"/>
+      <c r="A79" s="8">
+        <v>670</v>
+      </c>
+      <c r="B79" s="9">
+        <v>1</v>
+      </c>
       <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
+      <c r="D79" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>2573</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>2181</v>
+      </c>
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="9"/>
-      <c r="B80" s="9"/>
+      <c r="A80" s="8">
+        <v>680</v>
+      </c>
+      <c r="B80" s="9">
+        <v>1</v>
+      </c>
       <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
+      <c r="D80" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>2448</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>2088</v>
+      </c>
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
     </row>
@@ -27979,10 +28008,39 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
     </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="9"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="9"/>
+      <c r="H84" s="9"/>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="9"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="9"/>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="9"/>
+      <c r="H86" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F46">
-    <sortState ref="A2:F77">
-      <sortCondition ref="F1:F46"/>
+  <autoFilter ref="A1:F56">
+    <sortState ref="A2:F78">
+      <sortCondition ref="A1:A54"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28002,44 +28060,44 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2130</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2131</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2132</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2133</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -28047,13 +28105,13 @@
         <v>2087</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -28061,13 +28119,13 @@
         <v>2091</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2091</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -28075,13 +28133,13 @@
         <v>2085</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -28089,265 +28147,265 @@
         <v>2095</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>2139</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>2140</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>2141</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>459</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>989</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>2123</v>
+        <v>2121</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>1429</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -28355,13 +28413,13 @@
         <v>2102</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>459</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -28369,27 +28427,27 @@
         <v>2098</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>989</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30">
       <c r="A28" s="1" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -28397,13 +28455,13 @@
         <v>2100</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>1429</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -28411,69 +28469,69 @@
         <v>2104</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>964</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -28481,41 +28539,41 @@
         <v>2096</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>2096</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -28523,13 +28581,13 @@
         <v>2093</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -28537,27 +28595,27 @@
         <v>2088</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>2088</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -28565,21 +28623,21 @@
         <v>2089</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>964</v>
@@ -28588,10 +28646,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>964</v>
@@ -28609,7 +28667,7 @@
   <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="78" customWidth="1"/>
+    <col min="1" max="1" width="85.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="80" customWidth="1"/>
@@ -28617,13 +28675,13 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2187</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2188</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2189</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2020</v>
@@ -28631,7 +28689,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>2557</v>
+        <v>2552</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2035</v>
@@ -28640,43 +28698,43 @@
         <v>2019</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45">
       <c r="A3" s="1" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>2543</v>
+        <v>2538</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2517</v>
+        <v>2514</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2019</v>
@@ -28685,66 +28743,66 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>2512</v>
+        <v>2509</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>2525</v>
+        <v>2522</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2526</v>
+        <v>2523</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2019</v>
@@ -28753,27 +28811,27 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="F11" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>2524</v>
+        <v>2521</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2519</v>
+        <v>2516</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>2019</v>
@@ -28782,10 +28840,10 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>2505</v>
+        <v>2502</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2506</v>
+        <v>2503</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>2019</v>
@@ -28794,19 +28852,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>2535</v>
+        <v>2532</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2536</v>
+        <v>2533</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>2042</v>
@@ -28815,15 +28873,15 @@
         <v>2019</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2019</v>
@@ -28832,63 +28890,63 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2504</v>
+        <v>2501</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>2023</v>
@@ -28897,617 +28955,617 @@
         <v>2019</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
+        <v>2230</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>2232</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>2233</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>2235</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>2236</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>2237</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>2238</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>2238</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>2239</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>2240</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>2241</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>2242</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>2243</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>2244</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>2245</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>2246</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>2247</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>2248</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>2249</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>2250</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>2250</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>2251</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>2252</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>2253</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2527</v>
+        <v>2524</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>2255</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>2256</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>2257</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>2258</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>989</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2264</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>2265</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>2266</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>2267</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>2268</v>
       </c>
-      <c r="B38" s="1" t="s">
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1" t="s">
         <v>2269</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>2270</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="30">
-      <c r="A39" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>2271</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>2272</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>2273</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>2274</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>2275</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>2276</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
+        <v>2275</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>2276</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>2277</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>2278</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>2279</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>2280</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>2281</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>2282</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2539</v>
+        <v>2536</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>2284</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>2285</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>2286</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>2287</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
-        <v>2288</v>
+        <v>2286</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>1889</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>2290</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>2291</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>2292</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>2293</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>2294</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>2295</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>2296</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>2297</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>2298</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
+        <v>2297</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>2298</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>2299</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>2300</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>2301</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1" t="s">
-        <v>2302</v>
+        <v>2300</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>2096</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>2303</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>2303</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>2304</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>2305</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>2306</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
+        <v>2305</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>2306</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>2307</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>2308</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>2309</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>2309</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>2310</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>2311</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>2312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>2313</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>2314</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>2315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1" t="s">
+        <v>2314</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>2315</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>2316</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>2317</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>2318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>2319</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>2320</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>2321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>2321</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>2322</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>2323</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>2324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>2325</v>
+        <v>2323</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>2093</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>2326</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>2327</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>2328</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>2329</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1" t="s">
+        <v>2330</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>2331</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>2332</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>2333</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>2334</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="1" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>2335</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>2336</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>2337</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="1" t="s">
+        <v>2336</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>2337</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>2338</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>2339</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>2340</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>2341</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>2342</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>2343</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>2019</v>
@@ -29515,13 +29573,13 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>2542</v>
+        <v>2574</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
     </row>
   </sheetData>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5216" uniqueCount="2576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5225" uniqueCount="2577">
   <si>
     <t>part_used</t>
   </si>
@@ -7604,9 +7604,6 @@
     <t>DINYALAKAN|MENYALA</t>
   </si>
   <si>
-    <t>AFDA</t>
-  </si>
-  <si>
     <t>ADA</t>
   </si>
   <si>
@@ -7764,6 +7761,12 @@
   </si>
   <si>
     <t>ganti|replace|ir|sensor|LED IR</t>
+  </si>
+  <si>
+    <t>REPAIR_SHEET</t>
+  </si>
+  <si>
+    <t>AFDA|AADA</t>
   </si>
 </sst>
 </file>
@@ -22906,7 +22909,7 @@
     </row>
     <row r="1835" spans="1:2">
       <c r="A1835" s="6" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="B1835" s="1" t="s">
         <v>459</v>
@@ -22914,7 +22917,7 @@
     </row>
     <row r="1836" spans="1:2">
       <c r="A1836" s="6" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="B1836" s="7" t="s">
         <v>459</v>
@@ -22922,7 +22925,7 @@
     </row>
     <row r="1837" spans="1:2">
       <c r="A1837" s="6" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="B1837" s="1" t="s">
         <v>1826</v>
@@ -22930,7 +22933,7 @@
     </row>
     <row r="1838" spans="1:2">
       <c r="A1838" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="B1838" s="7" t="s">
         <v>1429</v>
@@ -22938,7 +22941,7 @@
     </row>
     <row r="1839" spans="1:2">
       <c r="A1839" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>214</v>
@@ -22946,7 +22949,7 @@
     </row>
     <row r="1840" spans="1:2">
       <c r="A1840" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="B1840" s="7" t="s">
         <v>964</v>
@@ -22954,7 +22957,7 @@
     </row>
     <row r="1841" spans="1:2">
       <c r="A1841" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="B1841" s="7" t="s">
         <v>964</v>
@@ -22984,18 +22987,18 @@
         <v>1941</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="10" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>1961</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -23094,7 +23097,7 @@
         <v>1961</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -23105,7 +23108,7 @@
         <v>1961</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>2568</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -23253,7 +23256,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="10" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>1961</v>
@@ -24111,13 +24114,13 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="10" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="B104" s="14" t="s">
         <v>1961</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -24133,13 +24136,13 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="10" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="B106" s="14" t="s">
         <v>1961</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -24166,13 +24169,13 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="10" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="B109" s="14" t="s">
         <v>1961</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -24210,7 +24213,7 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="10" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
       <c r="B113" s="14" t="s">
         <v>1961</v>
@@ -24265,7 +24268,7 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="10" t="s">
-        <v>2563</v>
+        <v>2562</v>
       </c>
       <c r="B118" s="14" t="s">
         <v>1961</v>
@@ -24287,13 +24290,13 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="10" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="B120" s="14" t="s">
         <v>1961</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -24437,7 +24440,7 @@
         <v>2021</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>2042</v>
@@ -24455,7 +24458,7 @@
         <v>2021</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>2037</v>
@@ -24473,7 +24476,7 @@
         <v>2021</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>2041</v>
@@ -24589,7 +24592,7 @@
         <v>2021</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>2055</v>
@@ -24609,7 +24612,7 @@
         <v>2021</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>2045</v>
@@ -24822,7 +24825,7 @@
         <v>2021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>2042</v>
@@ -24880,7 +24883,7 @@
         <v>2021</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>2037</v>
@@ -24920,7 +24923,7 @@
         <v>2021</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>2024</v>
@@ -24960,7 +24963,7 @@
         <v>2021</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>2055</v>
@@ -25078,7 +25081,7 @@
         <v>2021</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>2034</v>
@@ -25116,7 +25119,7 @@
         <v>2021</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>2515</v>
@@ -25234,7 +25237,7 @@
         <v>2021</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>2032</v>
@@ -25294,7 +25297,7 @@
         <v>2021</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>2025</v>
@@ -25391,7 +25394,7 @@
         <v>2021</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>2034</v>
@@ -25731,7 +25734,7 @@
         <v>2021</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>2515</v>
@@ -25870,7 +25873,7 @@
         <v>2021</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>2042</v>
@@ -25888,7 +25891,7 @@
         <v>2021</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>2042</v>
@@ -25920,7 +25923,7 @@
         <v>2021</v>
       </c>
       <c r="D83" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>2422</v>
@@ -25953,7 +25956,7 @@
         <v>2021</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>2041</v>
@@ -25971,7 +25974,7 @@
         <v>2021</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>2041</v>
@@ -26025,7 +26028,7 @@
         <v>2021</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>2055</v>
@@ -26130,7 +26133,7 @@
         <v>2021</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>2034</v>
@@ -26638,7 +26641,7 @@
         <v>2057</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>2089</v>
@@ -26958,7 +26961,7 @@
         <v>2057</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>2112</v>
@@ -27511,7 +27514,7 @@
         <v>2057</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
@@ -27910,7 +27913,7 @@
         <v>2057</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>2096</v>
@@ -27950,7 +27953,7 @@
         <v>2057</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>2181</v>
@@ -28049,7 +28052,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -28655,6 +28658,39 @@
         <v>964</v>
       </c>
       <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="6" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>964</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D43"/>
@@ -28689,7 +28725,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2035</v>
@@ -28731,7 +28767,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>2514</v>
@@ -28799,10 +28835,10 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
+        <v>2576</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>2522</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>2523</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2019</v>
@@ -28823,7 +28859,7 @@
         <v>2205</v>
       </c>
       <c r="F11" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -28852,10 +28888,10 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
+        <v>2531</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>2532</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>2533</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>2232</v>
@@ -29100,7 +29136,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>2252</v>
@@ -29254,7 +29290,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>2281</v>
@@ -29573,7 +29609,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>2181</v>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -29,14 +29,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">factory!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">panel_usage!$A$1:$B$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">part_list!$A$1:$B$1834</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">symptom!$A$1:$F$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">symptom!$A$1:$F$97</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5225" uniqueCount="2577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5288" uniqueCount="2590">
   <si>
     <t>part_used</t>
   </si>
@@ -7220,9 +7220,6 @@
     <t>Sample blank-part power/no-power cases.</t>
   </si>
   <si>
-    <t>layar kotor|kotor|semut</t>
-  </si>
-  <si>
     <t>Sample TAPE dirty/contaminated display case.</t>
   </si>
   <si>
@@ -7700,9 +7697,6 @@
     <t>L99|LAYAR KUNING|LAYAR ERROR|GERAKAN LAMBAT|Z99|LAYAR TIDAK BAGUS</t>
   </si>
   <si>
-    <t>LED KEDIP2|BERKEDIP|Kedip merah|REDUP SEBELAH|MERAH</t>
-  </si>
-  <si>
     <t>BERGARIS|Tampilan tidak normal|KUNING</t>
   </si>
   <si>
@@ -7767,6 +7761,51 @@
   </si>
   <si>
     <t>AFDA|AADA</t>
+  </si>
+  <si>
+    <t>4TC50AL1X</t>
+  </si>
+  <si>
+    <t>4TC50FL1X</t>
+  </si>
+  <si>
+    <t>4TC60AL1X</t>
+  </si>
+  <si>
+    <t>4TC75FK1X</t>
+  </si>
+  <si>
+    <t>8TC60DW1X</t>
+  </si>
+  <si>
+    <t>LC50SA5200X</t>
+  </si>
+  <si>
+    <t>LC50UE630X</t>
+  </si>
+  <si>
+    <t>LC60LE631M</t>
+  </si>
+  <si>
+    <t>GAMBAR TIDAK STABIL</t>
+  </si>
+  <si>
+    <t>LED KEDIP2|BERKEDIP|Kedip merah|REDUP SEBELAH|MERAH|REDUP</t>
+  </si>
+  <si>
+    <t>Z99</t>
+  </si>
+  <si>
+    <t>layar kotor|kotor|semut|GAMBAR TIDAK BAGUS</t>
+  </si>
+  <si>
+    <t>garis|line|vertical|horizontal|stripe|strip|baris|bergaris</t>
+  </si>
+  <si>
+    <t>25Q32STB/-L</t>
+  </si>
+  <si>
+    <t>30446005652+</t>
   </si>
 </sst>
 </file>
@@ -8228,7 +8267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1841"/>
+  <dimension ref="A1:B1843"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -22909,7 +22948,7 @@
     </row>
     <row r="1835" spans="1:2">
       <c r="A1835" s="6" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="B1835" s="1" t="s">
         <v>459</v>
@@ -22917,7 +22956,7 @@
     </row>
     <row r="1836" spans="1:2">
       <c r="A1836" s="6" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="B1836" s="7" t="s">
         <v>459</v>
@@ -22925,7 +22964,7 @@
     </row>
     <row r="1837" spans="1:2">
       <c r="A1837" s="6" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="B1837" s="1" t="s">
         <v>1826</v>
@@ -22933,7 +22972,7 @@
     </row>
     <row r="1838" spans="1:2">
       <c r="A1838" t="s">
-        <v>2568</v>
+        <v>2566</v>
       </c>
       <c r="B1838" s="7" t="s">
         <v>1429</v>
@@ -22941,7 +22980,7 @@
     </row>
     <row r="1839" spans="1:2">
       <c r="A1839" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>214</v>
@@ -22949,7 +22988,7 @@
     </row>
     <row r="1840" spans="1:2">
       <c r="A1840" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="B1840" s="7" t="s">
         <v>964</v>
@@ -22957,10 +22996,26 @@
     </row>
     <row r="1841" spans="1:2">
       <c r="A1841" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
       <c r="B1841" s="7" t="s">
         <v>964</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:2">
+      <c r="A1842" s="6" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B1842" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:2">
+      <c r="A1843" s="6" t="s">
+        <v>2589</v>
+      </c>
+      <c r="B1843" s="7" t="s">
+        <v>1875</v>
       </c>
     </row>
   </sheetData>
@@ -22971,7 +23026,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -22987,18 +23042,18 @@
         <v>1941</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="10" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>1961</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -23097,7 +23152,7 @@
         <v>1961</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -23108,7 +23163,7 @@
         <v>1961</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>2567</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -23256,7 +23311,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="10" t="s">
-        <v>2557</v>
+        <v>2555</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>1961</v>
@@ -23399,24 +23454,24 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="12" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="12" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -23509,13 +23564,13 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="12" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -23542,13 +23597,13 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="12" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -23564,13 +23619,13 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="12" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -23608,24 +23663,24 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="12" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="12" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -23641,35 +23696,35 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="12" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="12" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="12" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -23707,101 +23762,101 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="12" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="12" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="12" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="12" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="12" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="12" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="12" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="12" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="12" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -23817,46 +23872,46 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="12" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="12" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="12" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="12" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -23883,101 +23938,101 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="12" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>1943</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="12" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>1943</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="12" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="12" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="12" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="12" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="12" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="12" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="12" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -23993,24 +24048,24 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="12" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="15" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -24026,13 +24081,13 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="12" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>1943</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -24048,57 +24103,57 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="12" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="B98" s="14" t="s">
         <v>1943</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="12" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="B99" s="14" t="s">
         <v>1943</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="15" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="B100" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="12" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="B101" s="14" t="s">
         <v>1943</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="12" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -24114,13 +24169,13 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="10" t="s">
-        <v>2558</v>
+        <v>2556</v>
       </c>
       <c r="B104" s="14" t="s">
         <v>1961</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>2558</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -24136,13 +24191,13 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="10" t="s">
-        <v>2559</v>
+        <v>2557</v>
       </c>
       <c r="B106" s="14" t="s">
         <v>1961</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>2559</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -24169,24 +24224,24 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="10" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
       <c r="B109" s="14" t="s">
         <v>1961</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="12" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -24213,7 +24268,7 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="10" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
       <c r="B113" s="14" t="s">
         <v>1961</v>
@@ -24268,7 +24323,7 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="10" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="B118" s="14" t="s">
         <v>1961</v>
@@ -24279,24 +24334,24 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="12" t="s">
+        <v>2483</v>
+      </c>
+      <c r="B119" s="14" t="s">
         <v>2484</v>
       </c>
-      <c r="B119" s="14" t="s">
-        <v>2485</v>
-      </c>
       <c r="C119" s="12" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="10" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
       <c r="B120" s="14" t="s">
         <v>1961</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -24308,6 +24363,94 @@
       </c>
       <c r="C121" s="14" t="s">
         <v>2012</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="6" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>2484</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="6" t="s">
+        <v>2576</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>2484</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="6" t="s">
+        <v>2577</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>2484</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="6" t="s">
+        <v>2578</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>2484</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="6" t="s">
+        <v>2579</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>2484</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="6" t="s">
+        <v>2580</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>2484</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="6" t="s">
+        <v>2581</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>2484</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="6" t="s">
+        <v>2582</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>2484</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>2582</v>
       </c>
     </row>
   </sheetData>
@@ -24323,7 +24466,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -24365,7 +24508,7 @@
         <v>2021</v>
       </c>
       <c r="D2" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>2088</v>
@@ -24393,7 +24536,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="B4" t="s">
         <v>90</v>
@@ -24402,16 +24545,18 @@
         <v>2021</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2190</v>
+        <v>2357</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>2024</v>
-      </c>
-      <c r="F4" s="3"/>
+        <v>2034</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>2036</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="B5" t="s">
         <v>90</v>
@@ -24420,48 +24565,46 @@
         <v>2021</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2357</v>
+        <v>2190</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>2034</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>2036</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3">
-        <v>401</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>109</v>
+        <v>651</v>
+      </c>
+      <c r="B6" t="s">
+        <v>90</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2539</v>
+        <v>2583</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>2042</v>
+        <v>2055</v>
       </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3">
-        <v>402</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>109</v>
+        <v>652</v>
+      </c>
+      <c r="B7" t="s">
+        <v>107</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2540</v>
+        <v>2486</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>2037</v>
+        <v>2024</v>
       </c>
       <c r="F7" s="3"/>
     </row>
@@ -24476,7 +24619,7 @@
         <v>2021</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>2041</v>
@@ -24485,7 +24628,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>109</v>
@@ -24494,111 +24637,107 @@
         <v>2021</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2487</v>
+        <v>2538</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>2024</v>
+        <v>2042</v>
       </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2362</v>
+        <v>2539</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>2047</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>2061</v>
-      </c>
+        <v>2037</v>
+      </c>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3">
-        <v>660</v>
-      </c>
-      <c r="B11" t="s">
-        <v>128</v>
+        <v>403</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2357</v>
+        <v>2486</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>2034</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>2036</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>214</v>
+        <v>128</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2344</v>
+        <v>2362</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>2023</v>
+        <v>2047</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>2345</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3">
-        <v>30</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>214</v>
+        <v>660</v>
+      </c>
+      <c r="B13" t="s">
+        <v>128</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2342</v>
+        <v>2357</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>2022</v>
+        <v>2034</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>2343</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3">
-        <v>770</v>
-      </c>
-      <c r="B14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>214</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2554</v>
+        <v>2342</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>2055</v>
+        <v>2022</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>2366</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -24612,7 +24751,7 @@
         <v>2021</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>2045</v>
@@ -24623,7 +24762,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3">
-        <v>340</v>
+        <v>60</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>214</v>
@@ -24632,95 +24771,95 @@
         <v>2021</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2355</v>
+        <v>2344</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>2035</v>
+        <v>2023</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>2366</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3">
-        <v>670</v>
-      </c>
-      <c r="B17" t="s">
+        <v>340</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>214</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>2036</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3">
-        <v>780</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>322</v>
+        <v>670</v>
+      </c>
+      <c r="B18" t="s">
+        <v>214</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D18" t="s">
-        <v>2418</v>
+      <c r="D18" s="3" t="s">
+        <v>2357</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>2047</v>
+        <v>2034</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>2036</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3">
-        <v>330</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>345</v>
+        <v>770</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>214</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2030</v>
+        <v>2584</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>2031</v>
+        <v>2055</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>2060</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3">
-        <v>20</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>345</v>
+        <v>780</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>322</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>2342</v>
+      <c r="D20" t="s">
+        <v>2417</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>2022</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>2343</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>345</v>
@@ -24729,76 +24868,78 @@
         <v>2021</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3">
-        <v>680</v>
-      </c>
-      <c r="B22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>345</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2357</v>
+        <v>2344</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>2034</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>2036</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3">
-        <v>222</v>
+        <v>330</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>459</v>
+        <v>345</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2517</v>
+        <v>2030</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>2518</v>
-      </c>
-      <c r="F23" s="3"/>
+        <v>2031</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>2060</v>
+      </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3">
-        <v>280</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>459</v>
+        <v>680</v>
+      </c>
+      <c r="B24" t="s">
+        <v>345</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>2052</v>
+        <v>2357</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>2053</v>
+        <v>2034</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>2054</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>459</v>
@@ -24807,16 +24948,18 @@
         <v>2021</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2513</v>
+        <v>2355</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>2506</v>
-      </c>
-      <c r="F25" s="3"/>
+        <v>2035</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>2356</v>
+      </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="3">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>459</v>
@@ -24825,18 +24968,18 @@
         <v>2021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2541</v>
+        <v>2518</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>2042</v>
+        <v>2034</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>2043</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>459</v>
@@ -24844,19 +24987,19 @@
       <c r="C27" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>2038</v>
+      <c r="D27" s="5" t="s">
+        <v>2524</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>2040</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3">
-        <v>810</v>
+        <v>200</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>459</v>
@@ -24864,17 +25007,19 @@
       <c r="C28" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D28" t="s">
-        <v>2489</v>
+      <c r="D28" s="3" t="s">
+        <v>2549</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>2422</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>2037</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>2358</v>
+      </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>459</v>
@@ -24883,13 +25028,13 @@
         <v>2021</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>2550</v>
+        <v>2038</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>2358</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -24914,7 +25059,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="3">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>459</v>
@@ -24923,18 +25068,16 @@
         <v>2021</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>2549</v>
+        <v>2523</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>2024</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>2361</v>
-      </c>
+        <v>2514</v>
+      </c>
+      <c r="F31" s="3"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="3">
-        <v>290</v>
+        <v>222</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>459</v>
@@ -24943,18 +25086,16 @@
         <v>2021</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2490</v>
+        <v>2516</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>2055</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>2056</v>
-      </c>
+        <v>2517</v>
+      </c>
+      <c r="F32" s="3"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="3">
-        <v>291</v>
+        <v>230</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>459</v>
@@ -24963,16 +25104,18 @@
         <v>2021</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>2555</v>
+        <v>2548</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>2055</v>
-      </c>
-      <c r="F33" s="3"/>
+        <v>2024</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>2361</v>
+      </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="3">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>459</v>
@@ -24981,18 +25124,16 @@
         <v>2021</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>2044</v>
+        <v>2512</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>2045</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>2046</v>
-      </c>
+        <v>2505</v>
+      </c>
+      <c r="F34" s="3"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>459</v>
@@ -25001,18 +25142,18 @@
         <v>2021</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>2362</v>
+        <v>2540</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>459</v>
@@ -25021,18 +25162,18 @@
         <v>2021</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>2051</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="3">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>459</v>
@@ -25041,18 +25182,18 @@
         <v>2021</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>2355</v>
+        <v>2362</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>2035</v>
+        <v>2047</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>2356</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="3">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>459</v>
@@ -25061,18 +25202,18 @@
         <v>2021</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>2519</v>
+        <v>2049</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>2034</v>
+        <v>2050</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>2036</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="3">
-        <v>191</v>
+        <v>280</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>459</v>
@@ -25080,37 +25221,39 @@
       <c r="C39" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>2525</v>
+      <c r="D39" s="3" t="s">
+        <v>2052</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>2034</v>
+        <v>2053</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>2036</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="3">
-        <v>790</v>
-      </c>
-      <c r="B40" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>459</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>2420</v>
+        <v>2489</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>2421</v>
-      </c>
-      <c r="F40" s="3"/>
+        <v>2055</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>2056</v>
+      </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="3">
-        <v>221</v>
+        <v>291</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>459</v>
@@ -25119,56 +25262,52 @@
         <v>2021</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>2524</v>
+        <v>2553</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>2515</v>
+        <v>2055</v>
       </c>
       <c r="F41" s="3"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="3">
-        <v>50</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>989</v>
+        <v>790</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>459</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>2492</v>
+        <v>2419</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>2023</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>2345</v>
-      </c>
+        <v>2420</v>
+      </c>
+      <c r="F42" s="3"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="3">
-        <v>90</v>
+        <v>810</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>989</v>
+        <v>459</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>2510</v>
+      <c r="D43" t="s">
+        <v>2488</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>2023</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>2346</v>
-      </c>
+        <v>2421</v>
+      </c>
+      <c r="F43" s="3"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="3">
-        <v>170</v>
+        <v>10</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>989</v>
@@ -25177,18 +25316,18 @@
         <v>2021</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>2353</v>
+        <v>2342</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>2354</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="3">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>989</v>
@@ -25197,18 +25336,18 @@
         <v>2021</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>2030</v>
+        <v>2491</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>2031</v>
+        <v>2023</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>2351</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>989</v>
@@ -25217,18 +25356,18 @@
         <v>2021</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2491</v>
+        <v>2509</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>2348</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>989</v>
@@ -25237,18 +25376,18 @@
         <v>2021</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>2544</v>
+        <v>2507</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>2032</v>
+        <v>2025</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>2033</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3">
-        <v>740</v>
+        <v>101</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>989</v>
@@ -25257,18 +25396,18 @@
         <v>2021</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>2505</v>
+        <v>2552</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>2506</v>
+        <v>2025</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>2354</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>989</v>
@@ -25277,18 +25416,18 @@
         <v>2021</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>2508</v>
+        <v>2490</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="3">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>989</v>
@@ -25297,18 +25436,18 @@
         <v>2021</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>2553</v>
+        <v>2027</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="3">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>989</v>
@@ -25317,18 +25456,18 @@
         <v>2021</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>2027</v>
+        <v>2503</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="3">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>989</v>
@@ -25337,18 +25476,18 @@
         <v>2021</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>2504</v>
+        <v>2030</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="3">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>989</v>
@@ -25357,35 +25496,38 @@
         <v>2021</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>2342</v>
+        <v>2543</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>2022</v>
+        <v>2032</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>2343</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="3">
-        <v>730</v>
-      </c>
-      <c r="B54" t="s">
+        <v>160</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>989</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D54" t="s">
-        <v>2507</v>
+      <c r="D54" s="3" t="s">
+        <v>2525</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>2412</v>
+        <v>2034</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>2352</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="3">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>989</v>
@@ -25394,81 +25536,78 @@
         <v>2021</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>2526</v>
+        <v>2353</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>2034</v>
+        <v>2023</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="3">
-        <v>690</v>
+        <v>730</v>
       </c>
       <c r="B56" t="s">
-        <v>1398</v>
+        <v>989</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>2057</v>
+      <c r="D56" t="s">
+        <v>2506</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>2034</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>2036</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="3">
-        <v>300</v>
+        <v>740</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1429</v>
+        <v>989</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>2057</v>
+        <v>2504</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>2034</v>
+        <v>2505</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>2363</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="3">
-        <v>310</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>1660</v>
+        <v>690</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1398</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>2364</v>
+        <v>2057</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>2058</v>
+        <v>2034</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>2059</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="3">
-        <v>700</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1660</v>
+        <v>300</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>1429</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>2021</v>
@@ -25477,155 +25616,149 @@
         <v>2057</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>2415</v>
+        <v>2034</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>2036</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="3">
-        <v>320</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>1732</v>
+        <v>820</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1655</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>2057</v>
+        <v>2486</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>2050</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>2365</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="3">
-        <v>380</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>1811</v>
+        <v>821</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1655</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>2062</v>
+      <c r="D61" t="s">
+        <v>2512</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>2053</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>2063</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="3">
-        <v>630</v>
+        <v>310</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>1811</v>
+        <v>1660</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>2409</v>
+        <v>2364</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>2041</v>
+        <v>2058</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>2410</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="3">
-        <v>550</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>1816</v>
+        <v>700</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1660</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>2396</v>
+        <v>2057</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>2026</v>
+        <v>2414</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>2397</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="3">
-        <v>560</v>
+        <v>320</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>1816</v>
+        <v>1732</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>2398</v>
+        <v>2057</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>2032</v>
+        <v>2050</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>2399</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="3">
-        <v>540</v>
+        <v>380</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1816</v>
+        <v>1811</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>2394</v>
+        <v>2062</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>2025</v>
+        <v>2053</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>2395</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="3">
-        <v>40</v>
+        <v>630</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>1816</v>
+        <v>1811</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>2342</v>
+        <v>2408</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>2022</v>
+        <v>2041</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>2343</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="3">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>1816</v>
@@ -25634,18 +25767,18 @@
         <v>2021</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="3">
-        <v>620</v>
+        <v>80</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>1816</v>
@@ -25654,532 +25787,690 @@
         <v>2021</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>2407</v>
+        <v>2344</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>2034</v>
+        <v>2024</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>2408</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="3">
-        <v>350</v>
+        <v>111</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1826</v>
+        <v>1816</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>2367</v>
+        <v>2490</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>2055</v>
+        <v>2026</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>2368</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="3">
-        <v>351</v>
+        <v>540</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>1826</v>
+        <v>1816</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>2514</v>
+        <v>2586</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>2034</v>
+        <v>2025</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>2368</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="3">
-        <v>370</v>
+        <v>550</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>1889</v>
+        <v>1816</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>2369</v>
+        <v>2395</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>2041</v>
+        <v>2026</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>2370</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="3">
-        <v>222</v>
+        <v>560</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>1902</v>
+        <v>1816</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>2524</v>
+        <v>2397</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>2515</v>
+        <v>2032</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>2398</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="3">
-        <v>440</v>
-      </c>
-      <c r="B73" s="3"/>
+        <v>620</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C73" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>2375</v>
+        <v>2406</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>2376</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="3">
-        <v>222</v>
-      </c>
-      <c r="B74" s="3"/>
+        <v>621</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C74" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2517</v>
+        <v>2585</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>2518</v>
+        <v>2025</v>
       </c>
       <c r="F74" s="3"/>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="3">
-        <v>510</v>
-      </c>
-      <c r="B75" s="3"/>
+        <v>350</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>1826</v>
+      </c>
       <c r="C75" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>2388</v>
+        <v>2367</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>2032</v>
+        <v>2055</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>2389</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="3">
-        <v>520</v>
-      </c>
-      <c r="B76" s="3"/>
+        <v>351</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>1826</v>
+      </c>
       <c r="C76" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>2390</v>
+        <v>2513</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>2053</v>
+        <v>2034</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>2391</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="3">
-        <v>490</v>
-      </c>
-      <c r="B77" s="3"/>
+        <v>352</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>1875</v>
+      </c>
       <c r="C77" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>2384</v>
+        <v>2344</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>2385</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="3">
-        <v>580</v>
-      </c>
-      <c r="B78" s="3"/>
+        <v>353</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>1875</v>
+      </c>
       <c r="C78" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>2402</v>
+        <v>2587</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>2403</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="3">
-        <v>500</v>
-      </c>
-      <c r="B79" s="3"/>
+        <v>370</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>1889</v>
+      </c>
       <c r="C79" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>2386</v>
+        <v>2369</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>2028</v>
+        <v>2041</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>2387</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="3">
-        <v>470</v>
-      </c>
-      <c r="B80" s="3"/>
+        <v>222</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>1902</v>
+      </c>
       <c r="C80" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>2545</v>
+        <v>2523</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>2042</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>2381</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="3">
-        <v>471</v>
+        <v>222</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>2541</v>
+        <v>2516</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>2042</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>2381</v>
-      </c>
+        <v>2517</v>
+      </c>
+      <c r="F81" s="3"/>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="3">
-        <v>720</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="B82" s="3"/>
       <c r="C82" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>2038</v>
+        <v>2371</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>2039</v>
-      </c>
-      <c r="F82" s="3"/>
+        <v>2022</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>2372</v>
+      </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="3">
-        <v>800</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="B83" s="3"/>
       <c r="C83" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D83" t="s">
-        <v>2548</v>
+      <c r="D83" s="3" t="s">
+        <v>2486</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>2422</v>
+        <v>2024</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>2373</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="3">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>2371</v>
+        <v>2545</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>2022</v>
+        <v>2041</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="3">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>2546</v>
+        <v>2375</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>2041</v>
+        <v>2031</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>2374</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="3">
-        <v>610</v>
+        <v>450</v>
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>2542</v>
+        <v>2377</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>2041</v>
+        <v>2058</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>2406</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="3">
-        <v>420</v>
-      </c>
-      <c r="B87" s="3"/>
+        <v>460</v>
+      </c>
+      <c r="B87" s="4"/>
       <c r="C87" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>2487</v>
+        <v>2379</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>2024</v>
+        <v>2050</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>2373</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="3">
-        <v>570</v>
+        <v>470</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>2400</v>
+        <v>2544</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>2024</v>
+        <v>2042</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>2401</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="3">
-        <v>600</v>
+        <v>471</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>2543</v>
+        <v>2540</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>2055</v>
+        <v>2042</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>2405</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="3">
-        <v>760</v>
+        <v>480</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>2414</v>
+        <v>2382</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>2055</v>
+        <v>2035</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>2383</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="3">
-        <v>450</v>
+        <v>490</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>2377</v>
+        <v>2384</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>2058</v>
+        <v>2025</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>2378</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="3">
-        <v>460</v>
-      </c>
-      <c r="B92" s="13"/>
+        <v>500</v>
+      </c>
+      <c r="B92" s="3"/>
       <c r="C92" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>2379</v>
+        <v>2386</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>2050</v>
+        <v>2028</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>2380</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="3">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>2382</v>
+        <v>2388</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>2035</v>
+        <v>2032</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>2383</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="3">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="B94" s="3"/>
       <c r="C94" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>2034</v>
+        <v>2053</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="3">
-        <v>590</v>
+        <v>530</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>2547</v>
+        <v>2392</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>2404</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="3">
-        <v>710</v>
-      </c>
-      <c r="B96" s="12"/>
+        <v>570</v>
+      </c>
+      <c r="B96" s="3"/>
       <c r="C96" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>2357</v>
+        <v>2399</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>2034</v>
+        <v>2024</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>2036</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="3">
-        <v>791</v>
-      </c>
-      <c r="B97" s="4"/>
+        <v>580</v>
+      </c>
+      <c r="B97" s="3"/>
       <c r="C97" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D97" s="3" t="s">
+        <v>2401</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>2025</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="3">
+        <v>590</v>
+      </c>
+      <c r="B98" s="13"/>
+      <c r="C98" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>2546</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="3">
+        <v>600</v>
+      </c>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>2542</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>2055</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="3">
+        <v>610</v>
+      </c>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>2041</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="3">
+        <v>710</v>
+      </c>
+      <c r="B101" s="12"/>
+      <c r="C101" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>2357</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="3">
+        <v>720</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>2039</v>
+      </c>
+      <c r="F102" s="3"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" s="3">
+        <v>760</v>
+      </c>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>2413</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="3">
+        <v>791</v>
+      </c>
+      <c r="B104" s="4"/>
+      <c r="C104" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>2419</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>2420</v>
       </c>
-      <c r="E97" s="3" t="s">
+      <c r="F104" s="3"/>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="3">
+        <v>800</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D105" t="s">
+        <v>2547</v>
+      </c>
+      <c r="E105" s="3" t="s">
         <v>2421</v>
       </c>
-      <c r="F97" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F91">
-    <sortState ref="A2:F97">
-      <sortCondition ref="B1:B91"/>
+  <autoFilter ref="A1:F97">
+    <sortState ref="A2:F102">
+      <sortCondition ref="B1:B94"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26331,7 +26622,7 @@
         <v>2057</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>2085</v>
@@ -26351,7 +26642,7 @@
         <v>2057</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>2085</v>
@@ -26371,7 +26662,7 @@
         <v>2057</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>2085</v>
@@ -26391,7 +26682,7 @@
         <v>2057</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>2085</v>
@@ -26408,7 +26699,7 @@
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>2057</v>
@@ -26431,7 +26722,7 @@
         <v>2057</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>2085</v>
@@ -26451,7 +26742,7 @@
         <v>2057</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>2087</v>
@@ -26468,7 +26759,7 @@
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>2057</v>
@@ -26490,7 +26781,7 @@
         <v>2057</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>2057</v>
@@ -26513,7 +26804,7 @@
         <v>2057</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>2085</v>
@@ -26535,7 +26826,7 @@
         <v>2057</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>2085</v>
@@ -26599,7 +26890,7 @@
         <v>2057</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>2088</v>
@@ -26621,7 +26912,7 @@
         <v>2057</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>2088</v>
@@ -26641,7 +26932,7 @@
         <v>2057</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>2089</v>
@@ -26721,7 +27012,7 @@
         <v>2057</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>2096</v>
@@ -26829,7 +27120,7 @@
         <v>2057</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>2085</v>
@@ -26961,7 +27252,7 @@
         <v>2057</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>2574</v>
+        <v>2572</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>2112</v>
@@ -27071,7 +27362,7 @@
         <v>2057</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>2119</v>
@@ -27514,7 +27805,7 @@
         <v>2057</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
@@ -27553,7 +27844,7 @@
         <v>2057</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>2123</v>
@@ -27573,7 +27864,7 @@
         <v>2057</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>2119</v>
@@ -27593,7 +27884,7 @@
         <v>2057</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>2121</v>
@@ -27613,7 +27904,7 @@
         <v>2057</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>2119</v>
@@ -27633,7 +27924,7 @@
         <v>2057</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>2121</v>
@@ -27653,7 +27944,7 @@
         <v>2057</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>2119</v>
@@ -27673,7 +27964,7 @@
         <v>2057</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>2125</v>
@@ -27693,7 +27984,7 @@
         <v>2057</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>2127</v>
@@ -27713,7 +28004,7 @@
         <v>2057</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>2150</v>
@@ -27730,7 +28021,7 @@
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>2057</v>
@@ -27753,7 +28044,7 @@
         <v>2057</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>2121</v>
@@ -27773,7 +28064,7 @@
         <v>2057</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>2119</v>
@@ -27793,10 +28084,10 @@
         <v>2057</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>2436</v>
+      </c>
+      <c r="F71" s="9" t="s">
         <v>2437</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>2438</v>
       </c>
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
@@ -27810,7 +28101,7 @@
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>2057</v>
@@ -27833,7 +28124,7 @@
         <v>2057</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>2123</v>
@@ -27853,7 +28144,7 @@
         <v>2057</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>2118</v>
@@ -27873,7 +28164,7 @@
         <v>2057</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>2088</v>
@@ -27893,7 +28184,7 @@
         <v>2057</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>2125</v>
@@ -27913,7 +28204,7 @@
         <v>2057</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>2096</v>
@@ -27933,7 +28224,7 @@
         <v>2057</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>2095</v>
@@ -27953,7 +28244,7 @@
         <v>2057</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>2181</v>
@@ -27973,7 +28264,7 @@
         <v>2057</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>2088</v>
@@ -28661,7 +28952,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>2137</v>
@@ -28672,7 +28963,7 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>2137</v>
@@ -28725,7 +29016,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2035</v>
@@ -28753,7 +29044,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2192</v>
@@ -28767,10 +29058,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2019</v>
@@ -28793,7 +29084,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>2197</v>
@@ -28807,7 +29098,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>2199</v>
@@ -28835,10 +29126,10 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2019</v>
@@ -28859,15 +29150,15 @@
         <v>2205</v>
       </c>
       <c r="F11" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>2019</v>
@@ -28876,10 +29167,10 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>2501</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>2502</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>2503</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>2019</v>
@@ -28888,10 +29179,10 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
+        <v>2530</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>2531</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>2532</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>2232</v>
@@ -28914,10 +29205,10 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
+        <v>2510</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>2511</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>2512</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2019</v>
@@ -28982,7 +29273,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>2023</v>
@@ -29136,7 +29427,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>2252</v>
@@ -29290,7 +29581,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>2281</v>
@@ -29528,7 +29819,7 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>2328</v>
@@ -29598,10 +29889,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>2416</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>2417</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>2019</v>
@@ -29609,7 +29900,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>2181</v>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ARISAFARI\Works\Project Applications\tool-fcost\masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\kerjaan\Monitoring\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4016BA-9BC7-457A-B779-4CE056387507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -25,18 +26,18 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">action!$A$1:$F$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">branch!$A$1:$B$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">comment_synonyms!$A$1:$D$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">defect_category!$A$1:$D$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">defect_category!$A$1:$D$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">factory!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">panel_usage!$A$1:$B$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">part_list!$A$1:$B$1834</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">symptom!$A$1:$F$97</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5288" uniqueCount="2590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5251" uniqueCount="2561">
   <si>
     <t>part_used</t>
   </si>
@@ -6446,150 +6447,51 @@
     <t>NON_DEFECT</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>DEFECT</t>
   </si>
   <si>
     <t>SOFTWARE</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>REINSERT_SOCKET</t>
   </si>
   <si>
-    <t>76</t>
-  </si>
-  <si>
     <t>REINSERT_SPEAKER</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>REINSERT_WIFI_UNIT</t>
   </si>
   <si>
-    <t>73</t>
-  </si>
-  <si>
     <t>REPAIR_IR_UNIT</t>
   </si>
   <si>
-    <t>61</t>
-  </si>
-  <si>
     <t>REPAIR_LED_BAR</t>
   </si>
   <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>REPAIR_LVDS</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
     <t>REPAIR_PANEL</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
     <t>REPAIR_SPEAKER</t>
   </si>
   <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>REPAIR_TCON</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
     <t>REPAIR_WIFI_UNIT</t>
   </si>
   <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>REPLACE_PANEL_BEFORE_CHANGE</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
     <t>REPLACE_TAPE</t>
   </si>
   <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
     <t>REPLACE_WIFI_UNIT</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>SIGNAL</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>SUBTITUSI</t>
   </si>
   <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>VERIFIED_OK</t>
   </si>
   <si>
@@ -7806,12 +7708,24 @@
   </si>
   <si>
     <t>30446005652+</t>
+  </si>
+  <si>
+    <t>REINSERT_PANEL</t>
+  </si>
+  <si>
+    <t>FLASH_IC_MEMORY</t>
+  </si>
+  <si>
+    <t>REINSERT_LVDS_WIRE</t>
+  </si>
+  <si>
+    <t>REPAIR_LVDS_WIRE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="12">
     <font>
       <sz val="11"/>
@@ -7940,7 +7854,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7951,45 +7865,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10 3 14" xfId="7"/>
-    <cellStyle name="Normal 13 2 2 10 2 2 5 2 2 2 2" xfId="3"/>
-    <cellStyle name="Normal 13 2 2 2" xfId="4"/>
-    <cellStyle name="Normal 133 2 2" xfId="6"/>
-    <cellStyle name="Normal 195" xfId="8"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 2" xfId="10"/>
-    <cellStyle name="Normal 2 2 7 2 2 2" xfId="5"/>
-    <cellStyle name="Normal 315" xfId="9"/>
-    <cellStyle name="Normal 80" xfId="1"/>
+    <cellStyle name="Normal 10 3 14" xfId="7" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 13 2 2 10 2 2 5 2 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 13 2 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 133 2 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 195" xfId="8" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Normal 2 2 7 2 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Normal 315" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Normal 80" xfId="1" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8266,7 +8177,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B1843"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -22947,24 +22858,24 @@
       </c>
     </row>
     <row r="1835" spans="1:2">
-      <c r="A1835" s="6" t="s">
-        <v>2526</v>
+      <c r="A1835" s="5" t="s">
+        <v>2493</v>
       </c>
       <c r="B1835" s="1" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="1836" spans="1:2">
-      <c r="A1836" s="6" t="s">
-        <v>2527</v>
-      </c>
-      <c r="B1836" s="7" t="s">
+      <c r="A1836" s="5" t="s">
+        <v>2494</v>
+      </c>
+      <c r="B1836" s="1" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="1837" spans="1:2">
-      <c r="A1837" s="6" t="s">
-        <v>2528</v>
+      <c r="A1837" s="5" t="s">
+        <v>2495</v>
       </c>
       <c r="B1837" s="1" t="s">
         <v>1826</v>
@@ -22972,60 +22883,60 @@
     </row>
     <row r="1838" spans="1:2">
       <c r="A1838" t="s">
-        <v>2566</v>
-      </c>
-      <c r="B1838" s="7" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B1838" s="1" t="s">
         <v>1429</v>
       </c>
     </row>
     <row r="1839" spans="1:2">
       <c r="A1839" t="s">
-        <v>2567</v>
-      </c>
-      <c r="B1839" s="7" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B1839" s="1" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="1840" spans="1:2">
       <c r="A1840" t="s">
-        <v>2568</v>
-      </c>
-      <c r="B1840" s="7" t="s">
+        <v>2535</v>
+      </c>
+      <c r="B1840" s="1" t="s">
         <v>964</v>
       </c>
     </row>
     <row r="1841" spans="1:2">
       <c r="A1841" t="s">
-        <v>2569</v>
-      </c>
-      <c r="B1841" s="7" t="s">
+        <v>2536</v>
+      </c>
+      <c r="B1841" s="1" t="s">
         <v>964</v>
       </c>
     </row>
     <row r="1842" spans="1:2">
-      <c r="A1842" s="6" t="s">
-        <v>2588</v>
-      </c>
-      <c r="B1842" s="7" t="s">
+      <c r="A1842" s="5" t="s">
+        <v>2555</v>
+      </c>
+      <c r="B1842" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="1843" spans="1:2">
-      <c r="A1843" s="6" t="s">
-        <v>2589</v>
-      </c>
-      <c r="B1843" s="7" t="s">
+      <c r="A1843" s="5" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B1843" s="1" t="s">
         <v>1875</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1834"/>
+  <autoFilter ref="A1:B1834" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -23042,1420 +22953,1420 @@
         <v>1941</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2562</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="10" t="s">
-        <v>2554</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="6" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>2563</v>
+      <c r="C2" s="6" t="s">
+        <v>2530</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="1" t="s">
         <v>1960</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="1" t="s">
         <v>1960</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="1" t="s">
         <v>1962</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="1" t="s">
         <v>1962</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="1" t="s">
         <v>1963</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="1" t="s">
         <v>1964</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="1" t="s">
         <v>1964</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="1" t="s">
         <v>1964</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="1" t="s">
         <v>1965</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="1" t="s">
         <v>1966</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="1" t="s">
         <v>1966</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="1" t="s">
         <v>1966</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="1" t="s">
         <v>1967</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="1" t="s">
         <v>1967</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="1" t="s">
         <v>1968</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="1" t="s">
         <v>1968</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="1" t="s">
         <v>1969</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>2564</v>
+      <c r="C11" s="1" t="s">
+        <v>2531</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="1" t="s">
         <v>1970</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>2565</v>
+      <c r="C12" s="1" t="s">
+        <v>2532</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="1" t="s">
         <v>1971</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="1" t="s">
         <v>1971</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="1" t="s">
         <v>1972</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="1" t="s">
         <v>1972</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="1" t="s">
         <v>1973</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="1" t="s">
         <v>1973</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="1" t="s">
         <v>1974</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="1" t="s">
         <v>1973</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="1" t="s">
         <v>1975</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="1" t="s">
         <v>1975</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="1" t="s">
         <v>1976</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="1" t="s">
         <v>1976</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="1" t="s">
         <v>1977</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="1" t="s">
         <v>1979</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="1" t="s">
         <v>1978</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="1" t="s">
         <v>1979</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="1" t="s">
         <v>1979</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="1" t="s">
         <v>1979</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="1" t="s">
         <v>2013</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="1" t="s">
         <v>2014</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="1" t="s">
         <v>2013</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="1" t="s">
         <v>1942</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="1" t="s">
         <v>1943</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="1" t="s">
         <v>1944</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="1" t="s">
         <v>1944</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="1" t="s">
         <v>1943</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="1" t="s">
         <v>1944</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="1" t="s">
         <v>1980</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="1" t="s">
         <v>1980</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="10" t="s">
-        <v>2555</v>
-      </c>
-      <c r="B26" s="14" t="s">
+      <c r="A26" s="6" t="s">
+        <v>2522</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="1" t="s">
         <v>1980</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="1" t="s">
         <v>1981</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="1" t="s">
         <v>1981</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="1" t="s">
         <v>1982</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="1" t="s">
         <v>1982</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="1" t="s">
         <v>1983</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="1" t="s">
         <v>1983</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="1" t="s">
         <v>1984</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="1" t="s">
         <v>1984</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="1" t="s">
         <v>1985</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="1" t="s">
         <v>1984</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="1" t="s">
         <v>1986</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="1" t="s">
         <v>1986</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="1" t="s">
         <v>1987</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="1" t="s">
         <v>1987</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="1" t="s">
         <v>1988</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="1" t="s">
         <v>1987</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="1" t="s">
         <v>1989</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="1" t="s">
         <v>1989</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="1" t="s">
         <v>1990</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="1" t="s">
         <v>1990</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="1" t="s">
         <v>2015</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="1" t="s">
         <v>2014</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="1" t="s">
         <v>2015</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="1" t="s">
         <v>1991</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="1" t="s">
         <v>1991</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="12" t="s">
+      <c r="A39" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>2416</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="1" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="1" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="1" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="1" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="1" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="1" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="1" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="1" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="1" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="1" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="1" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="1" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="1" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="1" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>2420</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>2452</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>2452</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="1" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="1" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="1" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C67" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C69" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>2428</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C72" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>2431</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>2432</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C74" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="1" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>2434</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C77" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C78" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C79" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="1" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C83" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>2464</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C85" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C86" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>2440</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C87" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C88" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C89" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C90" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>2444</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>2452</v>
+      </c>
+      <c r="C91" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="1" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C93" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="9" t="s">
+        <v>2461</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="1" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C96" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="1" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>2465</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C98" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C99" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="9" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C101" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
         <v>2448</v>
       </c>
-      <c r="B39" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C39" s="12" t="s">
+      <c r="B102" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C102" t="s">
         <v>2448</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="12" t="s">
+    <row r="103" spans="1:3">
+      <c r="A103" s="1" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="6" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="1" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="6" t="s">
+        <v>2524</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="1" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="1" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="6" t="s">
+        <v>2525</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
         <v>2449</v>
       </c>
-      <c r="B40" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C40" s="12" t="s">
+      <c r="B110" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C110" t="s">
         <v>2449</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="14" t="s">
-        <v>1992</v>
-      </c>
-      <c r="B41" s="14" t="s">
+    <row r="111" spans="1:3">
+      <c r="A111" s="1" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C41" s="14" t="s">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="14" t="s">
-        <v>1993</v>
-      </c>
-      <c r="B42" s="14" t="s">
+      <c r="C111" s="1" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="1" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C42" s="14" t="s">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="14" t="s">
-        <v>1994</v>
-      </c>
-      <c r="B43" s="14" t="s">
+      <c r="C112" s="1" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="6" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="14" t="s">
-        <v>1995</v>
-      </c>
-      <c r="B44" s="14" t="s">
+      <c r="C113" s="6" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="1" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C44" s="14" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="14" t="s">
-        <v>1996</v>
-      </c>
-      <c r="B45" s="14" t="s">
+      <c r="C114" s="1" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="1" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C45" s="14" t="s">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="14" t="s">
-        <v>1997</v>
-      </c>
-      <c r="B46" s="14" t="s">
+      <c r="C115" s="1" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="1" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C46" s="14" t="s">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="14" t="s">
-        <v>1998</v>
-      </c>
-      <c r="B47" s="14" t="s">
+      <c r="C116" s="1" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="1" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C47" s="14" t="s">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="14" t="s">
-        <v>1945</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="12" t="s">
+      <c r="C117" s="1" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="6" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
         <v>2450</v>
       </c>
-      <c r="B49" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C49" s="12" t="s">
+      <c r="B119" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C119" t="s">
         <v>2450</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="14" t="s">
-        <v>1999</v>
-      </c>
-      <c r="B50" s="14" t="s">
+    <row r="120" spans="1:3">
+      <c r="A120" s="6" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C50" s="14" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="14" t="s">
-        <v>2000</v>
-      </c>
-      <c r="B51" s="14" t="s">
+      <c r="C120" s="6" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="1" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="C51" s="14" t="s">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="12" t="s">
+      <c r="C121" s="1" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="5" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>2451</v>
       </c>
-      <c r="B52" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C52" s="12" t="s">
+      <c r="C122" s="5" t="s">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="5" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>2451</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="14" t="s">
-        <v>1955</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>1956</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="12" t="s">
-        <v>2452</v>
-      </c>
-      <c r="B54" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>2452</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="14" t="s">
-        <v>2001</v>
-      </c>
-      <c r="B55" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="14" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B56" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="14" t="s">
-        <v>1947</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="12" t="s">
-        <v>2453</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>2485</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>2453</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="12" t="s">
-        <v>2454</v>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>2485</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>2454</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="14" t="s">
-        <v>1957</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>1956</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="12" t="s">
-        <v>2455</v>
-      </c>
-      <c r="B61" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>2455</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="12" t="s">
-        <v>2456</v>
-      </c>
-      <c r="B62" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>2456</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="12" t="s">
-        <v>2457</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>2457</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="14" t="s">
-        <v>1948</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="14" t="s">
-        <v>1949</v>
-      </c>
-      <c r="B65" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="14" t="s">
-        <v>1950</v>
-      </c>
-      <c r="B66" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="12" t="s">
-        <v>2458</v>
-      </c>
-      <c r="B67" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>2458</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="12" t="s">
-        <v>2459</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>2459</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="12" t="s">
-        <v>2460</v>
-      </c>
-      <c r="B69" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>2460</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="12" t="s">
-        <v>2461</v>
-      </c>
-      <c r="B70" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>2461</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="12" t="s">
-        <v>2462</v>
-      </c>
-      <c r="B71" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>2462</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="12" t="s">
-        <v>2463</v>
-      </c>
-      <c r="B72" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>2463</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="12" t="s">
-        <v>2464</v>
-      </c>
-      <c r="B73" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>2464</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="12" t="s">
-        <v>2465</v>
-      </c>
-      <c r="B74" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>2465</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="12" t="s">
-        <v>2466</v>
-      </c>
-      <c r="B75" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>2466</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="14" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B76" s="14" t="s">
-        <v>1956</v>
-      </c>
-      <c r="C76" s="14" t="s">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="12" t="s">
-        <v>2467</v>
-      </c>
-      <c r="B77" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>2467</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="12" t="s">
-        <v>2468</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>2468</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="12" t="s">
-        <v>2469</v>
-      </c>
-      <c r="B79" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>2469</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="12" t="s">
-        <v>2470</v>
-      </c>
-      <c r="B80" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C80" s="12" t="s">
-        <v>2470</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="14" t="s">
-        <v>1951</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C81" s="14" t="s">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="14" t="s">
-        <v>1952</v>
-      </c>
-      <c r="B82" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C82" s="14" t="s">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="12" t="s">
-        <v>2496</v>
-      </c>
-      <c r="B83" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>2496</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="12" t="s">
-        <v>2497</v>
-      </c>
-      <c r="B84" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C84" s="12" t="s">
-        <v>2497</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="12" t="s">
-        <v>2471</v>
-      </c>
-      <c r="B85" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="12" t="s">
-        <v>2472</v>
-      </c>
-      <c r="B86" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>2472</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="12" t="s">
-        <v>2473</v>
-      </c>
-      <c r="B87" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C87" s="12" t="s">
-        <v>2473</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="12" t="s">
-        <v>2474</v>
-      </c>
-      <c r="B88" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C88" s="12" t="s">
-        <v>2474</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="12" t="s">
-        <v>2475</v>
-      </c>
-      <c r="B89" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C89" s="12" t="s">
-        <v>2475</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="12" t="s">
-        <v>2476</v>
-      </c>
-      <c r="B90" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C90" s="12" t="s">
-        <v>2476</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="12" t="s">
-        <v>2477</v>
-      </c>
-      <c r="B91" s="14" t="s">
-        <v>2485</v>
-      </c>
-      <c r="C91" s="12" t="s">
-        <v>2477</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="14" t="s">
-        <v>1959</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>1956</v>
-      </c>
-      <c r="C92" s="14" t="s">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="12" t="s">
-        <v>2478</v>
-      </c>
-      <c r="B93" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>2478</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="15" t="s">
-        <v>2494</v>
-      </c>
-      <c r="B94" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C94" s="15" t="s">
-        <v>2494</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="14" t="s">
-        <v>1953</v>
-      </c>
-      <c r="B95" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C95" s="14" t="s">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="12" t="s">
-        <v>2499</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C96" s="12" t="s">
-        <v>2499</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="14" t="s">
-        <v>1954</v>
-      </c>
-      <c r="B97" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C97" s="14" t="s">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="12" t="s">
-        <v>2498</v>
-      </c>
-      <c r="B98" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C98" s="12" t="s">
-        <v>2498</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="12" t="s">
-        <v>2479</v>
-      </c>
-      <c r="B99" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C99" s="12" t="s">
-        <v>2479</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="15" t="s">
-        <v>2495</v>
-      </c>
-      <c r="B100" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C100" s="15" t="s">
-        <v>2495</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="12" t="s">
-        <v>2480</v>
-      </c>
-      <c r="B101" s="14" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C101" s="12" t="s">
-        <v>2480</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="12" t="s">
-        <v>2481</v>
-      </c>
-      <c r="B102" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C102" s="12" t="s">
-        <v>2481</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" s="14" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B103" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C103" s="14" t="s">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" s="10" t="s">
-        <v>2556</v>
-      </c>
-      <c r="B104" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>2556</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="14" t="s">
-        <v>2003</v>
-      </c>
-      <c r="B105" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C105" s="14" t="s">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" s="10" t="s">
-        <v>2557</v>
-      </c>
-      <c r="B106" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C106" s="10" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" s="14" t="s">
-        <v>2004</v>
-      </c>
-      <c r="B107" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C107" s="14" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" s="14" t="s">
-        <v>2005</v>
-      </c>
-      <c r="B108" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C108" s="14" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="10" t="s">
-        <v>2558</v>
-      </c>
-      <c r="B109" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>2558</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" s="12" t="s">
-        <v>2482</v>
-      </c>
-      <c r="B110" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C110" s="12" t="s">
-        <v>2482</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="14" t="s">
-        <v>2006</v>
-      </c>
-      <c r="B111" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C111" s="14" t="s">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="14" t="s">
-        <v>2007</v>
-      </c>
-      <c r="B112" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C112" s="14" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="10" t="s">
-        <v>2559</v>
-      </c>
-      <c r="B113" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="14" t="s">
-        <v>2008</v>
-      </c>
-      <c r="B114" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C114" s="14" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="14" t="s">
-        <v>2009</v>
-      </c>
-      <c r="B115" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C115" s="14" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="14" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B116" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C116" s="14" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="14" t="s">
-        <v>2011</v>
-      </c>
-      <c r="B117" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C117" s="14" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="10" t="s">
-        <v>2560</v>
-      </c>
-      <c r="B118" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="12" t="s">
-        <v>2483</v>
-      </c>
-      <c r="B119" s="14" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C119" s="12" t="s">
-        <v>2483</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="10" t="s">
-        <v>2561</v>
-      </c>
-      <c r="B120" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>2561</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="14" t="s">
-        <v>2012</v>
-      </c>
-      <c r="B121" s="14" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C121" s="14" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="6" t="s">
-        <v>2575</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>2575</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="6" t="s">
-        <v>2576</v>
-      </c>
-      <c r="B123" s="7" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>2576</v>
+      <c r="C123" s="5" t="s">
+        <v>2543</v>
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="6" t="s">
-        <v>2577</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>2577</v>
+      <c r="A124" s="5" t="s">
+        <v>2544</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>2544</v>
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="6" t="s">
-        <v>2578</v>
-      </c>
-      <c r="B125" s="7" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>2578</v>
+      <c r="A125" s="5" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>2545</v>
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="6" t="s">
-        <v>2579</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>2579</v>
+      <c r="A126" s="5" t="s">
+        <v>2546</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>2546</v>
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="6" t="s">
-        <v>2580</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>2580</v>
+      <c r="A127" s="5" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>2547</v>
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="6" t="s">
-        <v>2581</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>2581</v>
+      <c r="A128" s="5" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>2548</v>
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="6" t="s">
-        <v>2582</v>
-      </c>
-      <c r="B129" s="7" t="s">
-        <v>2484</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>2582</v>
+      <c r="A129" s="5" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>2549</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1">
-    <sortState ref="A2:C121">
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C121">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
@@ -24465,7 +24376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -24508,7 +24419,7 @@
         <v>2021</v>
       </c>
       <c r="D2" t="s">
-        <v>2412</v>
+        <v>2379</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>2088</v>
@@ -24545,7 +24456,7 @@
         <v>2021</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2357</v>
+        <v>2324</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>2034</v>
@@ -24565,7 +24476,7 @@
         <v>2021</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2190</v>
+        <v>2157</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>2024</v>
@@ -24583,7 +24494,7 @@
         <v>2021</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2583</v>
+        <v>2550</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>2055</v>
@@ -24601,7 +24512,7 @@
         <v>2021</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2486</v>
+        <v>2453</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>2024</v>
@@ -24619,7 +24530,7 @@
         <v>2021</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2537</v>
+        <v>2504</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>2041</v>
@@ -24637,7 +24548,7 @@
         <v>2021</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2538</v>
+        <v>2505</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>2042</v>
@@ -24655,7 +24566,7 @@
         <v>2021</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2539</v>
+        <v>2506</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>2037</v>
@@ -24673,7 +24584,7 @@
         <v>2021</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2486</v>
+        <v>2453</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>2024</v>
@@ -24691,7 +24602,7 @@
         <v>2021</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2362</v>
+        <v>2329</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>2047</v>
@@ -24711,7 +24622,7 @@
         <v>2021</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2357</v>
+        <v>2324</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>2034</v>
@@ -24731,13 +24642,13 @@
         <v>2021</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2342</v>
+        <v>2309</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>2343</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -24751,7 +24662,7 @@
         <v>2021</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2551</v>
+        <v>2518</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>2045</v>
@@ -24771,13 +24682,13 @@
         <v>2021</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2344</v>
+        <v>2311</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>2345</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -24791,13 +24702,13 @@
         <v>2021</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2355</v>
+        <v>2322</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>2035</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>2366</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -24811,7 +24722,7 @@
         <v>2021</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2357</v>
+        <v>2324</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>2034</v>
@@ -24824,34 +24735,34 @@
       <c r="A19" s="3">
         <v>770</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>214</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2584</v>
+        <v>2551</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>2055</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>2366</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3">
         <v>780</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="7" t="s">
         <v>322</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D20" t="s">
-        <v>2417</v>
+        <v>2384</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>2047</v>
@@ -24868,13 +24779,13 @@
         <v>2021</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2342</v>
+        <v>2309</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>2343</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -24888,13 +24799,13 @@
         <v>2021</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2344</v>
+        <v>2311</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>2345</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -24928,7 +24839,7 @@
         <v>2021</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>2357</v>
+        <v>2324</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>2034</v>
@@ -24948,13 +24859,13 @@
         <v>2021</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2355</v>
+        <v>2322</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>2035</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>2356</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -24968,7 +24879,7 @@
         <v>2021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2518</v>
+        <v>2485</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>2034</v>
@@ -24987,8 +24898,8 @@
       <c r="C27" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>2524</v>
+      <c r="D27" s="4" t="s">
+        <v>2491</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>2034</v>
@@ -25008,13 +24919,13 @@
         <v>2021</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>2549</v>
+        <v>2516</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>2037</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>2358</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -25048,13 +24959,13 @@
         <v>2021</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>2359</v>
+        <v>2326</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>2041</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>2360</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -25068,10 +24979,10 @@
         <v>2021</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>2523</v>
+        <v>2490</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>2514</v>
+        <v>2481</v>
       </c>
       <c r="F31" s="3"/>
     </row>
@@ -25086,10 +24997,10 @@
         <v>2021</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2516</v>
+        <v>2483</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>2517</v>
+        <v>2484</v>
       </c>
       <c r="F32" s="3"/>
     </row>
@@ -25104,13 +25015,13 @@
         <v>2021</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>2548</v>
+        <v>2515</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>2361</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -25124,10 +25035,10 @@
         <v>2021</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>2512</v>
+        <v>2479</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>2505</v>
+        <v>2472</v>
       </c>
       <c r="F34" s="3"/>
     </row>
@@ -25142,7 +25053,7 @@
         <v>2021</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>2540</v>
+        <v>2507</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>2042</v>
@@ -25182,7 +25093,7 @@
         <v>2021</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>2362</v>
+        <v>2329</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>2047</v>
@@ -25242,7 +25153,7 @@
         <v>2021</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>2489</v>
+        <v>2456</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>2055</v>
@@ -25262,7 +25173,7 @@
         <v>2021</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>2553</v>
+        <v>2520</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>2055</v>
@@ -25273,17 +25184,17 @@
       <c r="A42" s="3">
         <v>790</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>459</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>2419</v>
+        <v>2386</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>2420</v>
+        <v>2387</v>
       </c>
       <c r="F42" s="3"/>
     </row>
@@ -25298,10 +25209,10 @@
         <v>2021</v>
       </c>
       <c r="D43" t="s">
-        <v>2488</v>
+        <v>2455</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>2421</v>
+        <v>2388</v>
       </c>
       <c r="F43" s="3"/>
     </row>
@@ -25316,13 +25227,13 @@
         <v>2021</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>2342</v>
+        <v>2309</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>2343</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -25336,13 +25247,13 @@
         <v>2021</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>2491</v>
+        <v>2458</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>2345</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -25356,13 +25267,13 @@
         <v>2021</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2509</v>
+        <v>2476</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>2346</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -25376,13 +25287,13 @@
         <v>2021</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>2507</v>
+        <v>2474</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>2347</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -25396,13 +25307,13 @@
         <v>2021</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>2552</v>
+        <v>2519</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>2347</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -25416,13 +25327,13 @@
         <v>2021</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>2490</v>
+        <v>2457</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>2026</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>2348</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -25442,7 +25353,7 @@
         <v>2028</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>2349</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -25456,13 +25367,13 @@
         <v>2021</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>2503</v>
+        <v>2470</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>2029</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>2350</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -25482,7 +25393,7 @@
         <v>2031</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>2351</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -25496,7 +25407,7 @@
         <v>2021</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>2543</v>
+        <v>2510</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>2032</v>
@@ -25516,13 +25427,13 @@
         <v>2021</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>2525</v>
+        <v>2492</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>2352</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -25536,13 +25447,13 @@
         <v>2021</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>2353</v>
+        <v>2320</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>2354</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -25556,10 +25467,10 @@
         <v>2021</v>
       </c>
       <c r="D56" t="s">
-        <v>2506</v>
+        <v>2473</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>2411</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -25573,13 +25484,13 @@
         <v>2021</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>2504</v>
+        <v>2471</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>2505</v>
+        <v>2472</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>2354</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -25619,7 +25530,7 @@
         <v>2034</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>2363</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -25633,7 +25544,7 @@
         <v>2021</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>2486</v>
+        <v>2453</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>2024</v>
@@ -25650,7 +25561,7 @@
         <v>2021</v>
       </c>
       <c r="D61" t="s">
-        <v>2512</v>
+        <v>2479</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>2055</v>
@@ -25667,7 +25578,7 @@
         <v>2021</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>2364</v>
+        <v>2331</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>2058</v>
@@ -25690,7 +25601,7 @@
         <v>2057</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>2414</v>
+        <v>2381</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>2036</v>
@@ -25713,7 +25624,7 @@
         <v>2050</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>2365</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -25747,13 +25658,13 @@
         <v>2021</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>2408</v>
+        <v>2375</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>2041</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>2409</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -25767,13 +25678,13 @@
         <v>2021</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>2342</v>
+        <v>2309</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>2343</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -25787,13 +25698,13 @@
         <v>2021</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>2344</v>
+        <v>2311</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>2345</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -25807,13 +25718,13 @@
         <v>2021</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>2490</v>
+        <v>2457</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>2026</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>2348</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -25827,13 +25738,13 @@
         <v>2021</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>2586</v>
+        <v>2553</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>2394</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -25847,13 +25758,13 @@
         <v>2021</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>2395</v>
+        <v>2362</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>2026</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>2396</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -25867,13 +25778,13 @@
         <v>2021</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>2397</v>
+        <v>2364</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>2032</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>2398</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -25887,13 +25798,13 @@
         <v>2021</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>2406</v>
+        <v>2373</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>2407</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -25907,7 +25818,7 @@
         <v>2021</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2585</v>
+        <v>2552</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>2025</v>
@@ -25925,13 +25836,13 @@
         <v>2021</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>2367</v>
+        <v>2334</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>2055</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>2368</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -25945,53 +25856,53 @@
         <v>2021</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>2513</v>
+        <v>2480</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>2368</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="3">
         <v>352</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="5" t="s">
         <v>1875</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>2344</v>
+        <v>2311</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>2368</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="3">
         <v>353</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="5" t="s">
         <v>1875</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>2587</v>
+        <v>2554</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>2368</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -26005,13 +25916,13 @@
         <v>2021</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>2369</v>
+        <v>2336</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>2041</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>2370</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -26025,10 +25936,10 @@
         <v>2021</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>2523</v>
+        <v>2490</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>2514</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -26040,10 +25951,10 @@
         <v>2021</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>2516</v>
+        <v>2483</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>2517</v>
+        <v>2484</v>
       </c>
       <c r="F81" s="3"/>
     </row>
@@ -26056,13 +25967,13 @@
         <v>2021</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>2371</v>
+        <v>2338</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>2372</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -26074,13 +25985,13 @@
         <v>2021</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>2486</v>
+        <v>2453</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>2373</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -26092,13 +26003,13 @@
         <v>2021</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>2545</v>
+        <v>2512</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>2041</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>2374</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -26110,13 +26021,13 @@
         <v>2021</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>2375</v>
+        <v>2342</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>2031</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>2376</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -26128,31 +26039,31 @@
         <v>2021</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>2377</v>
+        <v>2344</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>2058</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>2378</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="3">
         <v>460</v>
       </c>
-      <c r="B87" s="4"/>
+      <c r="B87" s="3"/>
       <c r="C87" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>2379</v>
+        <v>2346</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>2050</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>2380</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -26164,13 +26075,13 @@
         <v>2021</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>2544</v>
+        <v>2511</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>2042</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>2381</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -26182,13 +26093,13 @@
         <v>2021</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>2540</v>
+        <v>2507</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>2042</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>2381</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -26200,13 +26111,13 @@
         <v>2021</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>2382</v>
+        <v>2349</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>2035</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>2383</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -26218,13 +26129,13 @@
         <v>2021</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>2384</v>
+        <v>2351</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>2385</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -26236,13 +26147,13 @@
         <v>2021</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>2386</v>
+        <v>2353</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>2028</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>2387</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -26254,13 +26165,13 @@
         <v>2021</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>2388</v>
+        <v>2355</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>2032</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>2389</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -26272,13 +26183,13 @@
         <v>2021</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>2390</v>
+        <v>2357</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>2053</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>2391</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -26290,13 +26201,13 @@
         <v>2021</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>2392</v>
+        <v>2359</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>2393</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -26308,13 +26219,13 @@
         <v>2021</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>2399</v>
+        <v>2366</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>2024</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>2400</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -26326,31 +26237,31 @@
         <v>2021</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>2401</v>
+        <v>2368</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>2025</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>2402</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="3">
         <v>590</v>
       </c>
-      <c r="B98" s="13"/>
+      <c r="B98" s="8"/>
       <c r="C98" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>2546</v>
+        <v>2513</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>2034</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>2403</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -26362,13 +26273,13 @@
         <v>2021</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>2542</v>
+        <v>2509</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>2055</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>2404</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -26380,25 +26291,24 @@
         <v>2021</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>2541</v>
+        <v>2508</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>2041</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>2405</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="3">
         <v>710</v>
       </c>
-      <c r="B101" s="12"/>
       <c r="C101" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>2357</v>
+        <v>2324</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>2034</v>
@@ -26431,7 +26341,7 @@
         <v>2021</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>2413</v>
+        <v>2380</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>2055</v>
@@ -26441,15 +26351,15 @@
       <c r="A104" s="3">
         <v>791</v>
       </c>
-      <c r="B104" s="4"/>
+      <c r="B104" s="3"/>
       <c r="C104" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>2419</v>
+        <v>2386</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>2420</v>
+        <v>2387</v>
       </c>
       <c r="F104" s="3"/>
     </row>
@@ -26461,15 +26371,15 @@
         <v>2021</v>
       </c>
       <c r="D105" t="s">
-        <v>2547</v>
+        <v>2514</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>2421</v>
+        <v>2388</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F97">
-    <sortState ref="A2:F102">
+  <autoFilter ref="A1:F97" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F102">
       <sortCondition ref="B1:B94"/>
     </sortState>
   </autoFilter>
@@ -26479,7 +26389,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -26526,13 +26436,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5"/>
+  <autoFilter ref="A1:B5" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -26573,14 +26483,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B4"/>
+  <autoFilter ref="A1:B4" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H86"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -26590,7 +26500,7 @@
     <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>2016</v>
       </c>
@@ -26610,7 +26520,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>10</v>
       </c>
@@ -26622,1718 +26532,1484 @@
         <v>2057</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2487</v>
+        <v>2454</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>2085</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>11</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>1816</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2057</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2487</v>
+        <v>2454</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>2085</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="8">
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
         <v>12</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="1" t="s">
+        <v>2454</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>2085</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-    </row>
-    <row r="5" spans="1:8">
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>13</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F5" s="8" t="s">
+      <c r="E5" s="1" t="s">
+        <v>2454</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>2085</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-    </row>
-    <row r="6" spans="1:8">
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>14</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9" t="s">
-        <v>2427</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" t="s">
+        <v>2394</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="1" t="s">
         <v>2085</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="8">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
         <v>15</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>2427</v>
-      </c>
-      <c r="F7" s="8" t="s">
+      <c r="E7" t="s">
+        <v>2394</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>2085</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-    </row>
-    <row r="8" spans="1:8">
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>16</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="9" t="s">
+      <c r="D8" t="s">
         <v>2057</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>2444</v>
-      </c>
-      <c r="F8" s="9" t="s">
+      <c r="E8" t="s">
+        <v>2411</v>
+      </c>
+      <c r="F8" t="s">
         <v>2087</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-    </row>
-    <row r="9" spans="1:8">
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>17</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9" t="s">
-        <v>2445</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="D9" t="s">
+        <v>2412</v>
+      </c>
+      <c r="E9" t="s">
         <v>2057</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" t="s">
         <v>2085</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="8">
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
         <v>18</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" t="s">
         <v>2057</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>2445</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="D10" t="s">
+        <v>2412</v>
+      </c>
+      <c r="E10" t="s">
         <v>2057</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" t="s">
         <v>2085</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" spans="1:8">
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>19</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9" t="s">
+      <c r="D11" t="s">
         <v>2057</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>2446</v>
-      </c>
-      <c r="F11" s="9" t="s">
+      <c r="E11" t="s">
+        <v>2413</v>
+      </c>
+      <c r="F11" t="s">
         <v>2085</v>
       </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" spans="1:8">
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>20</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" t="s">
         <v>2057</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="E12" s="1" t="s">
+        <v>2454</v>
+      </c>
+      <c r="F12" t="s">
         <v>2085</v>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="8">
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1">
         <v>21</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" t="s">
         <v>2057</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>2238</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="E13" s="1" t="s">
+        <v>2205</v>
+      </c>
+      <c r="F13" t="s">
         <v>2119</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="8">
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1">
         <v>30</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="1" t="s">
         <v>2086</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="1" t="s">
         <v>2087</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" spans="1:8" ht="30">
-      <c r="A15" s="8">
+    </row>
+    <row r="15" spans="1:6" ht="30">
+      <c r="A15" s="1">
         <v>40</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="1">
         <v>1</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8" t="s">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>2493</v>
-      </c>
-      <c r="F15" s="8" t="s">
+      <c r="E15" s="1" t="s">
+        <v>2460</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>2088</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" spans="1:8" ht="30">
-      <c r="A16" s="8">
+    </row>
+    <row r="16" spans="1:6" ht="30">
+      <c r="A16" s="1">
         <v>41</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="1">
         <v>1</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>2493</v>
-      </c>
-      <c r="F16" s="8" t="s">
+      <c r="E16" s="1" t="s">
+        <v>2460</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>2088</v>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="8">
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="1">
         <v>50</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8" t="s">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E17" s="8" t="s">
-        <v>2535</v>
-      </c>
-      <c r="F17" s="8" t="s">
+      <c r="E17" s="1" t="s">
+        <v>2502</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>2089</v>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="8">
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="1">
         <v>60</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="1">
         <v>1</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8" t="s">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="1" t="s">
         <v>2090</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="1" t="s">
         <v>2091</v>
       </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="8">
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="1">
         <v>70</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="1">
         <v>1</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8" t="s">
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="1" t="s">
         <v>2092</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="1" t="s">
         <v>2093</v>
       </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="8">
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="1">
         <v>80</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8" t="s">
+      <c r="C20" s="1"/>
+      <c r="D20" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="1" t="s">
         <v>2094</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="1" t="s">
         <v>2095</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8" ht="45">
-      <c r="A21" s="8">
+    </row>
+    <row r="21" spans="1:6" ht="45">
+      <c r="A21" s="1">
         <v>90</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8" t="s">
+      <c r="C21" s="1"/>
+      <c r="D21" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>2425</v>
-      </c>
-      <c r="F21" s="8" t="s">
+      <c r="E21" s="1" t="s">
+        <v>2392</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>2096</v>
       </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="8">
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="1">
         <v>100</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>989</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="C22" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="1" t="s">
         <v>2097</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="1" t="s">
         <v>2098</v>
       </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="8">
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="1">
         <v>110</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="1">
         <v>1</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8" t="s">
+      <c r="C23" s="1"/>
+      <c r="D23" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="1" t="s">
         <v>2097</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="1" t="s">
         <v>2098</v>
       </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="8">
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="1">
         <v>120</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="1">
         <v>1</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="1" t="s">
         <v>2099</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="1" t="s">
         <v>2100</v>
       </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="8">
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="1">
         <v>130</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="1">
         <v>1</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="D25" s="8" t="s">
+      <c r="C25" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="1" t="s">
         <v>2101</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="1" t="s">
         <v>2102</v>
       </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="8">
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="1">
         <v>140</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="1">
         <v>1</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="C26" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F26" s="8" t="s">
+      <c r="E26" s="1" t="s">
+        <v>2454</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>2085</v>
       </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="8">
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="1">
         <v>150</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="1">
         <v>1</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="1" t="s">
         <v>1660</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="1" t="s">
         <v>2103</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="1" t="s">
         <v>2104</v>
       </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="8">
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="1">
         <v>160</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="1">
         <v>1</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="1" t="s">
         <v>2105</v>
       </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="8">
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="1">
         <v>170</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="1">
         <v>1</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="1" t="s">
         <v>2106</v>
       </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="8">
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="1">
         <v>180</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="1">
         <v>1</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="1" t="s">
         <v>2107</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="1" t="s">
         <v>2108</v>
       </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="8">
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="1">
         <v>190</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="1">
         <v>1</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="1" t="s">
         <v>2109</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="1" t="s">
         <v>2110</v>
       </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="8">
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="1">
         <v>200</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="1">
         <v>1</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>2572</v>
-      </c>
-      <c r="F32" s="8" t="s">
+      <c r="E32" s="1" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>2112</v>
       </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="8">
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="1">
         <v>210</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="1">
         <v>1</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="1" t="s">
         <v>2111</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="1" t="s">
         <v>2112</v>
       </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="8">
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="1">
         <v>220</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="1">
         <v>1</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="1" t="s">
         <v>1732</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="1" t="s">
         <v>2113</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="1" t="s">
         <v>2114</v>
       </c>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="8">
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="1">
         <v>230</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="1">
         <v>1</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="1" t="s">
         <v>1826</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="1" t="s">
         <v>2115</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="1" t="s">
         <v>2116</v>
       </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="8">
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="1">
         <v>240</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="1">
         <v>1</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="1" t="s">
         <v>1811</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="1" t="s">
         <v>2117</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="1" t="s">
         <v>2118</v>
       </c>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8" ht="60">
-      <c r="A37" s="8">
+    </row>
+    <row r="37" spans="1:6" ht="60">
+      <c r="A37" s="1">
         <v>250</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="1">
         <v>1</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="D37" s="8" t="s">
+      <c r="C37" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E37" s="8" t="s">
-        <v>2492</v>
-      </c>
-      <c r="F37" s="8" t="s">
+      <c r="E37" s="1" t="s">
+        <v>2459</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>2119</v>
       </c>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8" ht="45">
-      <c r="A38" s="8">
+    </row>
+    <row r="38" spans="1:6" ht="45">
+      <c r="A38" s="1">
         <v>260</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="1">
         <v>1</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="1" t="s">
         <v>2120</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="F38" s="1" t="s">
         <v>2121</v>
       </c>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="8">
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="1">
         <v>270</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="1">
         <v>1</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="1" t="s">
         <v>1660</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="1" t="s">
         <v>2122</v>
       </c>
-      <c r="F39" s="8" t="s">
+      <c r="F39" s="1" t="s">
         <v>2123</v>
       </c>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="8">
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="1">
         <v>280</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="1">
         <v>1</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="1" t="s">
         <v>2124</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" s="1" t="s">
         <v>2125</v>
       </c>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="8">
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="1">
         <v>290</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="1">
         <v>1</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="1" t="s">
         <v>2126</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F41" s="1" t="s">
         <v>2127</v>
       </c>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="8">
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="1">
         <v>300</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="1">
         <v>1</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="1" t="s">
         <v>2126</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="1" t="s">
         <v>2127</v>
       </c>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="8">
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="1">
         <v>310</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="1">
         <v>1</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="1" t="s">
         <v>2100</v>
       </c>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="8">
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="1">
         <v>320</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="1">
         <v>1</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>989</v>
-      </c>
-      <c r="D44" s="8" t="s">
+      <c r="C44" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F44" s="1" t="s">
         <v>2098</v>
       </c>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="8">
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="1">
         <v>330</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="1">
         <v>1</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="D45" s="8" t="s">
+      <c r="C45" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="F45" s="1" t="s">
         <v>2102</v>
       </c>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="8">
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="1">
         <v>340</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="1">
         <v>1</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="1" t="s">
         <v>1660</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="1" t="s">
         <v>2104</v>
       </c>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="8">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="1">
         <v>350</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="1">
         <v>1</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="1" t="s">
         <v>1398</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="1" t="s">
         <v>2121</v>
       </c>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="8">
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="1">
         <v>360</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="1">
         <v>1</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="F48" s="1" t="s">
         <v>2105</v>
       </c>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="8">
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="1">
         <v>370</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="1">
         <v>1</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F49" s="8" t="s">
+      <c r="F49" s="1" t="s">
         <v>2119</v>
       </c>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="8">
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="1">
         <v>380</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="1">
         <v>1</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="F50" s="1" t="s">
         <v>2106</v>
       </c>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="8">
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="1">
         <v>390</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="1">
         <v>1</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="F51" s="1" t="s">
         <v>2110</v>
       </c>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="8">
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="1">
         <v>400</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="1">
         <v>1</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="F52" s="1" t="s">
         <v>2108</v>
       </c>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="8">
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="1">
         <v>410</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="1">
         <v>1</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="F53" s="1" t="s">
         <v>2112</v>
       </c>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="8">
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="1">
         <v>420</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="1">
         <v>1</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D54" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="F54" s="1" t="s">
         <v>2112</v>
       </c>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="8">
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="1">
         <v>430</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="1">
         <v>1</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="1" t="s">
         <v>1732</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D55" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F55" s="8" t="s">
+      <c r="F55" s="1" t="s">
         <v>2114</v>
       </c>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="8">
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="1">
         <v>440</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="1">
         <v>1</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="1" t="s">
         <v>1826</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D56" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="F56" s="1" t="s">
         <v>2116</v>
       </c>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="8">
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="1">
         <v>450</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="1">
         <v>1</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="1" t="s">
         <v>1811</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F57" s="8" t="s">
-        <v>2529</v>
-      </c>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="8">
+      <c r="F57" s="1" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="1">
         <v>460</v>
       </c>
-      <c r="B58" s="8">
+      <c r="B58" s="1">
         <v>1</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="C58" s="10" t="s">
         <v>1902</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="F58" s="8" t="s">
-        <v>2176</v>
-      </c>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="8">
+      <c r="F58" s="1" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="1">
         <v>470</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="1">
         <v>1</v>
       </c>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8" t="s">
+      <c r="C59" s="1"/>
+      <c r="D59" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E59" s="8" t="s">
-        <v>2422</v>
-      </c>
-      <c r="F59" s="8" t="s">
+      <c r="E59" s="1" t="s">
+        <v>2389</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>2123</v>
       </c>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-    </row>
-    <row r="60" spans="1:8" ht="60">
-      <c r="A60" s="8">
+    </row>
+    <row r="60" spans="1:6" ht="60">
+      <c r="A60" s="1">
         <v>480</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="1">
         <v>1</v>
       </c>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8" t="s">
+      <c r="C60" s="1"/>
+      <c r="D60" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E60" s="8" t="s">
-        <v>2429</v>
-      </c>
-      <c r="F60" s="8" t="s">
+      <c r="E60" s="1" t="s">
+        <v>2396</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>2119</v>
       </c>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-    </row>
-    <row r="61" spans="1:8" ht="45">
-      <c r="A61" s="8">
+    </row>
+    <row r="61" spans="1:6" ht="45">
+      <c r="A61" s="1">
         <v>490</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="1">
         <v>1</v>
       </c>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8" t="s">
+      <c r="C61" s="1"/>
+      <c r="D61" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E61" s="8" t="s">
-        <v>2428</v>
-      </c>
-      <c r="F61" s="8" t="s">
+      <c r="E61" s="1" t="s">
+        <v>2395</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>2121</v>
       </c>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="8">
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="1">
         <v>500</v>
       </c>
-      <c r="B62" s="8">
+      <c r="B62" s="1">
         <v>1</v>
       </c>
-      <c r="C62" s="9"/>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E62" s="9" t="s">
-        <v>2423</v>
-      </c>
-      <c r="F62" s="8" t="s">
+      <c r="E62" t="s">
+        <v>2390</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>2119</v>
       </c>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="8">
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="1">
         <v>510</v>
       </c>
-      <c r="B63" s="8">
+      <c r="B63" s="1">
         <v>1</v>
       </c>
-      <c r="C63" s="9"/>
-      <c r="D63" s="8" t="s">
+      <c r="D63" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E63" s="8" t="s">
-        <v>2430</v>
-      </c>
-      <c r="F63" s="8" t="s">
+      <c r="E63" s="1" t="s">
+        <v>2397</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>2121</v>
       </c>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="8">
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="1">
         <v>520</v>
       </c>
-      <c r="B64" s="8">
+      <c r="B64" s="1">
         <v>1</v>
       </c>
-      <c r="C64" s="9"/>
-      <c r="D64" s="8" t="s">
+      <c r="D64" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E64" s="9" t="s">
-        <v>2426</v>
-      </c>
-      <c r="F64" s="8" t="s">
+      <c r="E64" t="s">
+        <v>2393</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>2119</v>
       </c>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="8">
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="1">
         <v>530</v>
       </c>
-      <c r="B65" s="8">
+      <c r="B65" s="1">
         <v>1</v>
       </c>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8" t="s">
+      <c r="C65" s="1"/>
+      <c r="D65" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E65" s="8" t="s">
-        <v>2424</v>
-      </c>
-      <c r="F65" s="8" t="s">
+      <c r="E65" s="1" t="s">
+        <v>2391</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>2125</v>
       </c>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="8">
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="1">
         <v>540</v>
       </c>
-      <c r="B66" s="8">
+      <c r="B66" s="1">
         <v>1</v>
       </c>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8" t="s">
+      <c r="C66" s="1"/>
+      <c r="D66" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E66" s="9" t="s">
-        <v>2431</v>
-      </c>
-      <c r="F66" s="8" t="s">
+      <c r="E66" t="s">
+        <v>2398</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>2127</v>
       </c>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="8">
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="1">
         <v>550</v>
       </c>
-      <c r="B67" s="9">
+      <c r="B67">
         <v>1</v>
       </c>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8" t="s">
+      <c r="C67" s="1"/>
+      <c r="D67" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="E67" s="8" t="s">
-        <v>2432</v>
-      </c>
-      <c r="F67" s="8" t="s">
+      <c r="E67" s="1" t="s">
+        <v>2399</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="1">
+        <v>560</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="D68" t="s">
+        <v>2400</v>
+      </c>
+      <c r="E68" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F68" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="1">
+        <v>570</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="D69" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E69" t="s">
+        <v>2401</v>
+      </c>
+      <c r="F69" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="1">
+        <v>580</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="D70" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E70" t="s">
+        <v>2402</v>
+      </c>
+      <c r="F70" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="1">
+        <v>590</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="D71" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E71" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F71" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="1">
+        <v>600</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="D72" t="s">
+        <v>2405</v>
+      </c>
+      <c r="E72" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F72" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="1">
+        <v>610</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="D73" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E73" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F73" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="1">
+        <v>620</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="D74" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E74" t="s">
+        <v>2407</v>
+      </c>
+      <c r="F74" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="1">
+        <v>630</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="D75" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E75" t="s">
+        <v>2408</v>
+      </c>
+      <c r="F75" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="1">
+        <v>640</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="D76" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E76" t="s">
+        <v>2409</v>
+      </c>
+      <c r="F76" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="1">
+        <v>650</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E77" t="s">
+        <v>2499</v>
+      </c>
+      <c r="F77" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="1">
+        <v>660</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="D78" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E78" t="s">
+        <v>2410</v>
+      </c>
+      <c r="F78" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="1">
+        <v>670</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="D79" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E79" t="s">
+        <v>2537</v>
+      </c>
+      <c r="F79" t="s">
         <v>2150</v>
       </c>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="8">
-        <v>560</v>
-      </c>
-      <c r="B68" s="9">
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="1">
+        <v>680</v>
+      </c>
+      <c r="B80">
         <v>1</v>
       </c>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9" t="s">
-        <v>2433</v>
-      </c>
-      <c r="E68" s="9" t="s">
+      <c r="D80" t="s">
         <v>2057</v>
       </c>
-      <c r="F68" s="9" t="s">
-        <v>2121</v>
-      </c>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="8">
-        <v>570</v>
-      </c>
-      <c r="B69" s="9">
-        <v>1</v>
-      </c>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9" t="s">
-        <v>2057</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>2434</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>2121</v>
-      </c>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="8">
-        <v>580</v>
-      </c>
-      <c r="B70" s="9">
-        <v>1</v>
-      </c>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9" t="s">
-        <v>2057</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>2435</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>2119</v>
-      </c>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="8">
-        <v>590</v>
-      </c>
-      <c r="B71" s="9">
-        <v>1</v>
-      </c>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9" t="s">
-        <v>2057</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>2436</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>2437</v>
-      </c>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="8">
-        <v>600</v>
-      </c>
-      <c r="B72" s="9">
-        <v>1</v>
-      </c>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9" t="s">
-        <v>2438</v>
-      </c>
-      <c r="E72" s="9" t="s">
-        <v>2057</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>2123</v>
-      </c>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="8">
-        <v>610</v>
-      </c>
-      <c r="B73" s="9">
-        <v>1</v>
-      </c>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9" t="s">
-        <v>2057</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>2439</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>2123</v>
-      </c>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="8">
-        <v>620</v>
-      </c>
-      <c r="B74" s="9">
-        <v>1</v>
-      </c>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9" t="s">
-        <v>2057</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>2440</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>2118</v>
-      </c>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="8">
-        <v>630</v>
-      </c>
-      <c r="B75" s="9">
-        <v>1</v>
-      </c>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9" t="s">
-        <v>2057</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>2441</v>
-      </c>
-      <c r="F75" s="9" t="s">
+      <c r="E80" t="s">
+        <v>2414</v>
+      </c>
+      <c r="F80" t="s">
         <v>2088</v>
       </c>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="8">
-        <v>640</v>
-      </c>
-      <c r="B76" s="9">
-        <v>1</v>
-      </c>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9" t="s">
-        <v>2057</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>2442</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>2125</v>
-      </c>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="8">
-        <v>650</v>
-      </c>
-      <c r="B77" s="9">
-        <v>1</v>
-      </c>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9" t="s">
-        <v>2057</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>2532</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>2096</v>
-      </c>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="8">
-        <v>660</v>
-      </c>
-      <c r="B78" s="9">
-        <v>1</v>
-      </c>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9" t="s">
-        <v>2057</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>2443</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>2095</v>
-      </c>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-    </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="8">
-        <v>670</v>
-      </c>
-      <c r="B79" s="9">
-        <v>1</v>
-      </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9" t="s">
-        <v>2057</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>2570</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>2181</v>
-      </c>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="8">
-        <v>680</v>
-      </c>
-      <c r="B80" s="9">
-        <v>1</v>
-      </c>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9" t="s">
-        <v>2057</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>2447</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>2088</v>
-      </c>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="9"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="9"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="9"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="9"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="9"/>
-      <c r="H86" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F56">
-    <sortState ref="A2:F78">
+  <autoFilter ref="A1:F56" xr:uid="{00000000-0009-0000-0000-000005000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F78">
       <sortCondition ref="A1:A54"/>
     </sortState>
   </autoFilter>
@@ -28342,11 +28018,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
@@ -28367,554 +28043,554 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>2132</v>
+      <c r="A2" s="12" t="s">
+        <v>2088</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2133</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2133</v>
+        <v>2088</v>
+      </c>
+      <c r="D2" s="11">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2134</v>
+        <v>2096</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2133</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>2133</v>
+        <v>2088</v>
+      </c>
+      <c r="D3" s="11">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>2087</v>
+        <v>2091</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2133</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>2133</v>
+        <v>2088</v>
+      </c>
+      <c r="D4" s="11">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>2091</v>
+        <v>2149</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>2135</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2091</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>2136</v>
+        <v>2088</v>
+      </c>
+      <c r="D5" s="11">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>2085</v>
+        <v>2098</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2133</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>2133</v>
+        <v>989</v>
+      </c>
+      <c r="D6" s="11">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>2095</v>
+        <v>2143</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2138</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>2139</v>
+        <v>989</v>
+      </c>
+      <c r="D7" s="11">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>2127</v>
+        <v>2557</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>2140</v>
+        <v>989</v>
+      </c>
+      <c r="D8" s="11">
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>2125</v>
+        <v>2102</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>2141</v>
+        <v>459</v>
+      </c>
+      <c r="D9" s="11">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>2142</v>
+        <v>2119</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>2143</v>
+        <v>459</v>
+      </c>
+      <c r="D10" s="11">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>2144</v>
+        <v>2100</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>2145</v>
+        <v>1429</v>
+      </c>
+      <c r="D11" s="11">
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>2146</v>
+        <v>2121</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>2147</v>
+        <v>1429</v>
+      </c>
+      <c r="D12" s="11">
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>2148</v>
+        <v>2095</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>2137</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>2149</v>
+      <c r="D13" s="11">
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>2150</v>
+        <v>2093</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>2137</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>2151</v>
+      <c r="D14" s="11">
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>2152</v>
+        <v>2558</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>2137</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>2145</v>
+      <c r="D15" s="11">
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>2119</v>
+        <v>2106</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>2153</v>
+        <v>964</v>
+      </c>
+      <c r="D16" s="11">
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>2154</v>
+        <v>2560</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>2155</v>
+        <v>964</v>
+      </c>
+      <c r="D17" s="11">
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
-        <v>2121</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>2137</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>1429</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>2156</v>
+      <c r="A18" s="13" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>964</v>
+      </c>
+      <c r="D18" s="14">
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
-        <v>2123</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>2137</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="A19" s="13" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>964</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>2157</v>
+      <c r="D19" s="11">
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
-        <v>2158</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>2137</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="A20" s="13" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>964</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>2159</v>
+      <c r="D20" s="11">
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2160</v>
+        <v>2105</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>2161</v>
+      <c r="D21" s="14">
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="1" t="s">
-        <v>2162</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>2137</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="A22" s="13" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>964</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>2163</v>
+      <c r="D22" s="11">
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="1" t="s">
-        <v>2112</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>2137</v>
-      </c>
-      <c r="C23" s="1" t="s">
+      <c r="A23" s="13" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>964</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>2164</v>
+      <c r="D23" s="11">
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="1" t="s">
-        <v>2105</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>2137</v>
-      </c>
-      <c r="C24" s="1" t="s">
+      <c r="A24" s="13" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>964</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>2165</v>
+      <c r="D24" s="14">
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>2106</v>
+        <v>2139</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>2166</v>
+      <c r="D25" s="11">
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="1" t="s">
-        <v>2102</v>
+      <c r="A26" t="s">
+        <v>2116</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>2167</v>
+        <v>964</v>
+      </c>
+      <c r="D26" s="11">
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="1" t="s">
-        <v>2098</v>
+      <c r="A27" t="s">
+        <v>2404</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>2168</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="30">
+        <v>964</v>
+      </c>
+      <c r="D27" s="14">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>2169</v>
+        <v>2148</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2133</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>2145</v>
+        <v>964</v>
+      </c>
+      <c r="D28" s="11">
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>2100</v>
+        <v>2145</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1429</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>2170</v>
+        <v>964</v>
+      </c>
+      <c r="D29" s="11">
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>2104</v>
+        <v>2140</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>2171</v>
+      <c r="D30" s="14">
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>2114</v>
+        <v>2127</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>2172</v>
+      <c r="D31" s="11">
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2173</v>
+        <v>2104</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>2174</v>
+      <c r="D32" s="11">
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>2116</v>
+        <v>2123</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>2175</v>
+      <c r="D33" s="14">
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>2176</v>
+        <v>2138</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>2177</v>
+      <c r="D34" s="11">
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>2096</v>
+        <v>2147</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>2096</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>2178</v>
+        <v>964</v>
+      </c>
+      <c r="D35" s="11">
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>2179</v>
+        <v>2110</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2179</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>2180</v>
+        <v>964</v>
+      </c>
+      <c r="D36" s="14">
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>2181</v>
+        <v>2108</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>2133</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>2145</v>
+        <v>964</v>
+      </c>
+      <c r="D37" s="11">
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="1" t="s">
-        <v>2093</v>
+      <c r="A38" s="5" t="s">
+        <v>2118</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>2138</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>2182</v>
+        <v>964</v>
+      </c>
+      <c r="D38" s="11">
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
-        <v>2088</v>
+      <c r="A39" t="s">
+        <v>2540</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>2088</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>2183</v>
+        <v>964</v>
+      </c>
+      <c r="D39" s="14">
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>2184</v>
+        <v>2150</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2133</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>2133</v>
+        <v>964</v>
+      </c>
+      <c r="D40" s="11">
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>2089</v>
+        <v>2132</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>2133</v>
@@ -28922,75 +28598,106 @@
       <c r="C41" s="1" t="s">
         <v>2133</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>2145</v>
+      <c r="D41" s="11">
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>2110</v>
+        <v>2134</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>2137</v>
+        <v>2133</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="D42" s="1"/>
+        <v>2133</v>
+      </c>
+      <c r="D42" s="11">
+        <v>99</v>
+      </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2108</v>
+        <v>2087</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2137</v>
+        <v>2133</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="D43" s="1"/>
+        <v>2133</v>
+      </c>
+      <c r="D43" s="11">
+        <v>99</v>
+      </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" t="s">
-        <v>2437</v>
+      <c r="A44" s="1" t="s">
+        <v>2085</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>2137</v>
+        <v>2133</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>964</v>
+        <v>2133</v>
+      </c>
+      <c r="D44" s="11">
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>2573</v>
+      <c r="A45" s="1" t="s">
+        <v>2151</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>2137</v>
+        <v>2133</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>964</v>
+        <v>2133</v>
+      </c>
+      <c r="D45" s="11">
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="6" t="s">
-        <v>2118</v>
+      <c r="A46" s="1" t="s">
+        <v>2146</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>2137</v>
+        <v>2133</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>964</v>
+        <v>2133</v>
+      </c>
+      <c r="D46" s="11">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="1" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>2133</v>
+      </c>
+      <c r="D47" s="11">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D43"/>
+  <autoFilter ref="A1:D45" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D48">
+      <sortCondition ref="D1:D45"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -29002,13 +28709,13 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>2185</v>
+        <v>2152</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2186</v>
+        <v>2153</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2187</v>
+        <v>2154</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2020</v>
@@ -29016,7 +28723,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>2550</v>
+        <v>2517</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2035</v>
@@ -29025,43 +28732,43 @@
         <v>2019</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2188</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45">
       <c r="A3" s="1" t="s">
-        <v>2189</v>
+        <v>2156</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2190</v>
+        <v>2157</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2191</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>2410</v>
+        <v>2377</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2192</v>
+        <v>2159</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2193</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>2536</v>
+        <v>2503</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2513</v>
+        <v>2480</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2019</v>
@@ -29070,66 +28777,66 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>2194</v>
+        <v>2161</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2195</v>
+        <v>2162</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2196</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>2519</v>
+        <v>2486</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2197</v>
+        <v>2164</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2198</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>2508</v>
+        <v>2475</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2199</v>
+        <v>2166</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2200</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>2201</v>
+        <v>2168</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2202</v>
+        <v>2169</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2203</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>2574</v>
+        <v>2541</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2521</v>
+        <v>2488</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2019</v>
@@ -29138,27 +28845,27 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>2179</v>
+        <v>2149</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2204</v>
+        <v>2171</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2205</v>
+        <v>2172</v>
       </c>
       <c r="F11" t="s">
-        <v>2533</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>2520</v>
+        <v>2487</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2515</v>
+        <v>2482</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>2019</v>
@@ -29167,10 +28874,10 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>2501</v>
+        <v>2468</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2502</v>
+        <v>2469</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>2019</v>
@@ -29179,19 +28886,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>2530</v>
+        <v>2497</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2531</v>
+        <v>2498</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>2206</v>
+        <v>2173</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>2042</v>
@@ -29200,15 +28907,15 @@
         <v>2019</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2207</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>2510</v>
+        <v>2477</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2511</v>
+        <v>2478</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2019</v>
@@ -29217,63 +28924,63 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>2208</v>
+        <v>2175</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2209</v>
+        <v>2176</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2210</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>2211</v>
+        <v>2178</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2212</v>
+        <v>2179</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2213</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>2214</v>
+        <v>2181</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2215</v>
+        <v>2182</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2216</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>2217</v>
+        <v>2184</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2218</v>
+        <v>2185</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2219</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2500</v>
+        <v>2467</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>2023</v>
@@ -29282,617 +28989,617 @@
         <v>2019</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2220</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>2221</v>
+        <v>2188</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2222</v>
+        <v>2189</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2223</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>2224</v>
+        <v>2191</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2225</v>
+        <v>2192</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>2226</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>2227</v>
+        <v>2194</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2228</v>
+        <v>2195</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2229</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>2230</v>
+        <v>2197</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2231</v>
+        <v>2198</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2233</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>2234</v>
+        <v>2201</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2235</v>
+        <v>2202</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2236</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>2237</v>
+        <v>2204</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2238</v>
+        <v>2205</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2239</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>2240</v>
+        <v>2207</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2241</v>
+        <v>2208</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2242</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>2243</v>
+        <v>2210</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2244</v>
+        <v>2211</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2245</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>2246</v>
+        <v>2213</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2247</v>
+        <v>2214</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2248</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>2249</v>
+        <v>2216</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>2250</v>
+        <v>2217</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2251</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2522</v>
+        <v>2489</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>2252</v>
+        <v>2219</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2253</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>2254</v>
+        <v>2221</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>2255</v>
+        <v>2222</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2256</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>2257</v>
+        <v>2224</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2258</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>2259</v>
+        <v>2226</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>989</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2260</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>2261</v>
+        <v>2228</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2244</v>
+        <v>2211</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2262</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>2263</v>
+        <v>2230</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2264</v>
+        <v>2231</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>2232</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>2265</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>2266</v>
+        <v>2233</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2267</v>
+        <v>2234</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>2268</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>2269</v>
+        <v>2236</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2270</v>
+        <v>2237</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2271</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>2272</v>
+        <v>2239</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2273</v>
+        <v>2240</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2274</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>2275</v>
+        <v>2242</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>2276</v>
+        <v>2243</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2277</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>2278</v>
+        <v>2245</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>2279</v>
+        <v>2246</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>2280</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2534</v>
+        <v>2501</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2281</v>
+        <v>2248</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>2282</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>2283</v>
+        <v>2250</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>2284</v>
+        <v>2251</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>2285</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
-        <v>2286</v>
+        <v>2253</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>1889</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>2287</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
-        <v>2288</v>
+        <v>2255</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>2289</v>
+        <v>2256</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>2290</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>2291</v>
+        <v>2258</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>2292</v>
+        <v>2259</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>2293</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
-        <v>2294</v>
+        <v>2261</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>2295</v>
+        <v>2262</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>2296</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>2297</v>
+        <v>2264</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>2298</v>
+        <v>2265</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>2299</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1" t="s">
-        <v>2300</v>
+        <v>2267</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>2096</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>2301</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1" t="s">
-        <v>2302</v>
+        <v>2269</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>2303</v>
+        <v>2270</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>2304</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
-        <v>2305</v>
+        <v>2272</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>2306</v>
+        <v>2273</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>2307</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1" t="s">
-        <v>2308</v>
+        <v>2275</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>2309</v>
+        <v>2276</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>2310</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>2311</v>
+        <v>2278</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>2312</v>
+        <v>2279</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>2313</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1" t="s">
-        <v>2314</v>
+        <v>2281</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>2315</v>
+        <v>2282</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>2316</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1" t="s">
-        <v>2317</v>
+        <v>2284</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>2318</v>
+        <v>2285</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>2319</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
-        <v>2320</v>
+        <v>2287</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>2321</v>
+        <v>2288</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>2322</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>2323</v>
+        <v>2290</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>2093</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>2324</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1" t="s">
-        <v>2325</v>
+        <v>2292</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>2326</v>
+        <v>2293</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>2327</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>2418</v>
+        <v>2385</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>2328</v>
+        <v>2295</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>2329</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1" t="s">
-        <v>2330</v>
+        <v>2297</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>2331</v>
+        <v>2298</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>2332</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="1" t="s">
-        <v>2333</v>
+        <v>2300</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>2334</v>
+        <v>2301</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>2335</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="1" t="s">
-        <v>2336</v>
+        <v>2303</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>2337</v>
+        <v>2304</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>2338</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="1" t="s">
-        <v>2339</v>
+        <v>2306</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>2340</v>
+        <v>2307</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>2341</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>2415</v>
+        <v>2382</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>2416</v>
+        <v>2383</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>2019</v>
@@ -29900,17 +29607,17 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>2571</v>
+        <v>2538</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>2181</v>
+        <v>2150</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>2232</v>
+        <v>2199</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D64"/>
+  <autoFilter ref="A1:D64" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\kerjaan\Monitoring\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\kerjaan\Monitoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4016BA-9BC7-457A-B779-4CE056387507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2289406-0C66-4191-A5B3-6BCED12C0763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7797,6 +7797,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -7854,7 +7855,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7876,18 +7877,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28043,7 +28032,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="1" t="s">
         <v>2088</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -28052,7 +28041,7 @@
       <c r="C2" s="1" t="s">
         <v>2088</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="1">
         <v>11</v>
       </c>
     </row>
@@ -28066,7 +28055,7 @@
       <c r="C3" s="1" t="s">
         <v>2088</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="1">
         <v>12</v>
       </c>
     </row>
@@ -28080,7 +28069,7 @@
       <c r="C4" s="1" t="s">
         <v>2088</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="1">
         <v>13</v>
       </c>
     </row>
@@ -28094,7 +28083,7 @@
       <c r="C5" s="1" t="s">
         <v>2088</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="1">
         <v>14</v>
       </c>
     </row>
@@ -28108,7 +28097,7 @@
       <c r="C6" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="1">
         <v>20</v>
       </c>
     </row>
@@ -28122,7 +28111,7 @@
       <c r="C7" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="1">
         <v>21</v>
       </c>
     </row>
@@ -28136,7 +28125,7 @@
       <c r="C8" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="1">
         <v>22</v>
       </c>
     </row>
@@ -28150,7 +28139,7 @@
       <c r="C9" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="1">
         <v>30</v>
       </c>
     </row>
@@ -28164,7 +28153,7 @@
       <c r="C10" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="1">
         <v>31</v>
       </c>
     </row>
@@ -28178,7 +28167,7 @@
       <c r="C11" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="1">
         <v>40</v>
       </c>
     </row>
@@ -28192,7 +28181,7 @@
       <c r="C12" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="1">
         <v>41</v>
       </c>
     </row>
@@ -28206,7 +28195,7 @@
       <c r="C13" s="1" t="s">
         <v>2137</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="1">
         <v>50</v>
       </c>
     </row>
@@ -28220,7 +28209,7 @@
       <c r="C14" s="1" t="s">
         <v>2137</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="1">
         <v>51</v>
       </c>
     </row>
@@ -28234,7 +28223,7 @@
       <c r="C15" s="1" t="s">
         <v>2137</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="1">
         <v>52</v>
       </c>
     </row>
@@ -28248,7 +28237,7 @@
       <c r="C16" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="1">
         <v>60</v>
       </c>
     </row>
@@ -28262,49 +28251,49 @@
       <c r="C17" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="1">
         <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="1" t="s">
         <v>2559</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="1" t="s">
         <v>2136</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="1">
         <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="1" t="s">
         <v>2112</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="1" t="s">
         <v>2136</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="1">
         <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="1" t="s">
         <v>2141</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="1" t="s">
         <v>2136</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="1">
         <v>64</v>
       </c>
     </row>
@@ -28318,49 +28307,49 @@
       <c r="C21" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="1">
         <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="1" t="s">
         <v>2142</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="1" t="s">
         <v>2136</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="1">
         <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="1" t="s">
         <v>2114</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="1" t="s">
         <v>2136</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="1">
         <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="1" t="s">
         <v>2144</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="1" t="s">
         <v>2136</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="1">
         <v>68</v>
       </c>
     </row>
@@ -28374,7 +28363,7 @@
       <c r="C25" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="1">
         <v>69</v>
       </c>
     </row>
@@ -28388,7 +28377,7 @@
       <c r="C26" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="1">
         <v>70</v>
       </c>
     </row>
@@ -28402,7 +28391,7 @@
       <c r="C27" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="1">
         <v>71</v>
       </c>
     </row>
@@ -28416,7 +28405,7 @@
       <c r="C28" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="1">
         <v>72</v>
       </c>
     </row>
@@ -28430,7 +28419,7 @@
       <c r="C29" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="1">
         <v>73</v>
       </c>
     </row>
@@ -28444,7 +28433,7 @@
       <c r="C30" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="1">
         <v>74</v>
       </c>
     </row>
@@ -28458,7 +28447,7 @@
       <c r="C31" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="1">
         <v>75</v>
       </c>
     </row>
@@ -28472,7 +28461,7 @@
       <c r="C32" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="1">
         <v>76</v>
       </c>
     </row>
@@ -28486,7 +28475,7 @@
       <c r="C33" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="1">
         <v>77</v>
       </c>
     </row>
@@ -28500,7 +28489,7 @@
       <c r="C34" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="1">
         <v>78</v>
       </c>
     </row>
@@ -28514,7 +28503,7 @@
       <c r="C35" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="1">
         <v>79</v>
       </c>
     </row>
@@ -28528,7 +28517,7 @@
       <c r="C36" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="1">
         <v>80</v>
       </c>
     </row>
@@ -28542,7 +28531,7 @@
       <c r="C37" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="1">
         <v>81</v>
       </c>
     </row>
@@ -28556,7 +28545,7 @@
       <c r="C38" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="1">
         <v>82</v>
       </c>
     </row>
@@ -28570,7 +28559,7 @@
       <c r="C39" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="1">
         <v>83</v>
       </c>
     </row>
@@ -28584,7 +28573,7 @@
       <c r="C40" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="1">
         <v>84</v>
       </c>
     </row>
@@ -28598,8 +28587,8 @@
       <c r="C41" s="1" t="s">
         <v>2133</v>
       </c>
-      <c r="D41" s="11">
-        <v>99</v>
+      <c r="D41" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -28612,8 +28601,8 @@
       <c r="C42" s="1" t="s">
         <v>2133</v>
       </c>
-      <c r="D42" s="11">
-        <v>99</v>
+      <c r="D42" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -28626,8 +28615,8 @@
       <c r="C43" s="1" t="s">
         <v>2133</v>
       </c>
-      <c r="D43" s="11">
-        <v>99</v>
+      <c r="D43" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -28640,8 +28629,8 @@
       <c r="C44" s="1" t="s">
         <v>2133</v>
       </c>
-      <c r="D44" s="11">
-        <v>99</v>
+      <c r="D44" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -28654,8 +28643,8 @@
       <c r="C45" s="1" t="s">
         <v>2133</v>
       </c>
-      <c r="D45" s="11">
-        <v>99</v>
+      <c r="D45" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -28668,8 +28657,8 @@
       <c r="C46" s="1" t="s">
         <v>2133</v>
       </c>
-      <c r="D46" s="11">
-        <v>99</v>
+      <c r="D46" s="1">
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -28682,8 +28671,8 @@
       <c r="C47" s="1" t="s">
         <v>2133</v>
       </c>
-      <c r="D47" s="11">
-        <v>99</v>
+      <c r="D47" s="1">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/masters/master_table.xlsx
+++ b/masters/master_table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\kerjaan\Monitoring\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Koding\tool-fcost\masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2289406-0C66-4191-A5B3-6BCED12C0763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8685C3E-5AA9-4C77-8AB7-4CF622C918F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="part_list" sheetId="1" r:id="rId1"/>
@@ -6114,9 +6114,6 @@
     <t>NO_PICTURE</t>
   </si>
   <si>
-    <t>DISPLAY NG</t>
-  </si>
-  <si>
     <t>BLUR</t>
   </si>
   <si>
@@ -7720,6 +7717,9 @@
   </si>
   <si>
     <t>REPAIR_LVDS_WIRE</t>
+  </si>
+  <si>
+    <t>DISPLAY_NG</t>
   </si>
 </sst>
 </file>
@@ -7855,7 +7855,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7871,12 +7871,16 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22848,7 +22852,7 @@
     </row>
     <row r="1835" spans="1:2">
       <c r="A1835" s="5" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="B1835" s="1" t="s">
         <v>459</v>
@@ -22856,7 +22860,7 @@
     </row>
     <row r="1836" spans="1:2">
       <c r="A1836" s="5" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="B1836" s="1" t="s">
         <v>459</v>
@@ -22864,7 +22868,7 @@
     </row>
     <row r="1837" spans="1:2">
       <c r="A1837" s="5" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="B1837" s="1" t="s">
         <v>1826</v>
@@ -22872,7 +22876,7 @@
     </row>
     <row r="1838" spans="1:2">
       <c r="A1838" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="B1838" s="1" t="s">
         <v>1429</v>
@@ -22880,7 +22884,7 @@
     </row>
     <row r="1839" spans="1:2">
       <c r="A1839" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="B1839" s="1" t="s">
         <v>214</v>
@@ -22888,7 +22892,7 @@
     </row>
     <row r="1840" spans="1:2">
       <c r="A1840" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="B1840" s="1" t="s">
         <v>964</v>
@@ -22896,7 +22900,7 @@
     </row>
     <row r="1841" spans="1:2">
       <c r="A1841" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="B1841" s="1" t="s">
         <v>964</v>
@@ -22904,7 +22908,7 @@
     </row>
     <row r="1842" spans="1:2">
       <c r="A1842" s="5" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="B1842" s="1" t="s">
         <v>109</v>
@@ -22912,7 +22916,7 @@
     </row>
     <row r="1843" spans="1:2">
       <c r="A1843" s="5" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="B1843" s="1" t="s">
         <v>1875</v>
@@ -22942,18 +22946,18 @@
         <v>1941</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1961</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -23052,7 +23056,7 @@
         <v>1961</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -23063,7 +23067,7 @@
         <v>1961</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -23211,7 +23215,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>1961</v>
@@ -23354,24 +23358,24 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C39" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C40" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -23464,13 +23468,13 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C49" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -23497,13 +23501,13 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C52" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -23519,13 +23523,13 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C54" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -23563,24 +23567,24 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="C58" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="C59" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -23596,35 +23600,35 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C61" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C62" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C63" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -23662,101 +23666,101 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C67" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C68" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C69" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C70" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C71" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C72" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C73" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C74" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C75" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -23772,46 +23776,46 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C77" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C78" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C79" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C80" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -23838,101 +23842,101 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>1943</v>
       </c>
       <c r="C83" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>1943</v>
       </c>
       <c r="C84" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C85" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C86" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C87" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C88" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C89" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C90" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="C91" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -23948,24 +23952,24 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C93" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="9" t="s">
-        <v>2461</v>
+      <c r="A94" s="8" t="s">
+        <v>2460</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>2451</v>
-      </c>
-      <c r="C94" s="9" t="s">
-        <v>2461</v>
+        <v>2450</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>2460</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -23981,13 +23985,13 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>1943</v>
       </c>
       <c r="C96" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -24003,57 +24007,57 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>1943</v>
       </c>
       <c r="C98" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>1943</v>
       </c>
       <c r="C99" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="9" t="s">
-        <v>2462</v>
+      <c r="A100" s="8" t="s">
+        <v>2461</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>2451</v>
-      </c>
-      <c r="C100" s="9" t="s">
-        <v>2462</v>
+        <v>2450</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>2461</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>1943</v>
       </c>
       <c r="C101" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C102" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -24069,13 +24073,13 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="6" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>1961</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -24091,13 +24095,13 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="6" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>1961</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -24124,24 +24128,24 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="6" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>1961</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C110" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -24168,7 +24172,7 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="6" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>1961</v>
@@ -24223,7 +24227,7 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="6" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>1961</v>
@@ -24234,24 +24238,24 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>2450</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>2451</v>
-      </c>
       <c r="C119" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="6" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>1961</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -24267,90 +24271,90 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="5" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="5" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="5" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="5" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="5" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="5" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="5" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="5" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
     </row>
   </sheetData>
@@ -24399,567 +24403,563 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3">
-        <v>750</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2057</v>
+        <v>60</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D2" t="s">
-        <v>2379</v>
+      <c r="D2" s="3" t="s">
+        <v>2310</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>2088</v>
+        <v>2023</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>2311</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3">
-        <v>390</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>3</v>
+        <v>989</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2064</v>
+        <v>2457</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>2034</v>
+        <v>2023</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>2065</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3">
-        <v>640</v>
-      </c>
-      <c r="B4" t="s">
         <v>90</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>989</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2324</v>
+        <v>2475</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>2034</v>
+        <v>2023</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>2036</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3">
-        <v>650</v>
-      </c>
-      <c r="B5" t="s">
-        <v>90</v>
+        <v>170</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>989</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2157</v>
+        <v>2319</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>2024</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>2023</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>2320</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3">
-        <v>651</v>
-      </c>
-      <c r="B6" t="s">
-        <v>90</v>
+        <v>330</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2550</v>
+        <v>2029</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>2055</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>2030</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>2059</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3">
-        <v>652</v>
-      </c>
-      <c r="B7" t="s">
-        <v>107</v>
+        <v>140</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>989</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2453</v>
+        <v>2029</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>2024</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>2030</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>2317</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3">
-        <v>400</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>109</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2504</v>
+        <v>2341</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>2041</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>2030</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>2342</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3">
-        <v>401</v>
+        <v>222</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>109</v>
+        <v>459</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2505</v>
+        <v>2482</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>2042</v>
+        <v>2483</v>
       </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3">
-        <v>402</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>109</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2506</v>
+        <v>2482</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>2037</v>
+        <v>2483</v>
       </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3">
-        <v>403</v>
+        <v>110</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>109</v>
+        <v>989</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2453</v>
+        <v>2456</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>2024</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>2025</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>2314</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3">
-        <v>360</v>
+        <v>111</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>128</v>
+        <v>1816</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2329</v>
+        <v>2456</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>2047</v>
+        <v>2025</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>2061</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3">
-        <v>660</v>
-      </c>
-      <c r="B13" t="s">
-        <v>128</v>
+        <v>550</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1816</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2324</v>
+        <v>2361</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>2034</v>
+        <v>2025</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>2036</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>214</v>
+        <v>989</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2309</v>
+        <v>2509</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>2022</v>
+        <v>2031</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>2310</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3">
-        <v>31</v>
+        <v>560</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>214</v>
+        <v>1816</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2518</v>
+        <v>2363</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>2045</v>
+        <v>2031</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>2046</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3">
-        <v>60</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>214</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2311</v>
+        <v>2354</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>2023</v>
+        <v>2031</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>2312</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3">
-        <v>340</v>
+        <v>280</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>214</v>
+        <v>459</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2322</v>
+        <v>2051</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>2035</v>
+        <v>2052</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>2333</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3">
-        <v>670</v>
-      </c>
-      <c r="B18" t="s">
-        <v>214</v>
+        <v>380</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1811</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2324</v>
+        <v>2061</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>2034</v>
+        <v>2052</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>2036</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3">
-        <v>770</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>214</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2551</v>
+        <v>2356</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>2055</v>
+        <v>2052</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>2333</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3">
-        <v>780</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>322</v>
+        <v>231</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>459</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D20" t="s">
-        <v>2384</v>
+      <c r="D20" s="3" t="s">
+        <v>2478</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>2047</v>
-      </c>
+        <v>2471</v>
+      </c>
+      <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>345</v>
+        <v>989</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2309</v>
+        <v>2470</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>2022</v>
+        <v>2471</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>2310</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>345</v>
+        <v>989</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2311</v>
+        <v>2473</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>2024</v>
+        <v>2560</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3">
-        <v>330</v>
+        <v>101</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>345</v>
+        <v>989</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2030</v>
+        <v>2518</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>2031</v>
+        <v>2560</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>2060</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3">
-        <v>680</v>
-      </c>
-      <c r="B24" t="s">
-        <v>345</v>
+        <v>621</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>1816</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>2324</v>
+        <v>2551</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>2034</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>2036</v>
-      </c>
+        <v>2560</v>
+      </c>
+      <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3">
-        <v>180</v>
+        <v>540</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>459</v>
+        <v>1816</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2322</v>
+        <v>2552</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>2035</v>
+        <v>2560</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>2323</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="3">
-        <v>190</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>459</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="B26" s="3"/>
       <c r="C26" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2485</v>
+        <v>2350</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>2034</v>
+        <v>2560</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>2036</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3">
-        <v>191</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>459</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="B27" s="3"/>
       <c r="C27" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>2491</v>
+      <c r="D27" s="3" t="s">
+        <v>2367</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>2034</v>
+        <v>2560</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>2036</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>459</v>
+        <v>989</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>2516</v>
+        <v>2026</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>2037</v>
+        <v>2027</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>2325</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3">
-        <v>210</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>459</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>2038</v>
+        <v>2352</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>2039</v>
+        <v>2027</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>2040</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="3">
-        <v>220</v>
+        <v>401</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>459</v>
+        <v>109</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>2326</v>
+        <v>2504</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>2041</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>2327</v>
-      </c>
+      <c r="F30" s="3"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="3">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>459</v>
@@ -24968,72 +24968,74 @@
         <v>2021</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>2490</v>
+        <v>2506</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>2481</v>
-      </c>
-      <c r="F31" s="3"/>
+        <v>2041</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>2042</v>
+      </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="3">
-        <v>222</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>459</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2483</v>
+        <v>2510</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>2484</v>
-      </c>
-      <c r="F32" s="3"/>
+        <v>2041</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>2347</v>
+      </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="3">
-        <v>230</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>459</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="B33" s="3"/>
       <c r="C33" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>2515</v>
+        <v>2506</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>2024</v>
+        <v>2041</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>2328</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="3">
-        <v>231</v>
+        <v>130</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>459</v>
+        <v>989</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>2479</v>
+        <v>2469</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>2472</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>2028</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>2316</v>
+      </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>459</v>
@@ -25042,38 +25044,33 @@
         <v>2021</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>2507</v>
+        <v>2037</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>2042</v>
+        <v>2038</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3">
-        <v>250</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>459</v>
+        <v>720</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>2044</v>
+        <v>2037</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>2045</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>2046</v>
-      </c>
+        <v>2038</v>
+      </c>
+      <c r="F36" s="3"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="3">
-        <v>260</v>
+        <v>810</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>459</v>
@@ -25081,536 +25078,518 @@
       <c r="C37" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>2329</v>
+      <c r="D37" t="s">
+        <v>2454</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>2047</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>2048</v>
-      </c>
+        <v>2387</v>
+      </c>
+      <c r="F37" s="3"/>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="3">
-        <v>270</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>459</v>
+        <v>800</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>2049</v>
+      <c r="D38" t="s">
+        <v>2513</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>2050</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>2051</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="3">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>459</v>
+        <v>214</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>2052</v>
+        <v>2308</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>2053</v>
+        <v>2022</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>2054</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="3">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>459</v>
+        <v>345</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>2456</v>
+        <v>2308</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>2055</v>
+        <v>2022</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>2056</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="3">
-        <v>291</v>
+        <v>10</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>459</v>
+        <v>989</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>2520</v>
+        <v>2308</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>2055</v>
-      </c>
-      <c r="F41" s="3"/>
+        <v>2022</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>2309</v>
+      </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="3">
-        <v>790</v>
+        <v>40</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>459</v>
+        <v>1816</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>2386</v>
+        <v>2308</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>2387</v>
-      </c>
-      <c r="F42" s="3"/>
+        <v>2022</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>2309</v>
+      </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="3">
-        <v>810</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>459</v>
+        <v>353</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>1875</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D43" t="s">
-        <v>2455</v>
+      <c r="D43" s="3" t="s">
+        <v>2553</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>2388</v>
-      </c>
-      <c r="F43" s="3"/>
+        <v>2022</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>2334</v>
+      </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="3">
-        <v>10</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>989</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="B44" s="3"/>
       <c r="C44" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>2309</v>
+        <v>2337</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>2022</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>2310</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="3">
-        <v>50</v>
+        <v>402</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>989</v>
+        <v>109</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>2458</v>
+        <v>2505</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>2023</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>2312</v>
-      </c>
+        <v>2036</v>
+      </c>
+      <c r="F45" s="3"/>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>989</v>
+        <v>459</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2476</v>
+        <v>2515</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>2023</v>
+        <v>2036</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>2313</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>989</v>
+        <v>109</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>2474</v>
+        <v>2503</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>2025</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>2314</v>
-      </c>
+        <v>2040</v>
+      </c>
+      <c r="F47" s="3"/>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3">
-        <v>101</v>
+        <v>220</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>989</v>
+        <v>459</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>2519</v>
+        <v>2325</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>2025</v>
+        <v>2040</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>2314</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="3">
-        <v>110</v>
+        <v>630</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>989</v>
+        <v>1811</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>2457</v>
+        <v>2374</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>2026</v>
+        <v>2040</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>2315</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="3">
-        <v>120</v>
+        <v>370</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>989</v>
+        <v>1889</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>2027</v>
+        <v>2335</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>2028</v>
+        <v>2040</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>2316</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="3">
-        <v>130</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>989</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="B51" s="3"/>
       <c r="C51" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>2470</v>
+        <v>2511</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>2029</v>
+        <v>2040</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>2317</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="3">
-        <v>140</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>989</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="B52" s="3"/>
       <c r="C52" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>2030</v>
+        <v>2507</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>2031</v>
+        <v>2040</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>2318</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="3">
-        <v>150</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>989</v>
+        <v>650</v>
+      </c>
+      <c r="B53" t="s">
+        <v>90</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>2510</v>
+        <v>2156</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>2032</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>2033</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="F53" s="3"/>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="3">
-        <v>160</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>989</v>
+        <v>652</v>
+      </c>
+      <c r="B54" t="s">
+        <v>107</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>2492</v>
+        <v>2452</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>2034</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>2319</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="F54" s="3"/>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="3">
-        <v>170</v>
+        <v>403</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>989</v>
+        <v>109</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>2320</v>
+        <v>2452</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>2023</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>2321</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="F55" s="3"/>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="3">
-        <v>730</v>
-      </c>
-      <c r="B56" t="s">
-        <v>989</v>
+        <v>70</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D56" t="s">
-        <v>2473</v>
+      <c r="D56" s="3" t="s">
+        <v>2310</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>2378</v>
+        <v>2024</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>2311</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="3">
-        <v>740</v>
+        <v>230</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>989</v>
+        <v>459</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>2471</v>
+        <v>2514</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>2472</v>
+        <v>2024</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>2321</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="3">
-        <v>690</v>
+        <v>820</v>
       </c>
       <c r="B58" t="s">
-        <v>1398</v>
+        <v>1655</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>2057</v>
+        <v>2452</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>2034</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>2036</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="3">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1429</v>
+        <v>1816</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>2057</v>
+        <v>2310</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>2034</v>
+        <v>2024</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>2330</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="3">
-        <v>820</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1655</v>
+        <v>352</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>1875</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>2453</v>
+        <v>2310</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>2024</v>
       </c>
+      <c r="F60" s="3" t="s">
+        <v>2334</v>
+      </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="3">
-        <v>821</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1655</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="B61" s="3"/>
       <c r="C61" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D61" t="s">
-        <v>2479</v>
+      <c r="D61" s="3" t="s">
+        <v>2452</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>2055</v>
+        <v>2024</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>2339</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="3">
-        <v>310</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>1660</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="B62" s="3"/>
       <c r="C62" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>2331</v>
+        <v>2365</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>2058</v>
+        <v>2024</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>2059</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="3">
-        <v>700</v>
+        <v>651</v>
       </c>
       <c r="B63" t="s">
-        <v>1660</v>
+        <v>90</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>2057</v>
+        <v>2549</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>2381</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>2036</v>
-      </c>
+        <v>2054</v>
+      </c>
+      <c r="F63" s="3"/>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="3">
-        <v>320</v>
+        <v>770</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>1732</v>
+        <v>214</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>2057</v>
+        <v>2550</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>2050</v>
+        <v>2054</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>2332</v>
@@ -25618,758 +25597,783 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="3">
-        <v>380</v>
+        <v>290</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1811</v>
+        <v>459</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>2062</v>
+        <v>2455</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>2063</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="3">
-        <v>630</v>
+        <v>291</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>1811</v>
+        <v>459</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>2375</v>
+        <v>2519</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>2041</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>2376</v>
-      </c>
+        <v>2054</v>
+      </c>
+      <c r="F66" s="3"/>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="3">
-        <v>40</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>1816</v>
+        <v>821</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1655</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>2309</v>
+      <c r="D67" t="s">
+        <v>2478</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>2022</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>2310</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="3">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>1816</v>
+        <v>1826</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>2311</v>
+        <v>2333</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>2024</v>
+        <v>2054</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>2312</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="3">
-        <v>111</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>1816</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="B69" s="3"/>
       <c r="C69" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>2457</v>
+        <v>2508</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>2026</v>
+        <v>2054</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>2315</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="3">
-        <v>540</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>1816</v>
-      </c>
+        <v>760</v>
+      </c>
+      <c r="B70" s="3"/>
       <c r="C70" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>2553</v>
+        <v>2379</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>2025</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>2361</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="3">
-        <v>550</v>
+        <v>31</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>1816</v>
+        <v>214</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>2362</v>
+        <v>2517</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>2026</v>
+        <v>2044</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>2363</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="3">
-        <v>560</v>
+        <v>250</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>1816</v>
+        <v>459</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>2364</v>
+        <v>2043</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>2032</v>
+        <v>2044</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>2365</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="3">
-        <v>620</v>
+        <v>310</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>1816</v>
+        <v>1660</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>2373</v>
+        <v>2330</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>2034</v>
+        <v>2057</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>2374</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="3">
-        <v>621</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>1816</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="B74" s="3"/>
       <c r="C74" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2552</v>
+        <v>2343</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>2025</v>
-      </c>
-      <c r="F74" s="3"/>
+        <v>2057</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>2344</v>
+      </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="3">
-        <v>350</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>1826</v>
+        <v>700</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1660</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>2334</v>
+        <v>2056</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>2055</v>
+        <v>2380</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>2335</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="3">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>1826</v>
+        <v>128</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>2480</v>
+        <v>2328</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>2034</v>
+        <v>2046</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>2335</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="3">
-        <v>352</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>1875</v>
+        <v>780</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>322</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>2311</v>
+      <c r="D77" t="s">
+        <v>2383</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>2024</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>2335</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="3">
-        <v>353</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>1875</v>
+        <v>260</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>459</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>2554</v>
+        <v>2328</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>2022</v>
+        <v>2046</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>2335</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="3">
-        <v>370</v>
+        <v>270</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>1889</v>
+        <v>459</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>2336</v>
+        <v>2048</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>2041</v>
+        <v>2049</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>2337</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="3">
-        <v>222</v>
+        <v>320</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>1902</v>
+        <v>1732</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>2490</v>
+        <v>2056</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>2481</v>
+        <v>2049</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>2331</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="3">
-        <v>222</v>
+        <v>460</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>2483</v>
+        <v>2345</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>2484</v>
-      </c>
-      <c r="F81" s="3"/>
+        <v>2049</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>2346</v>
+      </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="3">
-        <v>410</v>
-      </c>
-      <c r="B82" s="3"/>
+        <v>730</v>
+      </c>
+      <c r="B82" t="s">
+        <v>989</v>
+      </c>
       <c r="C82" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>2338</v>
+      <c r="D82" t="s">
+        <v>2472</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>2022</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>2339</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="3">
-        <v>420</v>
-      </c>
-      <c r="B83" s="3"/>
+        <v>340</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="C83" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>2453</v>
+        <v>2321</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>2024</v>
+        <v>2034</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>2340</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="3">
-        <v>430</v>
-      </c>
-      <c r="B84" s="3"/>
+        <v>180</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>459</v>
+      </c>
       <c r="C84" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>2512</v>
+        <v>2321</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>2041</v>
+        <v>2034</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>2341</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="3">
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>2342</v>
+        <v>2348</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>2343</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="3">
-        <v>450</v>
-      </c>
-      <c r="B86" s="3"/>
+        <v>390</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="C86" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>2344</v>
+        <v>2063</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>2058</v>
+        <v>2033</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>2345</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="3">
-        <v>460</v>
-      </c>
-      <c r="B87" s="3"/>
+        <v>640</v>
+      </c>
+      <c r="B87" t="s">
+        <v>90</v>
+      </c>
       <c r="C87" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>2346</v>
+        <v>2323</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>2050</v>
+        <v>2033</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>2347</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="3">
-        <v>470</v>
-      </c>
-      <c r="B88" s="3"/>
+        <v>660</v>
+      </c>
+      <c r="B88" t="s">
+        <v>128</v>
+      </c>
       <c r="C88" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>2511</v>
+        <v>2323</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>2042</v>
+        <v>2033</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>2348</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="3">
-        <v>471</v>
-      </c>
-      <c r="B89" s="3"/>
+        <v>670</v>
+      </c>
+      <c r="B89" t="s">
+        <v>214</v>
+      </c>
       <c r="C89" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>2507</v>
+        <v>2323</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>2042</v>
+        <v>2033</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>2348</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="3">
-        <v>480</v>
-      </c>
-      <c r="B90" s="3"/>
+        <v>680</v>
+      </c>
+      <c r="B90" t="s">
+        <v>345</v>
+      </c>
       <c r="C90" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>2349</v>
+        <v>2323</v>
       </c>
       <c r="E90" s="3" t="s">
+        <v>2033</v>
+      </c>
+      <c r="F90" s="3" t="s">
         <v>2035</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>2350</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="3">
-        <v>490</v>
-      </c>
-      <c r="B91" s="3"/>
+        <v>190</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>459</v>
+      </c>
       <c r="C91" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>2351</v>
+        <v>2484</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>2025</v>
+        <v>2033</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>2352</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="3">
-        <v>500</v>
-      </c>
-      <c r="B92" s="3"/>
+        <v>191</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>459</v>
+      </c>
       <c r="C92" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D92" s="3" t="s">
-        <v>2353</v>
+      <c r="D92" s="4" t="s">
+        <v>2490</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>2028</v>
+        <v>2033</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>2354</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="3">
-        <v>510</v>
-      </c>
-      <c r="B93" s="3"/>
+        <v>160</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>989</v>
+      </c>
       <c r="C93" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>2355</v>
+        <v>2491</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>2356</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="3">
-        <v>520</v>
-      </c>
-      <c r="B94" s="3"/>
+        <v>690</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1398</v>
+      </c>
       <c r="C94" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>2357</v>
+        <v>2056</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>2053</v>
+        <v>2033</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>2358</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="3">
-        <v>530</v>
-      </c>
-      <c r="B95" s="3"/>
+        <v>300</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>1429</v>
+      </c>
       <c r="C95" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>2359</v>
+        <v>2056</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>2360</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="3">
-        <v>570</v>
-      </c>
-      <c r="B96" s="3"/>
+        <v>620</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>1816</v>
+      </c>
       <c r="C96" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>2366</v>
+        <v>2372</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>2024</v>
+        <v>2033</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>2367</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="3">
-        <v>580</v>
-      </c>
-      <c r="B97" s="3"/>
+        <v>351</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>1826</v>
+      </c>
       <c r="C97" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>2368</v>
+        <v>2479</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>2025</v>
+        <v>2033</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>2369</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="3">
-        <v>590</v>
-      </c>
-      <c r="B98" s="8"/>
+        <v>530</v>
+      </c>
+      <c r="B98" s="7"/>
       <c r="C98" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>2513</v>
+        <v>2358</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>2370</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="3">
-        <v>600</v>
-      </c>
-      <c r="B99" s="3"/>
+        <v>590</v>
+      </c>
+      <c r="B99" s="12"/>
       <c r="C99" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>2509</v>
+        <v>2512</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>2055</v>
+        <v>2033</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="3">
-        <v>610</v>
-      </c>
-      <c r="B100" s="3"/>
+        <v>710</v>
+      </c>
       <c r="C100" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>2508</v>
+        <v>2323</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>2041</v>
+        <v>2033</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>2372</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="3">
-        <v>710</v>
+        <v>790</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>459</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>2324</v>
+        <v>2385</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>2034</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>2036</v>
-      </c>
+        <v>2386</v>
+      </c>
+      <c r="F101" s="3"/>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="3">
-        <v>720</v>
-      </c>
+        <v>791</v>
+      </c>
+      <c r="B102" s="3"/>
       <c r="C102" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>2038</v>
+        <v>2385</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>2039</v>
+        <v>2386</v>
       </c>
       <c r="F102" s="3"/>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="3">
-        <v>760</v>
-      </c>
-      <c r="B103" s="3"/>
+        <v>750</v>
+      </c>
+      <c r="B103" t="s">
+        <v>2056</v>
+      </c>
       <c r="C103" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>2380</v>
+      <c r="D103" t="s">
+        <v>2378</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>2055</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="3">
-        <v>791</v>
-      </c>
-      <c r="B104" s="3"/>
+        <v>221</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>459</v>
+      </c>
       <c r="C104" s="3" t="s">
         <v>2021</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>2386</v>
+        <v>2489</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>2387</v>
+        <v>2480</v>
       </c>
       <c r="F104" s="3"/>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="3">
-        <v>800</v>
+        <v>222</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>1902</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>2021</v>
       </c>
-      <c r="D105" t="s">
-        <v>2514</v>
+      <c r="D105" s="3" t="s">
+        <v>2489</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>2388</v>
+        <v>2480</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F97" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F102">
-      <sortCondition ref="B1:B94"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F105">
+      <sortCondition ref="E1:E97"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26388,40 +26392,40 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2066</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2067</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2068</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2069</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2070</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2071</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>2072</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2073</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
     </row>
   </sheetData>
@@ -26441,34 +26445,34 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2075</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2076</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2077</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2078</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
     </row>
   </sheetData>
@@ -26494,19 +26498,19 @@
         <v>2016</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>2081</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2082</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>2083</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2084</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -26518,13 +26522,13 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -26538,13 +26542,13 @@
         <v>1816</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -26555,16 +26559,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -26576,13 +26580,13 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -26593,13 +26597,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -26610,13 +26614,13 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E7" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -26627,13 +26631,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E8" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="F8" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -26644,13 +26648,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="E9" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F9" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -26661,16 +26665,16 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="D10" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="E10" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F10" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -26681,13 +26685,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E11" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="F11" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -26701,13 +26705,13 @@
         <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="F12" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -26721,13 +26725,13 @@
         <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="F13" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -26738,16 +26742,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>2085</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>2086</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>2087</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30">
@@ -26759,13 +26763,13 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30">
@@ -26776,16 +26780,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -26797,13 +26801,13 @@
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -26815,13 +26819,13 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>2089</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>2090</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>2091</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -26833,13 +26837,13 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>2091</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>2092</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>2093</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -26851,13 +26855,13 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>2094</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="45">
@@ -26869,13 +26873,13 @@
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -26889,13 +26893,13 @@
         <v>989</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>2096</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>2097</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>2098</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -26907,13 +26911,13 @@
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>2096</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>2097</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>2098</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -26927,13 +26931,13 @@
         <v>1429</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>2098</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>2099</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>2100</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -26947,13 +26951,13 @@
         <v>459</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>2100</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>2101</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>2102</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -26967,13 +26971,13 @@
         <v>459</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -26987,13 +26991,13 @@
         <v>1660</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>2102</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>2103</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>2104</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -27007,13 +27011,13 @@
         <v>214</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -27027,13 +27031,13 @@
         <v>345</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -27047,13 +27051,13 @@
         <v>90</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>2106</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>2107</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>2108</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -27067,13 +27071,13 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>2108</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>2109</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>2110</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -27087,13 +27091,13 @@
         <v>128</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -27107,13 +27111,13 @@
         <v>322</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>2111</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>2112</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -27127,13 +27131,13 @@
         <v>1732</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>2113</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>2114</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -27147,13 +27151,13 @@
         <v>1826</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>2114</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>2115</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>2116</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -27167,13 +27171,13 @@
         <v>1811</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>2116</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>2117</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>2118</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="60">
@@ -27187,13 +27191,13 @@
         <v>459</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="45">
@@ -27207,13 +27211,13 @@
         <v>1429</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>2119</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>2120</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>2121</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -27227,13 +27231,13 @@
         <v>1660</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E39" s="1" t="s">
+        <v>2121</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>2122</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>2123</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -27247,13 +27251,13 @@
         <v>345</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>2123</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>2124</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>2125</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -27267,13 +27271,13 @@
         <v>37</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>2125</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>2126</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>2127</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -27287,13 +27291,13 @@
         <v>24</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E42" s="1" t="s">
+        <v>2125</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>2126</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>2127</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -27307,13 +27311,13 @@
         <v>1429</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -27327,13 +27331,13 @@
         <v>989</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -27347,13 +27351,13 @@
         <v>459</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -27367,13 +27371,13 @@
         <v>1660</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -27387,13 +27391,13 @@
         <v>1398</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -27407,13 +27411,13 @@
         <v>214</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -27427,13 +27431,13 @@
         <v>109</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -27447,13 +27451,13 @@
         <v>345</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -27467,13 +27471,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -27487,13 +27491,13 @@
         <v>90</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -27507,13 +27511,13 @@
         <v>128</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -27527,13 +27531,13 @@
         <v>322</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -27547,13 +27551,13 @@
         <v>1732</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -27567,13 +27571,13 @@
         <v>1826</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -27587,13 +27591,13 @@
         <v>1811</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -27603,17 +27607,17 @@
       <c r="B58" s="1">
         <v>1</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" s="9" t="s">
         <v>1902</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -27625,13 +27629,13 @@
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="60">
@@ -27643,13 +27647,13 @@
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="45">
@@ -27661,13 +27665,13 @@
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -27678,13 +27682,13 @@
         <v>1</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E62" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -27695,13 +27699,13 @@
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -27712,13 +27716,13 @@
         <v>1</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E64" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -27730,13 +27734,13 @@
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -27748,13 +27752,13 @@
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E66" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -27766,13 +27770,13 @@
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -27783,13 +27787,13 @@
         <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="E68" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F68" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -27800,13 +27804,13 @@
         <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E69" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="F69" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -27817,13 +27821,13 @@
         <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E70" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="F70" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -27834,13 +27838,13 @@
         <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E71" t="s">
+        <v>2402</v>
+      </c>
+      <c r="F71" t="s">
         <v>2403</v>
-      </c>
-      <c r="F71" t="s">
-        <v>2404</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -27851,13 +27855,13 @@
         <v>1</v>
       </c>
       <c r="D72" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="E72" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F72" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -27868,13 +27872,13 @@
         <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E73" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="F73" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -27885,13 +27889,13 @@
         <v>1</v>
       </c>
       <c r="D74" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E74" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="F74" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -27902,13 +27906,13 @@
         <v>1</v>
       </c>
       <c r="D75" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E75" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="F75" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -27919,13 +27923,13 @@
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E76" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="F76" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -27936,13 +27940,13 @@
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E77" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="F77" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -27953,13 +27957,13 @@
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E78" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="F78" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -27970,13 +27974,13 @@
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E79" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="F79" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -27987,13 +27991,13 @@
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E80" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="F80" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
     </row>
   </sheetData>
@@ -28019,27 +28023,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2128</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2129</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2130</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2131</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="D2" s="1">
         <v>11</v>
@@ -28047,13 +28051,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="D3" s="1">
         <v>12</v>
@@ -28061,13 +28065,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="D4" s="1">
         <v>13</v>
@@ -28075,13 +28079,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="D5" s="1">
         <v>14</v>
@@ -28089,10 +28093,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>989</v>
@@ -28103,10 +28107,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>989</v>
@@ -28117,10 +28121,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>989</v>
@@ -28131,10 +28135,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>459</v>
@@ -28145,10 +28149,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>459</v>
@@ -28159,10 +28163,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>1429</v>
@@ -28173,10 +28177,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1429</v>
@@ -28187,13 +28191,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>2136</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>2137</v>
       </c>
       <c r="D13" s="1">
         <v>50</v>
@@ -28201,13 +28205,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>2136</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>2137</v>
       </c>
       <c r="D14" s="1">
         <v>51</v>
@@ -28215,13 +28219,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>2136</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>2137</v>
       </c>
       <c r="D15" s="1">
         <v>52</v>
@@ -28229,10 +28233,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>964</v>
@@ -28243,10 +28247,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>964</v>
@@ -28257,10 +28261,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>964</v>
@@ -28271,10 +28275,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>964</v>
@@ -28285,10 +28289,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>964</v>
@@ -28299,10 +28303,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>964</v>
@@ -28313,10 +28317,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>964</v>
@@ -28327,10 +28331,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>964</v>
@@ -28341,10 +28345,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>964</v>
@@ -28355,10 +28359,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>964</v>
@@ -28369,10 +28373,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>964</v>
@@ -28383,10 +28387,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>964</v>
@@ -28397,10 +28401,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>964</v>
@@ -28411,10 +28415,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>964</v>
@@ -28425,10 +28429,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>964</v>
@@ -28439,10 +28443,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>964</v>
@@ -28453,10 +28457,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>964</v>
@@ -28467,10 +28471,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>964</v>
@@ -28481,10 +28485,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>964</v>
@@ -28495,10 +28499,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>964</v>
@@ -28509,10 +28513,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>964</v>
@@ -28523,10 +28527,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>964</v>
@@ -28537,10 +28541,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="5" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>964</v>
@@ -28551,10 +28555,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>964</v>
@@ -28565,10 +28569,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>964</v>
@@ -28579,13 +28583,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>2132</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>2133</v>
-      </c>
       <c r="C41" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="D41" s="1">
         <v>1</v>
@@ -28593,13 +28597,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
@@ -28607,13 +28611,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -28621,13 +28625,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="D44" s="1">
         <v>4</v>
@@ -28635,13 +28639,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="D45" s="1">
         <v>5</v>
@@ -28649,13 +28653,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="D46" s="1">
         <v>6</v>
@@ -28663,13 +28667,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="D47" s="1">
         <v>7</v>
@@ -28698,13 +28702,13 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2152</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2153</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2154</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2020</v>
@@ -28712,52 +28716,52 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45">
       <c r="A3" s="1" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2156</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2157</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2019</v>
@@ -28766,66 +28770,66 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>2161</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>2162</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>2168</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>2169</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2019</v>
@@ -28834,27 +28838,27 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="F11" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>2019</v>
@@ -28863,10 +28867,10 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>2467</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>2468</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>2469</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>2019</v>
@@ -28875,36 +28879,36 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>2497</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>2498</v>
-      </c>
       <c r="C14" s="1" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>2477</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>2478</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2019</v>
@@ -28913,63 +28917,63 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>2175</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>2176</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>2178</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>2179</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>2181</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>2182</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>2184</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>2185</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>2023</v>
@@ -28978,617 +28982,617 @@
         <v>2019</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>2188</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>2189</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="D22"